--- a/BOM/eSpark-BOM.xlsx
+++ b/BOM/eSpark-BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\matthewgraff-arduinomegapcb\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE52148-A605-4E19-80A5-356E72C9248F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F81E612-8541-4AC9-AED6-E3F3BE6A4D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="431">
   <si>
     <t>Component list</t>
   </si>
@@ -109,18 +109,9 @@
     <t>C1</t>
   </si>
   <si>
-    <t>C2, C7, C9, C10, C12, C13, C19, C20, C21, C22, C29, C30, C31, C32, C33, C34, C35, C37, C40, C41, C44, C45, C46, C47, C48, C49, C51</t>
-  </si>
-  <si>
     <t>C3, C5</t>
   </si>
   <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>C6, C36</t>
-  </si>
-  <si>
     <t>C8</t>
   </si>
   <si>
@@ -136,9 +127,6 @@
     <t>C42, C43</t>
   </si>
   <si>
-    <t>C50, C52, C53</t>
-  </si>
-  <si>
     <t>D1, D2, D3, D17, D18, D23, D24</t>
   </si>
   <si>
@@ -178,9 +166,6 @@
     <t>FB2, FB3, FB4, FB5, FB6, FB7, FB8, FB9</t>
   </si>
   <si>
-    <t>J1, J2, J3</t>
-  </si>
-  <si>
     <t>J4, J5, J6, J7, J11, J15</t>
   </si>
   <si>
@@ -208,12 +193,6 @@
     <t>L3</t>
   </si>
   <si>
-    <t>LED1, LED2</t>
-  </si>
-  <si>
-    <t>LED4</t>
-  </si>
-  <si>
     <t>LED5</t>
   </si>
   <si>
@@ -325,15 +304,9 @@
     <t>CAP CER 0.1UF 50V X5R 0603</t>
   </si>
   <si>
-    <t>CAP CER 22UF 25V X5R 1206</t>
-  </si>
-  <si>
     <t>CAP ALUM POLY 120UF 20% 20V SMD</t>
   </si>
   <si>
-    <t>CAP ALUM POLY 100UF 20% 25V SMD</t>
-  </si>
-  <si>
     <t>CAP TANT POLY 330UF 6.3V 2917</t>
   </si>
   <si>
@@ -391,9 +364,6 @@
     <t>CONN RCPT USB2.0 MICRO B SMD R/A</t>
   </si>
   <si>
-    <t>-40℃~+105℃ 20A 300V Green Corner pin Double - Walled(Double) 14~22 Straight pin 2 1 7.62mm Plugin,P=7.62mm Barrier Terminal Blocks ROHS</t>
-  </si>
-  <si>
     <t>CONN U.FL RCPT STR 50 OHM SMD</t>
   </si>
   <si>
@@ -418,15 +388,9 @@
     <t>FIXED IND 27NH 590MA 116MOHM SMD</t>
   </si>
   <si>
-    <t>LED RED CLEAR CHIP SMD</t>
-  </si>
-  <si>
     <t>Red 632nm LED Indication - Discrete 2.05V 0603 (1608 Metric)</t>
   </si>
   <si>
-    <t>Green 520~535nm 0402 Light Emitting Diodes (LED) RoHS</t>
-  </si>
-  <si>
     <t>1.5inch (128×128) SPI RGB OLED Display Module</t>
   </si>
   <si>
@@ -538,15 +502,9 @@
     <t>Cap-0603</t>
   </si>
   <si>
-    <t>Cap-1206</t>
-  </si>
-  <si>
     <t>20SVPF120M</t>
   </si>
   <si>
-    <t>25SVPF100M</t>
-  </si>
-  <si>
     <t>Case-D</t>
   </si>
   <si>
@@ -586,9 +544,6 @@
     <t>Ind-0805</t>
   </si>
   <si>
-    <t>JL762B-76202GA1</t>
-  </si>
-  <si>
     <t>XKNANO-113</t>
   </si>
   <si>
@@ -610,9 +565,6 @@
     <t>IND-0603 (1608 Metric)</t>
   </si>
   <si>
-    <t>LED-0402</t>
-  </si>
-  <si>
     <t>LED-0603</t>
   </si>
   <si>
@@ -673,9 +625,6 @@
     <t>CC0603KRX5R9BB104</t>
   </si>
   <si>
-    <t>C3216X5R1E226M160AB</t>
-  </si>
-  <si>
     <t>6TPB330ML</t>
   </si>
   <si>
@@ -742,15 +691,9 @@
     <t>LQW18AN27NG10D</t>
   </si>
   <si>
-    <t>XZMDK68W-2</t>
-  </si>
-  <si>
     <t>19-21/R7C-AK1L2BY/3T</t>
   </si>
   <si>
-    <t>16-213/GHC-YR1S1/3T</t>
-  </si>
-  <si>
     <t>1.5inch RGB OLED Module</t>
   </si>
   <si>
@@ -892,9 +835,6 @@
     <t>Amphenol FCI</t>
   </si>
   <si>
-    <t>JILN</t>
-  </si>
-  <si>
     <t>Hirose</t>
   </si>
   <si>
@@ -910,9 +850,6 @@
     <t>Chilisin Elec</t>
   </si>
   <si>
-    <t>SunLED</t>
-  </si>
-  <si>
     <t>Everlight Elec</t>
   </si>
   <si>
@@ -967,9 +904,6 @@
     <t>C186713</t>
   </si>
   <si>
-    <t>C136279</t>
-  </si>
-  <si>
     <t>C236293</t>
   </si>
   <si>
@@ -979,9 +913,6 @@
     <t>C14664</t>
   </si>
   <si>
-    <t>C441758</t>
-  </si>
-  <si>
     <t>C105621</t>
   </si>
   <si>
@@ -1024,9 +955,6 @@
     <t>C132563</t>
   </si>
   <si>
-    <t>C394551</t>
-  </si>
-  <si>
     <t>C88374</t>
   </si>
   <si>
@@ -1054,9 +982,6 @@
     <t>C1322287</t>
   </si>
   <si>
-    <t>C74338</t>
-  </si>
-  <si>
     <t>C93689</t>
   </si>
   <si>
@@ -1156,9 +1081,6 @@
     <t>120uF</t>
   </si>
   <si>
-    <t>100uF</t>
-  </si>
-  <si>
     <t>330uF</t>
   </si>
   <si>
@@ -1186,15 +1108,9 @@
     <t>27nH</t>
   </si>
   <si>
-    <t>Red</t>
-  </si>
-  <si>
     <t>RED</t>
   </si>
   <si>
-    <t>Green</t>
-  </si>
-  <si>
     <t>TEST POINT</t>
   </si>
   <si>
@@ -1321,15 +1237,9 @@
     <t>C34897</t>
   </si>
   <si>
-    <t xml:space="preserve">Ye Part Design me Change hoga </t>
-  </si>
-  <si>
     <t>LED1, LED2, LED3</t>
   </si>
   <si>
-    <t xml:space="preserve">Ye Part Remove krna ha BOM me se or design me change krna ha </t>
-  </si>
-  <si>
     <t>LED4, LED6, LED8, LED9</t>
   </si>
   <si>
@@ -1337,6 +1247,72 @@
   </si>
   <si>
     <t>Mega2560_Custom</t>
+  </si>
+  <si>
+    <t>25V 22uF X5R ±20% 0805</t>
+  </si>
+  <si>
+    <t>Cap-0805</t>
+  </si>
+  <si>
+    <t>CS2012X5R226M250NRE</t>
+  </si>
+  <si>
+    <t>Samwha Capacitor</t>
+  </si>
+  <si>
+    <t>C513764</t>
+  </si>
+  <si>
+    <t>C50, C52</t>
+  </si>
+  <si>
+    <t>C2, C7, C9, C10, C12, C13, C19, C20, C21, C22, C29, C30, C31, C32, C33, C34, C35, C37, C40, C41, C44, C45, C46, C47, C48, C49, C51, C54</t>
+  </si>
+  <si>
+    <t>J3</t>
+  </si>
+  <si>
+    <t>CONN RCPT USB2.0 MICRO B SMD</t>
+  </si>
+  <si>
+    <t>105133-0011</t>
+  </si>
+  <si>
+    <t>Molex</t>
+  </si>
+  <si>
+    <t>C586226</t>
+  </si>
+  <si>
+    <t>J1, J2</t>
+  </si>
+  <si>
+    <t>TERM BLK 2POS TOP ENT 5.08MM PCB</t>
+  </si>
+  <si>
+    <t>HA0200500000G</t>
+  </si>
+  <si>
+    <t>Amphenol</t>
+  </si>
+  <si>
+    <t>C967080</t>
+  </si>
+  <si>
+    <t>C6, C4, C36, C53</t>
+  </si>
+  <si>
+    <t>C53 Not Confirm</t>
+  </si>
+  <si>
+    <t>C526997</t>
+  </si>
+  <si>
+    <t>CC0402JRNPO8BN330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Less Stock On LCSC </t>
   </si>
 </sst>
 </file>
@@ -1348,7 +1324,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1518,46 +1494,14 @@
     </font>
     <font>
       <b/>
-      <strike/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1585,12 +1529,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1832,7 +1770,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1981,6 +1919,39 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2013,70 +1984,10 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2421,7 +2332,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S83"/>
+  <dimension ref="A1:S81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -2455,15 +2366,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="57"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="68"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2474,7 +2385,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="52" t="s">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2499,7 +2410,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="53" t="s">
-        <v>438</v>
+        <v>408</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2513,7 +2424,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="58"/>
+      <c r="S3" s="69"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2524,7 +2435,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="54" t="s">
-        <v>438</v>
+        <v>408</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2538,7 +2449,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="59"/>
+      <c r="S4" s="70"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2563,7 +2474,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="59"/>
+      <c r="S5" s="70"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2584,7 +2495,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="59"/>
+      <c r="S6" s="70"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2605,7 +2516,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="59"/>
+      <c r="S7" s="70"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2626,7 +2537,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="59"/>
+      <c r="S8" s="70"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2636,53 +2547,53 @@
       <c r="C9" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="66" t="s">
+      <c r="D9" s="56" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="F9" s="66" t="s">
-        <v>170</v>
+        <v>91</v>
+      </c>
+      <c r="F9" s="56" t="s">
+        <v>158</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="H9" s="66" t="s">
-        <v>274</v>
+        <v>198</v>
+      </c>
+      <c r="H9" s="56" t="s">
+        <v>255</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>412</v>
-      </c>
-      <c r="J9" s="66" t="s">
-        <v>311</v>
-      </c>
-      <c r="K9" s="67" t="s">
-        <v>413</v>
+        <v>384</v>
+      </c>
+      <c r="J9" s="56" t="s">
+        <v>290</v>
+      </c>
+      <c r="K9" s="57" t="s">
+        <v>385</v>
       </c>
       <c r="L9" s="30" t="s">
-        <v>408</v>
-      </c>
-      <c r="M9" s="68" t="s">
-        <v>417</v>
-      </c>
-      <c r="N9" s="66" t="s">
-        <v>418</v>
+        <v>380</v>
+      </c>
+      <c r="M9" s="58" t="s">
+        <v>389</v>
+      </c>
+      <c r="N9" s="56" t="s">
+        <v>390</v>
       </c>
       <c r="O9" s="30" t="s">
-        <v>414</v>
-      </c>
-      <c r="P9" s="66" t="s">
-        <v>419</v>
+        <v>386</v>
+      </c>
+      <c r="P9" s="56" t="s">
+        <v>391</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>420</v>
-      </c>
-      <c r="R9" s="66" t="s">
-        <v>415</v>
+        <v>392</v>
+      </c>
+      <c r="R9" s="56" t="s">
+        <v>387</v>
       </c>
       <c r="S9" s="30" t="s">
-        <v>416</v>
+        <v>388</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -2691,32 +2602,32 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="72" t="s">
+      <c r="C10" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="D10" s="65" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>374</v>
+        <v>349</v>
       </c>
       <c r="L10" s="37">
         <v>1</v>
@@ -2728,8 +2639,8 @@
       <c r="N10" s="37">
         <v>10</v>
       </c>
-      <c r="O10" s="69" t="s">
-        <v>422</v>
+      <c r="O10" s="59" t="s">
+        <v>394</v>
       </c>
       <c r="P10" s="39">
         <v>0.15939999999999999</v>
@@ -2744,48 +2655,48 @@
     <row r="11" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="49">
-        <f t="shared" ref="B11:B81" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B79" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="73" t="s">
+      <c r="C11" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="38" t="s">
-        <v>29</v>
+      <c r="D11" s="77" t="s">
+        <v>415</v>
       </c>
       <c r="E11" s="38" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>171</v>
-      </c>
-      <c r="G11" s="70" t="s">
-        <v>216</v>
+        <v>159</v>
+      </c>
+      <c r="G11" s="60" t="s">
+        <v>200</v>
       </c>
       <c r="H11" s="38" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="I11" s="38" t="s">
-        <v>423</v>
+        <v>395</v>
       </c>
       <c r="J11" s="38" t="s">
-        <v>313</v>
+        <v>292</v>
       </c>
       <c r="K11" s="38" t="s">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="L11" s="38">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M11" s="38">
         <f t="shared" ref="M11" si="1">L11*5</f>
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="N11" s="38">
         <v>150</v>
       </c>
-      <c r="O11" s="71" t="s">
-        <v>422</v>
+      <c r="O11" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P11" s="40">
         <v>1.04E-2</v>
@@ -2797,52 +2708,60 @@
       <c r="R11" s="38"/>
       <c r="S11" s="38"/>
     </row>
-    <row r="12" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="48">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="72" t="s">
+      <c r="C12" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="77" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="77" t="s">
-        <v>101</v>
-      </c>
-      <c r="F12" s="77" t="s">
-        <v>172</v>
-      </c>
-      <c r="G12" s="77" t="s">
-        <v>217</v>
-      </c>
-      <c r="H12" s="77" t="s">
-        <v>276</v>
-      </c>
-      <c r="I12" s="77"/>
-      <c r="J12" s="77"/>
-      <c r="K12" s="77" t="s">
-        <v>376</v>
-      </c>
-      <c r="L12" s="77">
+      <c r="D12" s="65" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="65" t="s">
+        <v>409</v>
+      </c>
+      <c r="F12" s="65" t="s">
+        <v>410</v>
+      </c>
+      <c r="G12" s="65" t="s">
+        <v>411</v>
+      </c>
+      <c r="H12" s="65" t="s">
+        <v>412</v>
+      </c>
+      <c r="I12" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J12" s="65" t="s">
+        <v>413</v>
+      </c>
+      <c r="K12" s="65" t="s">
+        <v>351</v>
+      </c>
+      <c r="L12" s="65">
         <v>2</v>
       </c>
-      <c r="M12" s="77">
+      <c r="M12" s="65">
         <f>L12*5</f>
         <v>10</v>
       </c>
-      <c r="N12" s="77"/>
-      <c r="O12" s="77"/>
-      <c r="P12" s="78"/>
-      <c r="Q12" s="78">
+      <c r="N12" s="65">
+        <v>20</v>
+      </c>
+      <c r="O12" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P12" s="66">
+        <v>6.2E-2</v>
+      </c>
+      <c r="Q12" s="66">
         <f>P12*N12</f>
-        <v>0</v>
-      </c>
-      <c r="R12" s="79" t="s">
-        <v>433</v>
-      </c>
+        <v>1.24</v>
+      </c>
+      <c r="R12" s="64"/>
       <c r="S12" s="37"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
@@ -2851,1270 +2770,1286 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="73" t="s">
+      <c r="C13" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="38" t="s">
-        <v>31</v>
+      <c r="D13" s="77" t="s">
+        <v>426</v>
       </c>
       <c r="E13" s="38" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>421</v>
+        <v>393</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="I13" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J13" s="38" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="K13" s="38" t="s">
-        <v>377</v>
+        <v>352</v>
       </c>
       <c r="L13" s="38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M13" s="38">
         <f t="shared" ref="M13" si="3">L13*5</f>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="N13" s="38">
-        <v>6</v>
-      </c>
-      <c r="O13" s="71" t="s">
-        <v>422</v>
+        <v>22</v>
+      </c>
+      <c r="O13" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P13" s="40">
-        <v>0.61299999999999999</v>
+        <v>0.49540000000000001</v>
       </c>
       <c r="Q13" s="40">
         <f t="shared" ref="Q13" si="4">P13*N13</f>
-        <v>3.6779999999999999</v>
-      </c>
-      <c r="R13" s="38"/>
+        <v>10.8988</v>
+      </c>
+      <c r="R13" s="78" t="s">
+        <v>427</v>
+      </c>
       <c r="S13" s="38"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="48">
-        <f>ROW(B14) - ROW($B$9)</f>
+      <c r="B14" s="49">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="72" t="s">
+      <c r="C14" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="F14" s="37" t="s">
-        <v>421</v>
-      </c>
-      <c r="G14" s="37" t="s">
-        <v>174</v>
-      </c>
-      <c r="H14" s="37" t="s">
-        <v>277</v>
-      </c>
-      <c r="I14" s="37"/>
-      <c r="J14" s="37" t="s">
-        <v>315</v>
-      </c>
-      <c r="K14" s="37" t="s">
-        <v>378</v>
-      </c>
-      <c r="L14" s="37">
-        <v>2</v>
-      </c>
-      <c r="M14" s="37">
-        <f>L14*5</f>
-        <v>10</v>
-      </c>
-      <c r="N14" s="37"/>
-      <c r="O14" s="37"/>
-      <c r="P14" s="39"/>
-      <c r="Q14" s="39">
-        <f>P14*N14</f>
-        <v>0</v>
-      </c>
-      <c r="R14" s="37"/>
+      <c r="D14" s="65" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="65" t="s">
+        <v>95</v>
+      </c>
+      <c r="F14" s="65" t="s">
+        <v>161</v>
+      </c>
+      <c r="G14" s="65" t="s">
+        <v>201</v>
+      </c>
+      <c r="H14" s="65" t="s">
+        <v>258</v>
+      </c>
+      <c r="I14" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J14" s="65" t="s">
+        <v>294</v>
+      </c>
+      <c r="K14" s="65" t="s">
+        <v>353</v>
+      </c>
+      <c r="L14" s="65">
+        <v>1</v>
+      </c>
+      <c r="M14" s="65">
+        <f t="shared" ref="M14" si="5">L14*5</f>
+        <v>5</v>
+      </c>
+      <c r="N14" s="65">
+        <v>6</v>
+      </c>
+      <c r="O14" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P14" s="66">
+        <v>0.91320000000000001</v>
+      </c>
+      <c r="Q14" s="66">
+        <f t="shared" ref="Q14" si="6">P14*N14</f>
+        <v>5.4792000000000005</v>
+      </c>
+      <c r="R14" s="64"/>
       <c r="S14" s="37"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="49">
-        <f t="shared" si="0"/>
+      <c r="B15" s="48">
+        <f>ROW(B15) - ROW($B$9)</f>
         <v>6</v>
       </c>
-      <c r="C15" s="73" t="s">
+      <c r="C15" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="38" t="s">
-        <v>33</v>
+      <c r="D15" s="77" t="s">
+        <v>31</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="H15" s="38" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="I15" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J15" s="38" t="s">
-        <v>316</v>
+        <v>295</v>
       </c>
       <c r="K15" s="38" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
       <c r="L15" s="38">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M15" s="38">
-        <f t="shared" ref="M15" si="5">L15*5</f>
-        <v>5</v>
+        <f>L15*5</f>
+        <v>60</v>
       </c>
       <c r="N15" s="38">
-        <v>6</v>
-      </c>
-      <c r="O15" s="71" t="s">
-        <v>422</v>
+        <v>100</v>
+      </c>
+      <c r="O15" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P15" s="40">
-        <v>0.91320000000000001</v>
+        <v>2.8E-3</v>
       </c>
       <c r="Q15" s="40">
-        <f t="shared" ref="Q15" si="6">P15*N15</f>
-        <v>5.4792000000000005</v>
+        <f>P15*N15</f>
+        <v>0.27999999999999997</v>
       </c>
       <c r="R15" s="38"/>
       <c r="S15" s="38"/>
     </row>
-    <row r="16" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="48">
-        <f>ROW(B16) - ROW($B$9)</f>
+      <c r="B16" s="49">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="72" t="s">
+      <c r="C16" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="F16" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="G16" s="37" t="s">
-        <v>219</v>
-      </c>
-      <c r="H16" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="I16" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J16" s="37" t="s">
-        <v>317</v>
-      </c>
-      <c r="K16" s="37" t="s">
-        <v>380</v>
-      </c>
-      <c r="L16" s="37">
-        <v>12</v>
-      </c>
-      <c r="M16" s="37">
-        <f>L16*5</f>
-        <v>60</v>
-      </c>
-      <c r="N16" s="37">
+      <c r="D16" s="65" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="65" t="s">
+        <v>97</v>
+      </c>
+      <c r="F16" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="G16" s="65" t="s">
+        <v>203</v>
+      </c>
+      <c r="H16" s="65" t="s">
+        <v>256</v>
+      </c>
+      <c r="I16" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J16" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="K16" s="65" t="s">
+        <v>355</v>
+      </c>
+      <c r="L16" s="65">
+        <v>1</v>
+      </c>
+      <c r="M16" s="65">
+        <f t="shared" ref="M16" si="7">L16*5</f>
+        <v>5</v>
+      </c>
+      <c r="N16" s="65">
         <v>100</v>
       </c>
-      <c r="O16" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P16" s="39">
-        <v>2.8E-3</v>
-      </c>
-      <c r="Q16" s="39">
-        <f>P16*N16</f>
-        <v>0.27999999999999997</v>
-      </c>
-      <c r="R16" s="37"/>
+      <c r="O16" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P16" s="66">
+        <v>4.8999999999999998E-3</v>
+      </c>
+      <c r="Q16" s="66">
+        <f t="shared" ref="Q16" si="8">P16*N16</f>
+        <v>0.49</v>
+      </c>
+      <c r="R16" s="64"/>
       <c r="S16" s="37"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="49">
-        <f t="shared" si="0"/>
+      <c r="B17" s="48">
+        <f>ROW(B17) - ROW($B$9)</f>
         <v>8</v>
       </c>
-      <c r="C17" s="73" t="s">
+      <c r="C17" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="38" t="s">
-        <v>35</v>
+      <c r="D17" s="77" t="s">
+        <v>33</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>171</v>
-      </c>
-      <c r="G17" s="38" t="s">
-        <v>220</v>
+        <v>162</v>
+      </c>
+      <c r="G17" s="60" t="s">
+        <v>204</v>
       </c>
       <c r="H17" s="38" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="I17" s="38" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="J17" s="38" t="s">
-        <v>318</v>
+        <v>428</v>
       </c>
       <c r="K17" s="38" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
       <c r="L17" s="38">
         <v>1</v>
       </c>
       <c r="M17" s="38">
-        <f t="shared" ref="M17" si="7">L17*5</f>
+        <f>L17*5</f>
         <v>5</v>
       </c>
       <c r="N17" s="38">
         <v>100</v>
       </c>
-      <c r="O17" s="71" t="s">
-        <v>422</v>
+      <c r="O17" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P17" s="40">
-        <v>4.8999999999999998E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q17" s="40">
-        <f t="shared" ref="Q17" si="8">P17*N17</f>
-        <v>0.49</v>
+        <f>P17*N17</f>
+        <v>0.13</v>
       </c>
       <c r="R17" s="38"/>
       <c r="S17" s="38"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="48">
-        <f>ROW(B18) - ROW($B$9)</f>
+      <c r="B18" s="49">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="72" t="s">
+      <c r="C18" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="F18" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="G18" s="37" t="s">
-        <v>221</v>
-      </c>
-      <c r="H18" s="37" t="s">
-        <v>278</v>
-      </c>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37" t="s">
-        <v>319</v>
-      </c>
-      <c r="K18" s="37" t="s">
-        <v>382</v>
-      </c>
-      <c r="L18" s="37">
-        <v>1</v>
-      </c>
-      <c r="M18" s="37">
-        <f>L18*5</f>
-        <v>5</v>
-      </c>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="39"/>
-      <c r="Q18" s="39">
-        <f>P18*N18</f>
-        <v>0</v>
-      </c>
-      <c r="R18" s="37"/>
+      <c r="D18" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="65" t="s">
+        <v>99</v>
+      </c>
+      <c r="F18" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="G18" s="65" t="s">
+        <v>205</v>
+      </c>
+      <c r="H18" s="65" t="s">
+        <v>256</v>
+      </c>
+      <c r="I18" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J18" s="65" t="s">
+        <v>297</v>
+      </c>
+      <c r="K18" s="65" t="s">
+        <v>357</v>
+      </c>
+      <c r="L18" s="65">
+        <v>2</v>
+      </c>
+      <c r="M18" s="65">
+        <f t="shared" ref="M18" si="9">L18*5</f>
+        <v>10</v>
+      </c>
+      <c r="N18" s="65">
+        <v>100</v>
+      </c>
+      <c r="O18" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P18" s="66">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="Q18" s="66">
+        <f t="shared" ref="Q18" si="10">P18*N18</f>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="R18" s="64"/>
       <c r="S18" s="37"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="49">
-        <f t="shared" si="0"/>
+      <c r="B19" s="48">
+        <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="73" t="s">
+      <c r="C19" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="38" t="s">
-        <v>37</v>
+      <c r="D19" s="77" t="s">
+        <v>414</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="F19" s="38" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="G19" s="38" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="H19" s="38" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="I19" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J19" s="38" t="s">
-        <v>320</v>
+        <v>298</v>
       </c>
       <c r="K19" s="38" t="s">
-        <v>383</v>
+        <v>358</v>
       </c>
       <c r="L19" s="38">
         <v>2</v>
       </c>
       <c r="M19" s="38">
-        <f t="shared" ref="M19" si="9">L19*5</f>
+        <f>L19*5</f>
         <v>10</v>
       </c>
       <c r="N19" s="38">
-        <v>100</v>
-      </c>
-      <c r="O19" s="71" t="s">
-        <v>422</v>
+        <v>20</v>
+      </c>
+      <c r="O19" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P19" s="40">
-        <v>2.8999999999999998E-3</v>
+        <v>2.3599999999999999E-2</v>
       </c>
       <c r="Q19" s="40">
-        <f t="shared" ref="Q19" si="10">P19*N19</f>
-        <v>0.28999999999999998</v>
+        <f>P19*N19</f>
+        <v>0.47199999999999998</v>
       </c>
       <c r="R19" s="38"/>
       <c r="S19" s="38"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="48">
-        <f>ROW(B20) - ROW($B$9)</f>
+      <c r="B20" s="49">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>109</v>
-      </c>
-      <c r="F20" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="G20" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="H20" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="I20" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J20" s="37" t="s">
-        <v>321</v>
-      </c>
-      <c r="K20" s="37" t="s">
-        <v>384</v>
-      </c>
-      <c r="L20" s="37">
-        <v>3</v>
-      </c>
-      <c r="M20" s="37">
-        <f>L20*5</f>
+      <c r="C20" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="65" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="65" t="s">
+        <v>101</v>
+      </c>
+      <c r="F20" s="65" t="s">
+        <v>163</v>
+      </c>
+      <c r="G20" s="65" t="s">
+        <v>207</v>
+      </c>
+      <c r="H20" s="65" t="s">
+        <v>260</v>
+      </c>
+      <c r="I20" s="65"/>
+      <c r="J20" s="65" t="s">
+        <v>299</v>
+      </c>
+      <c r="K20" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="L20" s="65">
+        <v>7</v>
+      </c>
+      <c r="M20" s="65">
+        <f t="shared" ref="M20" si="11">L20*5</f>
+        <v>35</v>
+      </c>
+      <c r="N20" s="65">
+        <v>40</v>
+      </c>
+      <c r="O20" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P20" s="66">
+        <v>6.3700000000000007E-2</v>
+      </c>
+      <c r="Q20" s="66">
+        <f t="shared" ref="Q20" si="12">P20*N20</f>
+        <v>2.548</v>
+      </c>
+      <c r="R20" s="64"/>
+      <c r="S20" s="37"/>
+    </row>
+    <row r="21" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="48">
+        <f>ROW(B21) - ROW($B$9)</f>
+        <v>12</v>
+      </c>
+      <c r="C21" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="77" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="F21" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="G21" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="H21" s="38" t="s">
+        <v>261</v>
+      </c>
+      <c r="I21" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J21" s="38" t="s">
+        <v>300</v>
+      </c>
+      <c r="K21" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L21" s="38">
+        <v>2</v>
+      </c>
+      <c r="M21" s="38">
+        <f>L21*5</f>
+        <v>10</v>
+      </c>
+      <c r="N21" s="38">
         <v>15</v>
       </c>
-      <c r="N20" s="37">
-        <v>20</v>
-      </c>
-      <c r="O20" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P20" s="39">
-        <v>2.3599999999999999E-2</v>
-      </c>
-      <c r="Q20" s="39">
-        <f>P20*N20</f>
-        <v>0.47199999999999998</v>
-      </c>
-      <c r="R20" s="37"/>
-      <c r="S20" s="37"/>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="49">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="C21" s="73" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="E21" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="F21" s="38" t="s">
-        <v>177</v>
-      </c>
-      <c r="G21" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="H21" s="38" t="s">
-        <v>279</v>
-      </c>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38" t="s">
-        <v>322</v>
-      </c>
-      <c r="K21" s="38" t="s">
-        <v>409</v>
-      </c>
-      <c r="L21" s="38">
-        <v>7</v>
-      </c>
-      <c r="M21" s="38">
-        <f t="shared" ref="M21" si="11">L21*5</f>
-        <v>35</v>
-      </c>
-      <c r="N21" s="38">
-        <v>40</v>
-      </c>
-      <c r="O21" s="71" t="s">
-        <v>422</v>
+      <c r="O21" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P21" s="40">
-        <v>6.3700000000000007E-2</v>
+        <v>8.6400000000000005E-2</v>
       </c>
       <c r="Q21" s="40">
-        <f t="shared" ref="Q21" si="12">P21*N21</f>
-        <v>2.548</v>
+        <f>P21*N21</f>
+        <v>1.296</v>
       </c>
       <c r="R21" s="38"/>
       <c r="S21" s="38"/>
     </row>
-    <row r="22" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="48">
-        <f>ROW(B22) - ROW($B$9)</f>
+      <c r="B22" s="49">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="72" t="s">
+      <c r="C22" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="E22" s="37" t="s">
-        <v>111</v>
-      </c>
-      <c r="F22" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="G22" s="37" t="s">
-        <v>225</v>
-      </c>
-      <c r="H22" s="37" t="s">
-        <v>280</v>
-      </c>
-      <c r="I22" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J22" s="37" t="s">
-        <v>323</v>
-      </c>
-      <c r="K22" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="L22" s="37">
-        <v>2</v>
-      </c>
-      <c r="M22" s="37">
-        <f>L22*5</f>
+      <c r="D22" s="65" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="65" t="s">
+        <v>103</v>
+      </c>
+      <c r="F22" s="65" t="s">
+        <v>165</v>
+      </c>
+      <c r="G22" s="65" t="s">
+        <v>209</v>
+      </c>
+      <c r="H22" s="65" t="s">
+        <v>262</v>
+      </c>
+      <c r="I22" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J22" s="65" t="s">
+        <v>301</v>
+      </c>
+      <c r="K22" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="L22" s="65">
+        <v>1</v>
+      </c>
+      <c r="M22" s="65">
+        <f t="shared" ref="M22" si="13">L22*5</f>
+        <v>5</v>
+      </c>
+      <c r="N22" s="65">
+        <v>20</v>
+      </c>
+      <c r="O22" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P22" s="66">
+        <v>3.32E-2</v>
+      </c>
+      <c r="Q22" s="66">
+        <f t="shared" ref="Q22" si="14">P22*N22</f>
+        <v>0.66400000000000003</v>
+      </c>
+      <c r="R22" s="64"/>
+      <c r="S22" s="37"/>
+    </row>
+    <row r="23" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="48">
+        <f>ROW(B23) - ROW($B$9)</f>
+        <v>14</v>
+      </c>
+      <c r="C23" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="N22" s="37">
-        <v>15</v>
-      </c>
-      <c r="O22" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P22" s="39">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="Q22" s="39">
-        <f>P22*N22</f>
-        <v>1.296</v>
-      </c>
-      <c r="R22" s="37"/>
-      <c r="S22" s="37"/>
-    </row>
-    <row r="23" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="49">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="C23" s="73" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="38" t="s">
-        <v>41</v>
+      <c r="D23" s="77" t="s">
+        <v>38</v>
       </c>
       <c r="E23" s="38" t="s">
-        <v>112</v>
+        <v>402</v>
       </c>
       <c r="F23" s="38" t="s">
-        <v>179</v>
+        <v>403</v>
       </c>
       <c r="G23" s="38" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="H23" s="38" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="I23" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J23" s="38" t="s">
-        <v>324</v>
+        <v>404</v>
       </c>
       <c r="K23" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="L23" s="38">
         <v>1</v>
       </c>
       <c r="M23" s="38">
-        <f t="shared" ref="M23" si="13">L23*5</f>
+        <f>L23*5</f>
         <v>5</v>
       </c>
       <c r="N23" s="38">
         <v>20</v>
       </c>
-      <c r="O23" s="71" t="s">
-        <v>422</v>
+      <c r="O23" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P23" s="40">
-        <v>3.32E-2</v>
+        <v>3.6200000000000003E-2</v>
       </c>
       <c r="Q23" s="40">
-        <f t="shared" ref="Q23" si="14">P23*N23</f>
-        <v>0.66400000000000003</v>
+        <f>P23*N23</f>
+        <v>0.72400000000000009</v>
       </c>
       <c r="R23" s="38"/>
       <c r="S23" s="38"/>
     </row>
     <row r="24" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="48">
-        <f>ROW(B24) - ROW($B$9)</f>
+      <c r="B24" s="49">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="72" t="s">
+      <c r="C24" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="E24" s="37" t="s">
-        <v>430</v>
-      </c>
-      <c r="F24" s="37" t="s">
-        <v>431</v>
-      </c>
-      <c r="G24" s="37" t="s">
-        <v>227</v>
-      </c>
-      <c r="H24" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="I24" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J24" s="37" t="s">
-        <v>432</v>
-      </c>
-      <c r="K24" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="L24" s="37">
+      <c r="D24" s="65" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="65" t="s">
+        <v>104</v>
+      </c>
+      <c r="F24" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="G24" s="65" t="s">
+        <v>211</v>
+      </c>
+      <c r="H24" s="65" t="s">
+        <v>264</v>
+      </c>
+      <c r="I24" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J24" s="65" t="s">
+        <v>302</v>
+      </c>
+      <c r="K24" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="L24" s="65">
+        <v>8</v>
+      </c>
+      <c r="M24" s="65">
+        <f t="shared" ref="M24" si="15">L24*5</f>
+        <v>40</v>
+      </c>
+      <c r="N24" s="65">
+        <v>60</v>
+      </c>
+      <c r="O24" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P24" s="66">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="Q24" s="66">
+        <f t="shared" ref="Q24" si="16">P24*N24</f>
+        <v>1.2240000000000002</v>
+      </c>
+      <c r="R24" s="64"/>
+      <c r="S24" s="37"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="48">
+        <f>ROW(B25) - ROW($B$9)</f>
+        <v>16</v>
+      </c>
+      <c r="C25" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="F25" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="G25" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="H25" s="38" t="s">
+        <v>265</v>
+      </c>
+      <c r="I25" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J25" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="K25" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L25" s="38">
         <v>1</v>
       </c>
-      <c r="M24" s="37">
-        <f>L24*5</f>
+      <c r="M25" s="38">
+        <f>L25*5</f>
         <v>5</v>
       </c>
-      <c r="N24" s="37">
-        <v>20</v>
-      </c>
-      <c r="O24" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P24" s="39">
-        <v>3.6200000000000003E-2</v>
-      </c>
-      <c r="Q24" s="39">
-        <f>P24*N24</f>
-        <v>0.72400000000000009</v>
-      </c>
-      <c r="R24" s="79" t="s">
-        <v>433</v>
-      </c>
-      <c r="S24" s="37"/>
-    </row>
-    <row r="25" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="49">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="C25" s="73" t="s">
+      <c r="N25" s="38">
         <v>10</v>
       </c>
-      <c r="D25" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="E25" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="F25" s="38" t="s">
-        <v>180</v>
-      </c>
-      <c r="G25" s="38" t="s">
-        <v>228</v>
-      </c>
-      <c r="H25" s="38" t="s">
-        <v>283</v>
-      </c>
-      <c r="I25" s="38" t="s">
-        <v>409</v>
-      </c>
-      <c r="J25" s="38" t="s">
-        <v>325</v>
-      </c>
-      <c r="K25" s="38" t="s">
-        <v>409</v>
-      </c>
-      <c r="L25" s="38">
-        <v>8</v>
-      </c>
-      <c r="M25" s="38">
-        <f t="shared" ref="M25" si="15">L25*5</f>
-        <v>40</v>
-      </c>
-      <c r="N25" s="38">
-        <v>60</v>
-      </c>
-      <c r="O25" s="71" t="s">
-        <v>422</v>
+      <c r="O25" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P25" s="40">
-        <v>2.0400000000000001E-2</v>
+        <v>0.104</v>
       </c>
       <c r="Q25" s="40">
-        <f t="shared" ref="Q25" si="16">P25*N25</f>
-        <v>1.2240000000000002</v>
+        <f>P25*N25</f>
+        <v>1.04</v>
       </c>
       <c r="R25" s="38"/>
       <c r="S25" s="38"/>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="48">
-        <f>ROW(B26) - ROW($B$9)</f>
+      <c r="B26" s="49">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="72" t="s">
+      <c r="C26" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26" s="37" t="s">
-        <v>114</v>
-      </c>
-      <c r="F26" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="G26" s="37" t="s">
-        <v>229</v>
-      </c>
-      <c r="H26" s="37" t="s">
-        <v>284</v>
-      </c>
-      <c r="I26" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J26" s="37" t="s">
-        <v>326</v>
-      </c>
-      <c r="K26" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="L26" s="37">
+      <c r="D26" s="65" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="65" t="s">
+        <v>106</v>
+      </c>
+      <c r="F26" s="65" t="s">
+        <v>168</v>
+      </c>
+      <c r="G26" s="65" t="s">
+        <v>213</v>
+      </c>
+      <c r="H26" s="65" t="s">
+        <v>266</v>
+      </c>
+      <c r="I26" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J26" s="65" t="s">
+        <v>304</v>
+      </c>
+      <c r="K26" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="L26" s="65">
+        <v>3</v>
+      </c>
+      <c r="M26" s="65">
+        <f t="shared" ref="M26" si="17">L26*5</f>
+        <v>15</v>
+      </c>
+      <c r="N26" s="65">
+        <v>20</v>
+      </c>
+      <c r="O26" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P26" s="66">
+        <v>3.1699999999999999E-2</v>
+      </c>
+      <c r="Q26" s="66">
+        <f t="shared" ref="Q26" si="18">P26*N26</f>
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="R26" s="64"/>
+      <c r="S26" s="37"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="48">
+        <f>ROW(B27) - ROW($B$9)</f>
+        <v>18</v>
+      </c>
+      <c r="C27" s="63" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="77" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="F27" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="G27" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="H27" s="38" t="s">
+        <v>267</v>
+      </c>
+      <c r="I27" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J27" s="38" t="s">
+        <v>305</v>
+      </c>
+      <c r="K27" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L27" s="38">
         <v>1</v>
       </c>
-      <c r="M26" s="37">
-        <f>L26*5</f>
+      <c r="M27" s="38">
+        <f>L27*5</f>
         <v>5</v>
       </c>
-      <c r="N26" s="37">
+      <c r="N27" s="38">
         <v>10</v>
       </c>
-      <c r="O26" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P26" s="39">
-        <v>0.104</v>
-      </c>
-      <c r="Q26" s="39">
-        <f>P26*N26</f>
-        <v>1.04</v>
-      </c>
-      <c r="R26" s="37"/>
-      <c r="S26" s="37"/>
-    </row>
-    <row r="27" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="49">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="C27" s="73" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="F27" s="38" t="s">
-        <v>182</v>
-      </c>
-      <c r="G27" s="38" t="s">
-        <v>230</v>
-      </c>
-      <c r="H27" s="38" t="s">
-        <v>285</v>
-      </c>
-      <c r="I27" s="38" t="s">
-        <v>409</v>
-      </c>
-      <c r="J27" s="38" t="s">
-        <v>327</v>
-      </c>
-      <c r="K27" s="38" t="s">
-        <v>409</v>
-      </c>
-      <c r="L27" s="38">
-        <v>3</v>
-      </c>
-      <c r="M27" s="38">
-        <f t="shared" ref="M27" si="17">L27*5</f>
-        <v>15</v>
-      </c>
-      <c r="N27" s="38">
-        <v>20</v>
-      </c>
-      <c r="O27" s="71" t="s">
-        <v>422</v>
+      <c r="O27" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P27" s="40">
-        <v>3.1699999999999999E-2</v>
+        <v>3.5400000000000001E-2</v>
       </c>
       <c r="Q27" s="40">
-        <f t="shared" ref="Q27" si="18">P27*N27</f>
-        <v>0.63400000000000001</v>
+        <f>P27*N27</f>
+        <v>0.35399999999999998</v>
       </c>
       <c r="R27" s="38"/>
       <c r="S27" s="38"/>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="48">
-        <f>ROW(B28) - ROW($B$9)</f>
+      <c r="B28" s="49">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="72" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="E28" s="37" t="s">
-        <v>116</v>
-      </c>
-      <c r="F28" s="37" t="s">
-        <v>183</v>
-      </c>
-      <c r="G28" s="37" t="s">
-        <v>231</v>
-      </c>
-      <c r="H28" s="37" t="s">
-        <v>286</v>
-      </c>
-      <c r="I28" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J28" s="37" t="s">
-        <v>328</v>
-      </c>
-      <c r="K28" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="L28" s="37">
+      <c r="C28" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="65" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" s="65" t="s">
+        <v>108</v>
+      </c>
+      <c r="F28" s="65" t="s">
+        <v>168</v>
+      </c>
+      <c r="G28" s="65" t="s">
+        <v>215</v>
+      </c>
+      <c r="H28" s="65" t="s">
+        <v>261</v>
+      </c>
+      <c r="I28" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J28" s="65" t="s">
+        <v>306</v>
+      </c>
+      <c r="K28" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="L28" s="65">
+        <v>5</v>
+      </c>
+      <c r="M28" s="65">
+        <f t="shared" ref="M28" si="19">L28*5</f>
+        <v>25</v>
+      </c>
+      <c r="N28" s="65">
+        <v>50</v>
+      </c>
+      <c r="O28" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P28" s="66">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="Q28" s="66">
+        <f t="shared" ref="Q28" si="20">P28*N28</f>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="R28" s="64"/>
+      <c r="S28" s="37"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="48">
+        <f>ROW(B29) - ROW($B$9)</f>
+        <v>20</v>
+      </c>
+      <c r="C29" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F29" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="G29" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="H29" s="38" t="s">
+        <v>268</v>
+      </c>
+      <c r="I29" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J29" s="38" t="s">
+        <v>307</v>
+      </c>
+      <c r="K29" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L29" s="38">
         <v>1</v>
       </c>
-      <c r="M28" s="37">
-        <f>L28*5</f>
+      <c r="M29" s="38">
+        <f>L29*5</f>
         <v>5</v>
       </c>
-      <c r="N28" s="37">
-        <v>10</v>
-      </c>
-      <c r="O28" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P28" s="39">
-        <v>3.5400000000000001E-2</v>
-      </c>
-      <c r="Q28" s="39">
-        <f>P28*N28</f>
-        <v>0.35399999999999998</v>
-      </c>
-      <c r="R28" s="37"/>
-      <c r="S28" s="37"/>
-    </row>
-    <row r="29" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-      <c r="B29" s="49">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="C29" s="73" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="F29" s="38" t="s">
-        <v>182</v>
-      </c>
-      <c r="G29" s="38" t="s">
-        <v>232</v>
-      </c>
-      <c r="H29" s="38" t="s">
-        <v>280</v>
-      </c>
-      <c r="I29" s="38" t="s">
-        <v>409</v>
-      </c>
-      <c r="J29" s="38" t="s">
-        <v>329</v>
-      </c>
-      <c r="K29" s="38" t="s">
-        <v>409</v>
-      </c>
-      <c r="L29" s="38">
-        <v>5</v>
-      </c>
-      <c r="M29" s="38">
-        <f t="shared" ref="M29" si="19">L29*5</f>
-        <v>25</v>
-      </c>
       <c r="N29" s="38">
-        <v>50</v>
-      </c>
-      <c r="O29" s="71" t="s">
-        <v>422</v>
+        <v>6</v>
+      </c>
+      <c r="O29" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P29" s="40">
-        <v>1.7999999999999999E-2</v>
+        <v>0.2319</v>
       </c>
       <c r="Q29" s="40">
-        <f t="shared" ref="Q29" si="20">P29*N29</f>
-        <v>0.89999999999999991</v>
+        <f>P29*N29</f>
+        <v>1.3914</v>
       </c>
       <c r="R29" s="38"/>
       <c r="S29" s="38"/>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="48">
-        <f>ROW(B30) - ROW($B$9)</f>
+      <c r="B30" s="49">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="72" t="s">
+      <c r="C30" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="D30" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="E30" s="37" t="s">
-        <v>118</v>
-      </c>
-      <c r="F30" s="37" t="s">
-        <v>184</v>
-      </c>
-      <c r="G30" s="37" t="s">
-        <v>233</v>
-      </c>
-      <c r="H30" s="37" t="s">
-        <v>287</v>
-      </c>
-      <c r="I30" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J30" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="K30" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="L30" s="37">
+      <c r="D30" s="65" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="65" t="s">
+        <v>110</v>
+      </c>
+      <c r="F30" s="65" t="s">
+        <v>171</v>
+      </c>
+      <c r="G30" s="65" t="s">
+        <v>217</v>
+      </c>
+      <c r="H30" s="65" t="s">
+        <v>269</v>
+      </c>
+      <c r="I30" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J30" s="65" t="s">
+        <v>399</v>
+      </c>
+      <c r="K30" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="L30" s="65">
+        <v>2</v>
+      </c>
+      <c r="M30" s="65">
+        <f t="shared" ref="M30" si="21">L30*5</f>
+        <v>10</v>
+      </c>
+      <c r="N30" s="65">
+        <v>20</v>
+      </c>
+      <c r="O30" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P30" s="66">
+        <v>4.5900000000000003E-2</v>
+      </c>
+      <c r="Q30" s="66">
+        <f t="shared" ref="Q30" si="22">P30*N30</f>
+        <v>0.91800000000000004</v>
+      </c>
+      <c r="R30" s="64"/>
+      <c r="S30" s="37"/>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="48">
+        <f>ROW(B31) - ROW($B$9)</f>
+        <v>22</v>
+      </c>
+      <c r="C31" s="63" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="77" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="F31" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="G31" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="H31" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="I31" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J31" s="38" t="s">
+        <v>308</v>
+      </c>
+      <c r="K31" s="38" t="s">
+        <v>359</v>
+      </c>
+      <c r="L31" s="38">
         <v>1</v>
       </c>
-      <c r="M30" s="37">
-        <f>L30*5</f>
+      <c r="M31" s="38">
+        <f>L31*5</f>
         <v>5</v>
       </c>
-      <c r="N30" s="37">
-        <v>6</v>
-      </c>
-      <c r="O30" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P30" s="39">
-        <v>0.2319</v>
-      </c>
-      <c r="Q30" s="39">
-        <f>P30*N30</f>
-        <v>1.3914</v>
-      </c>
-      <c r="R30" s="37"/>
-      <c r="S30" s="37"/>
-    </row>
-    <row r="31" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="B31" s="49">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="C31" s="73" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="E31" s="38" t="s">
-        <v>119</v>
-      </c>
-      <c r="F31" s="38" t="s">
-        <v>185</v>
-      </c>
-      <c r="G31" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="H31" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="I31" s="38" t="s">
-        <v>409</v>
-      </c>
-      <c r="J31" s="38" t="s">
-        <v>427</v>
-      </c>
-      <c r="K31" s="38" t="s">
-        <v>409</v>
-      </c>
-      <c r="L31" s="38">
-        <v>2</v>
-      </c>
-      <c r="M31" s="38">
-        <f t="shared" ref="M31" si="21">L31*5</f>
+      <c r="N31" s="38">
         <v>10</v>
       </c>
-      <c r="N31" s="38">
-        <v>20</v>
-      </c>
-      <c r="O31" s="71" t="s">
-        <v>422</v>
+      <c r="O31" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P31" s="40">
-        <v>4.5900000000000003E-2</v>
+        <v>0.1193</v>
       </c>
       <c r="Q31" s="40">
-        <f t="shared" ref="Q31" si="22">P31*N31</f>
-        <v>0.91800000000000004</v>
+        <f>P31*N31</f>
+        <v>1.1930000000000001</v>
       </c>
       <c r="R31" s="38"/>
       <c r="S31" s="38"/>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="48">
-        <f>ROW(B32) - ROW($B$9)</f>
+      <c r="B32" s="49">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="72" t="s">
+      <c r="C32" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="37" t="s">
+      <c r="D32" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="65" t="s">
+        <v>112</v>
+      </c>
+      <c r="F32" s="65" t="s">
+        <v>173</v>
+      </c>
+      <c r="G32" s="65" t="s">
+        <v>219</v>
+      </c>
+      <c r="H32" s="65" t="s">
+        <v>257</v>
+      </c>
+      <c r="I32" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J32" s="65" t="s">
+        <v>309</v>
+      </c>
+      <c r="K32" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="L32" s="65">
+        <v>8</v>
+      </c>
+      <c r="M32" s="65">
+        <f t="shared" ref="M32" si="23">L32*5</f>
+        <v>40</v>
+      </c>
+      <c r="N32" s="65">
         <v>50</v>
       </c>
-      <c r="E32" s="37" t="s">
-        <v>120</v>
-      </c>
-      <c r="F32" s="37" t="s">
-        <v>186</v>
-      </c>
-      <c r="G32" s="37" t="s">
-        <v>235</v>
-      </c>
-      <c r="H32" s="37" t="s">
-        <v>278</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J32" s="37" t="s">
-        <v>331</v>
-      </c>
-      <c r="K32" s="37" t="s">
-        <v>385</v>
-      </c>
-      <c r="L32" s="37">
-        <v>1</v>
-      </c>
-      <c r="M32" s="37">
-        <f>L32*5</f>
-        <v>5</v>
-      </c>
-      <c r="N32" s="37">
+      <c r="O32" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P32" s="66">
+        <v>4.5600000000000002E-2</v>
+      </c>
+      <c r="Q32" s="66">
+        <f t="shared" ref="Q32" si="24">P32*N32</f>
+        <v>2.2800000000000002</v>
+      </c>
+      <c r="R32" s="64"/>
+      <c r="S32" s="37"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="48">
+        <f>ROW(B33) - ROW($B$9)</f>
+        <v>24</v>
+      </c>
+      <c r="C33" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="77" t="s">
+        <v>421</v>
+      </c>
+      <c r="E33" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="F33" s="38" t="s">
+        <v>393</v>
+      </c>
+      <c r="G33" s="38" t="s">
+        <v>220</v>
+      </c>
+      <c r="H33" s="38" t="s">
+        <v>270</v>
+      </c>
+      <c r="I33" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J33" s="38" t="s">
+        <v>310</v>
+      </c>
+      <c r="K33" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L33" s="38">
+        <v>2</v>
+      </c>
+      <c r="M33" s="38">
+        <f>L33*5</f>
         <v>10</v>
       </c>
-      <c r="O32" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P32" s="39">
-        <v>0.1193</v>
-      </c>
-      <c r="Q32" s="39">
-        <f>P32*N32</f>
-        <v>1.1930000000000001</v>
-      </c>
-      <c r="R32" s="37"/>
-      <c r="S32" s="37"/>
-    </row>
-    <row r="33" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="B33" s="49">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="C33" s="73" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="E33" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="F33" s="38" t="s">
-        <v>187</v>
-      </c>
-      <c r="G33" s="38" t="s">
-        <v>236</v>
-      </c>
-      <c r="H33" s="38" t="s">
-        <v>276</v>
-      </c>
-      <c r="I33" s="38" t="s">
-        <v>409</v>
-      </c>
-      <c r="J33" s="38" t="s">
-        <v>332</v>
-      </c>
-      <c r="K33" s="38" t="s">
-        <v>409</v>
-      </c>
-      <c r="L33" s="38">
-        <v>8</v>
-      </c>
-      <c r="M33" s="38">
-        <f t="shared" ref="M33" si="23">L33*5</f>
-        <v>40</v>
-      </c>
       <c r="N33" s="38">
-        <v>50</v>
-      </c>
-      <c r="O33" s="71" t="s">
-        <v>422</v>
+        <v>12</v>
+      </c>
+      <c r="O33" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P33" s="40">
-        <v>4.5600000000000002E-2</v>
+        <v>0.1734</v>
       </c>
       <c r="Q33" s="40">
-        <f t="shared" ref="Q33" si="24">P33*N33</f>
-        <v>2.2800000000000002</v>
+        <f>P33*N33</f>
+        <v>2.0808</v>
       </c>
       <c r="R33" s="38"/>
       <c r="S33" s="38"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="48">
-        <f>ROW(B34) - ROW($B$9)</f>
+      <c r="B34" s="49">
+        <f t="shared" ref="B34" si="25">ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="72" t="s">
+      <c r="C34" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D34" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="E34" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="F34" s="37" t="s">
-        <v>421</v>
-      </c>
-      <c r="G34" s="37" t="s">
-        <v>237</v>
-      </c>
-      <c r="H34" s="37" t="s">
-        <v>289</v>
-      </c>
-      <c r="I34" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J34" s="37" t="s">
-        <v>333</v>
-      </c>
-      <c r="K34" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="L34" s="37">
-        <v>3</v>
-      </c>
-      <c r="M34" s="37">
-        <f>L34*5</f>
-        <v>15</v>
-      </c>
-      <c r="N34" s="37">
-        <v>17</v>
-      </c>
-      <c r="O34" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P34" s="39">
-        <v>0.1734</v>
-      </c>
-      <c r="Q34" s="39">
-        <f>P34*N34</f>
-        <v>2.9478</v>
-      </c>
-      <c r="R34" s="37"/>
+      <c r="D34" s="65" t="s">
+        <v>416</v>
+      </c>
+      <c r="E34" s="65" t="s">
+        <v>417</v>
+      </c>
+      <c r="F34" s="65">
+        <v>1051330011</v>
+      </c>
+      <c r="G34" s="65" t="s">
+        <v>418</v>
+      </c>
+      <c r="H34" s="65" t="s">
+        <v>419</v>
+      </c>
+      <c r="I34" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J34" s="65" t="s">
+        <v>420</v>
+      </c>
+      <c r="K34" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="L34" s="65">
+        <v>1</v>
+      </c>
+      <c r="M34" s="65">
+        <f t="shared" ref="M34" si="26">L34*5</f>
+        <v>5</v>
+      </c>
+      <c r="N34" s="65">
+        <v>6</v>
+      </c>
+      <c r="O34" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P34" s="66">
+        <v>0.41049999999999998</v>
+      </c>
+      <c r="Q34" s="66">
+        <f t="shared" ref="Q34" si="27">P34*N34</f>
+        <v>2.4630000000000001</v>
+      </c>
+      <c r="R34" s="64"/>
       <c r="S34" s="37"/>
     </row>
-    <row r="35" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="49">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="73" t="s">
+      <c r="C35" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="D35" s="38" t="s">
-        <v>53</v>
+      <c r="D35" s="77" t="s">
+        <v>48</v>
       </c>
       <c r="E35" s="38" t="s">
-        <v>123</v>
+        <v>422</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>421</v>
+        <v>393</v>
       </c>
       <c r="G35" s="38" t="s">
-        <v>188</v>
+        <v>423</v>
       </c>
       <c r="H35" s="38" t="s">
-        <v>290</v>
-      </c>
-      <c r="I35" s="38" t="s">
-        <v>409</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="I35" s="38"/>
       <c r="J35" s="38" t="s">
-        <v>334</v>
+        <v>425</v>
       </c>
       <c r="K35" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="L35" s="38">
         <v>6</v>
       </c>
       <c r="M35" s="38">
-        <f t="shared" ref="M35" si="25">L35*5</f>
+        <f t="shared" ref="M35" si="28">L35*5</f>
         <v>30</v>
       </c>
       <c r="N35" s="38">
-        <v>35</v>
-      </c>
-      <c r="O35" s="71" t="s">
-        <v>422</v>
+        <v>32</v>
+      </c>
+      <c r="O35" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P35" s="40">
-        <v>0.18360000000000001</v>
+        <v>0.55530000000000002</v>
       </c>
       <c r="Q35" s="40">
-        <f t="shared" ref="Q35" si="26">P35*N35</f>
-        <v>6.4260000000000002</v>
-      </c>
-      <c r="R35" s="38"/>
+        <f t="shared" ref="Q35" si="29">P35*N35</f>
+        <v>17.769600000000001</v>
+      </c>
+      <c r="R35" s="78" t="s">
+        <v>430</v>
+      </c>
       <c r="S35" s="38"/>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
@@ -4123,54 +4058,54 @@
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="72" t="s">
-        <v>424</v>
-      </c>
-      <c r="D36" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="E36" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="F36" s="37" t="s">
-        <v>421</v>
-      </c>
-      <c r="G36" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="H36" s="37" t="s">
-        <v>291</v>
-      </c>
-      <c r="I36" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J36" s="37" t="s">
-        <v>335</v>
-      </c>
-      <c r="K36" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="L36" s="37">
+      <c r="C36" s="62" t="s">
+        <v>396</v>
+      </c>
+      <c r="D36" s="65" t="s">
+        <v>49</v>
+      </c>
+      <c r="E36" s="65" t="s">
+        <v>114</v>
+      </c>
+      <c r="F36" s="65" t="s">
+        <v>393</v>
+      </c>
+      <c r="G36" s="65" t="s">
+        <v>221</v>
+      </c>
+      <c r="H36" s="65" t="s">
+        <v>271</v>
+      </c>
+      <c r="I36" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J36" s="65" t="s">
+        <v>311</v>
+      </c>
+      <c r="K36" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="L36" s="65">
         <v>2</v>
       </c>
-      <c r="M36" s="37">
+      <c r="M36" s="65">
         <f>L36*5</f>
         <v>10</v>
       </c>
-      <c r="N36" s="37">
+      <c r="N36" s="65">
         <v>15</v>
       </c>
-      <c r="O36" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P36" s="39">
+      <c r="O36" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P36" s="66">
         <v>8.9399999999999993E-2</v>
       </c>
-      <c r="Q36" s="39">
+      <c r="Q36" s="66">
         <f>P36*N36</f>
         <v>1.341</v>
       </c>
-      <c r="R36" s="37"/>
+      <c r="R36" s="64"/>
       <c r="S36" s="37"/>
     </row>
     <row r="37" spans="1:19" ht="48" x14ac:dyDescent="0.25">
@@ -4179,51 +4114,51 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="73" t="s">
+      <c r="C37" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="D37" s="38" t="s">
-        <v>55</v>
+      <c r="D37" s="77" t="s">
+        <v>50</v>
       </c>
       <c r="E37" s="38" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="F37" s="38" t="s">
-        <v>421</v>
+        <v>393</v>
       </c>
       <c r="G37" s="38" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="H37" s="38" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="I37" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J37" s="38" t="s">
-        <v>336</v>
+        <v>312</v>
       </c>
       <c r="K37" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="L37" s="38">
         <v>1</v>
       </c>
       <c r="M37" s="38">
-        <f t="shared" ref="M37" si="27">L37*5</f>
+        <f t="shared" ref="M37" si="30">L37*5</f>
         <v>5</v>
       </c>
       <c r="N37" s="38">
         <v>6</v>
       </c>
-      <c r="O37" s="71" t="s">
-        <v>422</v>
+      <c r="O37" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P37" s="40">
         <v>0.66820000000000002</v>
       </c>
       <c r="Q37" s="40">
-        <f t="shared" ref="Q37" si="28">P37*N37</f>
+        <f t="shared" ref="Q37" si="31">P37*N37</f>
         <v>4.0091999999999999</v>
       </c>
       <c r="R37" s="38"/>
@@ -4235,54 +4170,54 @@
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
-      <c r="C38" s="72" t="s">
+      <c r="C38" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="E38" s="37" t="s">
-        <v>126</v>
-      </c>
-      <c r="F38" s="37" t="s">
-        <v>421</v>
-      </c>
-      <c r="G38" s="37" t="s">
-        <v>190</v>
-      </c>
-      <c r="H38" s="37" t="s">
-        <v>293</v>
-      </c>
-      <c r="I38" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J38" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="K38" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="L38" s="37">
+      <c r="D38" s="65" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="65" t="s">
+        <v>116</v>
+      </c>
+      <c r="F38" s="65" t="s">
+        <v>393</v>
+      </c>
+      <c r="G38" s="65" t="s">
+        <v>175</v>
+      </c>
+      <c r="H38" s="65" t="s">
+        <v>273</v>
+      </c>
+      <c r="I38" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J38" s="65" t="s">
+        <v>313</v>
+      </c>
+      <c r="K38" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="L38" s="65">
         <v>1</v>
       </c>
-      <c r="M38" s="37">
+      <c r="M38" s="65">
         <f>L38*5</f>
         <v>5</v>
       </c>
-      <c r="N38" s="37">
+      <c r="N38" s="65">
         <v>10</v>
       </c>
-      <c r="O38" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P38" s="39">
+      <c r="O38" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P38" s="66">
         <v>9.3600000000000003E-2</v>
       </c>
-      <c r="Q38" s="39">
+      <c r="Q38" s="66">
         <f>P38*N38</f>
         <v>0.93600000000000005</v>
       </c>
-      <c r="R38" s="37"/>
+      <c r="R38" s="64"/>
       <c r="S38" s="37"/>
     </row>
     <row r="39" spans="1:19" ht="48" x14ac:dyDescent="0.25">
@@ -4291,51 +4226,51 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="73" t="s">
+      <c r="C39" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="D39" s="38" t="s">
-        <v>57</v>
+      <c r="D39" s="77" t="s">
+        <v>52</v>
       </c>
       <c r="E39" s="38" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>421</v>
+        <v>393</v>
       </c>
       <c r="G39" s="38" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="H39" s="38" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="I39" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J39" s="38" t="s">
-        <v>338</v>
+        <v>314</v>
       </c>
       <c r="K39" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="L39" s="38">
         <v>1</v>
       </c>
       <c r="M39" s="38">
-        <f t="shared" ref="M39" si="29">L39*5</f>
+        <f t="shared" ref="M39" si="32">L39*5</f>
         <v>5</v>
       </c>
       <c r="N39" s="38">
         <v>10</v>
       </c>
-      <c r="O39" s="71" t="s">
-        <v>422</v>
+      <c r="O39" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P39" s="40">
         <v>7.8100000000000003E-2</v>
       </c>
       <c r="Q39" s="40">
-        <f t="shared" ref="Q39" si="30">P39*N39</f>
+        <f t="shared" ref="Q39" si="33">P39*N39</f>
         <v>0.78100000000000003</v>
       </c>
       <c r="R39" s="38"/>
@@ -4347,54 +4282,54 @@
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="72" t="s">
+      <c r="C40" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="D40" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="E40" s="37" t="s">
-        <v>128</v>
-      </c>
-      <c r="F40" s="37" t="s">
-        <v>421</v>
-      </c>
-      <c r="G40" s="37" t="s">
-        <v>192</v>
-      </c>
-      <c r="H40" s="37" t="s">
-        <v>291</v>
-      </c>
-      <c r="I40" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J40" s="37" t="s">
-        <v>339</v>
-      </c>
-      <c r="K40" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="L40" s="37">
+      <c r="D40" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="E40" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="F40" s="65" t="s">
+        <v>393</v>
+      </c>
+      <c r="G40" s="65" t="s">
+        <v>177</v>
+      </c>
+      <c r="H40" s="65" t="s">
+        <v>271</v>
+      </c>
+      <c r="I40" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J40" s="65" t="s">
+        <v>315</v>
+      </c>
+      <c r="K40" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="L40" s="65">
         <v>1</v>
       </c>
-      <c r="M40" s="37">
+      <c r="M40" s="65">
         <f>L40*5</f>
         <v>5</v>
       </c>
-      <c r="N40" s="37">
+      <c r="N40" s="65">
         <v>6</v>
       </c>
-      <c r="O40" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P40" s="39">
+      <c r="O40" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P40" s="66">
         <v>1.4222999999999999</v>
       </c>
-      <c r="Q40" s="39">
+      <c r="Q40" s="66">
         <f>P40*N40</f>
         <v>8.5337999999999994</v>
       </c>
-      <c r="R40" s="37"/>
+      <c r="R40" s="64"/>
       <c r="S40" s="37"/>
     </row>
     <row r="41" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -4403,51 +4338,51 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="73" t="s">
+      <c r="C41" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="38" t="s">
-        <v>59</v>
+      <c r="D41" s="77" t="s">
+        <v>54</v>
       </c>
       <c r="E41" s="38" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="F41" s="38" t="s">
-        <v>421</v>
+        <v>393</v>
       </c>
       <c r="G41" s="38" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="H41" s="38" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="I41" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J41" s="38" t="s">
-        <v>340</v>
+        <v>316</v>
       </c>
       <c r="K41" s="38" t="s">
-        <v>386</v>
+        <v>360</v>
       </c>
       <c r="L41" s="38">
         <v>1</v>
       </c>
       <c r="M41" s="38">
-        <f t="shared" ref="M41" si="31">L41*5</f>
+        <f t="shared" ref="M41" si="34">L41*5</f>
         <v>5</v>
       </c>
       <c r="N41" s="38">
         <v>10</v>
       </c>
-      <c r="O41" s="71" t="s">
-        <v>422</v>
+      <c r="O41" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P41" s="40">
         <v>0.19500000000000001</v>
       </c>
       <c r="Q41" s="40">
-        <f t="shared" ref="Q41" si="32">P41*N41</f>
+        <f t="shared" ref="Q41" si="35">P41*N41</f>
         <v>1.9500000000000002</v>
       </c>
       <c r="R41" s="38"/>
@@ -4459,54 +4394,54 @@
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="72" t="s">
+      <c r="C42" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="D42" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="E42" s="37" t="s">
-        <v>130</v>
-      </c>
-      <c r="F42" s="37" t="s">
-        <v>421</v>
-      </c>
-      <c r="G42" s="37" t="s">
-        <v>194</v>
-      </c>
-      <c r="H42" s="37" t="s">
-        <v>295</v>
-      </c>
-      <c r="I42" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J42" s="37" t="s">
-        <v>341</v>
-      </c>
-      <c r="K42" s="37" t="s">
-        <v>386</v>
-      </c>
-      <c r="L42" s="37">
+      <c r="D42" s="65" t="s">
+        <v>55</v>
+      </c>
+      <c r="E42" s="65" t="s">
+        <v>120</v>
+      </c>
+      <c r="F42" s="65" t="s">
+        <v>393</v>
+      </c>
+      <c r="G42" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="H42" s="65" t="s">
+        <v>275</v>
+      </c>
+      <c r="I42" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J42" s="65" t="s">
+        <v>317</v>
+      </c>
+      <c r="K42" s="65" t="s">
+        <v>360</v>
+      </c>
+      <c r="L42" s="65">
         <v>1</v>
       </c>
-      <c r="M42" s="37">
+      <c r="M42" s="65">
         <f>L42*5</f>
         <v>5</v>
       </c>
-      <c r="N42" s="37">
+      <c r="N42" s="65">
         <v>6</v>
       </c>
-      <c r="O42" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P42" s="39">
+      <c r="O42" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P42" s="66">
         <v>0.35439999999999999</v>
       </c>
-      <c r="Q42" s="39">
+      <c r="Q42" s="66">
         <f>P42*N42</f>
         <v>2.1263999999999998</v>
       </c>
-      <c r="R42" s="37"/>
+      <c r="R42" s="64"/>
       <c r="S42" s="37"/>
     </row>
     <row r="43" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -4515,368 +4450,377 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="73" t="s">
+      <c r="C43" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="D43" s="38" t="s">
-        <v>61</v>
+      <c r="D43" s="77" t="s">
+        <v>56</v>
       </c>
       <c r="E43" s="38" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F43" s="38" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="G43" s="38" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="H43" s="38" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="I43" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J43" s="38" t="s">
-        <v>342</v>
+        <v>318</v>
       </c>
       <c r="K43" s="38" t="s">
-        <v>387</v>
+        <v>361</v>
       </c>
       <c r="L43" s="38">
         <v>1</v>
       </c>
       <c r="M43" s="38">
-        <f t="shared" ref="M43" si="33">L43*5</f>
+        <f t="shared" ref="M43" si="36">L43*5</f>
         <v>5</v>
       </c>
       <c r="N43" s="38">
         <v>10</v>
       </c>
-      <c r="O43" s="71" t="s">
-        <v>422</v>
+      <c r="O43" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P43" s="40">
         <v>6.4600000000000005E-2</v>
       </c>
       <c r="Q43" s="40">
-        <f t="shared" ref="Q43" si="34">P43*N43</f>
+        <f t="shared" ref="Q43" si="37">P43*N43</f>
         <v>0.64600000000000002</v>
       </c>
       <c r="R43" s="38"/>
       <c r="S43" s="38"/>
     </row>
-    <row r="44" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
-      <c r="B44" s="48">
-        <f>ROW(B44) - ROW($B$9)</f>
+      <c r="B44" s="49">
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="80" t="s">
+      <c r="C44" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="D44" s="81" t="s">
-        <v>62</v>
-      </c>
-      <c r="E44" s="81" t="s">
-        <v>132</v>
-      </c>
-      <c r="F44" s="81" t="s">
-        <v>196</v>
-      </c>
-      <c r="G44" s="81" t="s">
-        <v>240</v>
-      </c>
-      <c r="H44" s="81" t="s">
-        <v>296</v>
-      </c>
-      <c r="I44" s="81"/>
-      <c r="J44" s="81"/>
-      <c r="K44" s="81" t="s">
-        <v>388</v>
-      </c>
-      <c r="L44" s="81">
-        <v>2</v>
-      </c>
-      <c r="M44" s="81">
-        <f>L44*5</f>
-        <v>10</v>
-      </c>
-      <c r="N44" s="81"/>
-      <c r="O44" s="81"/>
-      <c r="P44" s="82"/>
-      <c r="Q44" s="82">
-        <f>P44*N44</f>
-        <v>0</v>
-      </c>
-      <c r="R44" s="84" t="s">
-        <v>435</v>
-      </c>
-      <c r="S44" s="81"/>
+      <c r="D44" s="65" t="s">
+        <v>405</v>
+      </c>
+      <c r="E44" s="65" t="s">
+        <v>122</v>
+      </c>
+      <c r="F44" s="65" t="s">
+        <v>181</v>
+      </c>
+      <c r="G44" s="65" t="s">
+        <v>223</v>
+      </c>
+      <c r="H44" s="65" t="s">
+        <v>276</v>
+      </c>
+      <c r="I44" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J44" s="65" t="s">
+        <v>319</v>
+      </c>
+      <c r="K44" s="65" t="s">
+        <v>362</v>
+      </c>
+      <c r="L44" s="65">
+        <v>3</v>
+      </c>
+      <c r="M44" s="65">
+        <f t="shared" ref="M44" si="38">L44*5</f>
+        <v>15</v>
+      </c>
+      <c r="N44" s="65">
+        <v>20</v>
+      </c>
+      <c r="O44" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P44" s="66">
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="Q44" s="66">
+        <f t="shared" ref="Q44" si="39">P44*N44</f>
+        <v>0.98199999999999998</v>
+      </c>
+      <c r="R44" s="64"/>
+      <c r="S44" s="37"/>
     </row>
     <row r="45" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
-      <c r="B45" s="49">
-        <f t="shared" si="0"/>
+      <c r="B45" s="48">
+        <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
       </c>
-      <c r="C45" s="73" t="s">
+      <c r="C45" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="D45" s="38" t="s">
-        <v>434</v>
+      <c r="D45" s="77" t="s">
+        <v>406</v>
       </c>
       <c r="E45" s="38" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="F45" s="38" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="G45" s="38" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="H45" s="38" t="s">
-        <v>297</v>
+        <v>276</v>
       </c>
       <c r="I45" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J45" s="38" t="s">
-        <v>343</v>
+        <v>320</v>
       </c>
       <c r="K45" s="38" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="L45" s="38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M45" s="38">
-        <f t="shared" ref="M45" si="35">L45*5</f>
-        <v>15</v>
+        <f>L45*5</f>
+        <v>20</v>
       </c>
       <c r="N45" s="38">
-        <v>20</v>
-      </c>
-      <c r="O45" s="71" t="s">
-        <v>422</v>
+        <v>40</v>
+      </c>
+      <c r="O45" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P45" s="40">
-        <v>4.9099999999999998E-2</v>
+        <v>3.2099999999999997E-2</v>
       </c>
       <c r="Q45" s="40">
-        <f t="shared" ref="Q45" si="36">P45*N45</f>
-        <v>0.98199999999999998</v>
+        <f>P45*N45</f>
+        <v>1.2839999999999998</v>
       </c>
       <c r="R45" s="38"/>
       <c r="S45" s="38"/>
     </row>
-    <row r="46" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
-      <c r="B46" s="48">
+      <c r="B46" s="49">
         <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
-      <c r="C46" s="85" t="s">
-        <v>20</v>
-      </c>
-      <c r="D46" s="83" t="s">
-        <v>63</v>
-      </c>
-      <c r="E46" s="83" t="s">
-        <v>134</v>
-      </c>
-      <c r="F46" s="83" t="s">
-        <v>196</v>
-      </c>
-      <c r="G46" s="83" t="s">
-        <v>242</v>
-      </c>
-      <c r="H46" s="83" t="s">
-        <v>297</v>
-      </c>
-      <c r="I46" s="83" t="s">
-        <v>409</v>
-      </c>
-      <c r="J46" s="83" t="s">
-        <v>344</v>
-      </c>
-      <c r="K46" s="83" t="s">
-        <v>390</v>
-      </c>
-      <c r="L46" s="83">
+      <c r="C46" s="62" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" s="65" t="s">
+        <v>57</v>
+      </c>
+      <c r="E46" s="65" t="s">
+        <v>123</v>
+      </c>
+      <c r="F46" s="65" t="s">
+        <v>182</v>
+      </c>
+      <c r="G46" s="65" t="s">
+        <v>224</v>
+      </c>
+      <c r="H46" s="65" t="s">
+        <v>277</v>
+      </c>
+      <c r="I46" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J46" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="K46" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="L46" s="65">
         <v>1</v>
       </c>
-      <c r="M46" s="83">
-        <f>L46*5</f>
+      <c r="M46" s="65">
+        <f t="shared" ref="M46" si="40">L46*5</f>
         <v>5</v>
       </c>
-      <c r="N46" s="83">
-        <v>10</v>
-      </c>
-      <c r="O46" s="86"/>
-      <c r="P46" s="87"/>
-      <c r="Q46" s="87">
-        <f>P46*N46</f>
-        <v>0</v>
-      </c>
-      <c r="R46" s="84" t="s">
-        <v>435</v>
-      </c>
-      <c r="S46" s="83"/>
-    </row>
-    <row r="47" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="N46" s="65">
+        <v>6</v>
+      </c>
+      <c r="O46" s="59" t="s">
+        <v>277</v>
+      </c>
+      <c r="P46" s="66">
+        <v>16.59</v>
+      </c>
+      <c r="Q46" s="66">
+        <f t="shared" ref="Q46" si="41">P46*N46</f>
+        <v>99.539999999999992</v>
+      </c>
+      <c r="R46" s="64"/>
+      <c r="S46" s="37"/>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="49">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="73" t="s">
+      <c r="C47" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="D47" s="38" t="s">
-        <v>64</v>
+      <c r="D47" s="77" t="s">
+        <v>58</v>
       </c>
       <c r="E47" s="38" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>198</v>
+        <v>381</v>
       </c>
       <c r="G47" s="38" t="s">
-        <v>243</v>
+        <v>183</v>
       </c>
       <c r="H47" s="38" t="s">
-        <v>298</v>
-      </c>
-      <c r="I47" s="38" t="s">
-        <v>409</v>
-      </c>
-      <c r="J47" s="38" t="s">
-        <v>409</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="I47" s="38"/>
+      <c r="J47" s="38"/>
       <c r="K47" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="L47" s="38">
         <v>1</v>
       </c>
       <c r="M47" s="38">
-        <f t="shared" ref="M47" si="37">L47*5</f>
+        <f t="shared" ref="M47" si="42">L47*5</f>
         <v>5</v>
       </c>
-      <c r="N47" s="38">
-        <v>6</v>
-      </c>
-      <c r="O47" s="71" t="s">
-        <v>298</v>
-      </c>
-      <c r="P47" s="40">
-        <v>16.59</v>
-      </c>
+      <c r="N47" s="38"/>
+      <c r="O47" s="61"/>
+      <c r="P47" s="40"/>
       <c r="Q47" s="40">
-        <f t="shared" ref="Q47" si="38">P47*N47</f>
-        <v>99.539999999999992</v>
+        <f t="shared" ref="Q47" si="43">P47*N47</f>
+        <v>0</v>
       </c>
       <c r="R47" s="38"/>
       <c r="S47" s="38"/>
     </row>
-    <row r="48" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="48">
         <f>ROW(B48) - ROW($B$9)</f>
         <v>39</v>
       </c>
-      <c r="C48" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="D48" s="37" t="s">
-        <v>436</v>
-      </c>
-      <c r="E48" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="F48" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="G48" s="37" t="s">
-        <v>244</v>
-      </c>
-      <c r="H48" s="37" t="s">
-        <v>297</v>
-      </c>
-      <c r="I48" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J48" s="37" t="s">
-        <v>345</v>
-      </c>
-      <c r="K48" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="L48" s="37">
-        <v>4</v>
-      </c>
-      <c r="M48" s="37">
+      <c r="C48" s="62" t="s">
+        <v>363</v>
+      </c>
+      <c r="D48" s="65" t="s">
+        <v>59</v>
+      </c>
+      <c r="E48" s="65" t="s">
+        <v>126</v>
+      </c>
+      <c r="F48" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="G48" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="H48" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="I48" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J48" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="K48" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="L48" s="65">
+        <v>6</v>
+      </c>
+      <c r="M48" s="65">
         <f>L48*5</f>
-        <v>20</v>
-      </c>
-      <c r="N48" s="37">
-        <v>40</v>
-      </c>
-      <c r="O48" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P48" s="39">
-        <v>3.2099999999999997E-2</v>
-      </c>
-      <c r="Q48" s="39">
-        <f>P48*N48</f>
-        <v>1.2839999999999998</v>
-      </c>
-      <c r="R48" s="37"/>
+        <v>30</v>
+      </c>
+      <c r="N48" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="O48" s="59" t="s">
+        <v>381</v>
+      </c>
+      <c r="P48" s="66" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q48" s="66" t="s">
+        <v>381</v>
+      </c>
+      <c r="R48" s="64"/>
       <c r="S48" s="37"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="49">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="73" t="s">
-        <v>21</v>
-      </c>
-      <c r="D49" s="38" t="s">
-        <v>65</v>
+      <c r="C49" s="63" t="s">
+        <v>22</v>
+      </c>
+      <c r="D49" s="77" t="s">
+        <v>60</v>
       </c>
       <c r="E49" s="38" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>409</v>
+        <v>185</v>
       </c>
       <c r="G49" s="38" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="H49" s="38" t="s">
-        <v>299</v>
-      </c>
-      <c r="I49" s="38"/>
-      <c r="J49" s="38"/>
+        <v>279</v>
+      </c>
+      <c r="I49" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J49" s="38" t="s">
+        <v>321</v>
+      </c>
       <c r="K49" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="L49" s="38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M49" s="38">
-        <f t="shared" ref="M49" si="39">L49*5</f>
-        <v>5</v>
-      </c>
-      <c r="N49" s="38"/>
-      <c r="O49" s="38"/>
-      <c r="P49" s="40"/>
+        <f t="shared" ref="M49" si="44">L49*5</f>
+        <v>20</v>
+      </c>
+      <c r="N49" s="38">
+        <v>40</v>
+      </c>
+      <c r="O49" s="61" t="s">
+        <v>394</v>
+      </c>
+      <c r="P49" s="40">
+        <v>3.2899999999999999E-2</v>
+      </c>
       <c r="Q49" s="40">
-        <f t="shared" ref="Q49" si="40">P49*N49</f>
-        <v>0</v>
+        <f t="shared" ref="Q49" si="45">P49*N49</f>
+        <v>1.3159999999999998</v>
       </c>
       <c r="R49" s="38"/>
       <c r="S49" s="38"/>
@@ -4887,165 +4831,166 @@
         <f>ROW(B50) - ROW($B$9)</f>
         <v>41</v>
       </c>
-      <c r="C50" s="74" t="s">
-        <v>391</v>
-      </c>
-      <c r="D50" s="75" t="s">
-        <v>66</v>
-      </c>
-      <c r="E50" s="75" t="s">
-        <v>138</v>
-      </c>
-      <c r="F50" s="75" t="s">
-        <v>200</v>
-      </c>
-      <c r="G50" s="75" t="s">
-        <v>409</v>
-      </c>
-      <c r="H50" s="75" t="s">
-        <v>409</v>
-      </c>
-      <c r="I50" s="75" t="s">
-        <v>409</v>
-      </c>
-      <c r="J50" s="75" t="s">
-        <v>409</v>
-      </c>
-      <c r="K50" s="75" t="s">
-        <v>409</v>
-      </c>
-      <c r="L50" s="75">
-        <v>6</v>
-      </c>
-      <c r="M50" s="75">
+      <c r="C50" s="62" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" s="65" t="s">
+        <v>61</v>
+      </c>
+      <c r="E50" s="65" t="s">
+        <v>128</v>
+      </c>
+      <c r="F50" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="G50" s="65" t="s">
+        <v>227</v>
+      </c>
+      <c r="H50" s="65" t="s">
+        <v>256</v>
+      </c>
+      <c r="I50" s="65" t="s">
+        <v>400</v>
+      </c>
+      <c r="J50" s="65" t="s">
+        <v>322</v>
+      </c>
+      <c r="K50" s="65" t="s">
+        <v>364</v>
+      </c>
+      <c r="L50" s="65">
+        <v>1</v>
+      </c>
+      <c r="M50" s="65">
         <f>L50*5</f>
-        <v>30</v>
-      </c>
-      <c r="N50" s="75" t="s">
-        <v>409</v>
-      </c>
-      <c r="O50" s="75" t="s">
-        <v>409</v>
-      </c>
-      <c r="P50" s="76" t="s">
-        <v>409</v>
-      </c>
-      <c r="Q50" s="76" t="s">
-        <v>409</v>
-      </c>
-      <c r="R50" s="75"/>
-      <c r="S50" s="75"/>
-    </row>
-    <row r="51" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="N50" s="65">
+        <v>20</v>
+      </c>
+      <c r="O50" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P50" s="66">
+        <v>2.7699999999999999E-2</v>
+      </c>
+      <c r="Q50" s="66">
+        <f>P50*N50</f>
+        <v>0.55399999999999994</v>
+      </c>
+      <c r="R50" s="64"/>
+      <c r="S50" s="37"/>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="49">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C51" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="D51" s="38" t="s">
-        <v>67</v>
+      <c r="C51" s="63" t="s">
+        <v>23</v>
+      </c>
+      <c r="D51" s="77" t="s">
+        <v>62</v>
       </c>
       <c r="E51" s="38" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="F51" s="38" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="G51" s="38" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="H51" s="38" t="s">
-        <v>300</v>
+        <v>256</v>
       </c>
       <c r="I51" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J51" s="38" t="s">
-        <v>346</v>
+        <v>323</v>
       </c>
       <c r="K51" s="38" t="s">
-        <v>409</v>
+        <v>383</v>
       </c>
       <c r="L51" s="38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M51" s="38">
-        <f t="shared" ref="M51" si="41">L51*5</f>
+        <f t="shared" ref="M51" si="46">L51*5</f>
+        <v>5</v>
+      </c>
+      <c r="N51" s="38">
         <v>20</v>
       </c>
-      <c r="N51" s="38">
-        <v>40</v>
-      </c>
-      <c r="O51" s="71" t="s">
-        <v>422</v>
+      <c r="O51" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P51" s="40">
-        <v>3.2899999999999999E-2</v>
+        <v>2.18E-2</v>
       </c>
       <c r="Q51" s="40">
-        <f t="shared" ref="Q51" si="42">P51*N51</f>
-        <v>1.3159999999999998</v>
+        <f t="shared" ref="Q51" si="47">P51*N51</f>
+        <v>0.436</v>
       </c>
       <c r="R51" s="38"/>
       <c r="S51" s="38"/>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="48">
         <f>ROW(B52) - ROW($B$9)</f>
         <v>43</v>
       </c>
-      <c r="C52" s="72" t="s">
+      <c r="C52" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="D52" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="E52" s="37" t="s">
-        <v>140</v>
-      </c>
-      <c r="F52" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="G52" s="37" t="s">
-        <v>246</v>
-      </c>
-      <c r="H52" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="I52" s="37" t="s">
-        <v>428</v>
-      </c>
-      <c r="J52" s="37" t="s">
-        <v>347</v>
-      </c>
-      <c r="K52" s="37" t="s">
-        <v>392</v>
-      </c>
-      <c r="L52" s="37">
-        <v>1</v>
-      </c>
-      <c r="M52" s="37">
+      <c r="D52" s="65" t="s">
+        <v>63</v>
+      </c>
+      <c r="E52" s="65" t="s">
+        <v>130</v>
+      </c>
+      <c r="F52" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="G52" s="65" t="s">
+        <v>229</v>
+      </c>
+      <c r="H52" s="65" t="s">
+        <v>256</v>
+      </c>
+      <c r="I52" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J52" s="65" t="s">
+        <v>324</v>
+      </c>
+      <c r="K52" s="65" t="s">
+        <v>365</v>
+      </c>
+      <c r="L52" s="65">
+        <v>13</v>
+      </c>
+      <c r="M52" s="65">
         <f>L52*5</f>
-        <v>5</v>
-      </c>
-      <c r="N52" s="37">
-        <v>20</v>
-      </c>
-      <c r="O52" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P52" s="39">
-        <v>2.7699999999999999E-2</v>
-      </c>
-      <c r="Q52" s="39">
+        <v>65</v>
+      </c>
+      <c r="N52" s="65">
+        <v>100</v>
+      </c>
+      <c r="O52" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P52" s="66">
+        <v>1E-3</v>
+      </c>
+      <c r="Q52" s="66">
         <f>P52*N52</f>
-        <v>0.55399999999999994</v>
-      </c>
-      <c r="R52" s="37"/>
+        <v>0.1</v>
+      </c>
+      <c r="R52" s="64"/>
       <c r="S52" s="37"/>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
@@ -5054,110 +4999,110 @@
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C53" s="73" t="s">
+      <c r="C53" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D53" s="38" t="s">
-        <v>69</v>
+      <c r="D53" s="77" t="s">
+        <v>64</v>
       </c>
       <c r="E53" s="38" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F53" s="38" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="G53" s="38" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="H53" s="38" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="I53" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J53" s="38" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="K53" s="38" t="s">
-        <v>411</v>
+        <v>366</v>
       </c>
       <c r="L53" s="38">
         <v>1</v>
       </c>
       <c r="M53" s="38">
-        <f t="shared" ref="M53" si="43">L53*5</f>
+        <f t="shared" ref="M53" si="48">L53*5</f>
         <v>5</v>
       </c>
       <c r="N53" s="38">
         <v>20</v>
       </c>
-      <c r="O53" s="71" t="s">
-        <v>422</v>
+      <c r="O53" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P53" s="40">
-        <v>2.18E-2</v>
+        <v>2.81E-2</v>
       </c>
       <c r="Q53" s="40">
-        <f t="shared" ref="Q53" si="44">P53*N53</f>
-        <v>0.436</v>
+        <f t="shared" ref="Q53" si="49">P53*N53</f>
+        <v>0.56200000000000006</v>
       </c>
       <c r="R53" s="38"/>
       <c r="S53" s="38"/>
     </row>
-    <row r="54" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="48">
         <f>ROW(B54) - ROW($B$9)</f>
         <v>45</v>
       </c>
-      <c r="C54" s="72" t="s">
+      <c r="C54" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="D54" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="E54" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="F54" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="G54" s="37" t="s">
-        <v>248</v>
-      </c>
-      <c r="H54" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="I54" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J54" s="37" t="s">
-        <v>349</v>
-      </c>
-      <c r="K54" s="37" t="s">
-        <v>393</v>
-      </c>
-      <c r="L54" s="37">
-        <v>13</v>
-      </c>
-      <c r="M54" s="37">
+      <c r="D54" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="E54" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="F54" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="G54" s="65" t="s">
+        <v>231</v>
+      </c>
+      <c r="H54" s="65" t="s">
+        <v>256</v>
+      </c>
+      <c r="I54" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J54" s="65" t="s">
+        <v>326</v>
+      </c>
+      <c r="K54" s="65" t="s">
+        <v>367</v>
+      </c>
+      <c r="L54" s="65">
+        <v>1</v>
+      </c>
+      <c r="M54" s="65">
         <f>L54*5</f>
-        <v>65</v>
-      </c>
-      <c r="N54" s="37">
-        <v>100</v>
-      </c>
-      <c r="O54" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P54" s="39">
-        <v>1E-3</v>
-      </c>
-      <c r="Q54" s="39">
+        <v>5</v>
+      </c>
+      <c r="N54" s="65">
+        <v>20</v>
+      </c>
+      <c r="O54" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P54" s="66">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="Q54" s="66">
         <f>P54*N54</f>
-        <v>0.1</v>
-      </c>
-      <c r="R54" s="37"/>
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="R54" s="64"/>
       <c r="S54" s="37"/>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
@@ -5166,52 +5111,52 @@
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C55" s="73" t="s">
+      <c r="C55" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D55" s="38" t="s">
-        <v>71</v>
+      <c r="D55" s="77" t="s">
+        <v>66</v>
       </c>
       <c r="E55" s="38" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="F55" s="38" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="G55" s="38" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="H55" s="38" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="I55" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J55" s="38" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="K55" s="38" t="s">
+        <v>368</v>
+      </c>
+      <c r="L55" s="38">
+        <v>2</v>
+      </c>
+      <c r="M55" s="38">
+        <f t="shared" ref="M55" si="50">L55*5</f>
+        <v>10</v>
+      </c>
+      <c r="N55" s="38">
+        <v>100</v>
+      </c>
+      <c r="O55" s="61" t="s">
         <v>394</v>
       </c>
-      <c r="L55" s="38">
-        <v>1</v>
-      </c>
-      <c r="M55" s="38">
-        <f t="shared" ref="M55" si="45">L55*5</f>
-        <v>5</v>
-      </c>
-      <c r="N55" s="38">
-        <v>20</v>
-      </c>
-      <c r="O55" s="71" t="s">
-        <v>422</v>
-      </c>
       <c r="P55" s="40">
-        <v>2.81E-2</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q55" s="40">
-        <f t="shared" ref="Q55" si="46">P55*N55</f>
-        <v>0.56200000000000006</v>
+        <f t="shared" ref="Q55" si="51">P55*N55</f>
+        <v>0.12</v>
       </c>
       <c r="R55" s="38"/>
       <c r="S55" s="38"/>
@@ -5222,54 +5167,54 @@
         <f>ROW(B56) - ROW($B$9)</f>
         <v>47</v>
       </c>
-      <c r="C56" s="72" t="s">
+      <c r="C56" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="D56" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="E56" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="F56" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="G56" s="37" t="s">
-        <v>250</v>
-      </c>
-      <c r="H56" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="I56" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J56" s="37" t="s">
-        <v>351</v>
-      </c>
-      <c r="K56" s="37" t="s">
-        <v>395</v>
-      </c>
-      <c r="L56" s="37">
-        <v>1</v>
-      </c>
-      <c r="M56" s="37">
+      <c r="D56" s="65" t="s">
+        <v>67</v>
+      </c>
+      <c r="E56" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="F56" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="G56" s="65" t="s">
+        <v>233</v>
+      </c>
+      <c r="H56" s="65" t="s">
+        <v>256</v>
+      </c>
+      <c r="I56" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J56" s="65" t="s">
+        <v>328</v>
+      </c>
+      <c r="K56" s="65" t="s">
+        <v>369</v>
+      </c>
+      <c r="L56" s="65">
+        <v>3</v>
+      </c>
+      <c r="M56" s="65">
         <f>L56*5</f>
-        <v>5</v>
-      </c>
-      <c r="N56" s="37">
-        <v>20</v>
-      </c>
-      <c r="O56" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P56" s="39">
-        <v>3.2300000000000002E-2</v>
-      </c>
-      <c r="Q56" s="39">
+        <v>15</v>
+      </c>
+      <c r="N56" s="65">
+        <v>100</v>
+      </c>
+      <c r="O56" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P56" s="66">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q56" s="66">
         <f>P56*N56</f>
-        <v>0.64600000000000002</v>
-      </c>
-      <c r="R56" s="37"/>
+        <v>0.13</v>
+      </c>
+      <c r="R56" s="64"/>
       <c r="S56" s="37"/>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
@@ -5278,52 +5223,52 @@
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C57" s="73" t="s">
+      <c r="C57" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D57" s="38" t="s">
-        <v>73</v>
+      <c r="D57" s="77" t="s">
+        <v>68</v>
       </c>
       <c r="E57" s="38" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="F57" s="38" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="G57" s="38" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="H57" s="38" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="I57" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J57" s="38" t="s">
-        <v>352</v>
+        <v>329</v>
       </c>
       <c r="K57" s="38" t="s">
-        <v>396</v>
+        <v>370</v>
       </c>
       <c r="L57" s="38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M57" s="38">
-        <f t="shared" ref="M57" si="47">L57*5</f>
-        <v>10</v>
+        <f t="shared" ref="M57" si="52">L57*5</f>
+        <v>20</v>
       </c>
       <c r="N57" s="38">
-        <v>100</v>
-      </c>
-      <c r="O57" s="71" t="s">
-        <v>422</v>
+        <v>50</v>
+      </c>
+      <c r="O57" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P57" s="40">
-        <v>1.1999999999999999E-3</v>
+        <v>9.2999999999999992E-3</v>
       </c>
       <c r="Q57" s="40">
-        <f t="shared" ref="Q57" si="48">P57*N57</f>
-        <v>0.12</v>
+        <f t="shared" ref="Q57" si="53">P57*N57</f>
+        <v>0.46499999999999997</v>
       </c>
       <c r="R57" s="38"/>
       <c r="S57" s="38"/>
@@ -5334,54 +5279,54 @@
         <f>ROW(B58) - ROW($B$9)</f>
         <v>49</v>
       </c>
-      <c r="C58" s="72" t="s">
+      <c r="C58" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="D58" s="37" t="s">
-        <v>74</v>
-      </c>
-      <c r="E58" s="37" t="s">
-        <v>146</v>
-      </c>
-      <c r="F58" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="G58" s="37" t="s">
-        <v>252</v>
-      </c>
-      <c r="H58" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="I58" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J58" s="37" t="s">
-        <v>353</v>
-      </c>
-      <c r="K58" s="37" t="s">
-        <v>397</v>
-      </c>
-      <c r="L58" s="37">
-        <v>3</v>
-      </c>
-      <c r="M58" s="37">
+      <c r="D58" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="E58" s="65" t="s">
+        <v>136</v>
+      </c>
+      <c r="F58" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="G58" s="65" t="s">
+        <v>235</v>
+      </c>
+      <c r="H58" s="65" t="s">
+        <v>256</v>
+      </c>
+      <c r="I58" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J58" s="65" t="s">
+        <v>330</v>
+      </c>
+      <c r="K58" s="65" t="s">
+        <v>371</v>
+      </c>
+      <c r="L58" s="65">
+        <v>1</v>
+      </c>
+      <c r="M58" s="65">
         <f>L58*5</f>
-        <v>15</v>
-      </c>
-      <c r="N58" s="37">
+        <v>5</v>
+      </c>
+      <c r="N58" s="65">
         <v>100</v>
       </c>
-      <c r="O58" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P58" s="39">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q58" s="39">
+      <c r="O58" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P58" s="66">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="Q58" s="66">
         <f>P58*N58</f>
-        <v>0.13</v>
-      </c>
-      <c r="R58" s="37"/>
+        <v>0.3</v>
+      </c>
+      <c r="R58" s="64"/>
       <c r="S58" s="37"/>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
@@ -5390,52 +5335,52 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C59" s="73" t="s">
+      <c r="C59" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D59" s="38" t="s">
-        <v>75</v>
+      <c r="D59" s="77" t="s">
+        <v>70</v>
       </c>
       <c r="E59" s="38" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="F59" s="38" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="G59" s="38" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="H59" s="38" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="I59" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J59" s="38" t="s">
-        <v>354</v>
+        <v>331</v>
       </c>
       <c r="K59" s="38" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
       <c r="L59" s="38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M59" s="38">
-        <f t="shared" ref="M59" si="49">L59*5</f>
-        <v>20</v>
+        <f t="shared" ref="M59" si="54">L59*5</f>
+        <v>15</v>
       </c>
       <c r="N59" s="38">
-        <v>50</v>
-      </c>
-      <c r="O59" s="71" t="s">
-        <v>422</v>
+        <v>100</v>
+      </c>
+      <c r="O59" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P59" s="40">
-        <v>9.2999999999999992E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q59" s="40">
-        <f t="shared" ref="Q59" si="50">P59*N59</f>
-        <v>0.46499999999999997</v>
+        <f t="shared" ref="Q59" si="55">P59*N59</f>
+        <v>0.12</v>
       </c>
       <c r="R59" s="38"/>
       <c r="S59" s="38"/>
@@ -5446,54 +5391,54 @@
         <f>ROW(B60) - ROW($B$9)</f>
         <v>51</v>
       </c>
-      <c r="C60" s="72" t="s">
+      <c r="C60" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="D60" s="37" t="s">
-        <v>76</v>
-      </c>
-      <c r="E60" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="F60" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="G60" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="H60" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="I60" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J60" s="37" t="s">
-        <v>355</v>
-      </c>
-      <c r="K60" s="37" t="s">
-        <v>399</v>
-      </c>
-      <c r="L60" s="37">
-        <v>1</v>
-      </c>
-      <c r="M60" s="37">
+      <c r="D60" s="65" t="s">
+        <v>71</v>
+      </c>
+      <c r="E60" s="65" t="s">
+        <v>138</v>
+      </c>
+      <c r="F60" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="G60" s="65" t="s">
+        <v>237</v>
+      </c>
+      <c r="H60" s="65" t="s">
+        <v>256</v>
+      </c>
+      <c r="I60" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J60" s="65" t="s">
+        <v>332</v>
+      </c>
+      <c r="K60" s="65" t="s">
+        <v>373</v>
+      </c>
+      <c r="L60" s="65">
+        <v>6</v>
+      </c>
+      <c r="M60" s="65">
         <f>L60*5</f>
-        <v>5</v>
-      </c>
-      <c r="N60" s="37">
+        <v>30</v>
+      </c>
+      <c r="N60" s="65">
         <v>100</v>
       </c>
-      <c r="O60" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P60" s="39">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="Q60" s="39">
+      <c r="O60" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P60" s="66">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q60" s="66">
         <f>P60*N60</f>
-        <v>0.3</v>
-      </c>
-      <c r="R60" s="37"/>
+        <v>0.11</v>
+      </c>
+      <c r="R60" s="64"/>
       <c r="S60" s="37"/>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
@@ -5502,52 +5447,52 @@
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C61" s="73" t="s">
+      <c r="C61" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D61" s="38" t="s">
-        <v>77</v>
+      <c r="D61" s="77" t="s">
+        <v>72</v>
       </c>
       <c r="E61" s="38" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="F61" s="38" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="G61" s="38" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="H61" s="38" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="I61" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J61" s="38" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="K61" s="38" t="s">
-        <v>400</v>
+        <v>374</v>
       </c>
       <c r="L61" s="38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M61" s="38">
-        <f t="shared" ref="M61" si="51">L61*5</f>
-        <v>15</v>
+        <f t="shared" ref="M61" si="56">L61*5</f>
+        <v>20</v>
       </c>
       <c r="N61" s="38">
         <v>100</v>
       </c>
-      <c r="O61" s="71" t="s">
-        <v>422</v>
+      <c r="O61" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P61" s="40">
-        <v>1.1999999999999999E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="Q61" s="40">
-        <f t="shared" ref="Q61" si="52">P61*N61</f>
-        <v>0.12</v>
+        <f t="shared" ref="Q61" si="57">P61*N61</f>
+        <v>0.1</v>
       </c>
       <c r="R61" s="38"/>
       <c r="S61" s="38"/>
@@ -5558,54 +5503,54 @@
         <f>ROW(B62) - ROW($B$9)</f>
         <v>53</v>
       </c>
-      <c r="C62" s="72" t="s">
+      <c r="C62" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="D62" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="E62" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="F62" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="G62" s="37" t="s">
+      <c r="D62" s="65" t="s">
+        <v>73</v>
+      </c>
+      <c r="E62" s="65" t="s">
+        <v>140</v>
+      </c>
+      <c r="F62" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="G62" s="65" t="s">
+        <v>239</v>
+      </c>
+      <c r="H62" s="65" t="s">
         <v>256</v>
       </c>
-      <c r="H62" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="I62" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J62" s="37" t="s">
-        <v>357</v>
-      </c>
-      <c r="K62" s="37" t="s">
-        <v>401</v>
-      </c>
-      <c r="L62" s="37">
-        <v>6</v>
-      </c>
-      <c r="M62" s="37">
+      <c r="I62" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J62" s="65" t="s">
+        <v>334</v>
+      </c>
+      <c r="K62" s="65" t="s">
+        <v>375</v>
+      </c>
+      <c r="L62" s="65">
+        <v>1</v>
+      </c>
+      <c r="M62" s="65">
         <f>L62*5</f>
-        <v>30</v>
-      </c>
-      <c r="N62" s="37">
+        <v>5</v>
+      </c>
+      <c r="N62" s="65">
         <v>100</v>
       </c>
-      <c r="O62" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P62" s="39">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="Q62" s="39">
+      <c r="O62" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P62" s="66">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q62" s="66">
         <f>P62*N62</f>
-        <v>0.11</v>
-      </c>
-      <c r="R62" s="37"/>
+        <v>0.13</v>
+      </c>
+      <c r="R62" s="64"/>
       <c r="S62" s="37"/>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.25">
@@ -5614,52 +5559,52 @@
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C63" s="73" t="s">
+      <c r="C63" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D63" s="38" t="s">
-        <v>79</v>
+      <c r="D63" s="77" t="s">
+        <v>74</v>
       </c>
       <c r="E63" s="38" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="F63" s="38" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="G63" s="38" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="H63" s="38" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="I63" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J63" s="38" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="K63" s="38" t="s">
-        <v>402</v>
+        <v>376</v>
       </c>
       <c r="L63" s="38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M63" s="38">
-        <f t="shared" ref="M63" si="53">L63*5</f>
-        <v>20</v>
+        <f t="shared" ref="M63" si="58">L63*5</f>
+        <v>15</v>
       </c>
       <c r="N63" s="38">
         <v>100</v>
       </c>
-      <c r="O63" s="71" t="s">
-        <v>422</v>
+      <c r="O63" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P63" s="40">
-        <v>1E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q63" s="40">
-        <f t="shared" ref="Q63" si="54">P63*N63</f>
-        <v>0.1</v>
+        <f t="shared" ref="Q63" si="59">P63*N63</f>
+        <v>0.13</v>
       </c>
       <c r="R63" s="38"/>
       <c r="S63" s="38"/>
@@ -5670,54 +5615,54 @@
         <f>ROW(B64) - ROW($B$9)</f>
         <v>55</v>
       </c>
-      <c r="C64" s="72" t="s">
+      <c r="C64" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="D64" s="37" t="s">
-        <v>80</v>
-      </c>
-      <c r="E64" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="F64" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="G64" s="37" t="s">
-        <v>258</v>
-      </c>
-      <c r="H64" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="I64" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J64" s="37" t="s">
-        <v>359</v>
-      </c>
-      <c r="K64" s="37" t="s">
-        <v>403</v>
-      </c>
-      <c r="L64" s="37">
+      <c r="D64" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="E64" s="65" t="s">
+        <v>142</v>
+      </c>
+      <c r="F64" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="G64" s="65" t="s">
+        <v>241</v>
+      </c>
+      <c r="H64" s="65" t="s">
+        <v>256</v>
+      </c>
+      <c r="I64" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J64" s="65" t="s">
+        <v>336</v>
+      </c>
+      <c r="K64" s="65" t="s">
+        <v>377</v>
+      </c>
+      <c r="L64" s="65">
         <v>1</v>
       </c>
-      <c r="M64" s="37">
+      <c r="M64" s="65">
         <f>L64*5</f>
         <v>5</v>
       </c>
-      <c r="N64" s="37">
+      <c r="N64" s="65">
         <v>100</v>
       </c>
-      <c r="O64" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P64" s="39">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q64" s="39">
+      <c r="O64" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P64" s="66">
+        <v>1.8E-3</v>
+      </c>
+      <c r="Q64" s="66">
         <f>P64*N64</f>
-        <v>0.13</v>
-      </c>
-      <c r="R64" s="37"/>
+        <v>0.18</v>
+      </c>
+      <c r="R64" s="64"/>
       <c r="S64" s="37"/>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.25">
@@ -5726,51 +5671,51 @@
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="C65" s="73" t="s">
+      <c r="C65" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D65" s="38" t="s">
-        <v>81</v>
+      <c r="D65" s="77" t="s">
+        <v>76</v>
       </c>
       <c r="E65" s="38" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="F65" s="38" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="G65" s="38" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="H65" s="38" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="I65" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J65" s="38" t="s">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="K65" s="38" t="s">
-        <v>404</v>
+        <v>378</v>
       </c>
       <c r="L65" s="38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M65" s="38">
-        <f t="shared" ref="M65" si="55">L65*5</f>
-        <v>15</v>
+        <f t="shared" ref="M65" si="60">L65*5</f>
+        <v>5</v>
       </c>
       <c r="N65" s="38">
         <v>100</v>
       </c>
-      <c r="O65" s="71" t="s">
-        <v>422</v>
+      <c r="O65" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P65" s="40">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q65" s="40">
-        <f t="shared" ref="Q65" si="56">P65*N65</f>
+        <f t="shared" ref="Q65" si="61">P65*N65</f>
         <v>0.13</v>
       </c>
       <c r="R65" s="38"/>
@@ -5782,54 +5727,54 @@
         <f>ROW(B66) - ROW($B$9)</f>
         <v>57</v>
       </c>
-      <c r="C66" s="72" t="s">
+      <c r="C66" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="D66" s="37" t="s">
-        <v>82</v>
-      </c>
-      <c r="E66" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="F66" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="G66" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="H66" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="I66" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J66" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="K66" s="37" t="s">
-        <v>405</v>
-      </c>
-      <c r="L66" s="37">
+      <c r="D66" s="65" t="s">
+        <v>77</v>
+      </c>
+      <c r="E66" s="65" t="s">
+        <v>144</v>
+      </c>
+      <c r="F66" s="65" t="s">
+        <v>187</v>
+      </c>
+      <c r="G66" s="65" t="s">
+        <v>243</v>
+      </c>
+      <c r="H66" s="65" t="s">
+        <v>256</v>
+      </c>
+      <c r="I66" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J66" s="65" t="s">
+        <v>401</v>
+      </c>
+      <c r="K66" s="65" t="s">
+        <v>372</v>
+      </c>
+      <c r="L66" s="65">
         <v>1</v>
       </c>
-      <c r="M66" s="37">
+      <c r="M66" s="65">
         <f>L66*5</f>
         <v>5</v>
       </c>
-      <c r="N66" s="37">
+      <c r="N66" s="65">
         <v>100</v>
       </c>
-      <c r="O66" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P66" s="39">
-        <v>1.8E-3</v>
-      </c>
-      <c r="Q66" s="39">
+      <c r="O66" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P66" s="66">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q66" s="66">
         <f>P66*N66</f>
-        <v>0.18</v>
-      </c>
-      <c r="R66" s="37"/>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="R66" s="64"/>
       <c r="S66" s="37"/>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.25">
@@ -5838,52 +5783,52 @@
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="C67" s="73" t="s">
+      <c r="C67" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D67" s="38" t="s">
-        <v>83</v>
+      <c r="D67" s="77" t="s">
+        <v>78</v>
       </c>
       <c r="E67" s="38" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="F67" s="38" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="G67" s="38" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="H67" s="38" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="I67" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J67" s="38" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="K67" s="38" t="s">
-        <v>406</v>
+        <v>379</v>
       </c>
       <c r="L67" s="38">
         <v>1</v>
       </c>
       <c r="M67" s="38">
-        <f t="shared" ref="M67" si="57">L67*5</f>
+        <f t="shared" ref="M67" si="62">L67*5</f>
         <v>5</v>
       </c>
       <c r="N67" s="38">
         <v>100</v>
       </c>
-      <c r="O67" s="71" t="s">
-        <v>422</v>
+      <c r="O67" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P67" s="40">
-        <v>1.2999999999999999E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q67" s="40">
-        <f t="shared" ref="Q67" si="58">P67*N67</f>
-        <v>0.13</v>
+        <f t="shared" ref="Q67" si="63">P67*N67</f>
+        <v>0.05</v>
       </c>
       <c r="R67" s="38"/>
       <c r="S67" s="38"/>
@@ -5894,54 +5839,53 @@
         <f>ROW(B68) - ROW($B$9)</f>
         <v>59</v>
       </c>
-      <c r="C68" s="72" t="s">
-        <v>23</v>
-      </c>
-      <c r="D68" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="E68" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="F68" s="37" t="s">
-        <v>203</v>
-      </c>
-      <c r="G68" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="H68" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="I68" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J68" s="37" t="s">
-        <v>429</v>
-      </c>
-      <c r="K68" s="37" t="s">
-        <v>400</v>
-      </c>
-      <c r="L68" s="37">
-        <v>1</v>
-      </c>
-      <c r="M68" s="37">
+      <c r="C68" s="62" t="s">
+        <v>397</v>
+      </c>
+      <c r="D68" s="65" t="s">
+        <v>79</v>
+      </c>
+      <c r="E68" s="65" t="s">
+        <v>146</v>
+      </c>
+      <c r="F68" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="G68" s="65" t="s">
+        <v>188</v>
+      </c>
+      <c r="H68" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="I68" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J68" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="K68" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="L68" s="65">
+        <v>2</v>
+      </c>
+      <c r="M68" s="65">
         <f>L68*5</f>
-        <v>5</v>
-      </c>
-      <c r="N68" s="37">
-        <v>100</v>
-      </c>
-      <c r="O68" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P68" s="39">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="Q68" s="39">
-        <f>P68*N68</f>
-        <v>6.9999999999999993E-2</v>
-      </c>
-      <c r="R68" s="37"/>
+        <v>10</v>
+      </c>
+      <c r="N68" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="O68" s="59" t="s">
+        <v>381</v>
+      </c>
+      <c r="P68" s="66" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q68" s="66" t="s">
+        <v>381</v>
+      </c>
+      <c r="R68" s="64"/>
       <c r="S68" s="37"/>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.25">
@@ -5950,163 +5894,164 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="C69" s="73" t="s">
-        <v>23</v>
-      </c>
-      <c r="D69" s="38" t="s">
-        <v>85</v>
+      <c r="C69" s="63" t="s">
+        <v>398</v>
+      </c>
+      <c r="D69" s="77" t="s">
+        <v>80</v>
       </c>
       <c r="E69" s="38" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="F69" s="38" t="s">
-        <v>203</v>
+        <v>381</v>
       </c>
       <c r="G69" s="38" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="H69" s="38" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I69" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J69" s="38" t="s">
-        <v>410</v>
+        <v>338</v>
       </c>
       <c r="K69" s="38" t="s">
-        <v>407</v>
+        <v>381</v>
       </c>
       <c r="L69" s="38">
         <v>1</v>
       </c>
       <c r="M69" s="38">
-        <f t="shared" ref="M69" si="59">L69*5</f>
+        <f t="shared" ref="M69" si="64">L69*5</f>
         <v>5</v>
       </c>
       <c r="N69" s="38">
-        <v>100</v>
-      </c>
-      <c r="O69" s="71" t="s">
-        <v>422</v>
+        <v>6</v>
+      </c>
+      <c r="O69" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P69" s="40">
-        <v>5.0000000000000001E-4</v>
+        <v>0.54410000000000003</v>
       </c>
       <c r="Q69" s="40">
-        <f t="shared" ref="Q69" si="60">P69*N69</f>
-        <v>0.05</v>
+        <f t="shared" ref="Q69" si="65">P69*N69</f>
+        <v>3.2646000000000002</v>
       </c>
       <c r="R69" s="38"/>
       <c r="S69" s="38"/>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="48">
         <f>ROW(B70) - ROW($B$9)</f>
         <v>61</v>
       </c>
-      <c r="C70" s="74" t="s">
-        <v>425</v>
-      </c>
-      <c r="D70" s="75" t="s">
-        <v>86</v>
-      </c>
-      <c r="E70" s="75" t="s">
-        <v>158</v>
-      </c>
-      <c r="F70" s="75" t="s">
-        <v>409</v>
-      </c>
-      <c r="G70" s="75" t="s">
-        <v>204</v>
-      </c>
-      <c r="H70" s="75" t="s">
-        <v>409</v>
-      </c>
-      <c r="I70" s="75" t="s">
-        <v>409</v>
-      </c>
-      <c r="J70" s="75" t="s">
-        <v>409</v>
-      </c>
-      <c r="K70" s="75" t="s">
-        <v>409</v>
-      </c>
-      <c r="L70" s="75">
-        <v>2</v>
-      </c>
-      <c r="M70" s="75">
+      <c r="C70" s="62" t="s">
+        <v>24</v>
+      </c>
+      <c r="D70" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="E70" s="65" t="s">
+        <v>148</v>
+      </c>
+      <c r="F70" s="65" t="s">
+        <v>189</v>
+      </c>
+      <c r="G70" s="65" t="s">
+        <v>246</v>
+      </c>
+      <c r="H70" s="65" t="s">
+        <v>281</v>
+      </c>
+      <c r="I70" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J70" s="65" t="s">
+        <v>339</v>
+      </c>
+      <c r="K70" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="L70" s="65">
+        <v>1</v>
+      </c>
+      <c r="M70" s="65">
         <f>L70*5</f>
+        <v>5</v>
+      </c>
+      <c r="N70" s="65">
         <v>10</v>
       </c>
-      <c r="N70" s="75" t="s">
-        <v>409</v>
-      </c>
-      <c r="O70" s="75" t="s">
-        <v>409</v>
-      </c>
-      <c r="P70" s="76" t="s">
-        <v>409</v>
-      </c>
-      <c r="Q70" s="76" t="s">
-        <v>409</v>
-      </c>
-      <c r="R70" s="75"/>
-      <c r="S70" s="75"/>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="O70" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P70" s="66">
+        <v>7.6300000000000007E-2</v>
+      </c>
+      <c r="Q70" s="66">
+        <f>P70*N70</f>
+        <v>0.76300000000000012</v>
+      </c>
+      <c r="R70" s="64"/>
+      <c r="S70" s="37"/>
+    </row>
+    <row r="71" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="49">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="C71" s="73" t="s">
-        <v>426</v>
-      </c>
-      <c r="D71" s="38" t="s">
-        <v>87</v>
+      <c r="C71" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="D71" s="77" t="s">
+        <v>82</v>
       </c>
       <c r="E71" s="38" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="F71" s="38" t="s">
-        <v>409</v>
+        <v>190</v>
       </c>
       <c r="G71" s="38" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="H71" s="38" t="s">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="I71" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J71" s="38" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="K71" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="L71" s="38">
         <v>1</v>
       </c>
       <c r="M71" s="38">
-        <f t="shared" ref="M71" si="61">L71*5</f>
+        <f t="shared" ref="M71" si="66">L71*5</f>
         <v>5</v>
       </c>
       <c r="N71" s="38">
         <v>6</v>
       </c>
-      <c r="O71" s="71" t="s">
-        <v>422</v>
+      <c r="O71" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P71" s="40">
-        <v>0.54410000000000003</v>
+        <v>3.1484999999999999</v>
       </c>
       <c r="Q71" s="40">
-        <f t="shared" ref="Q71" si="62">P71*N71</f>
-        <v>3.2646000000000002</v>
+        <f t="shared" ref="Q71" si="67">P71*N71</f>
+        <v>18.890999999999998</v>
       </c>
       <c r="R71" s="38"/>
       <c r="S71" s="38"/>
@@ -6117,166 +6062,166 @@
         <f>ROW(B72) - ROW($B$9)</f>
         <v>63</v>
       </c>
-      <c r="C72" s="72" t="s">
+      <c r="C72" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="D72" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="E72" s="37" t="s">
-        <v>160</v>
-      </c>
-      <c r="F72" s="37" t="s">
-        <v>205</v>
-      </c>
-      <c r="G72" s="37" t="s">
-        <v>265</v>
-      </c>
-      <c r="H72" s="37" t="s">
-        <v>302</v>
-      </c>
-      <c r="I72" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J72" s="37" t="s">
-        <v>364</v>
-      </c>
-      <c r="K72" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="L72" s="37">
+      <c r="D72" s="65" t="s">
+        <v>83</v>
+      </c>
+      <c r="E72" s="65" t="s">
+        <v>150</v>
+      </c>
+      <c r="F72" s="65" t="s">
+        <v>191</v>
+      </c>
+      <c r="G72" s="65" t="s">
+        <v>248</v>
+      </c>
+      <c r="H72" s="65" t="s">
+        <v>283</v>
+      </c>
+      <c r="I72" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J72" s="65" t="s">
+        <v>341</v>
+      </c>
+      <c r="K72" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="L72" s="65">
         <v>1</v>
       </c>
-      <c r="M72" s="37">
+      <c r="M72" s="65">
         <f>L72*5</f>
         <v>5</v>
       </c>
-      <c r="N72" s="37">
+      <c r="N72" s="65">
         <v>10</v>
       </c>
-      <c r="O72" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P72" s="39">
-        <v>7.6300000000000007E-2</v>
-      </c>
-      <c r="Q72" s="39">
+      <c r="O72" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P72" s="66">
+        <v>0.10920000000000001</v>
+      </c>
+      <c r="Q72" s="66">
         <f>P72*N72</f>
-        <v>0.76300000000000012</v>
-      </c>
-      <c r="R72" s="37"/>
+        <v>1.0920000000000001</v>
+      </c>
+      <c r="R72" s="64"/>
       <c r="S72" s="37"/>
     </row>
-    <row r="73" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="49">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="C73" s="73" t="s">
+      <c r="C73" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="D73" s="38" t="s">
-        <v>89</v>
+      <c r="D73" s="77" t="s">
+        <v>84</v>
       </c>
       <c r="E73" s="38" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="F73" s="38" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="G73" s="38" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="H73" s="38" t="s">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="I73" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J73" s="38" t="s">
-        <v>365</v>
+        <v>342</v>
       </c>
       <c r="K73" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="L73" s="38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M73" s="38">
-        <f t="shared" ref="M73" si="63">L73*5</f>
-        <v>5</v>
+        <f t="shared" ref="M73" si="68">L73*5</f>
+        <v>20</v>
       </c>
       <c r="N73" s="38">
-        <v>6</v>
-      </c>
-      <c r="O73" s="71" t="s">
-        <v>422</v>
+        <v>21</v>
+      </c>
+      <c r="O73" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P73" s="40">
-        <v>3.1484999999999999</v>
+        <v>7.5918999999999999</v>
       </c>
       <c r="Q73" s="40">
-        <f t="shared" ref="Q73" si="64">P73*N73</f>
-        <v>18.890999999999998</v>
+        <f t="shared" ref="Q73" si="69">P73*N73</f>
+        <v>159.4299</v>
       </c>
       <c r="R73" s="38"/>
       <c r="S73" s="38"/>
     </row>
-    <row r="74" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="48">
         <f>ROW(B74) - ROW($B$9)</f>
         <v>65</v>
       </c>
-      <c r="C74" s="72" t="s">
+      <c r="C74" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="D74" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="E74" s="37" t="s">
-        <v>162</v>
-      </c>
-      <c r="F74" s="37" t="s">
-        <v>207</v>
-      </c>
-      <c r="G74" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="H74" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="I74" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J74" s="37" t="s">
-        <v>366</v>
-      </c>
-      <c r="K74" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="L74" s="37">
-        <v>1</v>
-      </c>
-      <c r="M74" s="37">
+      <c r="D74" s="65" t="s">
+        <v>85</v>
+      </c>
+      <c r="E74" s="65" t="s">
+        <v>152</v>
+      </c>
+      <c r="F74" s="65" t="s">
+        <v>193</v>
+      </c>
+      <c r="G74" s="65" t="s">
+        <v>250</v>
+      </c>
+      <c r="H74" s="65" t="s">
+        <v>285</v>
+      </c>
+      <c r="I74" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J74" s="65" t="s">
+        <v>343</v>
+      </c>
+      <c r="K74" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="L74" s="65">
+        <v>2</v>
+      </c>
+      <c r="M74" s="65">
         <f>L74*5</f>
-        <v>5</v>
-      </c>
-      <c r="N74" s="37">
         <v>10</v>
       </c>
-      <c r="O74" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P74" s="39">
-        <v>0.10920000000000001</v>
-      </c>
-      <c r="Q74" s="39">
+      <c r="N74" s="65">
+        <v>11</v>
+      </c>
+      <c r="O74" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P74" s="66">
+        <v>0.73819999999999997</v>
+      </c>
+      <c r="Q74" s="66">
         <f>P74*N74</f>
-        <v>1.0920000000000001</v>
-      </c>
-      <c r="R74" s="37"/>
+        <v>8.1202000000000005</v>
+      </c>
+      <c r="R74" s="64"/>
       <c r="S74" s="37"/>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
@@ -6285,110 +6230,110 @@
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="C75" s="73" t="s">
+      <c r="C75" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="D75" s="38" t="s">
-        <v>91</v>
+      <c r="D75" s="77" t="s">
+        <v>86</v>
       </c>
       <c r="E75" s="38" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="F75" s="38" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="G75" s="38" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="H75" s="38" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="I75" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J75" s="38" t="s">
-        <v>367</v>
+        <v>344</v>
       </c>
       <c r="K75" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="L75" s="38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M75" s="38">
-        <f t="shared" ref="M75" si="65">L75*5</f>
-        <v>20</v>
+        <f t="shared" ref="M75" si="70">L75*5</f>
+        <v>5</v>
       </c>
       <c r="N75" s="38">
-        <v>21</v>
-      </c>
-      <c r="O75" s="71" t="s">
-        <v>422</v>
+        <v>6</v>
+      </c>
+      <c r="O75" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P75" s="40">
-        <v>7.5918999999999999</v>
+        <v>0.6905</v>
       </c>
       <c r="Q75" s="40">
-        <f t="shared" ref="Q75" si="66">P75*N75</f>
-        <v>159.4299</v>
+        <f t="shared" ref="Q75" si="71">P75*N75</f>
+        <v>4.1429999999999998</v>
       </c>
       <c r="R75" s="38"/>
       <c r="S75" s="38"/>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="48">
         <f>ROW(B76) - ROW($B$9)</f>
         <v>67</v>
       </c>
-      <c r="C76" s="72" t="s">
-        <v>24</v>
-      </c>
-      <c r="D76" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="E76" s="37" t="s">
-        <v>164</v>
-      </c>
-      <c r="F76" s="37" t="s">
-        <v>209</v>
-      </c>
-      <c r="G76" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="H76" s="37" t="s">
-        <v>306</v>
-      </c>
-      <c r="I76" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J76" s="37" t="s">
-        <v>368</v>
-      </c>
-      <c r="K76" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="L76" s="37">
-        <v>2</v>
-      </c>
-      <c r="M76" s="37">
+      <c r="C76" s="62" t="s">
+        <v>25</v>
+      </c>
+      <c r="D76" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="E76" s="65" t="s">
+        <v>154</v>
+      </c>
+      <c r="F76" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="G76" s="65" t="s">
+        <v>194</v>
+      </c>
+      <c r="H76" s="65" t="s">
+        <v>286</v>
+      </c>
+      <c r="I76" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J76" s="65" t="s">
+        <v>345</v>
+      </c>
+      <c r="K76" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="L76" s="65">
+        <v>1</v>
+      </c>
+      <c r="M76" s="65">
         <f>L76*5</f>
-        <v>10</v>
-      </c>
-      <c r="N76" s="37">
-        <v>11</v>
-      </c>
-      <c r="O76" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P76" s="39">
-        <v>0.73819999999999997</v>
-      </c>
-      <c r="Q76" s="39">
+        <v>5</v>
+      </c>
+      <c r="N76" s="65">
+        <v>6</v>
+      </c>
+      <c r="O76" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P76" s="66">
+        <v>20.79</v>
+      </c>
+      <c r="Q76" s="66">
         <f>P76*N76</f>
-        <v>8.1202000000000005</v>
-      </c>
-      <c r="R76" s="37"/>
+        <v>124.74</v>
+      </c>
+      <c r="R76" s="64"/>
       <c r="S76" s="37"/>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.25">
@@ -6397,408 +6342,299 @@
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="C77" s="73" t="s">
+      <c r="C77" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="D77" s="38" t="s">
-        <v>93</v>
+      <c r="D77" s="77" t="s">
+        <v>88</v>
       </c>
       <c r="E77" s="38" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="F77" s="38" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="G77" s="38" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="H77" s="38" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="I77" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J77" s="38" t="s">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="K77" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="L77" s="38">
         <v>1</v>
       </c>
       <c r="M77" s="38">
-        <f t="shared" ref="M77" si="67">L77*5</f>
+        <f t="shared" ref="M77" si="72">L77*5</f>
         <v>5</v>
       </c>
       <c r="N77" s="38">
         <v>6</v>
       </c>
-      <c r="O77" s="71" t="s">
-        <v>422</v>
+      <c r="O77" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P77" s="40">
-        <v>0.6905</v>
+        <v>11.400499999999999</v>
       </c>
       <c r="Q77" s="40">
-        <f t="shared" ref="Q77" si="68">P77*N77</f>
-        <v>4.1429999999999998</v>
+        <f t="shared" ref="Q77" si="73">P77*N77</f>
+        <v>68.402999999999992</v>
       </c>
       <c r="R77" s="38"/>
       <c r="S77" s="38"/>
     </row>
-    <row r="78" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="48">
         <f>ROW(B78) - ROW($B$9)</f>
         <v>69</v>
       </c>
-      <c r="C78" s="72" t="s">
-        <v>25</v>
-      </c>
-      <c r="D78" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="E78" s="37" t="s">
-        <v>166</v>
-      </c>
-      <c r="F78" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="G78" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="H78" s="37" t="s">
-        <v>307</v>
-      </c>
-      <c r="I78" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J78" s="37" t="s">
-        <v>370</v>
-      </c>
-      <c r="K78" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="L78" s="37">
+      <c r="C78" s="62" t="s">
+        <v>24</v>
+      </c>
+      <c r="D78" s="65" t="s">
+        <v>89</v>
+      </c>
+      <c r="E78" s="65" t="s">
+        <v>156</v>
+      </c>
+      <c r="F78" s="65" t="s">
+        <v>196</v>
+      </c>
+      <c r="G78" s="65" t="s">
+        <v>253</v>
+      </c>
+      <c r="H78" s="65" t="s">
+        <v>288</v>
+      </c>
+      <c r="I78" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J78" s="65" t="s">
+        <v>347</v>
+      </c>
+      <c r="K78" s="65" t="s">
+        <v>381</v>
+      </c>
+      <c r="L78" s="65">
         <v>1</v>
       </c>
-      <c r="M78" s="37">
+      <c r="M78" s="65">
         <f>L78*5</f>
         <v>5</v>
       </c>
-      <c r="N78" s="37">
+      <c r="N78" s="65">
         <v>6</v>
       </c>
-      <c r="O78" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P78" s="39">
-        <v>20.79</v>
-      </c>
-      <c r="Q78" s="39">
+      <c r="O78" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="P78" s="66">
+        <v>2.8128000000000002</v>
+      </c>
+      <c r="Q78" s="66">
         <f>P78*N78</f>
-        <v>124.74</v>
-      </c>
-      <c r="R78" s="37"/>
+        <v>16.876800000000003</v>
+      </c>
+      <c r="R78" s="64"/>
       <c r="S78" s="37"/>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="49">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="C79" s="73" t="s">
-        <v>24</v>
-      </c>
-      <c r="D79" s="38" t="s">
-        <v>95</v>
+      <c r="C79" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="D79" s="77" t="s">
+        <v>90</v>
       </c>
       <c r="E79" s="38" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="F79" s="38" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="G79" s="38" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="H79" s="38" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="I79" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="J79" s="38" t="s">
-        <v>371</v>
+        <v>348</v>
       </c>
       <c r="K79" s="38" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="L79" s="38">
         <v>1</v>
       </c>
       <c r="M79" s="38">
-        <f t="shared" ref="M79" si="69">L79*5</f>
+        <f t="shared" ref="M79" si="74">L79*5</f>
         <v>5</v>
       </c>
       <c r="N79" s="38">
-        <v>6</v>
-      </c>
-      <c r="O79" s="71" t="s">
-        <v>422</v>
+        <v>10</v>
+      </c>
+      <c r="O79" s="61" t="s">
+        <v>394</v>
       </c>
       <c r="P79" s="40">
-        <v>11.400499999999999</v>
+        <v>8.3400000000000002E-2</v>
       </c>
       <c r="Q79" s="40">
-        <f t="shared" ref="Q79" si="70">P79*N79</f>
-        <v>68.402999999999992</v>
+        <f t="shared" ref="Q79" si="75">P79*N79</f>
+        <v>0.83400000000000007</v>
       </c>
       <c r="R79" s="38"/>
       <c r="S79" s="38"/>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
-      <c r="B80" s="48">
-        <f>ROW(B80) - ROW($B$9)</f>
-        <v>71</v>
-      </c>
-      <c r="C80" s="72" t="s">
-        <v>24</v>
-      </c>
-      <c r="D80" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="E80" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="F80" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="G80" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="H80" s="37" t="s">
-        <v>309</v>
-      </c>
-      <c r="I80" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="J80" s="37" t="s">
-        <v>372</v>
-      </c>
-      <c r="K80" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="L80" s="37">
-        <v>1</v>
-      </c>
-      <c r="M80" s="37">
-        <f>L80*5</f>
+      <c r="B80" s="42"/>
+      <c r="C80" s="43"/>
+      <c r="D80" s="44"/>
+      <c r="E80" s="45"/>
+      <c r="F80" s="46"/>
+      <c r="G80" s="47"/>
+      <c r="H80" s="46"/>
+      <c r="I80" s="47"/>
+      <c r="J80" s="46"/>
+      <c r="K80" s="47"/>
+      <c r="L80" s="47"/>
+      <c r="M80" s="47"/>
+      <c r="N80" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="N80" s="37">
+      <c r="O80" s="76"/>
+      <c r="P80" s="76"/>
+      <c r="Q80" s="50">
+        <f>SUM(Q10:Q79)</f>
+        <v>594.24969999999996</v>
+      </c>
+      <c r="R80" s="71"/>
+      <c r="S80" s="72"/>
+    </row>
+    <row r="81" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="1"/>
+      <c r="B81" s="25"/>
+      <c r="C81" s="36"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="10"/>
+      <c r="F81" s="10"/>
+      <c r="G81" s="10"/>
+      <c r="H81" s="10"/>
+      <c r="I81" s="10"/>
+      <c r="J81" s="10"/>
+      <c r="K81" s="10"/>
+      <c r="L81" s="10"/>
+      <c r="M81" s="10"/>
+      <c r="N81" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="O80" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="P80" s="39">
-        <v>2.8128000000000002</v>
-      </c>
-      <c r="Q80" s="39">
-        <f>P80*N80</f>
-        <v>16.876800000000003</v>
-      </c>
-      <c r="R80" s="37"/>
-      <c r="S80" s="37"/>
-    </row>
-    <row r="81" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="1"/>
-      <c r="B81" s="49">
-        <f t="shared" si="0"/>
-        <v>72</v>
-      </c>
-      <c r="C81" s="73" t="s">
-        <v>26</v>
-      </c>
-      <c r="D81" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="E81" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="F81" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="G81" s="38" t="s">
-        <v>273</v>
-      </c>
-      <c r="H81" s="38" t="s">
-        <v>310</v>
-      </c>
-      <c r="I81" s="38" t="s">
-        <v>409</v>
-      </c>
-      <c r="J81" s="38" t="s">
-        <v>373</v>
-      </c>
-      <c r="K81" s="38" t="s">
-        <v>409</v>
-      </c>
-      <c r="L81" s="38">
-        <v>1</v>
-      </c>
-      <c r="M81" s="38">
-        <f t="shared" ref="M81" si="71">L81*5</f>
-        <v>5</v>
-      </c>
-      <c r="N81" s="38">
-        <v>10</v>
-      </c>
-      <c r="O81" s="71" t="s">
-        <v>422</v>
-      </c>
-      <c r="P81" s="40">
-        <v>8.3400000000000002E-2</v>
-      </c>
-      <c r="Q81" s="40">
-        <f t="shared" ref="Q81" si="72">P81*N81</f>
-        <v>0.83400000000000007</v>
-      </c>
-      <c r="R81" s="38"/>
-      <c r="S81" s="38"/>
-    </row>
-    <row r="82" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="1"/>
-      <c r="B82" s="42"/>
-      <c r="C82" s="43"/>
-      <c r="D82" s="44"/>
-      <c r="E82" s="45"/>
-      <c r="F82" s="46"/>
-      <c r="G82" s="47"/>
-      <c r="H82" s="46"/>
-      <c r="I82" s="47"/>
-      <c r="J82" s="46"/>
-      <c r="K82" s="47"/>
-      <c r="L82" s="47"/>
-      <c r="M82" s="47"/>
-      <c r="N82" s="64" t="s">
-        <v>5</v>
-      </c>
-      <c r="O82" s="65"/>
-      <c r="P82" s="65"/>
-      <c r="Q82" s="50">
-        <f>SUM(Q10:Q81)</f>
-        <v>572.71929999999998</v>
-      </c>
-      <c r="R82" s="60"/>
-      <c r="S82" s="61"/>
-    </row>
-    <row r="83" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="1"/>
-      <c r="B83" s="25"/>
-      <c r="C83" s="36"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="10"/>
-      <c r="F83" s="10"/>
-      <c r="G83" s="10"/>
-      <c r="H83" s="10"/>
-      <c r="I83" s="10"/>
-      <c r="J83" s="10"/>
-      <c r="K83" s="10"/>
-      <c r="L83" s="10"/>
-      <c r="M83" s="10"/>
-      <c r="N83" s="64" t="s">
-        <v>6</v>
-      </c>
-      <c r="O83" s="65"/>
-      <c r="P83" s="65"/>
-      <c r="Q83" s="51">
-        <f>Q82/5</f>
-        <v>114.54386</v>
-      </c>
-      <c r="R83" s="62"/>
-      <c r="S83" s="63"/>
+      <c r="O81" s="76"/>
+      <c r="P81" s="76"/>
+      <c r="Q81" s="51">
+        <f>Q80/5</f>
+        <v>118.84993999999999</v>
+      </c>
+      <c r="R81" s="73"/>
+      <c r="S81" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R82:S83"/>
-    <mergeCell ref="N82:P82"/>
-    <mergeCell ref="N83:P83"/>
+    <mergeCell ref="R80:S81"/>
+    <mergeCell ref="N80:P80"/>
+    <mergeCell ref="N81:P81"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1" xr:uid="{83330362-F0C7-46EF-A396-98923760856E}"/>
     <hyperlink ref="O11" r:id="rId2" xr:uid="{DB12CDE4-1E23-4DC3-AED9-E8614EF62035}"/>
     <hyperlink ref="O13" r:id="rId3" xr:uid="{8F3B8BE9-70CE-4D85-A311-45F063D386DE}"/>
-    <hyperlink ref="O15" r:id="rId4" xr:uid="{06EBE5D2-DD69-49E9-B95F-3DE9157408AC}"/>
-    <hyperlink ref="O16" r:id="rId5" xr:uid="{FBEAF86C-1250-42A9-862F-6E1D1F940422}"/>
-    <hyperlink ref="O17" r:id="rId6" xr:uid="{C55E2959-5F99-44C9-9C77-90D75CDD51E7}"/>
-    <hyperlink ref="O19" r:id="rId7" xr:uid="{324C4BE8-EFA4-4D83-B94F-D73DA115B8D6}"/>
-    <hyperlink ref="O20" r:id="rId8" xr:uid="{AC68A078-5AC7-4F87-AF9E-83FA24A08968}"/>
-    <hyperlink ref="O21" r:id="rId9" xr:uid="{65531464-2710-4ACA-B558-50D49C4EBFD5}"/>
-    <hyperlink ref="O22" r:id="rId10" xr:uid="{D294B23C-79F3-45A3-B0CB-83065DB0DFBE}"/>
-    <hyperlink ref="O23" r:id="rId11" xr:uid="{35BDF612-2500-4AAB-9A3C-389710CC8A13}"/>
-    <hyperlink ref="O25" r:id="rId12" xr:uid="{09995E25-E46C-41E4-A215-3AFA7BA38097}"/>
-    <hyperlink ref="O26" r:id="rId13" xr:uid="{D4A1ED2E-51BE-4BFB-8C67-4A5FBF716E81}"/>
-    <hyperlink ref="O27" r:id="rId14" xr:uid="{D9FDF2FF-7F17-4E92-BB05-1CB02A88AE46}"/>
-    <hyperlink ref="O28" r:id="rId15" xr:uid="{E5092E06-E380-4B03-80D7-16C56A0BFD76}"/>
-    <hyperlink ref="O29" r:id="rId16" xr:uid="{119F4900-2975-432E-9C8B-99A1B6DAEB20}"/>
-    <hyperlink ref="O30" r:id="rId17" xr:uid="{352461EC-DA11-46E9-92D4-B9C068E3C180}"/>
-    <hyperlink ref="O31" r:id="rId18" xr:uid="{A836E869-1683-4F1A-B273-33D366B89F95}"/>
-    <hyperlink ref="O32" r:id="rId19" xr:uid="{435EC6F6-0FAD-4A31-A582-C246D57C7D6F}"/>
-    <hyperlink ref="O33" r:id="rId20" xr:uid="{7DB9ABA3-1F74-4C4A-8795-93F417A50B5B}"/>
-    <hyperlink ref="O34" r:id="rId21" xr:uid="{5B4AF0FE-AE45-4674-A0B6-D52529DBEA42}"/>
-    <hyperlink ref="O35" r:id="rId22" xr:uid="{A526FB24-06D8-4BA8-A0A9-D625EB20D001}"/>
-    <hyperlink ref="O36" r:id="rId23" xr:uid="{7898B0DE-B99C-422B-93A1-C64000A2710F}"/>
-    <hyperlink ref="O37" r:id="rId24" xr:uid="{60F5EA99-FC5D-42DA-83AB-2503145247E5}"/>
-    <hyperlink ref="O38" r:id="rId25" xr:uid="{6EA8AF8A-1CB3-451C-A1FF-53A54C702D59}"/>
-    <hyperlink ref="O39" r:id="rId26" xr:uid="{B317581D-06A6-4EB4-891A-C0C139D8E474}"/>
-    <hyperlink ref="O40" r:id="rId27" xr:uid="{FDCBF760-4B93-4276-A3BA-7715546260C9}"/>
-    <hyperlink ref="O41" r:id="rId28" xr:uid="{8E648B41-42DE-4F16-91A7-315D4267BDAC}"/>
-    <hyperlink ref="O42" r:id="rId29" xr:uid="{90524ED7-C00A-44AB-8E3C-CF9BE029B7F7}"/>
-    <hyperlink ref="O43" r:id="rId30" xr:uid="{1F66A3F1-2879-418E-A260-EBF5779ADB9A}"/>
-    <hyperlink ref="O45" r:id="rId31" xr:uid="{D6253230-F78F-4F57-841E-6E32DA3F6F6B}"/>
-    <hyperlink ref="O47" r:id="rId32" xr:uid="{F92A08BD-DC56-49CB-BB49-C672D65AF7B6}"/>
-    <hyperlink ref="O48" r:id="rId33" xr:uid="{C983EB1D-0C91-45E9-BE66-3F32EFEBF11E}"/>
-    <hyperlink ref="O51" r:id="rId34" xr:uid="{D166F96C-85E9-4ECC-95F1-3B236295E9EA}"/>
-    <hyperlink ref="O52" r:id="rId35" xr:uid="{74E89379-FE6D-4A6D-9086-2E5F06F276D3}"/>
-    <hyperlink ref="O53" r:id="rId36" xr:uid="{9500BE23-7086-4D84-96D7-5D20AD5CA396}"/>
-    <hyperlink ref="O54" r:id="rId37" xr:uid="{7959F19A-CC8B-4CCD-9543-CFA937F95FE0}"/>
-    <hyperlink ref="O55" r:id="rId38" xr:uid="{C1A12F9C-529D-4C71-B8D0-1E662F17A4CF}"/>
-    <hyperlink ref="O56" r:id="rId39" xr:uid="{9FB226EB-05D0-4756-90EC-AB74DF432825}"/>
-    <hyperlink ref="O57" r:id="rId40" xr:uid="{2A083DAE-370B-4D83-8484-60F664F4D0FB}"/>
-    <hyperlink ref="O58" r:id="rId41" xr:uid="{2C97F014-F5E8-4B24-963D-FE80A7631953}"/>
-    <hyperlink ref="O59" r:id="rId42" xr:uid="{6F3D2A4A-F4D5-4F39-AA76-C26734A9F58D}"/>
-    <hyperlink ref="O60" r:id="rId43" xr:uid="{071B56B4-D644-4DBA-9C24-EAA419F04152}"/>
-    <hyperlink ref="O61" r:id="rId44" xr:uid="{FCEB1084-02FC-4396-A776-E5A840FCDC5C}"/>
-    <hyperlink ref="O62" r:id="rId45" xr:uid="{E366D270-8EAC-4607-849D-1D7110BF13C6}"/>
-    <hyperlink ref="O63" r:id="rId46" xr:uid="{21BB671E-15DA-47B2-9961-72F25541C5E2}"/>
-    <hyperlink ref="O64" r:id="rId47" xr:uid="{4F5D2B75-A643-4920-899E-536F91142938}"/>
-    <hyperlink ref="O65" r:id="rId48" xr:uid="{D6C832CC-6FCE-4894-B42E-1075C3474637}"/>
-    <hyperlink ref="O66" r:id="rId49" xr:uid="{46C226E9-81B8-4812-9A33-DA13B84C252D}"/>
-    <hyperlink ref="O67" r:id="rId50" xr:uid="{08B69DB7-9AAD-4B1C-BFEB-486DA2F5A169}"/>
-    <hyperlink ref="O68" r:id="rId51" xr:uid="{C942BC27-6E68-427F-9EC4-5A6A9F3691F9}"/>
-    <hyperlink ref="O69" r:id="rId52" xr:uid="{D6B78B63-B011-4041-9416-EA6C7F8D8AE7}"/>
-    <hyperlink ref="O71" r:id="rId53" xr:uid="{8429BF53-DDFF-45A2-9753-DFDC3A7EC73E}"/>
-    <hyperlink ref="O72" r:id="rId54" xr:uid="{69BB30E6-FCE6-4DD2-9033-50DBAEAFB28E}"/>
-    <hyperlink ref="O73" r:id="rId55" xr:uid="{9DBB4DF3-112E-4A0A-A8C2-64BB1FCB650F}"/>
-    <hyperlink ref="O74" r:id="rId56" xr:uid="{749C77DE-6558-4DB6-8849-7A73C148D4CE}"/>
-    <hyperlink ref="O75" r:id="rId57" xr:uid="{5FBFDDE4-D8E1-4DDC-8314-D97DA5D132A5}"/>
-    <hyperlink ref="O76" r:id="rId58" xr:uid="{FD33955C-3AAA-49E7-ADBD-08C8E8316B63}"/>
-    <hyperlink ref="O77" r:id="rId59" xr:uid="{10F92991-AF57-4F4E-ACEC-133226566204}"/>
-    <hyperlink ref="O78" r:id="rId60" xr:uid="{6027C0A4-5D1E-4433-85BF-CD2F57D6DA89}"/>
-    <hyperlink ref="O79" r:id="rId61" xr:uid="{29DDBCD9-DE51-47A5-B3C6-827913DA2387}"/>
-    <hyperlink ref="O80" r:id="rId62" xr:uid="{FC388204-E09E-47D1-A054-C8455D575E2E}"/>
-    <hyperlink ref="O81" r:id="rId63" xr:uid="{C573F08C-CF21-426E-B62B-392C975BBEB8}"/>
-    <hyperlink ref="O24" r:id="rId64" xr:uid="{A2463247-A92E-46A4-B1F2-C7859F430396}"/>
+    <hyperlink ref="O14" r:id="rId4" xr:uid="{06EBE5D2-DD69-49E9-B95F-3DE9157408AC}"/>
+    <hyperlink ref="O15" r:id="rId5" xr:uid="{FBEAF86C-1250-42A9-862F-6E1D1F940422}"/>
+    <hyperlink ref="O16" r:id="rId6" xr:uid="{C55E2959-5F99-44C9-9C77-90D75CDD51E7}"/>
+    <hyperlink ref="O18" r:id="rId7" xr:uid="{324C4BE8-EFA4-4D83-B94F-D73DA115B8D6}"/>
+    <hyperlink ref="O19" r:id="rId8" xr:uid="{AC68A078-5AC7-4F87-AF9E-83FA24A08968}"/>
+    <hyperlink ref="O20" r:id="rId9" xr:uid="{65531464-2710-4ACA-B558-50D49C4EBFD5}"/>
+    <hyperlink ref="O21" r:id="rId10" xr:uid="{D294B23C-79F3-45A3-B0CB-83065DB0DFBE}"/>
+    <hyperlink ref="O22" r:id="rId11" xr:uid="{35BDF612-2500-4AAB-9A3C-389710CC8A13}"/>
+    <hyperlink ref="O24" r:id="rId12" xr:uid="{09995E25-E46C-41E4-A215-3AFA7BA38097}"/>
+    <hyperlink ref="O25" r:id="rId13" xr:uid="{D4A1ED2E-51BE-4BFB-8C67-4A5FBF716E81}"/>
+    <hyperlink ref="O26" r:id="rId14" xr:uid="{D9FDF2FF-7F17-4E92-BB05-1CB02A88AE46}"/>
+    <hyperlink ref="O27" r:id="rId15" xr:uid="{E5092E06-E380-4B03-80D7-16C56A0BFD76}"/>
+    <hyperlink ref="O28" r:id="rId16" xr:uid="{119F4900-2975-432E-9C8B-99A1B6DAEB20}"/>
+    <hyperlink ref="O29" r:id="rId17" xr:uid="{352461EC-DA11-46E9-92D4-B9C068E3C180}"/>
+    <hyperlink ref="O30" r:id="rId18" xr:uid="{A836E869-1683-4F1A-B273-33D366B89F95}"/>
+    <hyperlink ref="O31" r:id="rId19" xr:uid="{435EC6F6-0FAD-4A31-A582-C246D57C7D6F}"/>
+    <hyperlink ref="O32" r:id="rId20" xr:uid="{7DB9ABA3-1F74-4C4A-8795-93F417A50B5B}"/>
+    <hyperlink ref="O33" r:id="rId21" xr:uid="{5B4AF0FE-AE45-4674-A0B6-D52529DBEA42}"/>
+    <hyperlink ref="O36" r:id="rId22" xr:uid="{7898B0DE-B99C-422B-93A1-C64000A2710F}"/>
+    <hyperlink ref="O37" r:id="rId23" xr:uid="{60F5EA99-FC5D-42DA-83AB-2503145247E5}"/>
+    <hyperlink ref="O38" r:id="rId24" xr:uid="{6EA8AF8A-1CB3-451C-A1FF-53A54C702D59}"/>
+    <hyperlink ref="O39" r:id="rId25" xr:uid="{B317581D-06A6-4EB4-891A-C0C139D8E474}"/>
+    <hyperlink ref="O40" r:id="rId26" xr:uid="{FDCBF760-4B93-4276-A3BA-7715546260C9}"/>
+    <hyperlink ref="O41" r:id="rId27" xr:uid="{8E648B41-42DE-4F16-91A7-315D4267BDAC}"/>
+    <hyperlink ref="O42" r:id="rId28" xr:uid="{90524ED7-C00A-44AB-8E3C-CF9BE029B7F7}"/>
+    <hyperlink ref="O43" r:id="rId29" xr:uid="{1F66A3F1-2879-418E-A260-EBF5779ADB9A}"/>
+    <hyperlink ref="O44" r:id="rId30" xr:uid="{D6253230-F78F-4F57-841E-6E32DA3F6F6B}"/>
+    <hyperlink ref="O46" r:id="rId31" xr:uid="{F92A08BD-DC56-49CB-BB49-C672D65AF7B6}"/>
+    <hyperlink ref="O45" r:id="rId32" xr:uid="{C983EB1D-0C91-45E9-BE66-3F32EFEBF11E}"/>
+    <hyperlink ref="O49" r:id="rId33" xr:uid="{D166F96C-85E9-4ECC-95F1-3B236295E9EA}"/>
+    <hyperlink ref="O50" r:id="rId34" xr:uid="{74E89379-FE6D-4A6D-9086-2E5F06F276D3}"/>
+    <hyperlink ref="O51" r:id="rId35" xr:uid="{9500BE23-7086-4D84-96D7-5D20AD5CA396}"/>
+    <hyperlink ref="O52" r:id="rId36" xr:uid="{7959F19A-CC8B-4CCD-9543-CFA937F95FE0}"/>
+    <hyperlink ref="O53" r:id="rId37" xr:uid="{C1A12F9C-529D-4C71-B8D0-1E662F17A4CF}"/>
+    <hyperlink ref="O54" r:id="rId38" xr:uid="{9FB226EB-05D0-4756-90EC-AB74DF432825}"/>
+    <hyperlink ref="O55" r:id="rId39" xr:uid="{2A083DAE-370B-4D83-8484-60F664F4D0FB}"/>
+    <hyperlink ref="O56" r:id="rId40" xr:uid="{2C97F014-F5E8-4B24-963D-FE80A7631953}"/>
+    <hyperlink ref="O57" r:id="rId41" xr:uid="{6F3D2A4A-F4D5-4F39-AA76-C26734A9F58D}"/>
+    <hyperlink ref="O58" r:id="rId42" xr:uid="{071B56B4-D644-4DBA-9C24-EAA419F04152}"/>
+    <hyperlink ref="O59" r:id="rId43" xr:uid="{FCEB1084-02FC-4396-A776-E5A840FCDC5C}"/>
+    <hyperlink ref="O60" r:id="rId44" xr:uid="{E366D270-8EAC-4607-849D-1D7110BF13C6}"/>
+    <hyperlink ref="O61" r:id="rId45" xr:uid="{21BB671E-15DA-47B2-9961-72F25541C5E2}"/>
+    <hyperlink ref="O62" r:id="rId46" xr:uid="{4F5D2B75-A643-4920-899E-536F91142938}"/>
+    <hyperlink ref="O63" r:id="rId47" xr:uid="{D6C832CC-6FCE-4894-B42E-1075C3474637}"/>
+    <hyperlink ref="O64" r:id="rId48" xr:uid="{46C226E9-81B8-4812-9A33-DA13B84C252D}"/>
+    <hyperlink ref="O65" r:id="rId49" xr:uid="{08B69DB7-9AAD-4B1C-BFEB-486DA2F5A169}"/>
+    <hyperlink ref="O66" r:id="rId50" xr:uid="{C942BC27-6E68-427F-9EC4-5A6A9F3691F9}"/>
+    <hyperlink ref="O67" r:id="rId51" xr:uid="{D6B78B63-B011-4041-9416-EA6C7F8D8AE7}"/>
+    <hyperlink ref="O69" r:id="rId52" xr:uid="{8429BF53-DDFF-45A2-9753-DFDC3A7EC73E}"/>
+    <hyperlink ref="O70" r:id="rId53" xr:uid="{69BB30E6-FCE6-4DD2-9033-50DBAEAFB28E}"/>
+    <hyperlink ref="O71" r:id="rId54" xr:uid="{9DBB4DF3-112E-4A0A-A8C2-64BB1FCB650F}"/>
+    <hyperlink ref="O72" r:id="rId55" xr:uid="{749C77DE-6558-4DB6-8849-7A73C148D4CE}"/>
+    <hyperlink ref="O73" r:id="rId56" xr:uid="{5FBFDDE4-D8E1-4DDC-8314-D97DA5D132A5}"/>
+    <hyperlink ref="O74" r:id="rId57" xr:uid="{FD33955C-3AAA-49E7-ADBD-08C8E8316B63}"/>
+    <hyperlink ref="O75" r:id="rId58" xr:uid="{10F92991-AF57-4F4E-ACEC-133226566204}"/>
+    <hyperlink ref="O76" r:id="rId59" xr:uid="{6027C0A4-5D1E-4433-85BF-CD2F57D6DA89}"/>
+    <hyperlink ref="O77" r:id="rId60" xr:uid="{29DDBCD9-DE51-47A5-B3C6-827913DA2387}"/>
+    <hyperlink ref="O78" r:id="rId61" xr:uid="{FC388204-E09E-47D1-A054-C8455D575E2E}"/>
+    <hyperlink ref="O79" r:id="rId62" xr:uid="{C573F08C-CF21-426E-B62B-392C975BBEB8}"/>
+    <hyperlink ref="O23" r:id="rId63" xr:uid="{A2463247-A92E-46A4-B1F2-C7859F430396}"/>
+    <hyperlink ref="O12" r:id="rId64" xr:uid="{8C42F702-13DB-4B89-BA91-C5903624B455}"/>
+    <hyperlink ref="O17" r:id="rId65" xr:uid="{71295E9A-7059-4DB8-9A46-8806E333672F}"/>
+    <hyperlink ref="O34" r:id="rId66" xr:uid="{31634445-58D7-420B-A9DF-F6B47E182EE9}"/>
+    <hyperlink ref="O35" r:id="rId67" xr:uid="{696C55EA-352D-4A6D-AE88-F7D6577A10B8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId65"/>
-  <drawing r:id="rId66"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId68"/>
+  <drawing r:id="rId69"/>
 </worksheet>
 </file>
--- a/BOM/eSpark-BOM.xlsx
+++ b/BOM/eSpark-BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\matthewgraff-arduinomegapcb\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F81E612-8541-4AC9-AED6-E3F3BE6A4D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF9E64C-E5EB-4237-9227-2EAF0EE59067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="447">
   <si>
     <t>Component list</t>
   </si>
@@ -1300,12 +1300,6 @@
     <t>C967080</t>
   </si>
   <si>
-    <t>C6, C4, C36, C53</t>
-  </si>
-  <si>
-    <t>C53 Not Confirm</t>
-  </si>
-  <si>
     <t>C526997</t>
   </si>
   <si>
@@ -1313,6 +1307,60 @@
   </si>
   <si>
     <t xml:space="preserve">Less Stock On LCSC </t>
+  </si>
+  <si>
+    <t>C6, C4, C36</t>
+  </si>
+  <si>
+    <t>C53</t>
+  </si>
+  <si>
+    <t>CAP ALUM POLY 47UF 20% 25V SMD</t>
+  </si>
+  <si>
+    <t>25SVPF47M</t>
+  </si>
+  <si>
+    <t>C136280</t>
+  </si>
+  <si>
+    <t>47uF</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>BW4GJWX195-13KJ</t>
+  </si>
+  <si>
+    <t>C497022</t>
+  </si>
+  <si>
+    <t>BAT WIRELESS</t>
+  </si>
+  <si>
+    <t>Antennas ROHS</t>
+  </si>
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>BWGNSCNX25-25B1Y2L120</t>
+  </si>
+  <si>
+    <t>C784385</t>
+  </si>
+  <si>
+    <t>IPEX-25x25x4.6mm Antennas ROHS</t>
+  </si>
+  <si>
+    <t>BWIPX1-SMA-1.13L200</t>
+  </si>
+  <si>
+    <t>65℃~+165℃ 200mm IPEX to SMA 1Gen - Radio Frequency Cable ROHS</t>
+  </si>
+  <si>
+    <t>C784405</t>
   </si>
 </sst>
 </file>
@@ -1324,7 +1372,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1500,6 +1548,38 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1533,7 +1613,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -1765,12 +1845,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1866,14 +1959,8 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="18" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1931,9 +2018,6 @@
     <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1950,6 +2034,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="19" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1984,11 +2074,71 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2332,7 +2482,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S81"/>
+  <dimension ref="A1:S85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -2366,15 +2516,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="68"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="67"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2384,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="11"/>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="50" t="s">
         <v>407</v>
       </c>
       <c r="G2" s="12"/>
@@ -2409,7 +2559,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="13"/>
-      <c r="F3" s="53" t="s">
+      <c r="F3" s="51" t="s">
         <v>408</v>
       </c>
       <c r="G3" s="13"/>
@@ -2424,7 +2574,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="69"/>
+      <c r="S3" s="68"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2434,7 +2584,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="13"/>
-      <c r="F4" s="54" t="s">
+      <c r="F4" s="52" t="s">
         <v>408</v>
       </c>
       <c r="G4" s="14"/>
@@ -2449,7 +2599,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="70"/>
+      <c r="S4" s="69"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2459,7 +2609,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="13"/>
-      <c r="F5" s="55" t="s">
+      <c r="F5" s="53" t="s">
         <v>7</v>
       </c>
       <c r="G5" s="15"/>
@@ -2474,7 +2624,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="70"/>
+      <c r="S5" s="69"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2495,7 +2645,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="70"/>
+      <c r="S6" s="69"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2516,7 +2666,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="70"/>
+      <c r="S7" s="69"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2537,7 +2687,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="70"/>
+      <c r="S8" s="69"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2547,49 +2697,49 @@
       <c r="C9" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="56" t="s">
+      <c r="D9" s="54" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="F9" s="56" t="s">
+      <c r="F9" s="54" t="s">
         <v>158</v>
       </c>
       <c r="G9" s="30" t="s">
         <v>198</v>
       </c>
-      <c r="H9" s="56" t="s">
+      <c r="H9" s="54" t="s">
         <v>255</v>
       </c>
       <c r="I9" s="30" t="s">
         <v>384</v>
       </c>
-      <c r="J9" s="56" t="s">
+      <c r="J9" s="54" t="s">
         <v>290</v>
       </c>
-      <c r="K9" s="57" t="s">
+      <c r="K9" s="55" t="s">
         <v>385</v>
       </c>
       <c r="L9" s="30" t="s">
         <v>380</v>
       </c>
-      <c r="M9" s="58" t="s">
+      <c r="M9" s="56" t="s">
         <v>389</v>
       </c>
-      <c r="N9" s="56" t="s">
+      <c r="N9" s="54" t="s">
         <v>390</v>
       </c>
       <c r="O9" s="30" t="s">
         <v>386</v>
       </c>
-      <c r="P9" s="56" t="s">
+      <c r="P9" s="54" t="s">
         <v>391</v>
       </c>
       <c r="Q9" s="30" t="s">
         <v>392</v>
       </c>
-      <c r="R9" s="56" t="s">
+      <c r="R9" s="54" t="s">
         <v>387</v>
       </c>
       <c r="S9" s="30" t="s">
@@ -2598,3972 +2748,4203 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="48">
+      <c r="B10" s="46">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="62" t="s">
+      <c r="C10" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="65" t="s">
+      <c r="D10" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E10" s="78" t="s">
         <v>92</v>
       </c>
-      <c r="F10" s="37" t="s">
+      <c r="F10" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="G10" s="37" t="s">
+      <c r="G10" s="78" t="s">
         <v>199</v>
       </c>
-      <c r="H10" s="37" t="s">
+      <c r="H10" s="78" t="s">
         <v>256</v>
       </c>
-      <c r="I10" s="37" t="s">
-        <v>381</v>
-      </c>
-      <c r="J10" s="37" t="s">
+      <c r="I10" s="78" t="s">
+        <v>381</v>
+      </c>
+      <c r="J10" s="78" t="s">
         <v>291</v>
       </c>
-      <c r="K10" s="37" t="s">
+      <c r="K10" s="78" t="s">
         <v>349</v>
       </c>
-      <c r="L10" s="37">
+      <c r="L10" s="78">
         <v>1</v>
       </c>
-      <c r="M10" s="37">
+      <c r="M10" s="78">
         <f>L10*5</f>
         <v>5</v>
       </c>
-      <c r="N10" s="37">
+      <c r="N10" s="78">
         <v>10</v>
       </c>
-      <c r="O10" s="59" t="s">
+      <c r="O10" s="79" t="s">
         <v>394</v>
       </c>
-      <c r="P10" s="39">
+      <c r="P10" s="80">
         <v>0.15939999999999999</v>
       </c>
-      <c r="Q10" s="39">
+      <c r="Q10" s="80">
         <f>P10*N10</f>
         <v>1.5939999999999999</v>
       </c>
-      <c r="R10" s="37"/>
-      <c r="S10" s="41"/>
+      <c r="R10" s="78"/>
+      <c r="S10" s="97"/>
     </row>
     <row r="11" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="49">
-        <f t="shared" ref="B11:B79" si="0">ROW(B11) - ROW($B$9)</f>
+      <c r="B11" s="47">
+        <f t="shared" ref="B11:B81" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="63" t="s">
+      <c r="C11" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="77" t="s">
+      <c r="D11" s="83" t="s">
         <v>415</v>
       </c>
-      <c r="E11" s="38" t="s">
+      <c r="E11" s="84" t="s">
         <v>93</v>
       </c>
-      <c r="F11" s="38" t="s">
+      <c r="F11" s="84" t="s">
         <v>159</v>
       </c>
-      <c r="G11" s="60" t="s">
+      <c r="G11" s="85" t="s">
         <v>200</v>
       </c>
-      <c r="H11" s="38" t="s">
+      <c r="H11" s="84" t="s">
         <v>256</v>
       </c>
-      <c r="I11" s="38" t="s">
+      <c r="I11" s="84" t="s">
         <v>395</v>
       </c>
-      <c r="J11" s="38" t="s">
+      <c r="J11" s="84" t="s">
         <v>292</v>
       </c>
-      <c r="K11" s="38" t="s">
+      <c r="K11" s="84" t="s">
         <v>350</v>
       </c>
-      <c r="L11" s="38">
+      <c r="L11" s="84">
         <v>28</v>
       </c>
-      <c r="M11" s="38">
+      <c r="M11" s="84">
         <f t="shared" ref="M11" si="1">L11*5</f>
         <v>140</v>
       </c>
-      <c r="N11" s="38">
+      <c r="N11" s="84">
         <v>150</v>
       </c>
-      <c r="O11" s="61" t="s">
+      <c r="O11" s="86" t="s">
         <v>394</v>
       </c>
-      <c r="P11" s="40">
+      <c r="P11" s="87">
         <v>1.04E-2</v>
       </c>
-      <c r="Q11" s="40">
+      <c r="Q11" s="87">
         <f t="shared" ref="Q11" si="2">P11*N11</f>
         <v>1.5599999999999998</v>
       </c>
-      <c r="R11" s="38"/>
-      <c r="S11" s="38"/>
+      <c r="R11" s="84"/>
+      <c r="S11" s="84"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="48">
+      <c r="B12" s="46">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="62" t="s">
+      <c r="C12" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="65" t="s">
+      <c r="D12" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="65" t="s">
+      <c r="E12" s="77" t="s">
         <v>409</v>
       </c>
-      <c r="F12" s="65" t="s">
+      <c r="F12" s="77" t="s">
         <v>410</v>
       </c>
-      <c r="G12" s="65" t="s">
+      <c r="G12" s="77" t="s">
         <v>411</v>
       </c>
-      <c r="H12" s="65" t="s">
+      <c r="H12" s="77" t="s">
         <v>412</v>
       </c>
-      <c r="I12" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J12" s="65" t="s">
+      <c r="I12" s="77" t="s">
+        <v>381</v>
+      </c>
+      <c r="J12" s="77" t="s">
         <v>413</v>
       </c>
-      <c r="K12" s="65" t="s">
+      <c r="K12" s="77" t="s">
         <v>351</v>
       </c>
-      <c r="L12" s="65">
+      <c r="L12" s="77">
         <v>2</v>
       </c>
-      <c r="M12" s="65">
+      <c r="M12" s="77">
         <f>L12*5</f>
         <v>10</v>
       </c>
-      <c r="N12" s="65">
+      <c r="N12" s="77">
         <v>20</v>
       </c>
-      <c r="O12" s="59" t="s">
+      <c r="O12" s="79" t="s">
         <v>394</v>
       </c>
-      <c r="P12" s="66">
+      <c r="P12" s="95">
         <v>6.2E-2</v>
       </c>
-      <c r="Q12" s="66">
+      <c r="Q12" s="95">
         <f>P12*N12</f>
         <v>1.24</v>
       </c>
-      <c r="R12" s="64"/>
-      <c r="S12" s="37"/>
+      <c r="R12" s="96"/>
+      <c r="S12" s="78"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="49">
+      <c r="B13" s="47">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="63" t="s">
+      <c r="C13" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="77" t="s">
-        <v>426</v>
-      </c>
-      <c r="E13" s="38" t="s">
+      <c r="D13" s="83" t="s">
+        <v>429</v>
+      </c>
+      <c r="E13" s="84" t="s">
         <v>94</v>
       </c>
-      <c r="F13" s="38" t="s">
+      <c r="F13" s="84" t="s">
         <v>393</v>
       </c>
-      <c r="G13" s="38" t="s">
+      <c r="G13" s="84" t="s">
         <v>160</v>
       </c>
-      <c r="H13" s="38" t="s">
+      <c r="H13" s="84" t="s">
         <v>258</v>
       </c>
-      <c r="I13" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J13" s="38" t="s">
+      <c r="I13" s="84" t="s">
+        <v>381</v>
+      </c>
+      <c r="J13" s="84" t="s">
         <v>293</v>
       </c>
-      <c r="K13" s="38" t="s">
+      <c r="K13" s="84" t="s">
         <v>352</v>
       </c>
-      <c r="L13" s="38">
-        <v>4</v>
-      </c>
-      <c r="M13" s="38">
+      <c r="L13" s="84">
+        <v>3</v>
+      </c>
+      <c r="M13" s="84">
         <f t="shared" ref="M13" si="3">L13*5</f>
-        <v>20</v>
-      </c>
-      <c r="N13" s="38">
-        <v>22</v>
-      </c>
-      <c r="O13" s="61" t="s">
+        <v>15</v>
+      </c>
+      <c r="N13" s="84">
+        <v>17</v>
+      </c>
+      <c r="O13" s="86" t="s">
         <v>394</v>
       </c>
-      <c r="P13" s="40">
+      <c r="P13" s="87">
         <v>0.49540000000000001</v>
       </c>
-      <c r="Q13" s="40">
+      <c r="Q13" s="87">
         <f t="shared" ref="Q13" si="4">P13*N13</f>
-        <v>10.8988</v>
-      </c>
-      <c r="R13" s="78" t="s">
-        <v>427</v>
-      </c>
-      <c r="S13" s="38"/>
+        <v>8.4217999999999993</v>
+      </c>
+      <c r="R13" s="88"/>
+      <c r="S13" s="84"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="49">
+      <c r="B14" s="47">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="62" t="s">
+      <c r="C14" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="65" t="s">
+      <c r="D14" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="65" t="s">
+      <c r="E14" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="F14" s="65" t="s">
+      <c r="F14" s="77" t="s">
         <v>161</v>
       </c>
-      <c r="G14" s="65" t="s">
+      <c r="G14" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="H14" s="65" t="s">
+      <c r="H14" s="77" t="s">
         <v>258</v>
       </c>
-      <c r="I14" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J14" s="65" t="s">
+      <c r="I14" s="77" t="s">
+        <v>381</v>
+      </c>
+      <c r="J14" s="77" t="s">
         <v>294</v>
       </c>
-      <c r="K14" s="65" t="s">
+      <c r="K14" s="77" t="s">
         <v>353</v>
       </c>
-      <c r="L14" s="65">
+      <c r="L14" s="77">
         <v>1</v>
       </c>
-      <c r="M14" s="65">
+      <c r="M14" s="77">
         <f t="shared" ref="M14" si="5">L14*5</f>
         <v>5</v>
       </c>
-      <c r="N14" s="65">
+      <c r="N14" s="77">
         <v>6</v>
       </c>
-      <c r="O14" s="59" t="s">
+      <c r="O14" s="79" t="s">
         <v>394</v>
       </c>
-      <c r="P14" s="66">
+      <c r="P14" s="95">
         <v>0.91320000000000001</v>
       </c>
-      <c r="Q14" s="66">
+      <c r="Q14" s="95">
         <f t="shared" ref="Q14" si="6">P14*N14</f>
         <v>5.4792000000000005</v>
       </c>
-      <c r="R14" s="64"/>
-      <c r="S14" s="37"/>
+      <c r="R14" s="96"/>
+      <c r="S14" s="78"/>
     </row>
     <row r="15" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="48">
+      <c r="B15" s="46">
         <f>ROW(B15) - ROW($B$9)</f>
         <v>6</v>
       </c>
-      <c r="C15" s="63" t="s">
+      <c r="C15" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="77" t="s">
+      <c r="D15" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="38" t="s">
+      <c r="E15" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="F15" s="38" t="s">
+      <c r="F15" s="84" t="s">
         <v>159</v>
       </c>
-      <c r="G15" s="38" t="s">
+      <c r="G15" s="84" t="s">
         <v>202</v>
       </c>
-      <c r="H15" s="38" t="s">
+      <c r="H15" s="84" t="s">
         <v>256</v>
       </c>
-      <c r="I15" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J15" s="38" t="s">
+      <c r="I15" s="84" t="s">
+        <v>381</v>
+      </c>
+      <c r="J15" s="84" t="s">
         <v>295</v>
       </c>
-      <c r="K15" s="38" t="s">
+      <c r="K15" s="84" t="s">
         <v>354</v>
       </c>
-      <c r="L15" s="38">
+      <c r="L15" s="84">
         <v>12</v>
       </c>
-      <c r="M15" s="38">
+      <c r="M15" s="84">
         <f>L15*5</f>
         <v>60</v>
       </c>
-      <c r="N15" s="38">
+      <c r="N15" s="84">
         <v>100</v>
       </c>
-      <c r="O15" s="61" t="s">
+      <c r="O15" s="86" t="s">
         <v>394</v>
       </c>
-      <c r="P15" s="40">
+      <c r="P15" s="87">
         <v>2.8E-3</v>
       </c>
-      <c r="Q15" s="40">
+      <c r="Q15" s="87">
         <f>P15*N15</f>
         <v>0.27999999999999997</v>
       </c>
-      <c r="R15" s="38"/>
-      <c r="S15" s="38"/>
+      <c r="R15" s="84"/>
+      <c r="S15" s="84"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="49">
+      <c r="B16" s="47">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="62" t="s">
+      <c r="C16" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="65" t="s">
+      <c r="D16" s="77" t="s">
         <v>32</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="77" t="s">
         <v>97</v>
       </c>
-      <c r="F16" s="65" t="s">
+      <c r="F16" s="77" t="s">
         <v>159</v>
       </c>
-      <c r="G16" s="65" t="s">
+      <c r="G16" s="77" t="s">
         <v>203</v>
       </c>
-      <c r="H16" s="65" t="s">
+      <c r="H16" s="77" t="s">
         <v>256</v>
       </c>
-      <c r="I16" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J16" s="65" t="s">
+      <c r="I16" s="77" t="s">
+        <v>381</v>
+      </c>
+      <c r="J16" s="77" t="s">
         <v>296</v>
       </c>
-      <c r="K16" s="65" t="s">
+      <c r="K16" s="77" t="s">
         <v>355</v>
       </c>
-      <c r="L16" s="65">
+      <c r="L16" s="77">
         <v>1</v>
       </c>
-      <c r="M16" s="65">
+      <c r="M16" s="77">
         <f t="shared" ref="M16" si="7">L16*5</f>
         <v>5</v>
       </c>
-      <c r="N16" s="65">
+      <c r="N16" s="77">
         <v>100</v>
       </c>
-      <c r="O16" s="59" t="s">
+      <c r="O16" s="79" t="s">
         <v>394</v>
       </c>
-      <c r="P16" s="66">
+      <c r="P16" s="95">
         <v>4.8999999999999998E-3</v>
       </c>
-      <c r="Q16" s="66">
+      <c r="Q16" s="95">
         <f t="shared" ref="Q16" si="8">P16*N16</f>
         <v>0.49</v>
       </c>
-      <c r="R16" s="64"/>
-      <c r="S16" s="37"/>
+      <c r="R16" s="96"/>
+      <c r="S16" s="78"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="48">
+      <c r="B17" s="46">
         <f>ROW(B17) - ROW($B$9)</f>
         <v>8</v>
       </c>
-      <c r="C17" s="63" t="s">
+      <c r="C17" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="77" t="s">
+      <c r="D17" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="38" t="s">
+      <c r="E17" s="84" t="s">
         <v>98</v>
       </c>
-      <c r="F17" s="38" t="s">
+      <c r="F17" s="84" t="s">
         <v>162</v>
       </c>
-      <c r="G17" s="60" t="s">
+      <c r="G17" s="85" t="s">
         <v>204</v>
       </c>
-      <c r="H17" s="38" t="s">
+      <c r="H17" s="84" t="s">
         <v>259</v>
       </c>
-      <c r="I17" s="38" t="s">
-        <v>429</v>
-      </c>
-      <c r="J17" s="38" t="s">
-        <v>428</v>
-      </c>
-      <c r="K17" s="38" t="s">
+      <c r="I17" s="84" t="s">
+        <v>427</v>
+      </c>
+      <c r="J17" s="84" t="s">
+        <v>426</v>
+      </c>
+      <c r="K17" s="84" t="s">
         <v>356</v>
       </c>
-      <c r="L17" s="38">
+      <c r="L17" s="84">
         <v>1</v>
       </c>
-      <c r="M17" s="38">
+      <c r="M17" s="84">
         <f>L17*5</f>
         <v>5</v>
       </c>
-      <c r="N17" s="38">
+      <c r="N17" s="84">
         <v>100</v>
       </c>
-      <c r="O17" s="61" t="s">
+      <c r="O17" s="86" t="s">
         <v>394</v>
       </c>
-      <c r="P17" s="40">
+      <c r="P17" s="87">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q17" s="40">
+      <c r="Q17" s="87">
         <f>P17*N17</f>
         <v>0.13</v>
       </c>
-      <c r="R17" s="38"/>
-      <c r="S17" s="38"/>
+      <c r="R17" s="84"/>
+      <c r="S17" s="84"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="49">
+      <c r="B18" s="47">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="62" t="s">
+      <c r="C18" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="65" t="s">
+      <c r="D18" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="E18" s="65" t="s">
+      <c r="E18" s="77" t="s">
         <v>99</v>
       </c>
-      <c r="F18" s="65" t="s">
+      <c r="F18" s="77" t="s">
         <v>159</v>
       </c>
-      <c r="G18" s="65" t="s">
+      <c r="G18" s="77" t="s">
         <v>205</v>
       </c>
-      <c r="H18" s="65" t="s">
+      <c r="H18" s="77" t="s">
         <v>256</v>
       </c>
-      <c r="I18" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J18" s="65" t="s">
+      <c r="I18" s="77" t="s">
+        <v>381</v>
+      </c>
+      <c r="J18" s="77" t="s">
         <v>297</v>
       </c>
-      <c r="K18" s="65" t="s">
+      <c r="K18" s="77" t="s">
         <v>357</v>
       </c>
-      <c r="L18" s="65">
+      <c r="L18" s="77">
         <v>2</v>
       </c>
-      <c r="M18" s="65">
+      <c r="M18" s="77">
         <f t="shared" ref="M18" si="9">L18*5</f>
         <v>10</v>
       </c>
-      <c r="N18" s="65">
+      <c r="N18" s="77">
         <v>100</v>
       </c>
-      <c r="O18" s="59" t="s">
+      <c r="O18" s="79" t="s">
         <v>394</v>
       </c>
-      <c r="P18" s="66">
+      <c r="P18" s="95">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="Q18" s="66">
+      <c r="Q18" s="95">
         <f t="shared" ref="Q18" si="10">P18*N18</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="R18" s="64"/>
-      <c r="S18" s="37"/>
+      <c r="R18" s="96"/>
+      <c r="S18" s="78"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="48">
+      <c r="B19" s="46">
         <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="63" t="s">
+      <c r="C19" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="77" t="s">
+      <c r="D19" s="83" t="s">
         <v>414</v>
       </c>
-      <c r="E19" s="38" t="s">
+      <c r="E19" s="84" t="s">
         <v>100</v>
       </c>
-      <c r="F19" s="38" t="s">
+      <c r="F19" s="84" t="s">
         <v>159</v>
       </c>
-      <c r="G19" s="38" t="s">
+      <c r="G19" s="84" t="s">
         <v>206</v>
       </c>
-      <c r="H19" s="38" t="s">
+      <c r="H19" s="84" t="s">
         <v>256</v>
       </c>
-      <c r="I19" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J19" s="38" t="s">
+      <c r="I19" s="84" t="s">
+        <v>381</v>
+      </c>
+      <c r="J19" s="84" t="s">
         <v>298</v>
       </c>
-      <c r="K19" s="38" t="s">
+      <c r="K19" s="84" t="s">
         <v>358</v>
       </c>
-      <c r="L19" s="38">
+      <c r="L19" s="84">
         <v>2</v>
       </c>
-      <c r="M19" s="38">
+      <c r="M19" s="84">
         <f>L19*5</f>
         <v>10</v>
       </c>
-      <c r="N19" s="38">
+      <c r="N19" s="84">
         <v>20</v>
       </c>
-      <c r="O19" s="61" t="s">
+      <c r="O19" s="86" t="s">
         <v>394</v>
       </c>
-      <c r="P19" s="40">
+      <c r="P19" s="87">
         <v>2.3599999999999999E-2</v>
       </c>
-      <c r="Q19" s="40">
+      <c r="Q19" s="87">
         <f>P19*N19</f>
         <v>0.47199999999999998</v>
       </c>
-      <c r="R19" s="38"/>
-      <c r="S19" s="38"/>
+      <c r="R19" s="84"/>
+      <c r="S19" s="84"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="49">
+      <c r="B20" s="46">
+        <f>ROW(B20) - ROW($B$9)</f>
+        <v>11</v>
+      </c>
+      <c r="C20" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="78" t="s">
+        <v>430</v>
+      </c>
+      <c r="E20" s="78" t="s">
+        <v>431</v>
+      </c>
+      <c r="F20" s="78" t="s">
+        <v>393</v>
+      </c>
+      <c r="G20" s="78" t="s">
+        <v>432</v>
+      </c>
+      <c r="H20" s="78" t="s">
+        <v>258</v>
+      </c>
+      <c r="I20" s="78" t="s">
+        <v>381</v>
+      </c>
+      <c r="J20" s="78" t="s">
+        <v>433</v>
+      </c>
+      <c r="K20" s="78" t="s">
+        <v>434</v>
+      </c>
+      <c r="L20" s="78">
+        <v>1</v>
+      </c>
+      <c r="M20" s="78">
+        <f>L20*5</f>
+        <v>5</v>
+      </c>
+      <c r="N20" s="78">
+        <v>6</v>
+      </c>
+      <c r="O20" s="79" t="s">
+        <v>394</v>
+      </c>
+      <c r="P20" s="80">
+        <v>0.51590000000000003</v>
+      </c>
+      <c r="Q20" s="80">
+        <f>P20*N20</f>
+        <v>3.0954000000000002</v>
+      </c>
+      <c r="R20" s="78"/>
+      <c r="S20" s="81"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="47">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="C20" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="65" t="s">
+      <c r="D21" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="E20" s="65" t="s">
+      <c r="E21" s="62" t="s">
         <v>101</v>
       </c>
-      <c r="F20" s="65" t="s">
+      <c r="F21" s="62" t="s">
         <v>163</v>
       </c>
-      <c r="G20" s="65" t="s">
+      <c r="G21" s="62" t="s">
         <v>207</v>
       </c>
-      <c r="H20" s="65" t="s">
+      <c r="H21" s="62" t="s">
         <v>260</v>
       </c>
-      <c r="I20" s="65"/>
-      <c r="J20" s="65" t="s">
+      <c r="I21" s="62"/>
+      <c r="J21" s="62" t="s">
         <v>299</v>
       </c>
-      <c r="K20" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="L20" s="65">
+      <c r="K21" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="L21" s="62">
         <v>7</v>
       </c>
-      <c r="M20" s="65">
-        <f t="shared" ref="M20" si="11">L20*5</f>
+      <c r="M21" s="62">
+        <f t="shared" ref="M21" si="11">L21*5</f>
         <v>35</v>
       </c>
-      <c r="N20" s="65">
+      <c r="N21" s="62">
         <v>40</v>
       </c>
-      <c r="O20" s="59" t="s">
+      <c r="O21" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="P20" s="66">
+      <c r="P21" s="63">
         <v>6.3700000000000007E-2</v>
       </c>
-      <c r="Q20" s="66">
-        <f t="shared" ref="Q20" si="12">P20*N20</f>
+      <c r="Q21" s="63">
+        <f t="shared" ref="Q21" si="12">P21*N21</f>
         <v>2.548</v>
       </c>
-      <c r="R20" s="64"/>
-      <c r="S20" s="37"/>
-    </row>
-    <row r="21" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="48">
-        <f>ROW(B21) - ROW($B$9)</f>
-        <v>12</v>
-      </c>
-      <c r="C21" s="63" t="s">
+      <c r="R21" s="61"/>
+      <c r="S21" s="37"/>
+    </row>
+    <row r="22" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="46">
+        <f>ROW(B22) - ROW($B$9)</f>
+        <v>13</v>
+      </c>
+      <c r="C22" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="77" t="s">
+      <c r="D22" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="E21" s="38" t="s">
+      <c r="E22" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="F21" s="38" t="s">
+      <c r="F22" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="G21" s="38" t="s">
+      <c r="G22" s="38" t="s">
         <v>208</v>
       </c>
-      <c r="H21" s="38" t="s">
+      <c r="H22" s="38" t="s">
         <v>261</v>
       </c>
-      <c r="I21" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J21" s="38" t="s">
+      <c r="I22" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J22" s="38" t="s">
         <v>300</v>
       </c>
-      <c r="K21" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="L21" s="38">
+      <c r="K22" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L22" s="38">
         <v>2</v>
       </c>
-      <c r="M21" s="38">
-        <f>L21*5</f>
+      <c r="M22" s="38">
+        <f>L22*5</f>
         <v>10</v>
       </c>
-      <c r="N21" s="38">
+      <c r="N22" s="38">
         <v>15</v>
       </c>
-      <c r="O21" s="61" t="s">
+      <c r="O22" s="58" t="s">
         <v>394</v>
       </c>
-      <c r="P21" s="40">
+      <c r="P22" s="39">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="Q21" s="40">
-        <f>P21*N21</f>
+      <c r="Q22" s="39">
+        <f>P22*N22</f>
         <v>1.296</v>
       </c>
-      <c r="R21" s="38"/>
-      <c r="S21" s="38"/>
-    </row>
-    <row r="22" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="49">
+      <c r="R22" s="38"/>
+      <c r="S22" s="38"/>
+    </row>
+    <row r="23" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="47">
         <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="C22" s="62" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="65" t="s">
+      <c r="D23" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="E22" s="65" t="s">
+      <c r="E23" s="62" t="s">
         <v>103</v>
       </c>
-      <c r="F22" s="65" t="s">
+      <c r="F23" s="62" t="s">
         <v>165</v>
       </c>
-      <c r="G22" s="65" t="s">
+      <c r="G23" s="62" t="s">
         <v>209</v>
       </c>
-      <c r="H22" s="65" t="s">
+      <c r="H23" s="62" t="s">
         <v>262</v>
       </c>
-      <c r="I22" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J22" s="65" t="s">
+      <c r="I23" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J23" s="62" t="s">
         <v>301</v>
       </c>
-      <c r="K22" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="L22" s="65">
+      <c r="K23" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="L23" s="62">
         <v>1</v>
       </c>
-      <c r="M22" s="65">
-        <f t="shared" ref="M22" si="13">L22*5</f>
+      <c r="M23" s="62">
+        <f t="shared" ref="M23" si="13">L23*5</f>
         <v>5</v>
       </c>
-      <c r="N22" s="65">
+      <c r="N23" s="62">
         <v>20</v>
       </c>
-      <c r="O22" s="59" t="s">
+      <c r="O23" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="P22" s="66">
+      <c r="P23" s="63">
         <v>3.32E-2</v>
       </c>
-      <c r="Q22" s="66">
-        <f t="shared" ref="Q22" si="14">P22*N22</f>
+      <c r="Q23" s="63">
+        <f t="shared" ref="Q23" si="14">P23*N23</f>
         <v>0.66400000000000003</v>
       </c>
-      <c r="R22" s="64"/>
-      <c r="S22" s="37"/>
-    </row>
-    <row r="23" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="48">
-        <f>ROW(B23) - ROW($B$9)</f>
-        <v>14</v>
-      </c>
-      <c r="C23" s="63" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="77" t="s">
-        <v>38</v>
-      </c>
-      <c r="E23" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="F23" s="38" t="s">
-        <v>403</v>
-      </c>
-      <c r="G23" s="38" t="s">
-        <v>210</v>
-      </c>
-      <c r="H23" s="38" t="s">
-        <v>263</v>
-      </c>
-      <c r="I23" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J23" s="38" t="s">
-        <v>404</v>
-      </c>
-      <c r="K23" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="L23" s="38">
-        <v>1</v>
-      </c>
-      <c r="M23" s="38">
-        <f>L23*5</f>
-        <v>5</v>
-      </c>
-      <c r="N23" s="38">
-        <v>20</v>
-      </c>
-      <c r="O23" s="61" t="s">
-        <v>394</v>
-      </c>
-      <c r="P23" s="40">
-        <v>3.6200000000000003E-2</v>
-      </c>
-      <c r="Q23" s="40">
-        <f>P23*N23</f>
-        <v>0.72400000000000009</v>
-      </c>
-      <c r="R23" s="38"/>
-      <c r="S23" s="38"/>
+      <c r="R23" s="61"/>
+      <c r="S23" s="37"/>
     </row>
     <row r="24" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="49">
+      <c r="B24" s="46">
+        <f>ROW(B24) - ROW($B$9)</f>
+        <v>15</v>
+      </c>
+      <c r="C24" s="60" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="64" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="38" t="s">
+        <v>402</v>
+      </c>
+      <c r="F24" s="38" t="s">
+        <v>403</v>
+      </c>
+      <c r="G24" s="38" t="s">
+        <v>210</v>
+      </c>
+      <c r="H24" s="38" t="s">
+        <v>263</v>
+      </c>
+      <c r="I24" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J24" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="K24" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L24" s="38">
+        <v>1</v>
+      </c>
+      <c r="M24" s="38">
+        <f>L24*5</f>
+        <v>5</v>
+      </c>
+      <c r="N24" s="38">
+        <v>20</v>
+      </c>
+      <c r="O24" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="P24" s="39">
+        <v>3.6200000000000003E-2</v>
+      </c>
+      <c r="Q24" s="39">
+        <f>P24*N24</f>
+        <v>0.72400000000000009</v>
+      </c>
+      <c r="R24" s="38"/>
+      <c r="S24" s="38"/>
+    </row>
+    <row r="25" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="47">
         <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C25" s="59" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="62" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="F25" s="62" t="s">
+        <v>166</v>
+      </c>
+      <c r="G25" s="62" t="s">
+        <v>211</v>
+      </c>
+      <c r="H25" s="62" t="s">
+        <v>264</v>
+      </c>
+      <c r="I25" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J25" s="62" t="s">
+        <v>302</v>
+      </c>
+      <c r="K25" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="L25" s="62">
+        <v>8</v>
+      </c>
+      <c r="M25" s="62">
+        <f t="shared" ref="M25" si="15">L25*5</f>
+        <v>40</v>
+      </c>
+      <c r="N25" s="62">
+        <v>60</v>
+      </c>
+      <c r="O25" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="P25" s="63">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="Q25" s="63">
+        <f t="shared" ref="Q25" si="16">P25*N25</f>
+        <v>1.2240000000000002</v>
+      </c>
+      <c r="R25" s="61"/>
+      <c r="S25" s="37"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="46">
+        <f>ROW(B26) - ROW($B$9)</f>
+        <v>17</v>
+      </c>
+      <c r="C26" s="60" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="F26" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="G26" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="H26" s="38" t="s">
+        <v>265</v>
+      </c>
+      <c r="I26" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J26" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="K26" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L26" s="38">
+        <v>1</v>
+      </c>
+      <c r="M26" s="38">
+        <f>L26*5</f>
+        <v>5</v>
+      </c>
+      <c r="N26" s="38">
+        <v>10</v>
+      </c>
+      <c r="O26" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="P26" s="39">
+        <v>0.104</v>
+      </c>
+      <c r="Q26" s="39">
+        <f>P26*N26</f>
+        <v>1.04</v>
+      </c>
+      <c r="R26" s="38"/>
+      <c r="S26" s="38"/>
+    </row>
+    <row r="27" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="47">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C27" s="59" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="62" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" s="62" t="s">
+        <v>106</v>
+      </c>
+      <c r="F27" s="62" t="s">
+        <v>168</v>
+      </c>
+      <c r="G27" s="62" t="s">
+        <v>213</v>
+      </c>
+      <c r="H27" s="62" t="s">
+        <v>266</v>
+      </c>
+      <c r="I27" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J27" s="62" t="s">
+        <v>304</v>
+      </c>
+      <c r="K27" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="L27" s="62">
+        <v>3</v>
+      </c>
+      <c r="M27" s="62">
+        <f t="shared" ref="M27" si="17">L27*5</f>
         <v>15</v>
       </c>
-      <c r="C24" s="62" t="s">
+      <c r="N27" s="62">
+        <v>20</v>
+      </c>
+      <c r="O27" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="P27" s="63">
+        <v>3.1699999999999999E-2</v>
+      </c>
+      <c r="Q27" s="63">
+        <f t="shared" ref="Q27" si="18">P27*N27</f>
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="R27" s="61"/>
+      <c r="S27" s="37"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="46">
+        <f>ROW(B28) - ROW($B$9)</f>
+        <v>19</v>
+      </c>
+      <c r="C28" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="64" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="F28" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="G28" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="H28" s="38" t="s">
+        <v>267</v>
+      </c>
+      <c r="I28" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J28" s="38" t="s">
+        <v>305</v>
+      </c>
+      <c r="K28" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L28" s="38">
+        <v>1</v>
+      </c>
+      <c r="M28" s="38">
+        <f>L28*5</f>
+        <v>5</v>
+      </c>
+      <c r="N28" s="38">
         <v>10</v>
       </c>
-      <c r="D24" s="65" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="65" t="s">
-        <v>104</v>
-      </c>
-      <c r="F24" s="65" t="s">
-        <v>166</v>
-      </c>
-      <c r="G24" s="65" t="s">
-        <v>211</v>
-      </c>
-      <c r="H24" s="65" t="s">
-        <v>264</v>
-      </c>
-      <c r="I24" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J24" s="65" t="s">
-        <v>302</v>
-      </c>
-      <c r="K24" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="L24" s="65">
+      <c r="O28" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="P28" s="39">
+        <v>3.5400000000000001E-2</v>
+      </c>
+      <c r="Q28" s="39">
+        <f>P28*N28</f>
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="R28" s="38"/>
+      <c r="S28" s="38"/>
+    </row>
+    <row r="29" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="47">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C29" s="59" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="62" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="62" t="s">
+        <v>108</v>
+      </c>
+      <c r="F29" s="62" t="s">
+        <v>168</v>
+      </c>
+      <c r="G29" s="62" t="s">
+        <v>215</v>
+      </c>
+      <c r="H29" s="62" t="s">
+        <v>261</v>
+      </c>
+      <c r="I29" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J29" s="62" t="s">
+        <v>306</v>
+      </c>
+      <c r="K29" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="L29" s="62">
+        <v>5</v>
+      </c>
+      <c r="M29" s="62">
+        <f t="shared" ref="M29" si="19">L29*5</f>
+        <v>25</v>
+      </c>
+      <c r="N29" s="62">
+        <v>50</v>
+      </c>
+      <c r="O29" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="P29" s="63">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="Q29" s="63">
+        <f t="shared" ref="Q29" si="20">P29*N29</f>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="R29" s="61"/>
+      <c r="S29" s="37"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="46">
+        <f>ROW(B30) - ROW($B$9)</f>
+        <v>21</v>
+      </c>
+      <c r="C30" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F30" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="G30" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="H30" s="38" t="s">
+        <v>268</v>
+      </c>
+      <c r="I30" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J30" s="38" t="s">
+        <v>307</v>
+      </c>
+      <c r="K30" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L30" s="38">
+        <v>1</v>
+      </c>
+      <c r="M30" s="38">
+        <f>L30*5</f>
+        <v>5</v>
+      </c>
+      <c r="N30" s="38">
+        <v>6</v>
+      </c>
+      <c r="O30" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="P30" s="39">
+        <v>0.2319</v>
+      </c>
+      <c r="Q30" s="39">
+        <f>P30*N30</f>
+        <v>1.3914</v>
+      </c>
+      <c r="R30" s="38"/>
+      <c r="S30" s="38"/>
+    </row>
+    <row r="31" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="47">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C31" s="59" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="62" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" s="62" t="s">
+        <v>171</v>
+      </c>
+      <c r="G31" s="62" t="s">
+        <v>217</v>
+      </c>
+      <c r="H31" s="62" t="s">
+        <v>269</v>
+      </c>
+      <c r="I31" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J31" s="62" t="s">
+        <v>399</v>
+      </c>
+      <c r="K31" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="L31" s="62">
+        <v>2</v>
+      </c>
+      <c r="M31" s="62">
+        <f t="shared" ref="M31" si="21">L31*5</f>
+        <v>10</v>
+      </c>
+      <c r="N31" s="62">
+        <v>20</v>
+      </c>
+      <c r="O31" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="P31" s="63">
+        <v>4.5900000000000003E-2</v>
+      </c>
+      <c r="Q31" s="63">
+        <f t="shared" ref="Q31" si="22">P31*N31</f>
+        <v>0.91800000000000004</v>
+      </c>
+      <c r="R31" s="61"/>
+      <c r="S31" s="37"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="46">
+        <f>ROW(B32) - ROW($B$9)</f>
+        <v>23</v>
+      </c>
+      <c r="C32" s="60" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="64" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="F32" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="G32" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="H32" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="I32" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J32" s="38" t="s">
+        <v>308</v>
+      </c>
+      <c r="K32" s="38" t="s">
+        <v>359</v>
+      </c>
+      <c r="L32" s="38">
+        <v>1</v>
+      </c>
+      <c r="M32" s="38">
+        <f>L32*5</f>
+        <v>5</v>
+      </c>
+      <c r="N32" s="38">
+        <v>10</v>
+      </c>
+      <c r="O32" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="P32" s="39">
+        <v>0.1193</v>
+      </c>
+      <c r="Q32" s="39">
+        <f>P32*N32</f>
+        <v>1.1930000000000001</v>
+      </c>
+      <c r="R32" s="38"/>
+      <c r="S32" s="38"/>
+    </row>
+    <row r="33" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="47">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C33" s="59" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="62" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="F33" s="62" t="s">
+        <v>173</v>
+      </c>
+      <c r="G33" s="62" t="s">
+        <v>219</v>
+      </c>
+      <c r="H33" s="62" t="s">
+        <v>257</v>
+      </c>
+      <c r="I33" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J33" s="62" t="s">
+        <v>309</v>
+      </c>
+      <c r="K33" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="L33" s="62">
         <v>8</v>
       </c>
-      <c r="M24" s="65">
-        <f t="shared" ref="M24" si="15">L24*5</f>
+      <c r="M33" s="62">
+        <f t="shared" ref="M33" si="23">L33*5</f>
         <v>40</v>
       </c>
-      <c r="N24" s="65">
-        <v>60</v>
-      </c>
-      <c r="O24" s="59" t="s">
+      <c r="N33" s="62">
+        <v>50</v>
+      </c>
+      <c r="O33" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="P24" s="66">
-        <v>2.0400000000000001E-2</v>
-      </c>
-      <c r="Q24" s="66">
-        <f t="shared" ref="Q24" si="16">P24*N24</f>
-        <v>1.2240000000000002</v>
-      </c>
-      <c r="R24" s="64"/>
-      <c r="S24" s="37"/>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="48">
-        <f>ROW(B25) - ROW($B$9)</f>
-        <v>16</v>
-      </c>
-      <c r="C25" s="63" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="77" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" s="38" t="s">
-        <v>105</v>
-      </c>
-      <c r="F25" s="38" t="s">
-        <v>167</v>
-      </c>
-      <c r="G25" s="38" t="s">
-        <v>212</v>
-      </c>
-      <c r="H25" s="38" t="s">
-        <v>265</v>
-      </c>
-      <c r="I25" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J25" s="38" t="s">
-        <v>303</v>
-      </c>
-      <c r="K25" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="L25" s="38">
-        <v>1</v>
-      </c>
-      <c r="M25" s="38">
-        <f>L25*5</f>
-        <v>5</v>
-      </c>
-      <c r="N25" s="38">
-        <v>10</v>
-      </c>
-      <c r="O25" s="61" t="s">
-        <v>394</v>
-      </c>
-      <c r="P25" s="40">
-        <v>0.104</v>
-      </c>
-      <c r="Q25" s="40">
-        <f>P25*N25</f>
-        <v>1.04</v>
-      </c>
-      <c r="R25" s="38"/>
-      <c r="S25" s="38"/>
-    </row>
-    <row r="26" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="49">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C26" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="65" t="s">
-        <v>41</v>
-      </c>
-      <c r="E26" s="65" t="s">
-        <v>106</v>
-      </c>
-      <c r="F26" s="65" t="s">
-        <v>168</v>
-      </c>
-      <c r="G26" s="65" t="s">
-        <v>213</v>
-      </c>
-      <c r="H26" s="65" t="s">
-        <v>266</v>
-      </c>
-      <c r="I26" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J26" s="65" t="s">
-        <v>304</v>
-      </c>
-      <c r="K26" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="L26" s="65">
-        <v>3</v>
-      </c>
-      <c r="M26" s="65">
-        <f t="shared" ref="M26" si="17">L26*5</f>
-        <v>15</v>
-      </c>
-      <c r="N26" s="65">
-        <v>20</v>
-      </c>
-      <c r="O26" s="59" t="s">
-        <v>394</v>
-      </c>
-      <c r="P26" s="66">
-        <v>3.1699999999999999E-2</v>
-      </c>
-      <c r="Q26" s="66">
-        <f t="shared" ref="Q26" si="18">P26*N26</f>
-        <v>0.63400000000000001</v>
-      </c>
-      <c r="R26" s="64"/>
-      <c r="S26" s="37"/>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="48">
-        <f>ROW(B27) - ROW($B$9)</f>
-        <v>18</v>
-      </c>
-      <c r="C27" s="63" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="77" t="s">
-        <v>42</v>
-      </c>
-      <c r="E27" s="38" t="s">
-        <v>107</v>
-      </c>
-      <c r="F27" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="G27" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="H27" s="38" t="s">
-        <v>267</v>
-      </c>
-      <c r="I27" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J27" s="38" t="s">
-        <v>305</v>
-      </c>
-      <c r="K27" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="L27" s="38">
-        <v>1</v>
-      </c>
-      <c r="M27" s="38">
-        <f>L27*5</f>
-        <v>5</v>
-      </c>
-      <c r="N27" s="38">
-        <v>10</v>
-      </c>
-      <c r="O27" s="61" t="s">
-        <v>394</v>
-      </c>
-      <c r="P27" s="40">
-        <v>3.5400000000000001E-2</v>
-      </c>
-      <c r="Q27" s="40">
-        <f>P27*N27</f>
-        <v>0.35399999999999998</v>
-      </c>
-      <c r="R27" s="38"/>
-      <c r="S27" s="38"/>
-    </row>
-    <row r="28" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
-      <c r="B28" s="49">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="C28" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="65" t="s">
-        <v>43</v>
-      </c>
-      <c r="E28" s="65" t="s">
-        <v>108</v>
-      </c>
-      <c r="F28" s="65" t="s">
-        <v>168</v>
-      </c>
-      <c r="G28" s="65" t="s">
-        <v>215</v>
-      </c>
-      <c r="H28" s="65" t="s">
-        <v>261</v>
-      </c>
-      <c r="I28" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J28" s="65" t="s">
-        <v>306</v>
-      </c>
-      <c r="K28" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="L28" s="65">
-        <v>5</v>
-      </c>
-      <c r="M28" s="65">
-        <f t="shared" ref="M28" si="19">L28*5</f>
-        <v>25</v>
-      </c>
-      <c r="N28" s="65">
-        <v>50</v>
-      </c>
-      <c r="O28" s="59" t="s">
-        <v>394</v>
-      </c>
-      <c r="P28" s="66">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="Q28" s="66">
-        <f t="shared" ref="Q28" si="20">P28*N28</f>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="R28" s="64"/>
-      <c r="S28" s="37"/>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-      <c r="B29" s="48">
-        <f>ROW(B29) - ROW($B$9)</f>
-        <v>20</v>
-      </c>
-      <c r="C29" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="D29" s="77" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="F29" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="G29" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="H29" s="38" t="s">
-        <v>268</v>
-      </c>
-      <c r="I29" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J29" s="38" t="s">
-        <v>307</v>
-      </c>
-      <c r="K29" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="L29" s="38">
-        <v>1</v>
-      </c>
-      <c r="M29" s="38">
-        <f>L29*5</f>
-        <v>5</v>
-      </c>
-      <c r="N29" s="38">
-        <v>6</v>
-      </c>
-      <c r="O29" s="61" t="s">
-        <v>394</v>
-      </c>
-      <c r="P29" s="40">
-        <v>0.2319</v>
-      </c>
-      <c r="Q29" s="40">
-        <f>P29*N29</f>
-        <v>1.3914</v>
-      </c>
-      <c r="R29" s="38"/>
-      <c r="S29" s="38"/>
-    </row>
-    <row r="30" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
-      <c r="B30" s="49">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="C30" s="62" t="s">
-        <v>12</v>
-      </c>
-      <c r="D30" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="E30" s="65" t="s">
-        <v>110</v>
-      </c>
-      <c r="F30" s="65" t="s">
-        <v>171</v>
-      </c>
-      <c r="G30" s="65" t="s">
-        <v>217</v>
-      </c>
-      <c r="H30" s="65" t="s">
-        <v>269</v>
-      </c>
-      <c r="I30" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J30" s="65" t="s">
-        <v>399</v>
-      </c>
-      <c r="K30" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="L30" s="65">
-        <v>2</v>
-      </c>
-      <c r="M30" s="65">
-        <f t="shared" ref="M30" si="21">L30*5</f>
-        <v>10</v>
-      </c>
-      <c r="N30" s="65">
-        <v>20</v>
-      </c>
-      <c r="O30" s="59" t="s">
-        <v>394</v>
-      </c>
-      <c r="P30" s="66">
-        <v>4.5900000000000003E-2</v>
-      </c>
-      <c r="Q30" s="66">
-        <f t="shared" ref="Q30" si="22">P30*N30</f>
-        <v>0.91800000000000004</v>
-      </c>
-      <c r="R30" s="64"/>
-      <c r="S30" s="37"/>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="B31" s="48">
-        <f>ROW(B31) - ROW($B$9)</f>
-        <v>22</v>
-      </c>
-      <c r="C31" s="63" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" s="77" t="s">
-        <v>46</v>
-      </c>
-      <c r="E31" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="F31" s="38" t="s">
-        <v>172</v>
-      </c>
-      <c r="G31" s="38" t="s">
-        <v>218</v>
-      </c>
-      <c r="H31" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="I31" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J31" s="38" t="s">
-        <v>308</v>
-      </c>
-      <c r="K31" s="38" t="s">
-        <v>359</v>
-      </c>
-      <c r="L31" s="38">
-        <v>1</v>
-      </c>
-      <c r="M31" s="38">
-        <f>L31*5</f>
-        <v>5</v>
-      </c>
-      <c r="N31" s="38">
-        <v>10</v>
-      </c>
-      <c r="O31" s="61" t="s">
-        <v>394</v>
-      </c>
-      <c r="P31" s="40">
-        <v>0.1193</v>
-      </c>
-      <c r="Q31" s="40">
-        <f>P31*N31</f>
-        <v>1.1930000000000001</v>
-      </c>
-      <c r="R31" s="38"/>
-      <c r="S31" s="38"/>
-    </row>
-    <row r="32" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="49">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="C32" s="62" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="65" t="s">
-        <v>47</v>
-      </c>
-      <c r="E32" s="65" t="s">
-        <v>112</v>
-      </c>
-      <c r="F32" s="65" t="s">
-        <v>173</v>
-      </c>
-      <c r="G32" s="65" t="s">
-        <v>219</v>
-      </c>
-      <c r="H32" s="65" t="s">
-        <v>257</v>
-      </c>
-      <c r="I32" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J32" s="65" t="s">
-        <v>309</v>
-      </c>
-      <c r="K32" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="L32" s="65">
-        <v>8</v>
-      </c>
-      <c r="M32" s="65">
-        <f t="shared" ref="M32" si="23">L32*5</f>
-        <v>40</v>
-      </c>
-      <c r="N32" s="65">
-        <v>50</v>
-      </c>
-      <c r="O32" s="59" t="s">
-        <v>394</v>
-      </c>
-      <c r="P32" s="66">
+      <c r="P33" s="63">
         <v>4.5600000000000002E-2</v>
       </c>
-      <c r="Q32" s="66">
-        <f t="shared" ref="Q32" si="24">P32*N32</f>
+      <c r="Q33" s="63">
+        <f t="shared" ref="Q33" si="24">P33*N33</f>
         <v>2.2800000000000002</v>
       </c>
-      <c r="R32" s="64"/>
-      <c r="S32" s="37"/>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="B33" s="48">
-        <f>ROW(B33) - ROW($B$9)</f>
-        <v>24</v>
-      </c>
-      <c r="C33" s="63" t="s">
-        <v>14</v>
-      </c>
-      <c r="D33" s="77" t="s">
-        <v>421</v>
-      </c>
-      <c r="E33" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="F33" s="38" t="s">
-        <v>393</v>
-      </c>
-      <c r="G33" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="H33" s="38" t="s">
-        <v>270</v>
-      </c>
-      <c r="I33" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J33" s="38" t="s">
-        <v>310</v>
-      </c>
-      <c r="K33" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="L33" s="38">
-        <v>2</v>
-      </c>
-      <c r="M33" s="38">
-        <f>L33*5</f>
-        <v>10</v>
-      </c>
-      <c r="N33" s="38">
-        <v>12</v>
-      </c>
-      <c r="O33" s="61" t="s">
-        <v>394</v>
-      </c>
-      <c r="P33" s="40">
-        <v>0.1734</v>
-      </c>
-      <c r="Q33" s="40">
-        <f>P33*N33</f>
-        <v>2.0808</v>
-      </c>
-      <c r="R33" s="38"/>
-      <c r="S33" s="38"/>
+      <c r="R33" s="61"/>
+      <c r="S33" s="37"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="49">
-        <f t="shared" ref="B34" si="25">ROW(B34) - ROW($B$9)</f>
+      <c r="B34" s="46">
+        <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="62" t="s">
+      <c r="C34" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="D34" s="65" t="s">
-        <v>416</v>
-      </c>
-      <c r="E34" s="65" t="s">
-        <v>417</v>
-      </c>
-      <c r="F34" s="65">
-        <v>1051330011</v>
-      </c>
-      <c r="G34" s="65" t="s">
-        <v>418</v>
-      </c>
-      <c r="H34" s="65" t="s">
-        <v>419</v>
-      </c>
-      <c r="I34" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J34" s="65" t="s">
-        <v>420</v>
-      </c>
-      <c r="K34" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="L34" s="65">
-        <v>1</v>
-      </c>
-      <c r="M34" s="65">
-        <f t="shared" ref="M34" si="26">L34*5</f>
-        <v>5</v>
-      </c>
-      <c r="N34" s="65">
-        <v>6</v>
-      </c>
-      <c r="O34" s="59" t="s">
+      <c r="D34" s="64" t="s">
+        <v>421</v>
+      </c>
+      <c r="E34" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="F34" s="38" t="s">
+        <v>393</v>
+      </c>
+      <c r="G34" s="38" t="s">
+        <v>220</v>
+      </c>
+      <c r="H34" s="38" t="s">
+        <v>270</v>
+      </c>
+      <c r="I34" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J34" s="38" t="s">
+        <v>310</v>
+      </c>
+      <c r="K34" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L34" s="38">
+        <v>2</v>
+      </c>
+      <c r="M34" s="38">
+        <f>L34*5</f>
+        <v>10</v>
+      </c>
+      <c r="N34" s="38">
+        <v>12</v>
+      </c>
+      <c r="O34" s="58" t="s">
         <v>394</v>
       </c>
-      <c r="P34" s="66">
-        <v>0.41049999999999998</v>
-      </c>
-      <c r="Q34" s="66">
-        <f t="shared" ref="Q34" si="27">P34*N34</f>
-        <v>2.4630000000000001</v>
-      </c>
-      <c r="R34" s="64"/>
-      <c r="S34" s="37"/>
+      <c r="P34" s="39">
+        <v>0.1734</v>
+      </c>
+      <c r="Q34" s="39">
+        <f>P34*N34</f>
+        <v>2.0808</v>
+      </c>
+      <c r="R34" s="38"/>
+      <c r="S34" s="38"/>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
-      <c r="B35" s="49">
-        <f t="shared" si="0"/>
+      <c r="B35" s="47">
+        <f t="shared" ref="B35" si="25">ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="63" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" s="77" t="s">
-        <v>48</v>
-      </c>
-      <c r="E35" s="38" t="s">
-        <v>422</v>
-      </c>
-      <c r="F35" s="38" t="s">
-        <v>393</v>
-      </c>
-      <c r="G35" s="38" t="s">
-        <v>423</v>
-      </c>
-      <c r="H35" s="38" t="s">
-        <v>424</v>
-      </c>
-      <c r="I35" s="38"/>
-      <c r="J35" s="38" t="s">
-        <v>425</v>
-      </c>
-      <c r="K35" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="L35" s="38">
+      <c r="C35" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" s="62" t="s">
+        <v>416</v>
+      </c>
+      <c r="E35" s="62" t="s">
+        <v>417</v>
+      </c>
+      <c r="F35" s="62">
+        <v>1051330011</v>
+      </c>
+      <c r="G35" s="62" t="s">
+        <v>418</v>
+      </c>
+      <c r="H35" s="62" t="s">
+        <v>419</v>
+      </c>
+      <c r="I35" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J35" s="62" t="s">
+        <v>420</v>
+      </c>
+      <c r="K35" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="L35" s="62">
+        <v>1</v>
+      </c>
+      <c r="M35" s="62">
+        <f t="shared" ref="M35" si="26">L35*5</f>
+        <v>5</v>
+      </c>
+      <c r="N35" s="62">
         <v>6</v>
       </c>
-      <c r="M35" s="38">
-        <f t="shared" ref="M35" si="28">L35*5</f>
-        <v>30</v>
-      </c>
-      <c r="N35" s="38">
-        <v>32</v>
-      </c>
-      <c r="O35" s="61" t="s">
+      <c r="O35" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="P35" s="40">
-        <v>0.55530000000000002</v>
-      </c>
-      <c r="Q35" s="40">
-        <f t="shared" ref="Q35" si="29">P35*N35</f>
-        <v>17.769600000000001</v>
-      </c>
-      <c r="R35" s="78" t="s">
-        <v>430</v>
-      </c>
-      <c r="S35" s="38"/>
+      <c r="P35" s="63">
+        <v>0.41049999999999998</v>
+      </c>
+      <c r="Q35" s="63">
+        <f t="shared" ref="Q35" si="27">P35*N35</f>
+        <v>2.4630000000000001</v>
+      </c>
+      <c r="R35" s="61"/>
+      <c r="S35" s="37"/>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="48">
-        <f>ROW(B36) - ROW($B$9)</f>
+      <c r="B36" s="47">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="62" t="s">
+      <c r="C36" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" s="38" t="s">
+        <v>422</v>
+      </c>
+      <c r="F36" s="38" t="s">
+        <v>393</v>
+      </c>
+      <c r="G36" s="38" t="s">
+        <v>423</v>
+      </c>
+      <c r="H36" s="38" t="s">
+        <v>424</v>
+      </c>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38" t="s">
+        <v>425</v>
+      </c>
+      <c r="K36" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L36" s="38">
+        <v>6</v>
+      </c>
+      <c r="M36" s="38">
+        <f t="shared" ref="M36" si="28">L36*5</f>
+        <v>30</v>
+      </c>
+      <c r="N36" s="38">
+        <v>32</v>
+      </c>
+      <c r="O36" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="P36" s="39">
+        <v>0.55530000000000002</v>
+      </c>
+      <c r="Q36" s="39">
+        <f t="shared" ref="Q36" si="29">P36*N36</f>
+        <v>17.769600000000001</v>
+      </c>
+      <c r="R36" s="65" t="s">
+        <v>428</v>
+      </c>
+      <c r="S36" s="38"/>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="46">
+        <f>ROW(B37) - ROW($B$9)</f>
+        <v>28</v>
+      </c>
+      <c r="C37" s="59" t="s">
         <v>396</v>
       </c>
-      <c r="D36" s="65" t="s">
+      <c r="D37" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="E36" s="65" t="s">
+      <c r="E37" s="62" t="s">
         <v>114</v>
       </c>
-      <c r="F36" s="65" t="s">
+      <c r="F37" s="62" t="s">
         <v>393</v>
       </c>
-      <c r="G36" s="65" t="s">
+      <c r="G37" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="H36" s="65" t="s">
+      <c r="H37" s="62" t="s">
         <v>271</v>
       </c>
-      <c r="I36" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J36" s="65" t="s">
+      <c r="I37" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J37" s="62" t="s">
         <v>311</v>
       </c>
-      <c r="K36" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="L36" s="65">
+      <c r="K37" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="L37" s="62">
         <v>2</v>
       </c>
-      <c r="M36" s="65">
-        <f>L36*5</f>
+      <c r="M37" s="62">
+        <f>L37*5</f>
         <v>10</v>
       </c>
-      <c r="N36" s="65">
+      <c r="N37" s="62">
         <v>15</v>
       </c>
-      <c r="O36" s="59" t="s">
+      <c r="O37" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="P36" s="66">
+      <c r="P37" s="63">
         <v>8.9399999999999993E-2</v>
       </c>
-      <c r="Q36" s="66">
-        <f>P36*N36</f>
+      <c r="Q37" s="63">
+        <f>P37*N37</f>
         <v>1.341</v>
       </c>
-      <c r="R36" s="64"/>
-      <c r="S36" s="37"/>
-    </row>
-    <row r="37" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
-      <c r="B37" s="49">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="C37" s="63" t="s">
-        <v>16</v>
-      </c>
-      <c r="D37" s="77" t="s">
-        <v>50</v>
-      </c>
-      <c r="E37" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="F37" s="38" t="s">
-        <v>393</v>
-      </c>
-      <c r="G37" s="38" t="s">
-        <v>174</v>
-      </c>
-      <c r="H37" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="I37" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J37" s="38" t="s">
-        <v>312</v>
-      </c>
-      <c r="K37" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="L37" s="38">
-        <v>1</v>
-      </c>
-      <c r="M37" s="38">
-        <f t="shared" ref="M37" si="30">L37*5</f>
-        <v>5</v>
-      </c>
-      <c r="N37" s="38">
-        <v>6</v>
-      </c>
-      <c r="O37" s="61" t="s">
-        <v>394</v>
-      </c>
-      <c r="P37" s="40">
-        <v>0.66820000000000002</v>
-      </c>
-      <c r="Q37" s="40">
-        <f t="shared" ref="Q37" si="31">P37*N37</f>
-        <v>4.0091999999999999</v>
-      </c>
-      <c r="R37" s="38"/>
-      <c r="S37" s="38"/>
+      <c r="R37" s="61"/>
+      <c r="S37" s="37"/>
     </row>
     <row r="38" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="48">
-        <f>ROW(B38) - ROW($B$9)</f>
+      <c r="B38" s="47">
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="62" t="s">
-        <v>17</v>
-      </c>
-      <c r="D38" s="65" t="s">
-        <v>51</v>
-      </c>
-      <c r="E38" s="65" t="s">
-        <v>116</v>
-      </c>
-      <c r="F38" s="65" t="s">
+      <c r="C38" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" s="64" t="s">
+        <v>50</v>
+      </c>
+      <c r="E38" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="F38" s="38" t="s">
         <v>393</v>
       </c>
-      <c r="G38" s="65" t="s">
-        <v>175</v>
-      </c>
-      <c r="H38" s="65" t="s">
-        <v>273</v>
-      </c>
-      <c r="I38" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J38" s="65" t="s">
-        <v>313</v>
-      </c>
-      <c r="K38" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="L38" s="65">
+      <c r="G38" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="H38" s="38" t="s">
+        <v>272</v>
+      </c>
+      <c r="I38" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J38" s="38" t="s">
+        <v>312</v>
+      </c>
+      <c r="K38" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L38" s="38">
         <v>1</v>
       </c>
-      <c r="M38" s="65">
-        <f>L38*5</f>
+      <c r="M38" s="38">
+        <f t="shared" ref="M38" si="30">L38*5</f>
         <v>5</v>
       </c>
-      <c r="N38" s="65">
-        <v>10</v>
-      </c>
-      <c r="O38" s="59" t="s">
+      <c r="N38" s="38">
+        <v>6</v>
+      </c>
+      <c r="O38" s="58" t="s">
         <v>394</v>
       </c>
-      <c r="P38" s="66">
-        <v>9.3600000000000003E-2</v>
-      </c>
-      <c r="Q38" s="66">
-        <f>P38*N38</f>
-        <v>0.93600000000000005</v>
-      </c>
-      <c r="R38" s="64"/>
-      <c r="S38" s="37"/>
+      <c r="P38" s="39">
+        <v>0.66820000000000002</v>
+      </c>
+      <c r="Q38" s="39">
+        <f t="shared" ref="Q38" si="31">P38*N38</f>
+        <v>4.0091999999999999</v>
+      </c>
+      <c r="R38" s="38"/>
+      <c r="S38" s="38"/>
     </row>
     <row r="39" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="B39" s="49">
+      <c r="B39" s="46">
+        <f>ROW(B39) - ROW($B$9)</f>
+        <v>30</v>
+      </c>
+      <c r="C39" s="59" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" s="62" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" s="62" t="s">
+        <v>116</v>
+      </c>
+      <c r="F39" s="62" t="s">
+        <v>393</v>
+      </c>
+      <c r="G39" s="62" t="s">
+        <v>175</v>
+      </c>
+      <c r="H39" s="62" t="s">
+        <v>273</v>
+      </c>
+      <c r="I39" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J39" s="62" t="s">
+        <v>313</v>
+      </c>
+      <c r="K39" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="L39" s="62">
+        <v>1</v>
+      </c>
+      <c r="M39" s="62">
+        <f>L39*5</f>
+        <v>5</v>
+      </c>
+      <c r="N39" s="62">
+        <v>10</v>
+      </c>
+      <c r="O39" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="P39" s="63">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="Q39" s="63">
+        <f>P39*N39</f>
+        <v>0.93600000000000005</v>
+      </c>
+      <c r="R39" s="61"/>
+      <c r="S39" s="37"/>
+    </row>
+    <row r="40" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="47">
         <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="C39" s="63" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="D39" s="77" t="s">
+      <c r="D40" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="E39" s="38" t="s">
+      <c r="E40" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="F39" s="38" t="s">
+      <c r="F40" s="38" t="s">
         <v>393</v>
       </c>
-      <c r="G39" s="38" t="s">
+      <c r="G40" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="H39" s="38" t="s">
+      <c r="H40" s="38" t="s">
         <v>273</v>
       </c>
-      <c r="I39" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J39" s="38" t="s">
+      <c r="I40" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J40" s="38" t="s">
         <v>314</v>
       </c>
-      <c r="K39" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="L39" s="38">
+      <c r="K40" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L40" s="38">
         <v>1</v>
       </c>
-      <c r="M39" s="38">
-        <f t="shared" ref="M39" si="32">L39*5</f>
+      <c r="M40" s="38">
+        <f t="shared" ref="M40" si="32">L40*5</f>
         <v>5</v>
       </c>
-      <c r="N39" s="38">
+      <c r="N40" s="38">
         <v>10</v>
       </c>
-      <c r="O39" s="61" t="s">
+      <c r="O40" s="58" t="s">
         <v>394</v>
       </c>
-      <c r="P39" s="40">
+      <c r="P40" s="39">
         <v>7.8100000000000003E-2</v>
       </c>
-      <c r="Q39" s="40">
-        <f t="shared" ref="Q39" si="33">P39*N39</f>
+      <c r="Q40" s="39">
+        <f t="shared" ref="Q40" si="33">P40*N40</f>
         <v>0.78100000000000003</v>
       </c>
-      <c r="R39" s="38"/>
-      <c r="S39" s="38"/>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
-      <c r="B40" s="48">
-        <f>ROW(B40) - ROW($B$9)</f>
-        <v>31</v>
-      </c>
-      <c r="C40" s="62" t="s">
+      <c r="R40" s="38"/>
+      <c r="S40" s="38"/>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+      <c r="B41" s="46">
+        <f>ROW(B41) - ROW($B$9)</f>
+        <v>32</v>
+      </c>
+      <c r="C41" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="D40" s="65" t="s">
+      <c r="D41" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="E40" s="65" t="s">
+      <c r="E41" s="62" t="s">
         <v>118</v>
       </c>
-      <c r="F40" s="65" t="s">
+      <c r="F41" s="62" t="s">
         <v>393</v>
       </c>
-      <c r="G40" s="65" t="s">
+      <c r="G41" s="62" t="s">
         <v>177</v>
       </c>
-      <c r="H40" s="65" t="s">
+      <c r="H41" s="62" t="s">
         <v>271</v>
       </c>
-      <c r="I40" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J40" s="65" t="s">
+      <c r="I41" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J41" s="62" t="s">
         <v>315</v>
       </c>
-      <c r="K40" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="L40" s="65">
+      <c r="K41" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="L41" s="62">
         <v>1</v>
       </c>
-      <c r="M40" s="65">
-        <f>L40*5</f>
+      <c r="M41" s="62">
+        <f>L41*5</f>
         <v>5</v>
       </c>
-      <c r="N40" s="65">
+      <c r="N41" s="62">
         <v>6</v>
       </c>
-      <c r="O40" s="59" t="s">
+      <c r="O41" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="P40" s="66">
+      <c r="P41" s="63">
         <v>1.4222999999999999</v>
       </c>
-      <c r="Q40" s="66">
-        <f>P40*N40</f>
+      <c r="Q41" s="63">
+        <f>P41*N41</f>
         <v>8.5337999999999994</v>
       </c>
-      <c r="R40" s="64"/>
-      <c r="S40" s="37"/>
-    </row>
-    <row r="41" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A41" s="1"/>
-      <c r="B41" s="49">
+      <c r="R41" s="61"/>
+      <c r="S41" s="37"/>
+    </row>
+    <row r="42" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
+      <c r="B42" s="47">
         <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="C41" s="63" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="77" t="s">
+      <c r="D42" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="E41" s="38" t="s">
+      <c r="E42" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="F41" s="38" t="s">
+      <c r="F42" s="38" t="s">
         <v>393</v>
       </c>
-      <c r="G41" s="38" t="s">
+      <c r="G42" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="H41" s="38" t="s">
+      <c r="H42" s="38" t="s">
         <v>274</v>
       </c>
-      <c r="I41" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J41" s="38" t="s">
+      <c r="I42" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J42" s="38" t="s">
         <v>316</v>
       </c>
-      <c r="K41" s="38" t="s">
+      <c r="K42" s="38" t="s">
         <v>360</v>
       </c>
-      <c r="L41" s="38">
+      <c r="L42" s="38">
         <v>1</v>
       </c>
-      <c r="M41" s="38">
-        <f t="shared" ref="M41" si="34">L41*5</f>
+      <c r="M42" s="38">
+        <f t="shared" ref="M42" si="34">L42*5</f>
         <v>5</v>
       </c>
-      <c r="N41" s="38">
+      <c r="N42" s="38">
         <v>10</v>
       </c>
-      <c r="O41" s="61" t="s">
+      <c r="O42" s="58" t="s">
         <v>394</v>
       </c>
-      <c r="P41" s="40">
+      <c r="P42" s="39">
         <v>0.19500000000000001</v>
       </c>
-      <c r="Q41" s="40">
-        <f t="shared" ref="Q41" si="35">P41*N41</f>
+      <c r="Q42" s="39">
+        <f t="shared" ref="Q42" si="35">P42*N42</f>
         <v>1.9500000000000002</v>
       </c>
-      <c r="R41" s="38"/>
-      <c r="S41" s="38"/>
-    </row>
-    <row r="42" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A42" s="1"/>
-      <c r="B42" s="48">
-        <f>ROW(B42) - ROW($B$9)</f>
-        <v>33</v>
-      </c>
-      <c r="C42" s="62" t="s">
+      <c r="R42" s="38"/>
+      <c r="S42" s="38"/>
+    </row>
+    <row r="43" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
+      <c r="B43" s="46">
+        <f>ROW(B43) - ROW($B$9)</f>
+        <v>34</v>
+      </c>
+      <c r="C43" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="D42" s="65" t="s">
+      <c r="D43" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="E42" s="65" t="s">
+      <c r="E43" s="62" t="s">
         <v>120</v>
       </c>
-      <c r="F42" s="65" t="s">
+      <c r="F43" s="62" t="s">
         <v>393</v>
       </c>
-      <c r="G42" s="65" t="s">
+      <c r="G43" s="62" t="s">
         <v>179</v>
       </c>
-      <c r="H42" s="65" t="s">
+      <c r="H43" s="62" t="s">
         <v>275</v>
       </c>
-      <c r="I42" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J42" s="65" t="s">
+      <c r="I43" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J43" s="62" t="s">
         <v>317</v>
       </c>
-      <c r="K42" s="65" t="s">
+      <c r="K43" s="62" t="s">
         <v>360</v>
       </c>
-      <c r="L42" s="65">
+      <c r="L43" s="62">
         <v>1</v>
       </c>
-      <c r="M42" s="65">
-        <f>L42*5</f>
+      <c r="M43" s="62">
+        <f>L43*5</f>
         <v>5</v>
       </c>
-      <c r="N42" s="65">
+      <c r="N43" s="62">
         <v>6</v>
       </c>
-      <c r="O42" s="59" t="s">
+      <c r="O43" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="P42" s="66">
+      <c r="P43" s="63">
         <v>0.35439999999999999</v>
       </c>
-      <c r="Q42" s="66">
-        <f>P42*N42</f>
+      <c r="Q43" s="63">
+        <f>P43*N43</f>
         <v>2.1263999999999998</v>
       </c>
-      <c r="R42" s="64"/>
-      <c r="S42" s="37"/>
-    </row>
-    <row r="43" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A43" s="1"/>
-      <c r="B43" s="49">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="C43" s="63" t="s">
-        <v>19</v>
-      </c>
-      <c r="D43" s="77" t="s">
-        <v>56</v>
-      </c>
-      <c r="E43" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="F43" s="38" t="s">
-        <v>180</v>
-      </c>
-      <c r="G43" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="H43" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="I43" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J43" s="38" t="s">
-        <v>318</v>
-      </c>
-      <c r="K43" s="38" t="s">
-        <v>361</v>
-      </c>
-      <c r="L43" s="38">
-        <v>1</v>
-      </c>
-      <c r="M43" s="38">
-        <f t="shared" ref="M43" si="36">L43*5</f>
-        <v>5</v>
-      </c>
-      <c r="N43" s="38">
-        <v>10</v>
-      </c>
-      <c r="O43" s="61" t="s">
-        <v>394</v>
-      </c>
-      <c r="P43" s="40">
-        <v>6.4600000000000005E-2</v>
-      </c>
-      <c r="Q43" s="40">
-        <f t="shared" ref="Q43" si="37">P43*N43</f>
-        <v>0.64600000000000002</v>
-      </c>
-      <c r="R43" s="38"/>
-      <c r="S43" s="38"/>
+      <c r="R43" s="61"/>
+      <c r="S43" s="37"/>
     </row>
     <row r="44" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
-      <c r="B44" s="49">
+      <c r="B44" s="47">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="62" t="s">
-        <v>20</v>
-      </c>
-      <c r="D44" s="65" t="s">
-        <v>405</v>
-      </c>
-      <c r="E44" s="65" t="s">
-        <v>122</v>
-      </c>
-      <c r="F44" s="65" t="s">
-        <v>181</v>
-      </c>
-      <c r="G44" s="65" t="s">
-        <v>223</v>
-      </c>
-      <c r="H44" s="65" t="s">
-        <v>276</v>
-      </c>
-      <c r="I44" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J44" s="65" t="s">
-        <v>319</v>
-      </c>
-      <c r="K44" s="65" t="s">
-        <v>362</v>
-      </c>
-      <c r="L44" s="65">
-        <v>3</v>
-      </c>
-      <c r="M44" s="65">
-        <f t="shared" ref="M44" si="38">L44*5</f>
-        <v>15</v>
-      </c>
-      <c r="N44" s="65">
-        <v>20</v>
-      </c>
-      <c r="O44" s="59" t="s">
+      <c r="C44" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="64" t="s">
+        <v>56</v>
+      </c>
+      <c r="E44" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="F44" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="G44" s="38" t="s">
+        <v>222</v>
+      </c>
+      <c r="H44" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="I44" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J44" s="38" t="s">
+        <v>318</v>
+      </c>
+      <c r="K44" s="38" t="s">
+        <v>361</v>
+      </c>
+      <c r="L44" s="38">
+        <v>1</v>
+      </c>
+      <c r="M44" s="38">
+        <f t="shared" ref="M44" si="36">L44*5</f>
+        <v>5</v>
+      </c>
+      <c r="N44" s="38">
+        <v>10</v>
+      </c>
+      <c r="O44" s="58" t="s">
         <v>394</v>
       </c>
-      <c r="P44" s="66">
-        <v>4.9099999999999998E-2</v>
-      </c>
-      <c r="Q44" s="66">
-        <f t="shared" ref="Q44" si="39">P44*N44</f>
-        <v>0.98199999999999998</v>
-      </c>
-      <c r="R44" s="64"/>
-      <c r="S44" s="37"/>
+      <c r="P44" s="39">
+        <v>6.4600000000000005E-2</v>
+      </c>
+      <c r="Q44" s="39">
+        <f t="shared" ref="Q44" si="37">P44*N44</f>
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="R44" s="38"/>
+      <c r="S44" s="38"/>
     </row>
     <row r="45" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
-      <c r="B45" s="48">
-        <f>ROW(B45) - ROW($B$9)</f>
+      <c r="B45" s="47">
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="63" t="s">
+      <c r="C45" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="D45" s="77" t="s">
-        <v>406</v>
-      </c>
-      <c r="E45" s="38" t="s">
-        <v>124</v>
-      </c>
-      <c r="F45" s="38" t="s">
+      <c r="D45" s="62" t="s">
+        <v>405</v>
+      </c>
+      <c r="E45" s="62" t="s">
+        <v>122</v>
+      </c>
+      <c r="F45" s="62" t="s">
         <v>181</v>
       </c>
-      <c r="G45" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="H45" s="38" t="s">
+      <c r="G45" s="62" t="s">
+        <v>223</v>
+      </c>
+      <c r="H45" s="62" t="s">
         <v>276</v>
       </c>
-      <c r="I45" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J45" s="38" t="s">
-        <v>320</v>
-      </c>
-      <c r="K45" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="L45" s="38">
-        <v>4</v>
-      </c>
-      <c r="M45" s="38">
-        <f>L45*5</f>
+      <c r="I45" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J45" s="62" t="s">
+        <v>319</v>
+      </c>
+      <c r="K45" s="62" t="s">
+        <v>362</v>
+      </c>
+      <c r="L45" s="62">
+        <v>3</v>
+      </c>
+      <c r="M45" s="62">
+        <f t="shared" ref="M45" si="38">L45*5</f>
+        <v>15</v>
+      </c>
+      <c r="N45" s="62">
         <v>20</v>
       </c>
-      <c r="N45" s="38">
-        <v>40</v>
-      </c>
-      <c r="O45" s="61" t="s">
+      <c r="O45" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="P45" s="40">
-        <v>3.2099999999999997E-2</v>
-      </c>
-      <c r="Q45" s="40">
-        <f>P45*N45</f>
-        <v>1.2839999999999998</v>
-      </c>
-      <c r="R45" s="38"/>
-      <c r="S45" s="38"/>
+      <c r="P45" s="63">
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="Q45" s="63">
+        <f t="shared" ref="Q45" si="39">P45*N45</f>
+        <v>0.98199999999999998</v>
+      </c>
+      <c r="R45" s="61"/>
+      <c r="S45" s="37"/>
     </row>
     <row r="46" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
-      <c r="B46" s="49">
+      <c r="B46" s="46">
         <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
-      <c r="C46" s="62" t="s">
+      <c r="C46" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="D46" s="64" t="s">
+        <v>406</v>
+      </c>
+      <c r="E46" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="F46" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="G46" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="H46" s="38" t="s">
+        <v>276</v>
+      </c>
+      <c r="I46" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J46" s="38" t="s">
+        <v>320</v>
+      </c>
+      <c r="K46" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L46" s="38">
+        <v>4</v>
+      </c>
+      <c r="M46" s="38">
+        <f>L46*5</f>
+        <v>20</v>
+      </c>
+      <c r="N46" s="38">
+        <v>40</v>
+      </c>
+      <c r="O46" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="P46" s="39">
+        <v>3.2099999999999997E-2</v>
+      </c>
+      <c r="Q46" s="39">
+        <f>P46*N46</f>
+        <v>1.2839999999999998</v>
+      </c>
+      <c r="R46" s="38"/>
+      <c r="S46" s="38"/>
+    </row>
+    <row r="47" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A47" s="1"/>
+      <c r="B47" s="47">
+        <f>ROW(B47) - ROW($B$9)</f>
+        <v>38</v>
+      </c>
+      <c r="C47" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="D46" s="65" t="s">
+      <c r="D47" s="62" t="s">
         <v>57</v>
       </c>
-      <c r="E46" s="65" t="s">
+      <c r="E47" s="62" t="s">
         <v>123</v>
       </c>
-      <c r="F46" s="65" t="s">
+      <c r="F47" s="62" t="s">
         <v>182</v>
       </c>
-      <c r="G46" s="65" t="s">
+      <c r="G47" s="62" t="s">
         <v>224</v>
       </c>
-      <c r="H46" s="65" t="s">
+      <c r="H47" s="62" t="s">
         <v>277</v>
       </c>
-      <c r="I46" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J46" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="K46" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="L46" s="65">
+      <c r="I47" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J47" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="K47" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="L47" s="62">
         <v>1</v>
       </c>
-      <c r="M46" s="65">
-        <f t="shared" ref="M46" si="40">L46*5</f>
+      <c r="M47" s="62">
+        <f t="shared" ref="M47" si="40">L47*5</f>
         <v>5</v>
       </c>
-      <c r="N46" s="65">
+      <c r="N47" s="62">
         <v>6</v>
       </c>
-      <c r="O46" s="59" t="s">
+      <c r="O47" s="57" t="s">
         <v>277</v>
       </c>
-      <c r="P46" s="66">
+      <c r="P47" s="63">
         <v>16.59</v>
       </c>
-      <c r="Q46" s="66">
-        <f t="shared" ref="Q46" si="41">P46*N46</f>
+      <c r="Q47" s="63">
+        <f t="shared" ref="Q47" si="41">P47*N47</f>
         <v>99.539999999999992</v>
       </c>
-      <c r="R46" s="64"/>
-      <c r="S46" s="37"/>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A47" s="1"/>
-      <c r="B47" s="49">
+      <c r="R47" s="61"/>
+      <c r="S47" s="37"/>
+    </row>
+    <row r="48" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
+      <c r="B48" s="47">
         <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="C47" s="63" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="D47" s="77" t="s">
+      <c r="D48" s="64" t="s">
         <v>58</v>
       </c>
-      <c r="E47" s="38" t="s">
+      <c r="E48" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="F47" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="G47" s="38" t="s">
+      <c r="F48" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="G48" s="38" t="s">
         <v>183</v>
       </c>
-      <c r="H47" s="38" t="s">
+      <c r="H48" s="38" t="s">
         <v>278</v>
       </c>
-      <c r="I47" s="38"/>
-      <c r="J47" s="38"/>
-      <c r="K47" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="L47" s="38">
+      <c r="I48" s="38"/>
+      <c r="J48" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="K48" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L48" s="38">
         <v>1</v>
       </c>
-      <c r="M47" s="38">
-        <f t="shared" ref="M47" si="42">L47*5</f>
+      <c r="M48" s="38">
+        <f t="shared" ref="M48" si="42">L48*5</f>
         <v>5</v>
       </c>
-      <c r="N47" s="38"/>
-      <c r="O47" s="61"/>
-      <c r="P47" s="40"/>
-      <c r="Q47" s="40">
-        <f t="shared" ref="Q47" si="43">P47*N47</f>
-        <v>0</v>
-      </c>
-      <c r="R47" s="38"/>
-      <c r="S47" s="38"/>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48" s="1"/>
-      <c r="B48" s="48">
-        <f>ROW(B48) - ROW($B$9)</f>
-        <v>39</v>
-      </c>
-      <c r="C48" s="62" t="s">
+      <c r="N48" s="38">
+        <v>6</v>
+      </c>
+      <c r="O48" s="58" t="s">
+        <v>278</v>
+      </c>
+      <c r="P48" s="39">
+        <v>13.9</v>
+      </c>
+      <c r="Q48" s="39">
+        <f t="shared" ref="Q48" si="43">P48*N48</f>
+        <v>83.4</v>
+      </c>
+      <c r="R48" s="38"/>
+      <c r="S48" s="38"/>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A49" s="1"/>
+      <c r="B49" s="46">
+        <f>ROW(B49) - ROW($B$9)</f>
+        <v>40</v>
+      </c>
+      <c r="C49" s="89" t="s">
         <v>363</v>
       </c>
-      <c r="D48" s="65" t="s">
+      <c r="D49" s="90" t="s">
         <v>59</v>
       </c>
-      <c r="E48" s="65" t="s">
+      <c r="E49" s="90" t="s">
         <v>126</v>
       </c>
-      <c r="F48" s="65" t="s">
+      <c r="F49" s="90" t="s">
         <v>184</v>
       </c>
-      <c r="G48" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="H48" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="I48" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J48" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="K48" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="L48" s="65">
+      <c r="G49" s="90" t="s">
+        <v>381</v>
+      </c>
+      <c r="H49" s="90" t="s">
+        <v>381</v>
+      </c>
+      <c r="I49" s="90" t="s">
+        <v>381</v>
+      </c>
+      <c r="J49" s="90" t="s">
+        <v>381</v>
+      </c>
+      <c r="K49" s="90" t="s">
+        <v>381</v>
+      </c>
+      <c r="L49" s="90">
         <v>6</v>
       </c>
-      <c r="M48" s="65">
-        <f>L48*5</f>
+      <c r="M49" s="90">
+        <f>L49*5</f>
         <v>30</v>
       </c>
-      <c r="N48" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="O48" s="59" t="s">
-        <v>381</v>
-      </c>
-      <c r="P48" s="66" t="s">
-        <v>381</v>
-      </c>
-      <c r="Q48" s="66" t="s">
-        <v>381</v>
-      </c>
-      <c r="R48" s="64"/>
-      <c r="S48" s="37"/>
-    </row>
-    <row r="49" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A49" s="1"/>
-      <c r="B49" s="49">
+      <c r="N49" s="90" t="s">
+        <v>381</v>
+      </c>
+      <c r="O49" s="91" t="s">
+        <v>381</v>
+      </c>
+      <c r="P49" s="92" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q49" s="92" t="s">
+        <v>381</v>
+      </c>
+      <c r="R49" s="90"/>
+      <c r="S49" s="90"/>
+    </row>
+    <row r="50" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="B50" s="47">
         <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="C50" s="60" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="E50" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="F50" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="G50" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="H50" s="38" t="s">
+        <v>279</v>
+      </c>
+      <c r="I50" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J50" s="38" t="s">
+        <v>321</v>
+      </c>
+      <c r="K50" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L50" s="38">
+        <v>4</v>
+      </c>
+      <c r="M50" s="38">
+        <f t="shared" ref="M50" si="44">L50*5</f>
+        <v>20</v>
+      </c>
+      <c r="N50" s="38">
         <v>40</v>
       </c>
-      <c r="C49" s="63" t="s">
-        <v>22</v>
-      </c>
-      <c r="D49" s="77" t="s">
-        <v>60</v>
-      </c>
-      <c r="E49" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="F49" s="38" t="s">
-        <v>185</v>
-      </c>
-      <c r="G49" s="38" t="s">
-        <v>226</v>
-      </c>
-      <c r="H49" s="38" t="s">
-        <v>279</v>
-      </c>
-      <c r="I49" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J49" s="38" t="s">
-        <v>321</v>
-      </c>
-      <c r="K49" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="L49" s="38">
-        <v>4</v>
-      </c>
-      <c r="M49" s="38">
-        <f t="shared" ref="M49" si="44">L49*5</f>
-        <v>20</v>
-      </c>
-      <c r="N49" s="38">
-        <v>40</v>
-      </c>
-      <c r="O49" s="61" t="s">
+      <c r="O50" s="58" t="s">
         <v>394</v>
       </c>
-      <c r="P49" s="40">
+      <c r="P50" s="39">
         <v>3.2899999999999999E-2</v>
       </c>
-      <c r="Q49" s="40">
-        <f t="shared" ref="Q49" si="45">P49*N49</f>
+      <c r="Q50" s="39">
+        <f t="shared" ref="Q50" si="45">P50*N50</f>
         <v>1.3159999999999998</v>
       </c>
-      <c r="R49" s="38"/>
-      <c r="S49" s="38"/>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A50" s="1"/>
-      <c r="B50" s="48">
-        <f>ROW(B50) - ROW($B$9)</f>
-        <v>41</v>
-      </c>
-      <c r="C50" s="62" t="s">
-        <v>23</v>
-      </c>
-      <c r="D50" s="65" t="s">
-        <v>61</v>
-      </c>
-      <c r="E50" s="65" t="s">
-        <v>128</v>
-      </c>
-      <c r="F50" s="65" t="s">
-        <v>186</v>
-      </c>
-      <c r="G50" s="65" t="s">
-        <v>227</v>
-      </c>
-      <c r="H50" s="65" t="s">
-        <v>256</v>
-      </c>
-      <c r="I50" s="65" t="s">
-        <v>400</v>
-      </c>
-      <c r="J50" s="65" t="s">
-        <v>322</v>
-      </c>
-      <c r="K50" s="65" t="s">
-        <v>364</v>
-      </c>
-      <c r="L50" s="65">
-        <v>1</v>
-      </c>
-      <c r="M50" s="65">
-        <f>L50*5</f>
-        <v>5</v>
-      </c>
-      <c r="N50" s="65">
-        <v>20</v>
-      </c>
-      <c r="O50" s="59" t="s">
-        <v>394</v>
-      </c>
-      <c r="P50" s="66">
-        <v>2.7699999999999999E-2</v>
-      </c>
-      <c r="Q50" s="66">
-        <f>P50*N50</f>
-        <v>0.55399999999999994</v>
-      </c>
-      <c r="R50" s="64"/>
-      <c r="S50" s="37"/>
+      <c r="R50" s="38"/>
+      <c r="S50" s="38"/>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
-      <c r="B51" s="49">
+      <c r="B51" s="46">
+        <f>ROW(B51) - ROW($B$9)</f>
+        <v>42</v>
+      </c>
+      <c r="C51" s="59" t="s">
+        <v>23</v>
+      </c>
+      <c r="D51" s="62" t="s">
+        <v>61</v>
+      </c>
+      <c r="E51" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="F51" s="62" t="s">
+        <v>186</v>
+      </c>
+      <c r="G51" s="62" t="s">
+        <v>227</v>
+      </c>
+      <c r="H51" s="62" t="s">
+        <v>256</v>
+      </c>
+      <c r="I51" s="62" t="s">
+        <v>400</v>
+      </c>
+      <c r="J51" s="62" t="s">
+        <v>322</v>
+      </c>
+      <c r="K51" s="62" t="s">
+        <v>364</v>
+      </c>
+      <c r="L51" s="62">
+        <v>1</v>
+      </c>
+      <c r="M51" s="62">
+        <f>L51*5</f>
+        <v>5</v>
+      </c>
+      <c r="N51" s="62">
+        <v>20</v>
+      </c>
+      <c r="O51" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="P51" s="63">
+        <v>2.7699999999999999E-2</v>
+      </c>
+      <c r="Q51" s="63">
+        <f>P51*N51</f>
+        <v>0.55399999999999994</v>
+      </c>
+      <c r="R51" s="61"/>
+      <c r="S51" s="37"/>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A52" s="1"/>
+      <c r="B52" s="47">
         <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="C51" s="63" t="s">
+        <v>43</v>
+      </c>
+      <c r="C52" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="D51" s="77" t="s">
+      <c r="D52" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="E51" s="38" t="s">
+      <c r="E52" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="F51" s="38" t="s">
+      <c r="F52" s="38" t="s">
         <v>186</v>
       </c>
-      <c r="G51" s="38" t="s">
+      <c r="G52" s="38" t="s">
         <v>228</v>
       </c>
-      <c r="H51" s="38" t="s">
+      <c r="H52" s="38" t="s">
         <v>256</v>
       </c>
-      <c r="I51" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J51" s="38" t="s">
+      <c r="I52" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J52" s="38" t="s">
         <v>323</v>
       </c>
-      <c r="K51" s="38" t="s">
+      <c r="K52" s="38" t="s">
         <v>383</v>
       </c>
-      <c r="L51" s="38">
+      <c r="L52" s="38">
         <v>1</v>
       </c>
-      <c r="M51" s="38">
-        <f t="shared" ref="M51" si="46">L51*5</f>
+      <c r="M52" s="38">
+        <f t="shared" ref="M52" si="46">L52*5</f>
         <v>5</v>
       </c>
-      <c r="N51" s="38">
+      <c r="N52" s="38">
         <v>20</v>
       </c>
-      <c r="O51" s="61" t="s">
+      <c r="O52" s="58" t="s">
         <v>394</v>
       </c>
-      <c r="P51" s="40">
+      <c r="P52" s="39">
         <v>2.18E-2</v>
       </c>
-      <c r="Q51" s="40">
-        <f t="shared" ref="Q51" si="47">P51*N51</f>
+      <c r="Q52" s="39">
+        <f t="shared" ref="Q52" si="47">P52*N52</f>
         <v>0.436</v>
       </c>
-      <c r="R51" s="38"/>
-      <c r="S51" s="38"/>
-    </row>
-    <row r="52" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A52" s="1"/>
-      <c r="B52" s="48">
-        <f>ROW(B52) - ROW($B$9)</f>
-        <v>43</v>
-      </c>
-      <c r="C52" s="62" t="s">
+      <c r="R52" s="38"/>
+      <c r="S52" s="38"/>
+    </row>
+    <row r="53" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A53" s="1"/>
+      <c r="B53" s="46">
+        <f>ROW(B53) - ROW($B$9)</f>
+        <v>44</v>
+      </c>
+      <c r="C53" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="D52" s="65" t="s">
+      <c r="D53" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="E52" s="65" t="s">
+      <c r="E53" s="62" t="s">
         <v>130</v>
       </c>
-      <c r="F52" s="65" t="s">
+      <c r="F53" s="62" t="s">
         <v>186</v>
       </c>
-      <c r="G52" s="65" t="s">
+      <c r="G53" s="62" t="s">
         <v>229</v>
       </c>
-      <c r="H52" s="65" t="s">
+      <c r="H53" s="62" t="s">
         <v>256</v>
       </c>
-      <c r="I52" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J52" s="65" t="s">
+      <c r="I53" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J53" s="62" t="s">
         <v>324</v>
       </c>
-      <c r="K52" s="65" t="s">
+      <c r="K53" s="62" t="s">
         <v>365</v>
       </c>
-      <c r="L52" s="65">
+      <c r="L53" s="62">
         <v>13</v>
       </c>
-      <c r="M52" s="65">
-        <f>L52*5</f>
+      <c r="M53" s="62">
+        <f>L53*5</f>
         <v>65</v>
       </c>
-      <c r="N52" s="65">
+      <c r="N53" s="62">
         <v>100</v>
       </c>
-      <c r="O52" s="59" t="s">
+      <c r="O53" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="P52" s="66">
+      <c r="P53" s="63">
         <v>1E-3</v>
       </c>
-      <c r="Q52" s="66">
-        <f>P52*N52</f>
+      <c r="Q53" s="63">
+        <f>P53*N53</f>
         <v>0.1</v>
       </c>
-      <c r="R52" s="64"/>
-      <c r="S52" s="37"/>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A53" s="1"/>
-      <c r="B53" s="49">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="C53" s="63" t="s">
-        <v>23</v>
-      </c>
-      <c r="D53" s="77" t="s">
-        <v>64</v>
-      </c>
-      <c r="E53" s="38" t="s">
-        <v>131</v>
-      </c>
-      <c r="F53" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="G53" s="38" t="s">
-        <v>230</v>
-      </c>
-      <c r="H53" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="I53" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J53" s="38" t="s">
-        <v>325</v>
-      </c>
-      <c r="K53" s="38" t="s">
-        <v>366</v>
-      </c>
-      <c r="L53" s="38">
-        <v>1</v>
-      </c>
-      <c r="M53" s="38">
-        <f t="shared" ref="M53" si="48">L53*5</f>
-        <v>5</v>
-      </c>
-      <c r="N53" s="38">
-        <v>20</v>
-      </c>
-      <c r="O53" s="61" t="s">
-        <v>394</v>
-      </c>
-      <c r="P53" s="40">
-        <v>2.81E-2</v>
-      </c>
-      <c r="Q53" s="40">
-        <f t="shared" ref="Q53" si="49">P53*N53</f>
-        <v>0.56200000000000006</v>
-      </c>
-      <c r="R53" s="38"/>
-      <c r="S53" s="38"/>
+      <c r="R53" s="61"/>
+      <c r="S53" s="37"/>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
-      <c r="B54" s="48">
-        <f>ROW(B54) - ROW($B$9)</f>
+      <c r="B54" s="47">
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C54" s="62" t="s">
+      <c r="C54" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="D54" s="65" t="s">
-        <v>65</v>
-      </c>
-      <c r="E54" s="65" t="s">
-        <v>132</v>
-      </c>
-      <c r="F54" s="65" t="s">
+      <c r="D54" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="E54" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="F54" s="38" t="s">
         <v>186</v>
       </c>
-      <c r="G54" s="65" t="s">
-        <v>231</v>
-      </c>
-      <c r="H54" s="65" t="s">
+      <c r="G54" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="H54" s="38" t="s">
         <v>256</v>
       </c>
-      <c r="I54" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J54" s="65" t="s">
-        <v>326</v>
-      </c>
-      <c r="K54" s="65" t="s">
-        <v>367</v>
-      </c>
-      <c r="L54" s="65">
+      <c r="I54" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J54" s="38" t="s">
+        <v>325</v>
+      </c>
+      <c r="K54" s="38" t="s">
+        <v>366</v>
+      </c>
+      <c r="L54" s="38">
         <v>1</v>
       </c>
-      <c r="M54" s="65">
-        <f>L54*5</f>
+      <c r="M54" s="38">
+        <f t="shared" ref="M54" si="48">L54*5</f>
         <v>5</v>
       </c>
-      <c r="N54" s="65">
+      <c r="N54" s="38">
         <v>20</v>
       </c>
-      <c r="O54" s="59" t="s">
+      <c r="O54" s="58" t="s">
         <v>394</v>
       </c>
-      <c r="P54" s="66">
-        <v>3.2300000000000002E-2</v>
-      </c>
-      <c r="Q54" s="66">
-        <f>P54*N54</f>
-        <v>0.64600000000000002</v>
-      </c>
-      <c r="R54" s="64"/>
-      <c r="S54" s="37"/>
+      <c r="P54" s="39">
+        <v>2.81E-2</v>
+      </c>
+      <c r="Q54" s="39">
+        <f t="shared" ref="Q54" si="49">P54*N54</f>
+        <v>0.56200000000000006</v>
+      </c>
+      <c r="R54" s="38"/>
+      <c r="S54" s="38"/>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
-      <c r="B55" s="49">
-        <f t="shared" si="0"/>
+      <c r="B55" s="46">
+        <f>ROW(B55) - ROW($B$9)</f>
         <v>46</v>
       </c>
-      <c r="C55" s="63" t="s">
+      <c r="C55" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="D55" s="77" t="s">
-        <v>66</v>
-      </c>
-      <c r="E55" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="F55" s="38" t="s">
+      <c r="D55" s="62" t="s">
+        <v>65</v>
+      </c>
+      <c r="E55" s="62" t="s">
+        <v>132</v>
+      </c>
+      <c r="F55" s="62" t="s">
         <v>186</v>
       </c>
-      <c r="G55" s="38" t="s">
-        <v>232</v>
-      </c>
-      <c r="H55" s="38" t="s">
+      <c r="G55" s="62" t="s">
+        <v>231</v>
+      </c>
+      <c r="H55" s="62" t="s">
         <v>256</v>
       </c>
-      <c r="I55" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J55" s="38" t="s">
-        <v>327</v>
-      </c>
-      <c r="K55" s="38" t="s">
-        <v>368</v>
-      </c>
-      <c r="L55" s="38">
-        <v>2</v>
-      </c>
-      <c r="M55" s="38">
-        <f t="shared" ref="M55" si="50">L55*5</f>
-        <v>10</v>
-      </c>
-      <c r="N55" s="38">
-        <v>100</v>
-      </c>
-      <c r="O55" s="61" t="s">
+      <c r="I55" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J55" s="62" t="s">
+        <v>326</v>
+      </c>
+      <c r="K55" s="62" t="s">
+        <v>367</v>
+      </c>
+      <c r="L55" s="62">
+        <v>1</v>
+      </c>
+      <c r="M55" s="62">
+        <f>L55*5</f>
+        <v>5</v>
+      </c>
+      <c r="N55" s="62">
+        <v>20</v>
+      </c>
+      <c r="O55" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="P55" s="40">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q55" s="40">
-        <f t="shared" ref="Q55" si="51">P55*N55</f>
-        <v>0.12</v>
-      </c>
-      <c r="R55" s="38"/>
-      <c r="S55" s="38"/>
+      <c r="P55" s="63">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="Q55" s="63">
+        <f>P55*N55</f>
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="R55" s="61"/>
+      <c r="S55" s="37"/>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
-      <c r="B56" s="48">
-        <f>ROW(B56) - ROW($B$9)</f>
+      <c r="B56" s="47">
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="C56" s="62" t="s">
+      <c r="C56" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="D56" s="65" t="s">
-        <v>67</v>
-      </c>
-      <c r="E56" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="F56" s="65" t="s">
+      <c r="D56" s="64" t="s">
+        <v>66</v>
+      </c>
+      <c r="E56" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="F56" s="38" t="s">
         <v>186</v>
       </c>
-      <c r="G56" s="65" t="s">
-        <v>233</v>
-      </c>
-      <c r="H56" s="65" t="s">
+      <c r="G56" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="H56" s="38" t="s">
         <v>256</v>
       </c>
-      <c r="I56" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J56" s="65" t="s">
-        <v>328</v>
-      </c>
-      <c r="K56" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="L56" s="65">
-        <v>3</v>
-      </c>
-      <c r="M56" s="65">
-        <f>L56*5</f>
-        <v>15</v>
-      </c>
-      <c r="N56" s="65">
+      <c r="I56" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J56" s="38" t="s">
+        <v>327</v>
+      </c>
+      <c r="K56" s="38" t="s">
+        <v>368</v>
+      </c>
+      <c r="L56" s="38">
+        <v>2</v>
+      </c>
+      <c r="M56" s="38">
+        <f t="shared" ref="M56" si="50">L56*5</f>
+        <v>10</v>
+      </c>
+      <c r="N56" s="38">
         <v>100</v>
       </c>
-      <c r="O56" s="59" t="s">
+      <c r="O56" s="58" t="s">
         <v>394</v>
       </c>
-      <c r="P56" s="66">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q56" s="66">
-        <f>P56*N56</f>
-        <v>0.13</v>
-      </c>
-      <c r="R56" s="64"/>
-      <c r="S56" s="37"/>
+      <c r="P56" s="39">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q56" s="39">
+        <f t="shared" ref="Q56" si="51">P56*N56</f>
+        <v>0.12</v>
+      </c>
+      <c r="R56" s="38"/>
+      <c r="S56" s="38"/>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
-      <c r="B57" s="49">
-        <f t="shared" si="0"/>
+      <c r="B57" s="46">
+        <f>ROW(B57) - ROW($B$9)</f>
         <v>48</v>
       </c>
-      <c r="C57" s="63" t="s">
+      <c r="C57" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="D57" s="77" t="s">
-        <v>68</v>
-      </c>
-      <c r="E57" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="F57" s="38" t="s">
+      <c r="D57" s="62" t="s">
+        <v>67</v>
+      </c>
+      <c r="E57" s="62" t="s">
+        <v>134</v>
+      </c>
+      <c r="F57" s="62" t="s">
         <v>186</v>
       </c>
-      <c r="G57" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="H57" s="38" t="s">
+      <c r="G57" s="62" t="s">
+        <v>233</v>
+      </c>
+      <c r="H57" s="62" t="s">
         <v>256</v>
       </c>
-      <c r="I57" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J57" s="38" t="s">
-        <v>329</v>
-      </c>
-      <c r="K57" s="38" t="s">
-        <v>370</v>
-      </c>
-      <c r="L57" s="38">
-        <v>4</v>
-      </c>
-      <c r="M57" s="38">
-        <f t="shared" ref="M57" si="52">L57*5</f>
-        <v>20</v>
-      </c>
-      <c r="N57" s="38">
-        <v>50</v>
-      </c>
-      <c r="O57" s="61" t="s">
+      <c r="I57" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J57" s="62" t="s">
+        <v>328</v>
+      </c>
+      <c r="K57" s="62" t="s">
+        <v>369</v>
+      </c>
+      <c r="L57" s="62">
+        <v>3</v>
+      </c>
+      <c r="M57" s="62">
+        <f>L57*5</f>
+        <v>15</v>
+      </c>
+      <c r="N57" s="62">
+        <v>100</v>
+      </c>
+      <c r="O57" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="P57" s="40">
-        <v>9.2999999999999992E-3</v>
-      </c>
-      <c r="Q57" s="40">
-        <f t="shared" ref="Q57" si="53">P57*N57</f>
-        <v>0.46499999999999997</v>
-      </c>
-      <c r="R57" s="38"/>
-      <c r="S57" s="38"/>
+      <c r="P57" s="63">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q57" s="63">
+        <f>P57*N57</f>
+        <v>0.13</v>
+      </c>
+      <c r="R57" s="61"/>
+      <c r="S57" s="37"/>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
-      <c r="B58" s="48">
-        <f>ROW(B58) - ROW($B$9)</f>
+      <c r="B58" s="47">
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="C58" s="62" t="s">
+      <c r="C58" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="D58" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="E58" s="65" t="s">
-        <v>136</v>
-      </c>
-      <c r="F58" s="65" t="s">
+      <c r="D58" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="E58" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="F58" s="38" t="s">
         <v>186</v>
       </c>
-      <c r="G58" s="65" t="s">
-        <v>235</v>
-      </c>
-      <c r="H58" s="65" t="s">
+      <c r="G58" s="38" t="s">
+        <v>234</v>
+      </c>
+      <c r="H58" s="38" t="s">
         <v>256</v>
       </c>
-      <c r="I58" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J58" s="65" t="s">
-        <v>330</v>
-      </c>
-      <c r="K58" s="65" t="s">
-        <v>371</v>
-      </c>
-      <c r="L58" s="65">
-        <v>1</v>
-      </c>
-      <c r="M58" s="65">
-        <f>L58*5</f>
-        <v>5</v>
-      </c>
-      <c r="N58" s="65">
-        <v>100</v>
-      </c>
-      <c r="O58" s="59" t="s">
+      <c r="I58" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J58" s="38" t="s">
+        <v>329</v>
+      </c>
+      <c r="K58" s="38" t="s">
+        <v>370</v>
+      </c>
+      <c r="L58" s="38">
+        <v>4</v>
+      </c>
+      <c r="M58" s="38">
+        <f t="shared" ref="M58" si="52">L58*5</f>
+        <v>20</v>
+      </c>
+      <c r="N58" s="38">
+        <v>50</v>
+      </c>
+      <c r="O58" s="58" t="s">
         <v>394</v>
       </c>
-      <c r="P58" s="66">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="Q58" s="66">
-        <f>P58*N58</f>
-        <v>0.3</v>
-      </c>
-      <c r="R58" s="64"/>
-      <c r="S58" s="37"/>
+      <c r="P58" s="39">
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="Q58" s="39">
+        <f t="shared" ref="Q58" si="53">P58*N58</f>
+        <v>0.46499999999999997</v>
+      </c>
+      <c r="R58" s="38"/>
+      <c r="S58" s="38"/>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
-      <c r="B59" s="49">
-        <f t="shared" si="0"/>
+      <c r="B59" s="46">
+        <f>ROW(B59) - ROW($B$9)</f>
         <v>50</v>
       </c>
-      <c r="C59" s="63" t="s">
+      <c r="C59" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="D59" s="77" t="s">
-        <v>70</v>
-      </c>
-      <c r="E59" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="F59" s="38" t="s">
+      <c r="D59" s="62" t="s">
+        <v>69</v>
+      </c>
+      <c r="E59" s="62" t="s">
+        <v>136</v>
+      </c>
+      <c r="F59" s="62" t="s">
         <v>186</v>
       </c>
-      <c r="G59" s="38" t="s">
-        <v>236</v>
-      </c>
-      <c r="H59" s="38" t="s">
+      <c r="G59" s="62" t="s">
+        <v>235</v>
+      </c>
+      <c r="H59" s="62" t="s">
         <v>256</v>
       </c>
-      <c r="I59" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J59" s="38" t="s">
-        <v>331</v>
-      </c>
-      <c r="K59" s="38" t="s">
-        <v>372</v>
-      </c>
-      <c r="L59" s="38">
-        <v>3</v>
-      </c>
-      <c r="M59" s="38">
-        <f t="shared" ref="M59" si="54">L59*5</f>
-        <v>15</v>
-      </c>
-      <c r="N59" s="38">
+      <c r="I59" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J59" s="62" t="s">
+        <v>330</v>
+      </c>
+      <c r="K59" s="62" t="s">
+        <v>371</v>
+      </c>
+      <c r="L59" s="62">
+        <v>1</v>
+      </c>
+      <c r="M59" s="62">
+        <f>L59*5</f>
+        <v>5</v>
+      </c>
+      <c r="N59" s="62">
         <v>100</v>
       </c>
-      <c r="O59" s="61" t="s">
+      <c r="O59" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="P59" s="40">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q59" s="40">
-        <f t="shared" ref="Q59" si="55">P59*N59</f>
-        <v>0.12</v>
-      </c>
-      <c r="R59" s="38"/>
-      <c r="S59" s="38"/>
+      <c r="P59" s="63">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="Q59" s="63">
+        <f>P59*N59</f>
+        <v>0.3</v>
+      </c>
+      <c r="R59" s="61"/>
+      <c r="S59" s="37"/>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
-      <c r="B60" s="48">
-        <f>ROW(B60) - ROW($B$9)</f>
+      <c r="B60" s="47">
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C60" s="62" t="s">
+      <c r="C60" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="D60" s="65" t="s">
-        <v>71</v>
-      </c>
-      <c r="E60" s="65" t="s">
-        <v>138</v>
-      </c>
-      <c r="F60" s="65" t="s">
+      <c r="D60" s="64" t="s">
+        <v>70</v>
+      </c>
+      <c r="E60" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="F60" s="38" t="s">
         <v>186</v>
       </c>
-      <c r="G60" s="65" t="s">
-        <v>237</v>
-      </c>
-      <c r="H60" s="65" t="s">
+      <c r="G60" s="38" t="s">
+        <v>236</v>
+      </c>
+      <c r="H60" s="38" t="s">
         <v>256</v>
       </c>
-      <c r="I60" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J60" s="65" t="s">
-        <v>332</v>
-      </c>
-      <c r="K60" s="65" t="s">
-        <v>373</v>
-      </c>
-      <c r="L60" s="65">
-        <v>6</v>
-      </c>
-      <c r="M60" s="65">
-        <f>L60*5</f>
-        <v>30</v>
-      </c>
-      <c r="N60" s="65">
+      <c r="I60" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J60" s="38" t="s">
+        <v>331</v>
+      </c>
+      <c r="K60" s="38" t="s">
+        <v>372</v>
+      </c>
+      <c r="L60" s="38">
+        <v>3</v>
+      </c>
+      <c r="M60" s="38">
+        <f t="shared" ref="M60" si="54">L60*5</f>
+        <v>15</v>
+      </c>
+      <c r="N60" s="38">
         <v>100</v>
       </c>
-      <c r="O60" s="59" t="s">
+      <c r="O60" s="58" t="s">
         <v>394</v>
       </c>
-      <c r="P60" s="66">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="Q60" s="66">
-        <f>P60*N60</f>
-        <v>0.11</v>
-      </c>
-      <c r="R60" s="64"/>
-      <c r="S60" s="37"/>
+      <c r="P60" s="39">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q60" s="39">
+        <f t="shared" ref="Q60" si="55">P60*N60</f>
+        <v>0.12</v>
+      </c>
+      <c r="R60" s="38"/>
+      <c r="S60" s="38"/>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
-      <c r="B61" s="49">
-        <f t="shared" si="0"/>
+      <c r="B61" s="46">
+        <f>ROW(B61) - ROW($B$9)</f>
         <v>52</v>
       </c>
-      <c r="C61" s="63" t="s">
+      <c r="C61" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="D61" s="77" t="s">
-        <v>72</v>
-      </c>
-      <c r="E61" s="38" t="s">
-        <v>139</v>
-      </c>
-      <c r="F61" s="38" t="s">
+      <c r="D61" s="62" t="s">
+        <v>71</v>
+      </c>
+      <c r="E61" s="62" t="s">
+        <v>138</v>
+      </c>
+      <c r="F61" s="62" t="s">
         <v>186</v>
       </c>
-      <c r="G61" s="38" t="s">
-        <v>238</v>
-      </c>
-      <c r="H61" s="38" t="s">
+      <c r="G61" s="62" t="s">
+        <v>237</v>
+      </c>
+      <c r="H61" s="62" t="s">
         <v>256</v>
       </c>
-      <c r="I61" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J61" s="38" t="s">
-        <v>333</v>
-      </c>
-      <c r="K61" s="38" t="s">
-        <v>374</v>
-      </c>
-      <c r="L61" s="38">
-        <v>4</v>
-      </c>
-      <c r="M61" s="38">
-        <f t="shared" ref="M61" si="56">L61*5</f>
-        <v>20</v>
-      </c>
-      <c r="N61" s="38">
+      <c r="I61" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J61" s="62" t="s">
+        <v>332</v>
+      </c>
+      <c r="K61" s="62" t="s">
+        <v>373</v>
+      </c>
+      <c r="L61" s="62">
+        <v>6</v>
+      </c>
+      <c r="M61" s="62">
+        <f>L61*5</f>
+        <v>30</v>
+      </c>
+      <c r="N61" s="62">
         <v>100</v>
       </c>
-      <c r="O61" s="61" t="s">
+      <c r="O61" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="P61" s="40">
-        <v>1E-3</v>
-      </c>
-      <c r="Q61" s="40">
-        <f t="shared" ref="Q61" si="57">P61*N61</f>
-        <v>0.1</v>
-      </c>
-      <c r="R61" s="38"/>
-      <c r="S61" s="38"/>
+      <c r="P61" s="63">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q61" s="63">
+        <f>P61*N61</f>
+        <v>0.11</v>
+      </c>
+      <c r="R61" s="61"/>
+      <c r="S61" s="37"/>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
-      <c r="B62" s="48">
-        <f>ROW(B62) - ROW($B$9)</f>
+      <c r="B62" s="47">
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="C62" s="62" t="s">
+      <c r="C62" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="D62" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="E62" s="65" t="s">
-        <v>140</v>
-      </c>
-      <c r="F62" s="65" t="s">
+      <c r="D62" s="64" t="s">
+        <v>72</v>
+      </c>
+      <c r="E62" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="F62" s="38" t="s">
         <v>186</v>
       </c>
-      <c r="G62" s="65" t="s">
-        <v>239</v>
-      </c>
-      <c r="H62" s="65" t="s">
+      <c r="G62" s="38" t="s">
+        <v>238</v>
+      </c>
+      <c r="H62" s="38" t="s">
         <v>256</v>
       </c>
-      <c r="I62" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J62" s="65" t="s">
-        <v>334</v>
-      </c>
-      <c r="K62" s="65" t="s">
-        <v>375</v>
-      </c>
-      <c r="L62" s="65">
-        <v>1</v>
-      </c>
-      <c r="M62" s="65">
-        <f>L62*5</f>
-        <v>5</v>
-      </c>
-      <c r="N62" s="65">
+      <c r="I62" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J62" s="38" t="s">
+        <v>333</v>
+      </c>
+      <c r="K62" s="38" t="s">
+        <v>374</v>
+      </c>
+      <c r="L62" s="38">
+        <v>4</v>
+      </c>
+      <c r="M62" s="38">
+        <f t="shared" ref="M62" si="56">L62*5</f>
+        <v>20</v>
+      </c>
+      <c r="N62" s="38">
         <v>100</v>
       </c>
-      <c r="O62" s="59" t="s">
+      <c r="O62" s="58" t="s">
         <v>394</v>
       </c>
-      <c r="P62" s="66">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q62" s="66">
-        <f>P62*N62</f>
-        <v>0.13</v>
-      </c>
-      <c r="R62" s="64"/>
-      <c r="S62" s="37"/>
+      <c r="P62" s="39">
+        <v>1E-3</v>
+      </c>
+      <c r="Q62" s="39">
+        <f t="shared" ref="Q62" si="57">P62*N62</f>
+        <v>0.1</v>
+      </c>
+      <c r="R62" s="38"/>
+      <c r="S62" s="38"/>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
-      <c r="B63" s="49">
-        <f t="shared" si="0"/>
+      <c r="B63" s="46">
+        <f>ROW(B63) - ROW($B$9)</f>
         <v>54</v>
       </c>
-      <c r="C63" s="63" t="s">
+      <c r="C63" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="D63" s="77" t="s">
-        <v>74</v>
-      </c>
-      <c r="E63" s="38" t="s">
-        <v>141</v>
-      </c>
-      <c r="F63" s="38" t="s">
+      <c r="D63" s="62" t="s">
+        <v>73</v>
+      </c>
+      <c r="E63" s="62" t="s">
+        <v>140</v>
+      </c>
+      <c r="F63" s="62" t="s">
         <v>186</v>
       </c>
-      <c r="G63" s="38" t="s">
-        <v>240</v>
-      </c>
-      <c r="H63" s="38" t="s">
+      <c r="G63" s="62" t="s">
+        <v>239</v>
+      </c>
+      <c r="H63" s="62" t="s">
         <v>256</v>
       </c>
-      <c r="I63" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J63" s="38" t="s">
-        <v>335</v>
-      </c>
-      <c r="K63" s="38" t="s">
-        <v>376</v>
-      </c>
-      <c r="L63" s="38">
-        <v>3</v>
-      </c>
-      <c r="M63" s="38">
-        <f t="shared" ref="M63" si="58">L63*5</f>
-        <v>15</v>
-      </c>
-      <c r="N63" s="38">
+      <c r="I63" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J63" s="62" t="s">
+        <v>334</v>
+      </c>
+      <c r="K63" s="62" t="s">
+        <v>375</v>
+      </c>
+      <c r="L63" s="62">
+        <v>1</v>
+      </c>
+      <c r="M63" s="62">
+        <f>L63*5</f>
+        <v>5</v>
+      </c>
+      <c r="N63" s="62">
         <v>100</v>
       </c>
-      <c r="O63" s="61" t="s">
+      <c r="O63" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="P63" s="40">
+      <c r="P63" s="63">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q63" s="40">
-        <f t="shared" ref="Q63" si="59">P63*N63</f>
+      <c r="Q63" s="63">
+        <f>P63*N63</f>
         <v>0.13</v>
       </c>
-      <c r="R63" s="38"/>
-      <c r="S63" s="38"/>
+      <c r="R63" s="61"/>
+      <c r="S63" s="37"/>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
-      <c r="B64" s="48">
-        <f>ROW(B64) - ROW($B$9)</f>
+      <c r="B64" s="47">
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="C64" s="62" t="s">
+      <c r="C64" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="D64" s="65" t="s">
-        <v>75</v>
-      </c>
-      <c r="E64" s="65" t="s">
-        <v>142</v>
-      </c>
-      <c r="F64" s="65" t="s">
+      <c r="D64" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="E64" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="F64" s="38" t="s">
         <v>186</v>
       </c>
-      <c r="G64" s="65" t="s">
-        <v>241</v>
-      </c>
-      <c r="H64" s="65" t="s">
+      <c r="G64" s="38" t="s">
+        <v>240</v>
+      </c>
+      <c r="H64" s="38" t="s">
         <v>256</v>
       </c>
-      <c r="I64" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J64" s="65" t="s">
-        <v>336</v>
-      </c>
-      <c r="K64" s="65" t="s">
-        <v>377</v>
-      </c>
-      <c r="L64" s="65">
-        <v>1</v>
-      </c>
-      <c r="M64" s="65">
-        <f>L64*5</f>
-        <v>5</v>
-      </c>
-      <c r="N64" s="65">
+      <c r="I64" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J64" s="38" t="s">
+        <v>335</v>
+      </c>
+      <c r="K64" s="38" t="s">
+        <v>376</v>
+      </c>
+      <c r="L64" s="38">
+        <v>3</v>
+      </c>
+      <c r="M64" s="38">
+        <f t="shared" ref="M64" si="58">L64*5</f>
+        <v>15</v>
+      </c>
+      <c r="N64" s="38">
         <v>100</v>
       </c>
-      <c r="O64" s="59" t="s">
+      <c r="O64" s="58" t="s">
         <v>394</v>
       </c>
-      <c r="P64" s="66">
-        <v>1.8E-3</v>
-      </c>
-      <c r="Q64" s="66">
-        <f>P64*N64</f>
-        <v>0.18</v>
-      </c>
-      <c r="R64" s="64"/>
-      <c r="S64" s="37"/>
+      <c r="P64" s="39">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q64" s="39">
+        <f t="shared" ref="Q64" si="59">P64*N64</f>
+        <v>0.13</v>
+      </c>
+      <c r="R64" s="38"/>
+      <c r="S64" s="38"/>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
-      <c r="B65" s="49">
-        <f t="shared" si="0"/>
+      <c r="B65" s="46">
+        <f>ROW(B65) - ROW($B$9)</f>
         <v>56</v>
       </c>
-      <c r="C65" s="63" t="s">
+      <c r="C65" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="D65" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="E65" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="F65" s="38" t="s">
+      <c r="D65" s="62" t="s">
+        <v>75</v>
+      </c>
+      <c r="E65" s="62" t="s">
+        <v>142</v>
+      </c>
+      <c r="F65" s="62" t="s">
         <v>186</v>
       </c>
-      <c r="G65" s="38" t="s">
-        <v>242</v>
-      </c>
-      <c r="H65" s="38" t="s">
+      <c r="G65" s="62" t="s">
+        <v>241</v>
+      </c>
+      <c r="H65" s="62" t="s">
         <v>256</v>
       </c>
-      <c r="I65" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J65" s="38" t="s">
-        <v>337</v>
-      </c>
-      <c r="K65" s="38" t="s">
-        <v>378</v>
-      </c>
-      <c r="L65" s="38">
+      <c r="I65" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J65" s="62" t="s">
+        <v>336</v>
+      </c>
+      <c r="K65" s="62" t="s">
+        <v>377</v>
+      </c>
+      <c r="L65" s="62">
         <v>1</v>
       </c>
-      <c r="M65" s="38">
-        <f t="shared" ref="M65" si="60">L65*5</f>
+      <c r="M65" s="62">
+        <f>L65*5</f>
         <v>5</v>
       </c>
-      <c r="N65" s="38">
+      <c r="N65" s="62">
         <v>100</v>
       </c>
-      <c r="O65" s="61" t="s">
+      <c r="O65" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="P65" s="40">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q65" s="40">
-        <f t="shared" ref="Q65" si="61">P65*N65</f>
-        <v>0.13</v>
-      </c>
-      <c r="R65" s="38"/>
-      <c r="S65" s="38"/>
+      <c r="P65" s="63">
+        <v>1.8E-3</v>
+      </c>
+      <c r="Q65" s="63">
+        <f>P65*N65</f>
+        <v>0.18</v>
+      </c>
+      <c r="R65" s="61"/>
+      <c r="S65" s="37"/>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
-      <c r="B66" s="48">
-        <f>ROW(B66) - ROW($B$9)</f>
+      <c r="B66" s="47">
+        <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="C66" s="62" t="s">
+      <c r="C66" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="D66" s="65" t="s">
-        <v>77</v>
-      </c>
-      <c r="E66" s="65" t="s">
-        <v>144</v>
-      </c>
-      <c r="F66" s="65" t="s">
-        <v>187</v>
-      </c>
-      <c r="G66" s="65" t="s">
-        <v>243</v>
-      </c>
-      <c r="H66" s="65" t="s">
+      <c r="D66" s="64" t="s">
+        <v>76</v>
+      </c>
+      <c r="E66" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="F66" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="G66" s="38" t="s">
+        <v>242</v>
+      </c>
+      <c r="H66" s="38" t="s">
         <v>256</v>
       </c>
-      <c r="I66" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J66" s="65" t="s">
-        <v>401</v>
-      </c>
-      <c r="K66" s="65" t="s">
-        <v>372</v>
-      </c>
-      <c r="L66" s="65">
+      <c r="I66" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J66" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="K66" s="38" t="s">
+        <v>378</v>
+      </c>
+      <c r="L66" s="38">
         <v>1</v>
       </c>
-      <c r="M66" s="65">
-        <f>L66*5</f>
+      <c r="M66" s="38">
+        <f t="shared" ref="M66" si="60">L66*5</f>
         <v>5</v>
       </c>
-      <c r="N66" s="65">
+      <c r="N66" s="38">
         <v>100</v>
       </c>
-      <c r="O66" s="59" t="s">
+      <c r="O66" s="58" t="s">
         <v>394</v>
       </c>
-      <c r="P66" s="66">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="Q66" s="66">
-        <f>P66*N66</f>
-        <v>6.9999999999999993E-2</v>
-      </c>
-      <c r="R66" s="64"/>
-      <c r="S66" s="37"/>
+      <c r="P66" s="39">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q66" s="39">
+        <f t="shared" ref="Q66" si="61">P66*N66</f>
+        <v>0.13</v>
+      </c>
+      <c r="R66" s="38"/>
+      <c r="S66" s="38"/>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
-      <c r="B67" s="49">
-        <f t="shared" si="0"/>
+      <c r="B67" s="46">
+        <f>ROW(B67) - ROW($B$9)</f>
         <v>58</v>
       </c>
-      <c r="C67" s="63" t="s">
+      <c r="C67" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="D67" s="77" t="s">
-        <v>78</v>
-      </c>
-      <c r="E67" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="F67" s="38" t="s">
+      <c r="D67" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="E67" s="62" t="s">
+        <v>144</v>
+      </c>
+      <c r="F67" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="G67" s="38" t="s">
-        <v>244</v>
-      </c>
-      <c r="H67" s="38" t="s">
+      <c r="G67" s="62" t="s">
+        <v>243</v>
+      </c>
+      <c r="H67" s="62" t="s">
         <v>256</v>
       </c>
-      <c r="I67" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J67" s="38" t="s">
-        <v>382</v>
-      </c>
-      <c r="K67" s="38" t="s">
-        <v>379</v>
-      </c>
-      <c r="L67" s="38">
+      <c r="I67" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J67" s="62" t="s">
+        <v>401</v>
+      </c>
+      <c r="K67" s="62" t="s">
+        <v>372</v>
+      </c>
+      <c r="L67" s="62">
         <v>1</v>
       </c>
-      <c r="M67" s="38">
-        <f t="shared" ref="M67" si="62">L67*5</f>
+      <c r="M67" s="62">
+        <f>L67*5</f>
         <v>5</v>
       </c>
-      <c r="N67" s="38">
+      <c r="N67" s="62">
         <v>100</v>
       </c>
-      <c r="O67" s="61" t="s">
+      <c r="O67" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="P67" s="40">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="Q67" s="40">
-        <f t="shared" ref="Q67" si="63">P67*N67</f>
-        <v>0.05</v>
-      </c>
-      <c r="R67" s="38"/>
-      <c r="S67" s="38"/>
+      <c r="P67" s="63">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q67" s="63">
+        <f>P67*N67</f>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="R67" s="61"/>
+      <c r="S67" s="37"/>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
-      <c r="B68" s="48">
-        <f>ROW(B68) - ROW($B$9)</f>
+      <c r="B68" s="47">
+        <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="C68" s="62" t="s">
-        <v>397</v>
-      </c>
-      <c r="D68" s="65" t="s">
-        <v>79</v>
-      </c>
-      <c r="E68" s="65" t="s">
-        <v>146</v>
-      </c>
-      <c r="F68" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="G68" s="65" t="s">
-        <v>188</v>
-      </c>
-      <c r="H68" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="I68" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J68" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="K68" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="L68" s="65">
-        <v>2</v>
-      </c>
-      <c r="M68" s="65">
-        <f>L68*5</f>
-        <v>10</v>
-      </c>
-      <c r="N68" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="O68" s="59" t="s">
-        <v>381</v>
-      </c>
-      <c r="P68" s="66" t="s">
-        <v>381</v>
-      </c>
-      <c r="Q68" s="66" t="s">
-        <v>381</v>
-      </c>
-      <c r="R68" s="64"/>
-      <c r="S68" s="37"/>
+      <c r="C68" s="60" t="s">
+        <v>23</v>
+      </c>
+      <c r="D68" s="64" t="s">
+        <v>78</v>
+      </c>
+      <c r="E68" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F68" s="38" t="s">
+        <v>187</v>
+      </c>
+      <c r="G68" s="38" t="s">
+        <v>244</v>
+      </c>
+      <c r="H68" s="38" t="s">
+        <v>256</v>
+      </c>
+      <c r="I68" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J68" s="38" t="s">
+        <v>382</v>
+      </c>
+      <c r="K68" s="38" t="s">
+        <v>379</v>
+      </c>
+      <c r="L68" s="38">
+        <v>1</v>
+      </c>
+      <c r="M68" s="38">
+        <f t="shared" ref="M68" si="62">L68*5</f>
+        <v>5</v>
+      </c>
+      <c r="N68" s="38">
+        <v>100</v>
+      </c>
+      <c r="O68" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="P68" s="39">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="Q68" s="39">
+        <f t="shared" ref="Q68" si="63">P68*N68</f>
+        <v>0.05</v>
+      </c>
+      <c r="R68" s="38"/>
+      <c r="S68" s="38"/>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
-      <c r="B69" s="49">
+      <c r="B69" s="46">
+        <f>ROW(B69) - ROW($B$9)</f>
+        <v>60</v>
+      </c>
+      <c r="C69" s="89" t="s">
+        <v>397</v>
+      </c>
+      <c r="D69" s="90" t="s">
+        <v>79</v>
+      </c>
+      <c r="E69" s="90" t="s">
+        <v>146</v>
+      </c>
+      <c r="F69" s="90" t="s">
+        <v>381</v>
+      </c>
+      <c r="G69" s="90" t="s">
+        <v>188</v>
+      </c>
+      <c r="H69" s="90" t="s">
+        <v>381</v>
+      </c>
+      <c r="I69" s="90" t="s">
+        <v>381</v>
+      </c>
+      <c r="J69" s="90" t="s">
+        <v>381</v>
+      </c>
+      <c r="K69" s="90" t="s">
+        <v>381</v>
+      </c>
+      <c r="L69" s="90">
+        <v>2</v>
+      </c>
+      <c r="M69" s="90">
+        <f>L69*5</f>
+        <v>10</v>
+      </c>
+      <c r="N69" s="90" t="s">
+        <v>381</v>
+      </c>
+      <c r="O69" s="91" t="s">
+        <v>381</v>
+      </c>
+      <c r="P69" s="92" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q69" s="92" t="s">
+        <v>381</v>
+      </c>
+      <c r="R69" s="90"/>
+      <c r="S69" s="90"/>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A70" s="1"/>
+      <c r="B70" s="47">
         <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-      <c r="C69" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="C70" s="60" t="s">
         <v>398</v>
       </c>
-      <c r="D69" s="77" t="s">
+      <c r="D70" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="E69" s="38" t="s">
+      <c r="E70" s="38" t="s">
         <v>147</v>
       </c>
-      <c r="F69" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="G69" s="38" t="s">
+      <c r="F70" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="G70" s="38" t="s">
         <v>245</v>
       </c>
-      <c r="H69" s="38" t="s">
+      <c r="H70" s="38" t="s">
         <v>280</v>
       </c>
-      <c r="I69" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J69" s="38" t="s">
+      <c r="I70" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J70" s="38" t="s">
         <v>338</v>
       </c>
-      <c r="K69" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="L69" s="38">
+      <c r="K70" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L70" s="38">
         <v>1</v>
       </c>
-      <c r="M69" s="38">
-        <f t="shared" ref="M69" si="64">L69*5</f>
+      <c r="M70" s="38">
+        <f t="shared" ref="M70" si="64">L70*5</f>
         <v>5</v>
       </c>
-      <c r="N69" s="38">
+      <c r="N70" s="38">
         <v>6</v>
       </c>
-      <c r="O69" s="61" t="s">
+      <c r="O70" s="58" t="s">
         <v>394</v>
       </c>
-      <c r="P69" s="40">
+      <c r="P70" s="39">
         <v>0.54410000000000003</v>
       </c>
-      <c r="Q69" s="40">
-        <f t="shared" ref="Q69" si="65">P69*N69</f>
+      <c r="Q70" s="39">
+        <f t="shared" ref="Q70" si="65">P70*N70</f>
         <v>3.2646000000000002</v>
       </c>
-      <c r="R69" s="38"/>
-      <c r="S69" s="38"/>
-    </row>
-    <row r="70" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A70" s="1"/>
-      <c r="B70" s="48">
-        <f>ROW(B70) - ROW($B$9)</f>
-        <v>61</v>
-      </c>
-      <c r="C70" s="62" t="s">
+      <c r="R70" s="38"/>
+      <c r="S70" s="38"/>
+    </row>
+    <row r="71" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A71" s="1"/>
+      <c r="B71" s="46">
+        <f>ROW(B71) - ROW($B$9)</f>
+        <v>62</v>
+      </c>
+      <c r="C71" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="D70" s="65" t="s">
+      <c r="D71" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="E70" s="65" t="s">
+      <c r="E71" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="F70" s="65" t="s">
+      <c r="F71" s="62" t="s">
         <v>189</v>
       </c>
-      <c r="G70" s="65" t="s">
+      <c r="G71" s="62" t="s">
         <v>246</v>
       </c>
-      <c r="H70" s="65" t="s">
+      <c r="H71" s="62" t="s">
         <v>281</v>
       </c>
-      <c r="I70" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J70" s="65" t="s">
+      <c r="I71" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J71" s="62" t="s">
         <v>339</v>
       </c>
-      <c r="K70" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="L70" s="65">
+      <c r="K71" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="L71" s="62">
         <v>1</v>
       </c>
-      <c r="M70" s="65">
-        <f>L70*5</f>
+      <c r="M71" s="62">
+        <f>L71*5</f>
         <v>5</v>
       </c>
-      <c r="N70" s="65">
+      <c r="N71" s="62">
         <v>10</v>
       </c>
-      <c r="O70" s="59" t="s">
+      <c r="O71" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="P70" s="66">
+      <c r="P71" s="63">
         <v>7.6300000000000007E-2</v>
       </c>
-      <c r="Q70" s="66">
-        <f>P70*N70</f>
+      <c r="Q71" s="63">
+        <f>P71*N71</f>
         <v>0.76300000000000012</v>
       </c>
-      <c r="R70" s="64"/>
-      <c r="S70" s="37"/>
-    </row>
-    <row r="71" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A71" s="1"/>
-      <c r="B71" s="49">
+      <c r="R71" s="61"/>
+      <c r="S71" s="37"/>
+    </row>
+    <row r="72" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A72" s="1"/>
+      <c r="B72" s="47">
         <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-      <c r="C71" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="C72" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="D71" s="77" t="s">
+      <c r="D72" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="E71" s="38" t="s">
+      <c r="E72" s="38" t="s">
         <v>149</v>
       </c>
-      <c r="F71" s="38" t="s">
+      <c r="F72" s="38" t="s">
         <v>190</v>
       </c>
-      <c r="G71" s="38" t="s">
+      <c r="G72" s="38" t="s">
         <v>247</v>
       </c>
-      <c r="H71" s="38" t="s">
+      <c r="H72" s="38" t="s">
         <v>282</v>
       </c>
-      <c r="I71" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J71" s="38" t="s">
+      <c r="I72" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J72" s="38" t="s">
         <v>340</v>
       </c>
-      <c r="K71" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="L71" s="38">
+      <c r="K72" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L72" s="38">
         <v>1</v>
       </c>
-      <c r="M71" s="38">
-        <f t="shared" ref="M71" si="66">L71*5</f>
+      <c r="M72" s="38">
+        <f t="shared" ref="M72" si="66">L72*5</f>
         <v>5</v>
       </c>
-      <c r="N71" s="38">
+      <c r="N72" s="38">
         <v>6</v>
       </c>
-      <c r="O71" s="61" t="s">
+      <c r="O72" s="58" t="s">
         <v>394</v>
       </c>
-      <c r="P71" s="40">
+      <c r="P72" s="39">
         <v>3.1484999999999999</v>
       </c>
-      <c r="Q71" s="40">
-        <f t="shared" ref="Q71" si="67">P71*N71</f>
+      <c r="Q72" s="39">
+        <f t="shared" ref="Q72" si="67">P72*N72</f>
         <v>18.890999999999998</v>
       </c>
-      <c r="R71" s="38"/>
-      <c r="S71" s="38"/>
-    </row>
-    <row r="72" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A72" s="1"/>
-      <c r="B72" s="48">
-        <f>ROW(B72) - ROW($B$9)</f>
-        <v>63</v>
-      </c>
-      <c r="C72" s="62" t="s">
+      <c r="R72" s="38"/>
+      <c r="S72" s="38"/>
+    </row>
+    <row r="73" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A73" s="1"/>
+      <c r="B73" s="46">
+        <f>ROW(B73) - ROW($B$9)</f>
+        <v>64</v>
+      </c>
+      <c r="C73" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="D72" s="65" t="s">
+      <c r="D73" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="E72" s="65" t="s">
+      <c r="E73" s="62" t="s">
         <v>150</v>
       </c>
-      <c r="F72" s="65" t="s">
+      <c r="F73" s="62" t="s">
         <v>191</v>
       </c>
-      <c r="G72" s="65" t="s">
+      <c r="G73" s="62" t="s">
         <v>248</v>
       </c>
-      <c r="H72" s="65" t="s">
+      <c r="H73" s="62" t="s">
         <v>283</v>
       </c>
-      <c r="I72" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J72" s="65" t="s">
+      <c r="I73" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J73" s="62" t="s">
         <v>341</v>
       </c>
-      <c r="K72" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="L72" s="65">
+      <c r="K73" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="L73" s="62">
         <v>1</v>
       </c>
-      <c r="M72" s="65">
-        <f>L72*5</f>
+      <c r="M73" s="62">
+        <f>L73*5</f>
         <v>5</v>
       </c>
-      <c r="N72" s="65">
+      <c r="N73" s="62">
         <v>10</v>
       </c>
-      <c r="O72" s="59" t="s">
+      <c r="O73" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="P72" s="66">
+      <c r="P73" s="63">
         <v>0.10920000000000001</v>
       </c>
-      <c r="Q72" s="66">
-        <f>P72*N72</f>
+      <c r="Q73" s="63">
+        <f>P73*N73</f>
         <v>1.0920000000000001</v>
       </c>
-      <c r="R72" s="64"/>
-      <c r="S72" s="37"/>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A73" s="1"/>
-      <c r="B73" s="49">
-        <f t="shared" si="0"/>
-        <v>64</v>
-      </c>
-      <c r="C73" s="63" t="s">
-        <v>24</v>
-      </c>
-      <c r="D73" s="77" t="s">
-        <v>84</v>
-      </c>
-      <c r="E73" s="38" t="s">
-        <v>151</v>
-      </c>
-      <c r="F73" s="38" t="s">
-        <v>192</v>
-      </c>
-      <c r="G73" s="38" t="s">
-        <v>249</v>
-      </c>
-      <c r="H73" s="38" t="s">
-        <v>284</v>
-      </c>
-      <c r="I73" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J73" s="38" t="s">
-        <v>342</v>
-      </c>
-      <c r="K73" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="L73" s="38">
-        <v>4</v>
-      </c>
-      <c r="M73" s="38">
-        <f t="shared" ref="M73" si="68">L73*5</f>
-        <v>20</v>
-      </c>
-      <c r="N73" s="38">
-        <v>21</v>
-      </c>
-      <c r="O73" s="61" t="s">
-        <v>394</v>
-      </c>
-      <c r="P73" s="40">
-        <v>7.5918999999999999</v>
-      </c>
-      <c r="Q73" s="40">
-        <f t="shared" ref="Q73" si="69">P73*N73</f>
-        <v>159.4299</v>
-      </c>
-      <c r="R73" s="38"/>
-      <c r="S73" s="38"/>
+      <c r="R73" s="61"/>
+      <c r="S73" s="37"/>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
-      <c r="B74" s="48">
-        <f>ROW(B74) - ROW($B$9)</f>
+      <c r="B74" s="47">
+        <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="C74" s="62" t="s">
+      <c r="C74" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="D74" s="65" t="s">
-        <v>85</v>
-      </c>
-      <c r="E74" s="65" t="s">
-        <v>152</v>
-      </c>
-      <c r="F74" s="65" t="s">
-        <v>193</v>
-      </c>
-      <c r="G74" s="65" t="s">
-        <v>250</v>
-      </c>
-      <c r="H74" s="65" t="s">
-        <v>285</v>
-      </c>
-      <c r="I74" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J74" s="65" t="s">
-        <v>343</v>
-      </c>
-      <c r="K74" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="L74" s="65">
-        <v>2</v>
-      </c>
-      <c r="M74" s="65">
-        <f>L74*5</f>
-        <v>10</v>
-      </c>
-      <c r="N74" s="65">
-        <v>11</v>
-      </c>
-      <c r="O74" s="59" t="s">
+      <c r="D74" s="64" t="s">
+        <v>84</v>
+      </c>
+      <c r="E74" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="F74" s="38" t="s">
+        <v>192</v>
+      </c>
+      <c r="G74" s="38" t="s">
+        <v>249</v>
+      </c>
+      <c r="H74" s="38" t="s">
+        <v>284</v>
+      </c>
+      <c r="I74" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J74" s="38" t="s">
+        <v>342</v>
+      </c>
+      <c r="K74" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L74" s="38">
+        <v>4</v>
+      </c>
+      <c r="M74" s="38">
+        <f t="shared" ref="M74" si="68">L74*5</f>
+        <v>20</v>
+      </c>
+      <c r="N74" s="38">
+        <v>21</v>
+      </c>
+      <c r="O74" s="58" t="s">
         <v>394</v>
       </c>
-      <c r="P74" s="66">
-        <v>0.73819999999999997</v>
-      </c>
-      <c r="Q74" s="66">
-        <f>P74*N74</f>
-        <v>8.1202000000000005</v>
-      </c>
-      <c r="R74" s="64"/>
-      <c r="S74" s="37"/>
+      <c r="P74" s="39">
+        <v>7.5918999999999999</v>
+      </c>
+      <c r="Q74" s="39">
+        <f t="shared" ref="Q74" si="69">P74*N74</f>
+        <v>159.4299</v>
+      </c>
+      <c r="R74" s="38"/>
+      <c r="S74" s="38"/>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
-      <c r="B75" s="49">
+      <c r="B75" s="46">
+        <f>ROW(B75) - ROW($B$9)</f>
+        <v>66</v>
+      </c>
+      <c r="C75" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="D75" s="62" t="s">
+        <v>85</v>
+      </c>
+      <c r="E75" s="62" t="s">
+        <v>152</v>
+      </c>
+      <c r="F75" s="62" t="s">
+        <v>193</v>
+      </c>
+      <c r="G75" s="62" t="s">
+        <v>250</v>
+      </c>
+      <c r="H75" s="62" t="s">
+        <v>285</v>
+      </c>
+      <c r="I75" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J75" s="62" t="s">
+        <v>343</v>
+      </c>
+      <c r="K75" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="L75" s="62">
+        <v>2</v>
+      </c>
+      <c r="M75" s="62">
+        <f>L75*5</f>
+        <v>10</v>
+      </c>
+      <c r="N75" s="62">
+        <v>11</v>
+      </c>
+      <c r="O75" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="P75" s="63">
+        <v>0.73819999999999997</v>
+      </c>
+      <c r="Q75" s="63">
+        <f>P75*N75</f>
+        <v>8.1202000000000005</v>
+      </c>
+      <c r="R75" s="61"/>
+      <c r="S75" s="37"/>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A76" s="1"/>
+      <c r="B76" s="47">
         <f t="shared" si="0"/>
-        <v>66</v>
-      </c>
-      <c r="C75" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="C76" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="D75" s="77" t="s">
+      <c r="D76" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="E75" s="38" t="s">
+      <c r="E76" s="38" t="s">
         <v>153</v>
       </c>
-      <c r="F75" s="38" t="s">
+      <c r="F76" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="G75" s="38" t="s">
+      <c r="G76" s="38" t="s">
         <v>251</v>
       </c>
-      <c r="H75" s="38" t="s">
+      <c r="H76" s="38" t="s">
         <v>285</v>
       </c>
-      <c r="I75" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J75" s="38" t="s">
+      <c r="I76" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J76" s="38" t="s">
         <v>344</v>
       </c>
-      <c r="K75" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="L75" s="38">
+      <c r="K76" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L76" s="38">
         <v>1</v>
       </c>
-      <c r="M75" s="38">
-        <f t="shared" ref="M75" si="70">L75*5</f>
+      <c r="M76" s="38">
+        <f t="shared" ref="M76" si="70">L76*5</f>
         <v>5</v>
       </c>
-      <c r="N75" s="38">
+      <c r="N76" s="38">
         <v>6</v>
       </c>
-      <c r="O75" s="61" t="s">
+      <c r="O76" s="58" t="s">
         <v>394</v>
       </c>
-      <c r="P75" s="40">
+      <c r="P76" s="39">
         <v>0.6905</v>
       </c>
-      <c r="Q75" s="40">
-        <f t="shared" ref="Q75" si="71">P75*N75</f>
+      <c r="Q76" s="39">
+        <f t="shared" ref="Q76" si="71">P76*N76</f>
         <v>4.1429999999999998</v>
       </c>
-      <c r="R75" s="38"/>
-      <c r="S75" s="38"/>
-    </row>
-    <row r="76" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A76" s="1"/>
-      <c r="B76" s="48">
-        <f>ROW(B76) - ROW($B$9)</f>
-        <v>67</v>
-      </c>
-      <c r="C76" s="62" t="s">
+      <c r="R76" s="38"/>
+      <c r="S76" s="38"/>
+    </row>
+    <row r="77" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A77" s="1"/>
+      <c r="B77" s="46">
+        <f>ROW(B77) - ROW($B$9)</f>
+        <v>68</v>
+      </c>
+      <c r="C77" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="D76" s="65" t="s">
+      <c r="D77" s="62" t="s">
         <v>87</v>
       </c>
-      <c r="E76" s="65" t="s">
+      <c r="E77" s="62" t="s">
         <v>154</v>
       </c>
-      <c r="F76" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="G76" s="65" t="s">
+      <c r="F77" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="G77" s="62" t="s">
         <v>194</v>
       </c>
-      <c r="H76" s="65" t="s">
+      <c r="H77" s="62" t="s">
         <v>286</v>
       </c>
-      <c r="I76" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J76" s="65" t="s">
+      <c r="I77" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J77" s="62" t="s">
         <v>345</v>
       </c>
-      <c r="K76" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="L76" s="65">
+      <c r="K77" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="L77" s="62">
         <v>1</v>
       </c>
-      <c r="M76" s="65">
-        <f>L76*5</f>
+      <c r="M77" s="62">
+        <f>L77*5</f>
         <v>5</v>
       </c>
-      <c r="N76" s="65">
+      <c r="N77" s="62">
         <v>6</v>
       </c>
-      <c r="O76" s="59" t="s">
+      <c r="O77" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="P76" s="66">
+      <c r="P77" s="63">
         <v>20.79</v>
       </c>
-      <c r="Q76" s="66">
-        <f>P76*N76</f>
+      <c r="Q77" s="63">
+        <f>P77*N77</f>
         <v>124.74</v>
       </c>
-      <c r="R76" s="64"/>
-      <c r="S76" s="37"/>
-    </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A77" s="1"/>
-      <c r="B77" s="49">
-        <f t="shared" si="0"/>
-        <v>68</v>
-      </c>
-      <c r="C77" s="63" t="s">
-        <v>24</v>
-      </c>
-      <c r="D77" s="77" t="s">
-        <v>88</v>
-      </c>
-      <c r="E77" s="38" t="s">
-        <v>155</v>
-      </c>
-      <c r="F77" s="38" t="s">
-        <v>195</v>
-      </c>
-      <c r="G77" s="38" t="s">
-        <v>252</v>
-      </c>
-      <c r="H77" s="38" t="s">
-        <v>287</v>
-      </c>
-      <c r="I77" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J77" s="38" t="s">
-        <v>346</v>
-      </c>
-      <c r="K77" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="L77" s="38">
-        <v>1</v>
-      </c>
-      <c r="M77" s="38">
-        <f t="shared" ref="M77" si="72">L77*5</f>
-        <v>5</v>
-      </c>
-      <c r="N77" s="38">
-        <v>6</v>
-      </c>
-      <c r="O77" s="61" t="s">
-        <v>394</v>
-      </c>
-      <c r="P77" s="40">
-        <v>11.400499999999999</v>
-      </c>
-      <c r="Q77" s="40">
-        <f t="shared" ref="Q77" si="73">P77*N77</f>
-        <v>68.402999999999992</v>
-      </c>
-      <c r="R77" s="38"/>
-      <c r="S77" s="38"/>
+      <c r="R77" s="61"/>
+      <c r="S77" s="37"/>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
-      <c r="B78" s="48">
-        <f>ROW(B78) - ROW($B$9)</f>
+      <c r="B78" s="47">
+        <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="C78" s="62" t="s">
+      <c r="C78" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="D78" s="65" t="s">
+      <c r="D78" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="E78" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="F78" s="38" t="s">
+        <v>195</v>
+      </c>
+      <c r="G78" s="38" t="s">
+        <v>252</v>
+      </c>
+      <c r="H78" s="38" t="s">
+        <v>287</v>
+      </c>
+      <c r="I78" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J78" s="38" t="s">
+        <v>346</v>
+      </c>
+      <c r="K78" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L78" s="38">
+        <v>1</v>
+      </c>
+      <c r="M78" s="38">
+        <f t="shared" ref="M78" si="72">L78*5</f>
+        <v>5</v>
+      </c>
+      <c r="N78" s="38">
+        <v>6</v>
+      </c>
+      <c r="O78" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="P78" s="39">
+        <v>11.400499999999999</v>
+      </c>
+      <c r="Q78" s="39">
+        <f t="shared" ref="Q78" si="73">P78*N78</f>
+        <v>68.402999999999992</v>
+      </c>
+      <c r="R78" s="38"/>
+      <c r="S78" s="38"/>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A79" s="1"/>
+      <c r="B79" s="46">
+        <f>ROW(B79) - ROW($B$9)</f>
+        <v>70</v>
+      </c>
+      <c r="C79" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="D79" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="E78" s="65" t="s">
+      <c r="E79" s="62" t="s">
         <v>156</v>
       </c>
-      <c r="F78" s="65" t="s">
+      <c r="F79" s="62" t="s">
         <v>196</v>
       </c>
-      <c r="G78" s="65" t="s">
+      <c r="G79" s="62" t="s">
         <v>253</v>
       </c>
-      <c r="H78" s="65" t="s">
+      <c r="H79" s="62" t="s">
         <v>288</v>
       </c>
-      <c r="I78" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="J78" s="65" t="s">
+      <c r="I79" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="J79" s="62" t="s">
         <v>347</v>
       </c>
-      <c r="K78" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="L78" s="65">
+      <c r="K79" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="L79" s="62">
         <v>1</v>
       </c>
-      <c r="M78" s="65">
-        <f>L78*5</f>
+      <c r="M79" s="62">
+        <f>L79*5</f>
         <v>5</v>
       </c>
-      <c r="N78" s="65">
+      <c r="N79" s="62">
         <v>6</v>
       </c>
-      <c r="O78" s="59" t="s">
+      <c r="O79" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="P78" s="66">
+      <c r="P79" s="63">
         <v>2.8128000000000002</v>
       </c>
-      <c r="Q78" s="66">
-        <f>P78*N78</f>
+      <c r="Q79" s="63">
+        <f>P79*N79</f>
         <v>16.876800000000003</v>
       </c>
-      <c r="R78" s="64"/>
-      <c r="S78" s="37"/>
-    </row>
-    <row r="79" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="1"/>
-      <c r="B79" s="49">
+      <c r="R79" s="61"/>
+      <c r="S79" s="37"/>
+    </row>
+    <row r="80" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A80" s="1"/>
+      <c r="B80" s="47">
         <f t="shared" si="0"/>
-        <v>70</v>
-      </c>
-      <c r="C79" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="C80" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="D79" s="77" t="s">
+      <c r="D80" s="64" t="s">
         <v>90</v>
       </c>
-      <c r="E79" s="38" t="s">
+      <c r="E80" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="F79" s="38" t="s">
+      <c r="F80" s="38" t="s">
         <v>197</v>
       </c>
-      <c r="G79" s="38" t="s">
+      <c r="G80" s="38" t="s">
         <v>254</v>
       </c>
-      <c r="H79" s="38" t="s">
+      <c r="H80" s="38" t="s">
         <v>289</v>
       </c>
-      <c r="I79" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J79" s="38" t="s">
+      <c r="I80" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J80" s="38" t="s">
         <v>348</v>
       </c>
-      <c r="K79" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="L79" s="38">
+      <c r="K80" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L80" s="38">
         <v>1</v>
       </c>
-      <c r="M79" s="38">
-        <f t="shared" ref="M79" si="74">L79*5</f>
+      <c r="M80" s="38">
+        <f t="shared" ref="M80:M83" si="74">L80*5</f>
         <v>5</v>
       </c>
-      <c r="N79" s="38">
+      <c r="N80" s="38">
         <v>10</v>
       </c>
-      <c r="O79" s="61" t="s">
+      <c r="O80" s="58" t="s">
         <v>394</v>
       </c>
-      <c r="P79" s="40">
+      <c r="P80" s="39">
         <v>8.3400000000000002E-2</v>
       </c>
-      <c r="Q79" s="40">
-        <f t="shared" ref="Q79" si="75">P79*N79</f>
+      <c r="Q80" s="39">
+        <f t="shared" ref="Q80" si="75">P80*N80</f>
         <v>0.83400000000000007</v>
       </c>
-      <c r="R79" s="38"/>
-      <c r="S79" s="38"/>
-    </row>
-    <row r="80" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="1"/>
-      <c r="B80" s="42"/>
-      <c r="C80" s="43"/>
-      <c r="D80" s="44"/>
-      <c r="E80" s="45"/>
-      <c r="F80" s="46"/>
-      <c r="G80" s="47"/>
-      <c r="H80" s="46"/>
-      <c r="I80" s="47"/>
-      <c r="J80" s="46"/>
-      <c r="K80" s="47"/>
-      <c r="L80" s="47"/>
-      <c r="M80" s="47"/>
-      <c r="N80" s="75" t="s">
+      <c r="R80" s="38"/>
+      <c r="S80" s="38"/>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A81" s="1"/>
+      <c r="B81" s="47">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="C81" s="82" t="s">
+        <v>435</v>
+      </c>
+      <c r="D81" s="93" t="s">
+        <v>440</v>
+      </c>
+      <c r="E81" s="84" t="s">
+        <v>439</v>
+      </c>
+      <c r="F81" s="84" t="s">
+        <v>393</v>
+      </c>
+      <c r="G81" s="84" t="s">
+        <v>436</v>
+      </c>
+      <c r="H81" s="84" t="s">
+        <v>438</v>
+      </c>
+      <c r="I81" s="84" t="s">
+        <v>381</v>
+      </c>
+      <c r="J81" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="K81" s="84" t="s">
+        <v>381</v>
+      </c>
+      <c r="L81" s="84">
+        <v>1</v>
+      </c>
+      <c r="M81" s="84">
+        <f t="shared" si="74"/>
         <v>5</v>
       </c>
-      <c r="O80" s="76"/>
-      <c r="P80" s="76"/>
-      <c r="Q80" s="50">
-        <f>SUM(Q10:Q79)</f>
-        <v>594.24969999999996</v>
-      </c>
-      <c r="R80" s="71"/>
-      <c r="S80" s="72"/>
-    </row>
-    <row r="81" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="1"/>
-      <c r="B81" s="25"/>
-      <c r="C81" s="36"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="10"/>
-      <c r="F81" s="10"/>
-      <c r="G81" s="10"/>
-      <c r="H81" s="10"/>
-      <c r="I81" s="10"/>
-      <c r="J81" s="10"/>
-      <c r="K81" s="10"/>
-      <c r="L81" s="10"/>
-      <c r="M81" s="10"/>
-      <c r="N81" s="75" t="s">
+      <c r="N81" s="84">
         <v>6</v>
       </c>
-      <c r="O81" s="76"/>
-      <c r="P81" s="76"/>
-      <c r="Q81" s="51">
-        <f>Q80/5</f>
-        <v>118.84993999999999</v>
-      </c>
-      <c r="R81" s="73"/>
-      <c r="S81" s="74"/>
+      <c r="O81" s="86" t="s">
+        <v>394</v>
+      </c>
+      <c r="P81" s="87">
+        <v>1.5643</v>
+      </c>
+      <c r="Q81" s="87">
+        <f>P81*N81</f>
+        <v>9.3857999999999997</v>
+      </c>
+      <c r="R81" s="84"/>
+      <c r="S81" s="84"/>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A82" s="1"/>
+      <c r="B82" s="47">
+        <f t="shared" ref="B82:B83" si="76">ROW(B82) - ROW($B$9)</f>
+        <v>73</v>
+      </c>
+      <c r="C82" s="60" t="s">
+        <v>435</v>
+      </c>
+      <c r="D82" s="94" t="s">
+        <v>440</v>
+      </c>
+      <c r="E82" s="38" t="s">
+        <v>443</v>
+      </c>
+      <c r="F82" s="38" t="s">
+        <v>393</v>
+      </c>
+      <c r="G82" s="38" t="s">
+        <v>441</v>
+      </c>
+      <c r="H82" s="38" t="s">
+        <v>438</v>
+      </c>
+      <c r="I82" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J82" s="38" t="s">
+        <v>442</v>
+      </c>
+      <c r="K82" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="L82" s="38">
+        <v>1</v>
+      </c>
+      <c r="M82" s="38">
+        <f t="shared" si="74"/>
+        <v>5</v>
+      </c>
+      <c r="N82" s="38">
+        <v>6</v>
+      </c>
+      <c r="O82" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="P82" s="39">
+        <v>2.0146999999999999</v>
+      </c>
+      <c r="Q82" s="39">
+        <f>P82*N82</f>
+        <v>12.088200000000001</v>
+      </c>
+      <c r="R82" s="38"/>
+      <c r="S82" s="38"/>
+    </row>
+    <row r="83" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="1"/>
+      <c r="B83" s="47">
+        <f t="shared" si="76"/>
+        <v>74</v>
+      </c>
+      <c r="C83" s="82" t="s">
+        <v>435</v>
+      </c>
+      <c r="D83" s="93" t="s">
+        <v>440</v>
+      </c>
+      <c r="E83" s="84" t="s">
+        <v>445</v>
+      </c>
+      <c r="F83" s="84" t="s">
+        <v>393</v>
+      </c>
+      <c r="G83" s="84" t="s">
+        <v>444</v>
+      </c>
+      <c r="H83" s="84" t="s">
+        <v>438</v>
+      </c>
+      <c r="I83" s="84" t="s">
+        <v>381</v>
+      </c>
+      <c r="J83" s="84" t="s">
+        <v>446</v>
+      </c>
+      <c r="K83" s="84" t="s">
+        <v>381</v>
+      </c>
+      <c r="L83" s="84">
+        <v>1</v>
+      </c>
+      <c r="M83" s="84">
+        <f t="shared" si="74"/>
+        <v>5</v>
+      </c>
+      <c r="N83" s="84">
+        <v>6</v>
+      </c>
+      <c r="O83" s="86" t="s">
+        <v>394</v>
+      </c>
+      <c r="P83" s="87">
+        <v>0.80110000000000003</v>
+      </c>
+      <c r="Q83" s="87">
+        <f>P83*N83</f>
+        <v>4.8066000000000004</v>
+      </c>
+      <c r="R83" s="84"/>
+      <c r="S83" s="84"/>
+    </row>
+    <row r="84" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="1"/>
+      <c r="B84" s="40"/>
+      <c r="C84" s="41"/>
+      <c r="D84" s="42"/>
+      <c r="E84" s="43"/>
+      <c r="F84" s="44"/>
+      <c r="G84" s="45"/>
+      <c r="H84" s="44"/>
+      <c r="I84" s="45"/>
+      <c r="J84" s="44"/>
+      <c r="K84" s="45"/>
+      <c r="L84" s="45"/>
+      <c r="M84" s="45"/>
+      <c r="N84" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="O84" s="75"/>
+      <c r="P84" s="75"/>
+      <c r="Q84" s="48">
+        <f>SUM(Q10:Q81)</f>
+        <v>687.65389999999991</v>
+      </c>
+      <c r="R84" s="70"/>
+      <c r="S84" s="71"/>
+    </row>
+    <row r="85" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="1"/>
+      <c r="B85" s="25"/>
+      <c r="C85" s="36"/>
+      <c r="D85" s="9"/>
+      <c r="E85" s="10"/>
+      <c r="F85" s="10"/>
+      <c r="G85" s="10"/>
+      <c r="H85" s="10"/>
+      <c r="I85" s="10"/>
+      <c r="J85" s="10"/>
+      <c r="K85" s="10"/>
+      <c r="L85" s="10"/>
+      <c r="M85" s="10"/>
+      <c r="N85" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="O85" s="75"/>
+      <c r="P85" s="75"/>
+      <c r="Q85" s="49">
+        <f>Q84/5</f>
+        <v>137.53077999999999</v>
+      </c>
+      <c r="R85" s="72"/>
+      <c r="S85" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R80:S81"/>
-    <mergeCell ref="N80:P80"/>
-    <mergeCell ref="N81:P81"/>
+    <mergeCell ref="R84:S85"/>
+    <mergeCell ref="N84:P84"/>
+    <mergeCell ref="N85:P85"/>
   </mergeCells>
+  <phoneticPr fontId="27" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1" xr:uid="{83330362-F0C7-46EF-A396-98923760856E}"/>
     <hyperlink ref="O11" r:id="rId2" xr:uid="{DB12CDE4-1E23-4DC3-AED9-E8614EF62035}"/>
@@ -6573,68 +6954,73 @@
     <hyperlink ref="O16" r:id="rId6" xr:uid="{C55E2959-5F99-44C9-9C77-90D75CDD51E7}"/>
     <hyperlink ref="O18" r:id="rId7" xr:uid="{324C4BE8-EFA4-4D83-B94F-D73DA115B8D6}"/>
     <hyperlink ref="O19" r:id="rId8" xr:uid="{AC68A078-5AC7-4F87-AF9E-83FA24A08968}"/>
-    <hyperlink ref="O20" r:id="rId9" xr:uid="{65531464-2710-4ACA-B558-50D49C4EBFD5}"/>
-    <hyperlink ref="O21" r:id="rId10" xr:uid="{D294B23C-79F3-45A3-B0CB-83065DB0DFBE}"/>
-    <hyperlink ref="O22" r:id="rId11" xr:uid="{35BDF612-2500-4AAB-9A3C-389710CC8A13}"/>
-    <hyperlink ref="O24" r:id="rId12" xr:uid="{09995E25-E46C-41E4-A215-3AFA7BA38097}"/>
-    <hyperlink ref="O25" r:id="rId13" xr:uid="{D4A1ED2E-51BE-4BFB-8C67-4A5FBF716E81}"/>
-    <hyperlink ref="O26" r:id="rId14" xr:uid="{D9FDF2FF-7F17-4E92-BB05-1CB02A88AE46}"/>
-    <hyperlink ref="O27" r:id="rId15" xr:uid="{E5092E06-E380-4B03-80D7-16C56A0BFD76}"/>
-    <hyperlink ref="O28" r:id="rId16" xr:uid="{119F4900-2975-432E-9C8B-99A1B6DAEB20}"/>
-    <hyperlink ref="O29" r:id="rId17" xr:uid="{352461EC-DA11-46E9-92D4-B9C068E3C180}"/>
-    <hyperlink ref="O30" r:id="rId18" xr:uid="{A836E869-1683-4F1A-B273-33D366B89F95}"/>
-    <hyperlink ref="O31" r:id="rId19" xr:uid="{435EC6F6-0FAD-4A31-A582-C246D57C7D6F}"/>
-    <hyperlink ref="O32" r:id="rId20" xr:uid="{7DB9ABA3-1F74-4C4A-8795-93F417A50B5B}"/>
-    <hyperlink ref="O33" r:id="rId21" xr:uid="{5B4AF0FE-AE45-4674-A0B6-D52529DBEA42}"/>
-    <hyperlink ref="O36" r:id="rId22" xr:uid="{7898B0DE-B99C-422B-93A1-C64000A2710F}"/>
-    <hyperlink ref="O37" r:id="rId23" xr:uid="{60F5EA99-FC5D-42DA-83AB-2503145247E5}"/>
-    <hyperlink ref="O38" r:id="rId24" xr:uid="{6EA8AF8A-1CB3-451C-A1FF-53A54C702D59}"/>
-    <hyperlink ref="O39" r:id="rId25" xr:uid="{B317581D-06A6-4EB4-891A-C0C139D8E474}"/>
-    <hyperlink ref="O40" r:id="rId26" xr:uid="{FDCBF760-4B93-4276-A3BA-7715546260C9}"/>
-    <hyperlink ref="O41" r:id="rId27" xr:uid="{8E648B41-42DE-4F16-91A7-315D4267BDAC}"/>
-    <hyperlink ref="O42" r:id="rId28" xr:uid="{90524ED7-C00A-44AB-8E3C-CF9BE029B7F7}"/>
-    <hyperlink ref="O43" r:id="rId29" xr:uid="{1F66A3F1-2879-418E-A260-EBF5779ADB9A}"/>
-    <hyperlink ref="O44" r:id="rId30" xr:uid="{D6253230-F78F-4F57-841E-6E32DA3F6F6B}"/>
-    <hyperlink ref="O46" r:id="rId31" xr:uid="{F92A08BD-DC56-49CB-BB49-C672D65AF7B6}"/>
-    <hyperlink ref="O45" r:id="rId32" xr:uid="{C983EB1D-0C91-45E9-BE66-3F32EFEBF11E}"/>
-    <hyperlink ref="O49" r:id="rId33" xr:uid="{D166F96C-85E9-4ECC-95F1-3B236295E9EA}"/>
-    <hyperlink ref="O50" r:id="rId34" xr:uid="{74E89379-FE6D-4A6D-9086-2E5F06F276D3}"/>
-    <hyperlink ref="O51" r:id="rId35" xr:uid="{9500BE23-7086-4D84-96D7-5D20AD5CA396}"/>
-    <hyperlink ref="O52" r:id="rId36" xr:uid="{7959F19A-CC8B-4CCD-9543-CFA937F95FE0}"/>
-    <hyperlink ref="O53" r:id="rId37" xr:uid="{C1A12F9C-529D-4C71-B8D0-1E662F17A4CF}"/>
-    <hyperlink ref="O54" r:id="rId38" xr:uid="{9FB226EB-05D0-4756-90EC-AB74DF432825}"/>
-    <hyperlink ref="O55" r:id="rId39" xr:uid="{2A083DAE-370B-4D83-8484-60F664F4D0FB}"/>
-    <hyperlink ref="O56" r:id="rId40" xr:uid="{2C97F014-F5E8-4B24-963D-FE80A7631953}"/>
-    <hyperlink ref="O57" r:id="rId41" xr:uid="{6F3D2A4A-F4D5-4F39-AA76-C26734A9F58D}"/>
-    <hyperlink ref="O58" r:id="rId42" xr:uid="{071B56B4-D644-4DBA-9C24-EAA419F04152}"/>
-    <hyperlink ref="O59" r:id="rId43" xr:uid="{FCEB1084-02FC-4396-A776-E5A840FCDC5C}"/>
-    <hyperlink ref="O60" r:id="rId44" xr:uid="{E366D270-8EAC-4607-849D-1D7110BF13C6}"/>
-    <hyperlink ref="O61" r:id="rId45" xr:uid="{21BB671E-15DA-47B2-9961-72F25541C5E2}"/>
-    <hyperlink ref="O62" r:id="rId46" xr:uid="{4F5D2B75-A643-4920-899E-536F91142938}"/>
-    <hyperlink ref="O63" r:id="rId47" xr:uid="{D6C832CC-6FCE-4894-B42E-1075C3474637}"/>
-    <hyperlink ref="O64" r:id="rId48" xr:uid="{46C226E9-81B8-4812-9A33-DA13B84C252D}"/>
-    <hyperlink ref="O65" r:id="rId49" xr:uid="{08B69DB7-9AAD-4B1C-BFEB-486DA2F5A169}"/>
-    <hyperlink ref="O66" r:id="rId50" xr:uid="{C942BC27-6E68-427F-9EC4-5A6A9F3691F9}"/>
-    <hyperlink ref="O67" r:id="rId51" xr:uid="{D6B78B63-B011-4041-9416-EA6C7F8D8AE7}"/>
-    <hyperlink ref="O69" r:id="rId52" xr:uid="{8429BF53-DDFF-45A2-9753-DFDC3A7EC73E}"/>
-    <hyperlink ref="O70" r:id="rId53" xr:uid="{69BB30E6-FCE6-4DD2-9033-50DBAEAFB28E}"/>
-    <hyperlink ref="O71" r:id="rId54" xr:uid="{9DBB4DF3-112E-4A0A-A8C2-64BB1FCB650F}"/>
-    <hyperlink ref="O72" r:id="rId55" xr:uid="{749C77DE-6558-4DB6-8849-7A73C148D4CE}"/>
-    <hyperlink ref="O73" r:id="rId56" xr:uid="{5FBFDDE4-D8E1-4DDC-8314-D97DA5D132A5}"/>
-    <hyperlink ref="O74" r:id="rId57" xr:uid="{FD33955C-3AAA-49E7-ADBD-08C8E8316B63}"/>
-    <hyperlink ref="O75" r:id="rId58" xr:uid="{10F92991-AF57-4F4E-ACEC-133226566204}"/>
-    <hyperlink ref="O76" r:id="rId59" xr:uid="{6027C0A4-5D1E-4433-85BF-CD2F57D6DA89}"/>
-    <hyperlink ref="O77" r:id="rId60" xr:uid="{29DDBCD9-DE51-47A5-B3C6-827913DA2387}"/>
-    <hyperlink ref="O78" r:id="rId61" xr:uid="{FC388204-E09E-47D1-A054-C8455D575E2E}"/>
-    <hyperlink ref="O79" r:id="rId62" xr:uid="{C573F08C-CF21-426E-B62B-392C975BBEB8}"/>
-    <hyperlink ref="O23" r:id="rId63" xr:uid="{A2463247-A92E-46A4-B1F2-C7859F430396}"/>
+    <hyperlink ref="O21" r:id="rId9" xr:uid="{65531464-2710-4ACA-B558-50D49C4EBFD5}"/>
+    <hyperlink ref="O22" r:id="rId10" xr:uid="{D294B23C-79F3-45A3-B0CB-83065DB0DFBE}"/>
+    <hyperlink ref="O23" r:id="rId11" xr:uid="{35BDF612-2500-4AAB-9A3C-389710CC8A13}"/>
+    <hyperlink ref="O25" r:id="rId12" xr:uid="{09995E25-E46C-41E4-A215-3AFA7BA38097}"/>
+    <hyperlink ref="O26" r:id="rId13" xr:uid="{D4A1ED2E-51BE-4BFB-8C67-4A5FBF716E81}"/>
+    <hyperlink ref="O27" r:id="rId14" xr:uid="{D9FDF2FF-7F17-4E92-BB05-1CB02A88AE46}"/>
+    <hyperlink ref="O28" r:id="rId15" xr:uid="{E5092E06-E380-4B03-80D7-16C56A0BFD76}"/>
+    <hyperlink ref="O29" r:id="rId16" xr:uid="{119F4900-2975-432E-9C8B-99A1B6DAEB20}"/>
+    <hyperlink ref="O30" r:id="rId17" xr:uid="{352461EC-DA11-46E9-92D4-B9C068E3C180}"/>
+    <hyperlink ref="O31" r:id="rId18" xr:uid="{A836E869-1683-4F1A-B273-33D366B89F95}"/>
+    <hyperlink ref="O32" r:id="rId19" xr:uid="{435EC6F6-0FAD-4A31-A582-C246D57C7D6F}"/>
+    <hyperlink ref="O33" r:id="rId20" xr:uid="{7DB9ABA3-1F74-4C4A-8795-93F417A50B5B}"/>
+    <hyperlink ref="O34" r:id="rId21" xr:uid="{5B4AF0FE-AE45-4674-A0B6-D52529DBEA42}"/>
+    <hyperlink ref="O37" r:id="rId22" xr:uid="{7898B0DE-B99C-422B-93A1-C64000A2710F}"/>
+    <hyperlink ref="O38" r:id="rId23" xr:uid="{60F5EA99-FC5D-42DA-83AB-2503145247E5}"/>
+    <hyperlink ref="O39" r:id="rId24" xr:uid="{6EA8AF8A-1CB3-451C-A1FF-53A54C702D59}"/>
+    <hyperlink ref="O40" r:id="rId25" xr:uid="{B317581D-06A6-4EB4-891A-C0C139D8E474}"/>
+    <hyperlink ref="O41" r:id="rId26" xr:uid="{FDCBF760-4B93-4276-A3BA-7715546260C9}"/>
+    <hyperlink ref="O42" r:id="rId27" xr:uid="{8E648B41-42DE-4F16-91A7-315D4267BDAC}"/>
+    <hyperlink ref="O43" r:id="rId28" xr:uid="{90524ED7-C00A-44AB-8E3C-CF9BE029B7F7}"/>
+    <hyperlink ref="O44" r:id="rId29" xr:uid="{1F66A3F1-2879-418E-A260-EBF5779ADB9A}"/>
+    <hyperlink ref="O45" r:id="rId30" xr:uid="{D6253230-F78F-4F57-841E-6E32DA3F6F6B}"/>
+    <hyperlink ref="O47" r:id="rId31" xr:uid="{F92A08BD-DC56-49CB-BB49-C672D65AF7B6}"/>
+    <hyperlink ref="O46" r:id="rId32" xr:uid="{C983EB1D-0C91-45E9-BE66-3F32EFEBF11E}"/>
+    <hyperlink ref="O50" r:id="rId33" xr:uid="{D166F96C-85E9-4ECC-95F1-3B236295E9EA}"/>
+    <hyperlink ref="O51" r:id="rId34" xr:uid="{74E89379-FE6D-4A6D-9086-2E5F06F276D3}"/>
+    <hyperlink ref="O52" r:id="rId35" xr:uid="{9500BE23-7086-4D84-96D7-5D20AD5CA396}"/>
+    <hyperlink ref="O53" r:id="rId36" xr:uid="{7959F19A-CC8B-4CCD-9543-CFA937F95FE0}"/>
+    <hyperlink ref="O54" r:id="rId37" xr:uid="{C1A12F9C-529D-4C71-B8D0-1E662F17A4CF}"/>
+    <hyperlink ref="O55" r:id="rId38" xr:uid="{9FB226EB-05D0-4756-90EC-AB74DF432825}"/>
+    <hyperlink ref="O56" r:id="rId39" xr:uid="{2A083DAE-370B-4D83-8484-60F664F4D0FB}"/>
+    <hyperlink ref="O57" r:id="rId40" xr:uid="{2C97F014-F5E8-4B24-963D-FE80A7631953}"/>
+    <hyperlink ref="O58" r:id="rId41" xr:uid="{6F3D2A4A-F4D5-4F39-AA76-C26734A9F58D}"/>
+    <hyperlink ref="O59" r:id="rId42" xr:uid="{071B56B4-D644-4DBA-9C24-EAA419F04152}"/>
+    <hyperlink ref="O60" r:id="rId43" xr:uid="{FCEB1084-02FC-4396-A776-E5A840FCDC5C}"/>
+    <hyperlink ref="O61" r:id="rId44" xr:uid="{E366D270-8EAC-4607-849D-1D7110BF13C6}"/>
+    <hyperlink ref="O62" r:id="rId45" xr:uid="{21BB671E-15DA-47B2-9961-72F25541C5E2}"/>
+    <hyperlink ref="O63" r:id="rId46" xr:uid="{4F5D2B75-A643-4920-899E-536F91142938}"/>
+    <hyperlink ref="O64" r:id="rId47" xr:uid="{D6C832CC-6FCE-4894-B42E-1075C3474637}"/>
+    <hyperlink ref="O65" r:id="rId48" xr:uid="{46C226E9-81B8-4812-9A33-DA13B84C252D}"/>
+    <hyperlink ref="O66" r:id="rId49" xr:uid="{08B69DB7-9AAD-4B1C-BFEB-486DA2F5A169}"/>
+    <hyperlink ref="O67" r:id="rId50" xr:uid="{C942BC27-6E68-427F-9EC4-5A6A9F3691F9}"/>
+    <hyperlink ref="O68" r:id="rId51" xr:uid="{D6B78B63-B011-4041-9416-EA6C7F8D8AE7}"/>
+    <hyperlink ref="O70" r:id="rId52" xr:uid="{8429BF53-DDFF-45A2-9753-DFDC3A7EC73E}"/>
+    <hyperlink ref="O71" r:id="rId53" xr:uid="{69BB30E6-FCE6-4DD2-9033-50DBAEAFB28E}"/>
+    <hyperlink ref="O72" r:id="rId54" xr:uid="{9DBB4DF3-112E-4A0A-A8C2-64BB1FCB650F}"/>
+    <hyperlink ref="O73" r:id="rId55" xr:uid="{749C77DE-6558-4DB6-8849-7A73C148D4CE}"/>
+    <hyperlink ref="O74" r:id="rId56" xr:uid="{5FBFDDE4-D8E1-4DDC-8314-D97DA5D132A5}"/>
+    <hyperlink ref="O75" r:id="rId57" xr:uid="{FD33955C-3AAA-49E7-ADBD-08C8E8316B63}"/>
+    <hyperlink ref="O76" r:id="rId58" xr:uid="{10F92991-AF57-4F4E-ACEC-133226566204}"/>
+    <hyperlink ref="O77" r:id="rId59" xr:uid="{6027C0A4-5D1E-4433-85BF-CD2F57D6DA89}"/>
+    <hyperlink ref="O78" r:id="rId60" xr:uid="{29DDBCD9-DE51-47A5-B3C6-827913DA2387}"/>
+    <hyperlink ref="O79" r:id="rId61" xr:uid="{FC388204-E09E-47D1-A054-C8455D575E2E}"/>
+    <hyperlink ref="O80" r:id="rId62" xr:uid="{C573F08C-CF21-426E-B62B-392C975BBEB8}"/>
+    <hyperlink ref="O24" r:id="rId63" xr:uid="{A2463247-A92E-46A4-B1F2-C7859F430396}"/>
     <hyperlink ref="O12" r:id="rId64" xr:uid="{8C42F702-13DB-4B89-BA91-C5903624B455}"/>
     <hyperlink ref="O17" r:id="rId65" xr:uid="{71295E9A-7059-4DB8-9A46-8806E333672F}"/>
-    <hyperlink ref="O34" r:id="rId66" xr:uid="{31634445-58D7-420B-A9DF-F6B47E182EE9}"/>
-    <hyperlink ref="O35" r:id="rId67" xr:uid="{696C55EA-352D-4A6D-AE88-F7D6577A10B8}"/>
+    <hyperlink ref="O35" r:id="rId66" xr:uid="{31634445-58D7-420B-A9DF-F6B47E182EE9}"/>
+    <hyperlink ref="O36" r:id="rId67" xr:uid="{696C55EA-352D-4A6D-AE88-F7D6577A10B8}"/>
+    <hyperlink ref="O20" r:id="rId68" xr:uid="{F67ACF00-C62E-4EB8-A65F-317350E7C6CF}"/>
+    <hyperlink ref="O48" r:id="rId69" xr:uid="{B72543AB-3101-4A9B-892E-15300936BBF9}"/>
+    <hyperlink ref="O81" r:id="rId70" xr:uid="{387305BF-5056-46E6-9C42-81E1A79E261A}"/>
+    <hyperlink ref="O82" r:id="rId71" xr:uid="{EB956738-249B-40D1-8C80-EEE1E1ED8710}"/>
+    <hyperlink ref="O83" r:id="rId72" xr:uid="{6864A1C4-75C3-4A42-AD86-1617EF24C777}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId68"/>
-  <drawing r:id="rId69"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId73"/>
+  <drawing r:id="rId74"/>
 </worksheet>
 </file>
--- a/BOM/eSpark-BOM.xlsx
+++ b/BOM/eSpark-BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\matthewgraff-arduinomegapcb\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF9E64C-E5EB-4237-9227-2EAF0EE59067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CA6982-4EE4-4D13-B070-D6F62FFA9621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="447">
   <si>
     <t>Component list</t>
   </si>
@@ -964,9 +964,6 @@
     <t>C492442</t>
   </si>
   <si>
-    <t>C492441</t>
-  </si>
-  <si>
     <t>C597972</t>
   </si>
   <si>
@@ -1361,6 +1358,9 @@
   </si>
   <si>
     <t>C784405</t>
+  </si>
+  <si>
+    <t>DNP</t>
   </si>
 </sst>
 </file>
@@ -2042,6 +2042,72 @@
     <xf numFmtId="0" fontId="24" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2073,72 +2139,6 @@
     <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2516,15 +2516,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="66"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="67"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="88"/>
+      <c r="Q1" s="88"/>
+      <c r="R1" s="88"/>
+      <c r="S1" s="89"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="50" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="51" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2574,7 +2574,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="68"/>
+      <c r="S3" s="90"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="52" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2599,7 +2599,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="69"/>
+      <c r="S4" s="91"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2624,7 +2624,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="69"/>
+      <c r="S5" s="91"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2645,7 +2645,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="69"/>
+      <c r="S6" s="91"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2666,7 +2666,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="69"/>
+      <c r="S7" s="91"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2687,7 +2687,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="69"/>
+      <c r="S8" s="91"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2713,37 +2713,37 @@
         <v>255</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J9" s="54" t="s">
         <v>290</v>
       </c>
       <c r="K9" s="55" t="s">
+        <v>384</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>379</v>
+      </c>
+      <c r="M9" s="56" t="s">
+        <v>388</v>
+      </c>
+      <c r="N9" s="54" t="s">
+        <v>389</v>
+      </c>
+      <c r="O9" s="30" t="s">
         <v>385</v>
       </c>
-      <c r="L9" s="30" t="s">
-        <v>380</v>
-      </c>
-      <c r="M9" s="56" t="s">
-        <v>389</v>
-      </c>
-      <c r="N9" s="54" t="s">
+      <c r="P9" s="54" t="s">
         <v>390</v>
       </c>
-      <c r="O9" s="30" t="s">
+      <c r="Q9" s="30" t="s">
+        <v>391</v>
+      </c>
+      <c r="R9" s="54" t="s">
         <v>386</v>
       </c>
-      <c r="P9" s="54" t="s">
-        <v>391</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>392</v>
-      </c>
-      <c r="R9" s="54" t="s">
+      <c r="S9" s="30" t="s">
         <v>387</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -2752,55 +2752,55 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="76" t="s">
+      <c r="C10" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="77" t="s">
+      <c r="D10" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="78" t="s">
+      <c r="E10" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="F10" s="78" t="s">
+      <c r="F10" s="68" t="s">
         <v>159</v>
       </c>
-      <c r="G10" s="78" t="s">
+      <c r="G10" s="68" t="s">
         <v>199</v>
       </c>
-      <c r="H10" s="78" t="s">
+      <c r="H10" s="68" t="s">
         <v>256</v>
       </c>
-      <c r="I10" s="78" t="s">
-        <v>381</v>
-      </c>
-      <c r="J10" s="78" t="s">
+      <c r="I10" s="68" t="s">
+        <v>380</v>
+      </c>
+      <c r="J10" s="68" t="s">
         <v>291</v>
       </c>
-      <c r="K10" s="78" t="s">
-        <v>349</v>
-      </c>
-      <c r="L10" s="78">
+      <c r="K10" s="68" t="s">
+        <v>348</v>
+      </c>
+      <c r="L10" s="68">
         <v>1</v>
       </c>
-      <c r="M10" s="78">
+      <c r="M10" s="68">
         <f>L10*5</f>
         <v>5</v>
       </c>
-      <c r="N10" s="78">
+      <c r="N10" s="68">
         <v>10</v>
       </c>
-      <c r="O10" s="79" t="s">
-        <v>394</v>
-      </c>
-      <c r="P10" s="80">
+      <c r="O10" s="69" t="s">
+        <v>393</v>
+      </c>
+      <c r="P10" s="70">
         <v>0.15939999999999999</v>
       </c>
-      <c r="Q10" s="80">
+      <c r="Q10" s="70">
         <f>P10*N10</f>
         <v>1.5939999999999999</v>
       </c>
-      <c r="R10" s="78"/>
-      <c r="S10" s="97"/>
+      <c r="R10" s="68"/>
+      <c r="S10" s="87"/>
     </row>
     <row r="11" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
@@ -2808,55 +2808,55 @@
         <f t="shared" ref="B11:B81" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="82" t="s">
+      <c r="C11" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="83" t="s">
-        <v>415</v>
-      </c>
-      <c r="E11" s="84" t="s">
+      <c r="D11" s="73" t="s">
+        <v>414</v>
+      </c>
+      <c r="E11" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="F11" s="84" t="s">
+      <c r="F11" s="74" t="s">
         <v>159</v>
       </c>
-      <c r="G11" s="85" t="s">
+      <c r="G11" s="75" t="s">
         <v>200</v>
       </c>
-      <c r="H11" s="84" t="s">
+      <c r="H11" s="74" t="s">
         <v>256</v>
       </c>
-      <c r="I11" s="84" t="s">
-        <v>395</v>
-      </c>
-      <c r="J11" s="84" t="s">
+      <c r="I11" s="74" t="s">
+        <v>394</v>
+      </c>
+      <c r="J11" s="74" t="s">
         <v>292</v>
       </c>
-      <c r="K11" s="84" t="s">
-        <v>350</v>
-      </c>
-      <c r="L11" s="84">
+      <c r="K11" s="74" t="s">
+        <v>349</v>
+      </c>
+      <c r="L11" s="74">
         <v>28</v>
       </c>
-      <c r="M11" s="84">
+      <c r="M11" s="74">
         <f t="shared" ref="M11" si="1">L11*5</f>
         <v>140</v>
       </c>
-      <c r="N11" s="84">
+      <c r="N11" s="74">
         <v>150</v>
       </c>
-      <c r="O11" s="86" t="s">
-        <v>394</v>
-      </c>
-      <c r="P11" s="87">
+      <c r="O11" s="76" t="s">
+        <v>393</v>
+      </c>
+      <c r="P11" s="77">
         <v>1.04E-2</v>
       </c>
-      <c r="Q11" s="87">
+      <c r="Q11" s="77">
         <f t="shared" ref="Q11" si="2">P11*N11</f>
         <v>1.5599999999999998</v>
       </c>
-      <c r="R11" s="84"/>
-      <c r="S11" s="84"/>
+      <c r="R11" s="74"/>
+      <c r="S11" s="74"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
@@ -2864,55 +2864,55 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="76" t="s">
+      <c r="C12" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="77" t="s">
+      <c r="D12" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="77" t="s">
+      <c r="E12" s="67" t="s">
+        <v>408</v>
+      </c>
+      <c r="F12" s="67" t="s">
         <v>409</v>
       </c>
-      <c r="F12" s="77" t="s">
+      <c r="G12" s="67" t="s">
         <v>410</v>
       </c>
-      <c r="G12" s="77" t="s">
+      <c r="H12" s="67" t="s">
         <v>411</v>
       </c>
-      <c r="H12" s="77" t="s">
+      <c r="I12" s="67" t="s">
+        <v>380</v>
+      </c>
+      <c r="J12" s="67" t="s">
         <v>412</v>
       </c>
-      <c r="I12" s="77" t="s">
-        <v>381</v>
-      </c>
-      <c r="J12" s="77" t="s">
-        <v>413</v>
-      </c>
-      <c r="K12" s="77" t="s">
-        <v>351</v>
-      </c>
-      <c r="L12" s="77">
+      <c r="K12" s="67" t="s">
+        <v>350</v>
+      </c>
+      <c r="L12" s="67">
         <v>2</v>
       </c>
-      <c r="M12" s="77">
+      <c r="M12" s="67">
         <f>L12*5</f>
         <v>10</v>
       </c>
-      <c r="N12" s="77">
+      <c r="N12" s="67">
         <v>20</v>
       </c>
-      <c r="O12" s="79" t="s">
-        <v>394</v>
-      </c>
-      <c r="P12" s="95">
+      <c r="O12" s="69" t="s">
+        <v>393</v>
+      </c>
+      <c r="P12" s="85">
         <v>6.2E-2</v>
       </c>
-      <c r="Q12" s="95">
+      <c r="Q12" s="85">
         <f>P12*N12</f>
         <v>1.24</v>
       </c>
-      <c r="R12" s="96"/>
-      <c r="S12" s="78"/>
+      <c r="R12" s="86"/>
+      <c r="S12" s="68"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
@@ -2920,55 +2920,55 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="82" t="s">
+      <c r="C13" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="83" t="s">
-        <v>429</v>
-      </c>
-      <c r="E13" s="84" t="s">
+      <c r="D13" s="73" t="s">
+        <v>428</v>
+      </c>
+      <c r="E13" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="F13" s="84" t="s">
-        <v>393</v>
-      </c>
-      <c r="G13" s="84" t="s">
+      <c r="F13" s="74" t="s">
+        <v>392</v>
+      </c>
+      <c r="G13" s="74" t="s">
         <v>160</v>
       </c>
-      <c r="H13" s="84" t="s">
+      <c r="H13" s="74" t="s">
         <v>258</v>
       </c>
-      <c r="I13" s="84" t="s">
-        <v>381</v>
-      </c>
-      <c r="J13" s="84" t="s">
+      <c r="I13" s="74" t="s">
+        <v>380</v>
+      </c>
+      <c r="J13" s="74" t="s">
         <v>293</v>
       </c>
-      <c r="K13" s="84" t="s">
-        <v>352</v>
-      </c>
-      <c r="L13" s="84">
+      <c r="K13" s="74" t="s">
+        <v>351</v>
+      </c>
+      <c r="L13" s="74">
         <v>3</v>
       </c>
-      <c r="M13" s="84">
+      <c r="M13" s="74">
         <f t="shared" ref="M13" si="3">L13*5</f>
         <v>15</v>
       </c>
-      <c r="N13" s="84">
+      <c r="N13" s="74">
         <v>17</v>
       </c>
-      <c r="O13" s="86" t="s">
-        <v>394</v>
-      </c>
-      <c r="P13" s="87">
+      <c r="O13" s="76" t="s">
+        <v>393</v>
+      </c>
+      <c r="P13" s="77">
         <v>0.49540000000000001</v>
       </c>
-      <c r="Q13" s="87">
+      <c r="Q13" s="77">
         <f t="shared" ref="Q13" si="4">P13*N13</f>
         <v>8.4217999999999993</v>
       </c>
-      <c r="R13" s="88"/>
-      <c r="S13" s="84"/>
+      <c r="R13" s="78"/>
+      <c r="S13" s="74"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
@@ -2976,55 +2976,55 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="76" t="s">
+      <c r="C14" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="77" t="s">
+      <c r="D14" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="77" t="s">
+      <c r="E14" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="F14" s="77" t="s">
+      <c r="F14" s="67" t="s">
         <v>161</v>
       </c>
-      <c r="G14" s="77" t="s">
+      <c r="G14" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="H14" s="77" t="s">
+      <c r="H14" s="67" t="s">
         <v>258</v>
       </c>
-      <c r="I14" s="77" t="s">
-        <v>381</v>
-      </c>
-      <c r="J14" s="77" t="s">
+      <c r="I14" s="67" t="s">
+        <v>380</v>
+      </c>
+      <c r="J14" s="67" t="s">
         <v>294</v>
       </c>
-      <c r="K14" s="77" t="s">
-        <v>353</v>
-      </c>
-      <c r="L14" s="77">
+      <c r="K14" s="67" t="s">
+        <v>352</v>
+      </c>
+      <c r="L14" s="67">
         <v>1</v>
       </c>
-      <c r="M14" s="77">
+      <c r="M14" s="67">
         <f t="shared" ref="M14" si="5">L14*5</f>
         <v>5</v>
       </c>
-      <c r="N14" s="77">
+      <c r="N14" s="67">
         <v>6</v>
       </c>
-      <c r="O14" s="79" t="s">
-        <v>394</v>
-      </c>
-      <c r="P14" s="95">
+      <c r="O14" s="69" t="s">
+        <v>393</v>
+      </c>
+      <c r="P14" s="85">
         <v>0.91320000000000001</v>
       </c>
-      <c r="Q14" s="95">
+      <c r="Q14" s="85">
         <f t="shared" ref="Q14" si="6">P14*N14</f>
         <v>5.4792000000000005</v>
       </c>
-      <c r="R14" s="96"/>
-      <c r="S14" s="78"/>
+      <c r="R14" s="86"/>
+      <c r="S14" s="68"/>
     </row>
     <row r="15" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
@@ -3032,55 +3032,55 @@
         <f>ROW(B15) - ROW($B$9)</f>
         <v>6</v>
       </c>
-      <c r="C15" s="82" t="s">
+      <c r="C15" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="83" t="s">
+      <c r="D15" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="84" t="s">
+      <c r="E15" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="F15" s="84" t="s">
+      <c r="F15" s="74" t="s">
         <v>159</v>
       </c>
-      <c r="G15" s="84" t="s">
+      <c r="G15" s="74" t="s">
         <v>202</v>
       </c>
-      <c r="H15" s="84" t="s">
+      <c r="H15" s="74" t="s">
         <v>256</v>
       </c>
-      <c r="I15" s="84" t="s">
-        <v>381</v>
-      </c>
-      <c r="J15" s="84" t="s">
+      <c r="I15" s="74" t="s">
+        <v>380</v>
+      </c>
+      <c r="J15" s="74" t="s">
         <v>295</v>
       </c>
-      <c r="K15" s="84" t="s">
-        <v>354</v>
-      </c>
-      <c r="L15" s="84">
+      <c r="K15" s="74" t="s">
+        <v>353</v>
+      </c>
+      <c r="L15" s="74">
         <v>12</v>
       </c>
-      <c r="M15" s="84">
+      <c r="M15" s="74">
         <f>L15*5</f>
         <v>60</v>
       </c>
-      <c r="N15" s="84">
+      <c r="N15" s="74">
         <v>100</v>
       </c>
-      <c r="O15" s="86" t="s">
-        <v>394</v>
-      </c>
-      <c r="P15" s="87">
+      <c r="O15" s="76" t="s">
+        <v>393</v>
+      </c>
+      <c r="P15" s="77">
         <v>2.8E-3</v>
       </c>
-      <c r="Q15" s="87">
+      <c r="Q15" s="77">
         <f>P15*N15</f>
         <v>0.27999999999999997</v>
       </c>
-      <c r="R15" s="84"/>
-      <c r="S15" s="84"/>
+      <c r="R15" s="74"/>
+      <c r="S15" s="74"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
@@ -3088,55 +3088,55 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="76" t="s">
+      <c r="C16" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="77" t="s">
+      <c r="D16" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="E16" s="77" t="s">
+      <c r="E16" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="F16" s="77" t="s">
+      <c r="F16" s="67" t="s">
         <v>159</v>
       </c>
-      <c r="G16" s="77" t="s">
+      <c r="G16" s="67" t="s">
         <v>203</v>
       </c>
-      <c r="H16" s="77" t="s">
+      <c r="H16" s="67" t="s">
         <v>256</v>
       </c>
-      <c r="I16" s="77" t="s">
-        <v>381</v>
-      </c>
-      <c r="J16" s="77" t="s">
+      <c r="I16" s="67" t="s">
+        <v>380</v>
+      </c>
+      <c r="J16" s="67" t="s">
         <v>296</v>
       </c>
-      <c r="K16" s="77" t="s">
-        <v>355</v>
-      </c>
-      <c r="L16" s="77">
+      <c r="K16" s="67" t="s">
+        <v>354</v>
+      </c>
+      <c r="L16" s="67">
         <v>1</v>
       </c>
-      <c r="M16" s="77">
+      <c r="M16" s="67">
         <f t="shared" ref="M16" si="7">L16*5</f>
         <v>5</v>
       </c>
-      <c r="N16" s="77">
+      <c r="N16" s="67">
         <v>100</v>
       </c>
-      <c r="O16" s="79" t="s">
-        <v>394</v>
-      </c>
-      <c r="P16" s="95">
+      <c r="O16" s="69" t="s">
+        <v>393</v>
+      </c>
+      <c r="P16" s="85">
         <v>4.8999999999999998E-3</v>
       </c>
-      <c r="Q16" s="95">
+      <c r="Q16" s="85">
         <f t="shared" ref="Q16" si="8">P16*N16</f>
         <v>0.49</v>
       </c>
-      <c r="R16" s="96"/>
-      <c r="S16" s="78"/>
+      <c r="R16" s="86"/>
+      <c r="S16" s="68"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
@@ -3144,55 +3144,55 @@
         <f>ROW(B17) - ROW($B$9)</f>
         <v>8</v>
       </c>
-      <c r="C17" s="82" t="s">
+      <c r="C17" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="83" t="s">
+      <c r="D17" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="84" t="s">
+      <c r="E17" s="74" t="s">
         <v>98</v>
       </c>
-      <c r="F17" s="84" t="s">
+      <c r="F17" s="74" t="s">
         <v>162</v>
       </c>
-      <c r="G17" s="85" t="s">
+      <c r="G17" s="75" t="s">
         <v>204</v>
       </c>
-      <c r="H17" s="84" t="s">
+      <c r="H17" s="74" t="s">
         <v>259</v>
       </c>
-      <c r="I17" s="84" t="s">
-        <v>427</v>
-      </c>
-      <c r="J17" s="84" t="s">
+      <c r="I17" s="74" t="s">
         <v>426</v>
       </c>
-      <c r="K17" s="84" t="s">
-        <v>356</v>
-      </c>
-      <c r="L17" s="84">
+      <c r="J17" s="74" t="s">
+        <v>425</v>
+      </c>
+      <c r="K17" s="74" t="s">
+        <v>355</v>
+      </c>
+      <c r="L17" s="74">
         <v>1</v>
       </c>
-      <c r="M17" s="84">
+      <c r="M17" s="74">
         <f>L17*5</f>
         <v>5</v>
       </c>
-      <c r="N17" s="84">
+      <c r="N17" s="74">
         <v>100</v>
       </c>
-      <c r="O17" s="86" t="s">
-        <v>394</v>
-      </c>
-      <c r="P17" s="87">
+      <c r="O17" s="76" t="s">
+        <v>393</v>
+      </c>
+      <c r="P17" s="77">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q17" s="87">
+      <c r="Q17" s="77">
         <f>P17*N17</f>
         <v>0.13</v>
       </c>
-      <c r="R17" s="84"/>
-      <c r="S17" s="84"/>
+      <c r="R17" s="74"/>
+      <c r="S17" s="74"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
@@ -3200,55 +3200,55 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="76" t="s">
+      <c r="C18" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="77" t="s">
+      <c r="D18" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="E18" s="77" t="s">
+      <c r="E18" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="F18" s="77" t="s">
+      <c r="F18" s="67" t="s">
         <v>159</v>
       </c>
-      <c r="G18" s="77" t="s">
+      <c r="G18" s="67" t="s">
         <v>205</v>
       </c>
-      <c r="H18" s="77" t="s">
+      <c r="H18" s="67" t="s">
         <v>256</v>
       </c>
-      <c r="I18" s="77" t="s">
-        <v>381</v>
-      </c>
-      <c r="J18" s="77" t="s">
+      <c r="I18" s="67" t="s">
+        <v>380</v>
+      </c>
+      <c r="J18" s="67" t="s">
         <v>297</v>
       </c>
-      <c r="K18" s="77" t="s">
-        <v>357</v>
-      </c>
-      <c r="L18" s="77">
+      <c r="K18" s="67" t="s">
+        <v>356</v>
+      </c>
+      <c r="L18" s="67">
         <v>2</v>
       </c>
-      <c r="M18" s="77">
+      <c r="M18" s="67">
         <f t="shared" ref="M18" si="9">L18*5</f>
         <v>10</v>
       </c>
-      <c r="N18" s="77">
+      <c r="N18" s="67">
         <v>100</v>
       </c>
-      <c r="O18" s="79" t="s">
-        <v>394</v>
-      </c>
-      <c r="P18" s="95">
+      <c r="O18" s="69" t="s">
+        <v>393</v>
+      </c>
+      <c r="P18" s="85">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="Q18" s="95">
+      <c r="Q18" s="85">
         <f t="shared" ref="Q18" si="10">P18*N18</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="R18" s="96"/>
-      <c r="S18" s="78"/>
+      <c r="R18" s="86"/>
+      <c r="S18" s="68"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
@@ -3256,55 +3256,55 @@
         <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="82" t="s">
+      <c r="C19" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="83" t="s">
-        <v>414</v>
-      </c>
-      <c r="E19" s="84" t="s">
+      <c r="D19" s="73" t="s">
+        <v>413</v>
+      </c>
+      <c r="E19" s="74" t="s">
         <v>100</v>
       </c>
-      <c r="F19" s="84" t="s">
+      <c r="F19" s="74" t="s">
         <v>159</v>
       </c>
-      <c r="G19" s="84" t="s">
+      <c r="G19" s="74" t="s">
         <v>206</v>
       </c>
-      <c r="H19" s="84" t="s">
+      <c r="H19" s="74" t="s">
         <v>256</v>
       </c>
-      <c r="I19" s="84" t="s">
-        <v>381</v>
-      </c>
-      <c r="J19" s="84" t="s">
+      <c r="I19" s="74" t="s">
+        <v>380</v>
+      </c>
+      <c r="J19" s="74" t="s">
         <v>298</v>
       </c>
-      <c r="K19" s="84" t="s">
-        <v>358</v>
-      </c>
-      <c r="L19" s="84">
+      <c r="K19" s="74" t="s">
+        <v>357</v>
+      </c>
+      <c r="L19" s="74">
         <v>2</v>
       </c>
-      <c r="M19" s="84">
+      <c r="M19" s="74">
         <f>L19*5</f>
         <v>10</v>
       </c>
-      <c r="N19" s="84">
+      <c r="N19" s="74">
         <v>20</v>
       </c>
-      <c r="O19" s="86" t="s">
-        <v>394</v>
-      </c>
-      <c r="P19" s="87">
+      <c r="O19" s="76" t="s">
+        <v>393</v>
+      </c>
+      <c r="P19" s="77">
         <v>2.3599999999999999E-2</v>
       </c>
-      <c r="Q19" s="87">
+      <c r="Q19" s="77">
         <f>P19*N19</f>
         <v>0.47199999999999998</v>
       </c>
-      <c r="R19" s="84"/>
-      <c r="S19" s="84"/>
+      <c r="R19" s="74"/>
+      <c r="S19" s="74"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
@@ -3315,52 +3315,52 @@
       <c r="C20" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="78" t="s">
+      <c r="D20" s="68" t="s">
+        <v>429</v>
+      </c>
+      <c r="E20" s="68" t="s">
         <v>430</v>
       </c>
-      <c r="E20" s="78" t="s">
+      <c r="F20" s="68" t="s">
+        <v>392</v>
+      </c>
+      <c r="G20" s="68" t="s">
         <v>431</v>
       </c>
-      <c r="F20" s="78" t="s">
-        <v>393</v>
-      </c>
-      <c r="G20" s="78" t="s">
+      <c r="H20" s="68" t="s">
+        <v>258</v>
+      </c>
+      <c r="I20" s="68" t="s">
+        <v>380</v>
+      </c>
+      <c r="J20" s="68" t="s">
         <v>432</v>
       </c>
-      <c r="H20" s="78" t="s">
-        <v>258</v>
-      </c>
-      <c r="I20" s="78" t="s">
-        <v>381</v>
-      </c>
-      <c r="J20" s="78" t="s">
+      <c r="K20" s="68" t="s">
         <v>433</v>
       </c>
-      <c r="K20" s="78" t="s">
-        <v>434</v>
-      </c>
-      <c r="L20" s="78">
+      <c r="L20" s="68">
         <v>1</v>
       </c>
-      <c r="M20" s="78">
+      <c r="M20" s="68">
         <f>L20*5</f>
         <v>5</v>
       </c>
-      <c r="N20" s="78">
+      <c r="N20" s="68">
         <v>6</v>
       </c>
-      <c r="O20" s="79" t="s">
-        <v>394</v>
-      </c>
-      <c r="P20" s="80">
+      <c r="O20" s="69" t="s">
+        <v>393</v>
+      </c>
+      <c r="P20" s="70">
         <v>0.51590000000000003</v>
       </c>
-      <c r="Q20" s="80">
+      <c r="Q20" s="70">
         <f>P20*N20</f>
         <v>3.0954000000000002</v>
       </c>
-      <c r="R20" s="78"/>
-      <c r="S20" s="81"/>
+      <c r="R20" s="68"/>
+      <c r="S20" s="71"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
@@ -3391,7 +3391,7 @@
         <v>299</v>
       </c>
       <c r="K21" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L21" s="62">
         <v>7</v>
@@ -3404,7 +3404,7 @@
         <v>40</v>
       </c>
       <c r="O21" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P21" s="63">
         <v>6.3700000000000007E-2</v>
@@ -3441,13 +3441,13 @@
         <v>261</v>
       </c>
       <c r="I22" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J22" s="38" t="s">
         <v>300</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L22" s="38">
         <v>2</v>
@@ -3460,7 +3460,7 @@
         <v>15</v>
       </c>
       <c r="O22" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P22" s="39">
         <v>8.6400000000000005E-2</v>
@@ -3497,13 +3497,13 @@
         <v>262</v>
       </c>
       <c r="I23" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J23" s="62" t="s">
         <v>301</v>
       </c>
       <c r="K23" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L23" s="62">
         <v>1</v>
@@ -3516,7 +3516,7 @@
         <v>20</v>
       </c>
       <c r="O23" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P23" s="63">
         <v>3.32E-2</v>
@@ -3541,10 +3541,10 @@
         <v>38</v>
       </c>
       <c r="E24" s="38" t="s">
+        <v>401</v>
+      </c>
+      <c r="F24" s="38" t="s">
         <v>402</v>
-      </c>
-      <c r="F24" s="38" t="s">
-        <v>403</v>
       </c>
       <c r="G24" s="38" t="s">
         <v>210</v>
@@ -3553,13 +3553,13 @@
         <v>263</v>
       </c>
       <c r="I24" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J24" s="38" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K24" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L24" s="38">
         <v>1</v>
@@ -3572,7 +3572,7 @@
         <v>20</v>
       </c>
       <c r="O24" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P24" s="39">
         <v>3.6200000000000003E-2</v>
@@ -3609,13 +3609,13 @@
         <v>264</v>
       </c>
       <c r="I25" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J25" s="62" t="s">
         <v>302</v>
       </c>
       <c r="K25" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L25" s="62">
         <v>8</v>
@@ -3628,7 +3628,7 @@
         <v>60</v>
       </c>
       <c r="O25" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P25" s="63">
         <v>2.0400000000000001E-2</v>
@@ -3665,13 +3665,13 @@
         <v>265</v>
       </c>
       <c r="I26" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J26" s="38" t="s">
         <v>303</v>
       </c>
       <c r="K26" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L26" s="38">
         <v>1</v>
@@ -3684,7 +3684,7 @@
         <v>10</v>
       </c>
       <c r="O26" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P26" s="39">
         <v>0.104</v>
@@ -3721,13 +3721,13 @@
         <v>266</v>
       </c>
       <c r="I27" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J27" s="62" t="s">
         <v>304</v>
       </c>
       <c r="K27" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L27" s="62">
         <v>3</v>
@@ -3740,7 +3740,7 @@
         <v>20</v>
       </c>
       <c r="O27" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P27" s="63">
         <v>3.1699999999999999E-2</v>
@@ -3777,13 +3777,13 @@
         <v>267</v>
       </c>
       <c r="I28" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J28" s="38" t="s">
         <v>305</v>
       </c>
       <c r="K28" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L28" s="38">
         <v>1</v>
@@ -3796,7 +3796,7 @@
         <v>10</v>
       </c>
       <c r="O28" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P28" s="39">
         <v>3.5400000000000001E-2</v>
@@ -3833,13 +3833,13 @@
         <v>261</v>
       </c>
       <c r="I29" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J29" s="62" t="s">
         <v>306</v>
       </c>
       <c r="K29" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L29" s="62">
         <v>5</v>
@@ -3852,7 +3852,7 @@
         <v>50</v>
       </c>
       <c r="O29" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P29" s="63">
         <v>1.7999999999999999E-2</v>
@@ -3889,13 +3889,13 @@
         <v>268</v>
       </c>
       <c r="I30" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J30" s="38" t="s">
         <v>307</v>
       </c>
       <c r="K30" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L30" s="38">
         <v>1</v>
@@ -3908,7 +3908,7 @@
         <v>6</v>
       </c>
       <c r="O30" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P30" s="39">
         <v>0.2319</v>
@@ -3945,13 +3945,13 @@
         <v>269</v>
       </c>
       <c r="I31" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J31" s="62" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K31" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L31" s="62">
         <v>2</v>
@@ -3964,7 +3964,7 @@
         <v>20</v>
       </c>
       <c r="O31" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P31" s="63">
         <v>4.5900000000000003E-2</v>
@@ -4001,13 +4001,13 @@
         <v>259</v>
       </c>
       <c r="I32" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J32" s="38" t="s">
         <v>308</v>
       </c>
       <c r="K32" s="38" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="L32" s="38">
         <v>1</v>
@@ -4020,7 +4020,7 @@
         <v>10</v>
       </c>
       <c r="O32" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P32" s="39">
         <v>0.1193</v>
@@ -4057,13 +4057,13 @@
         <v>257</v>
       </c>
       <c r="I33" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J33" s="62" t="s">
         <v>309</v>
       </c>
       <c r="K33" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L33" s="62">
         <v>8</v>
@@ -4076,7 +4076,7 @@
         <v>50</v>
       </c>
       <c r="O33" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P33" s="63">
         <v>4.5600000000000002E-2</v>
@@ -4098,13 +4098,13 @@
         <v>14</v>
       </c>
       <c r="D34" s="64" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E34" s="38" t="s">
         <v>113</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G34" s="38" t="s">
         <v>220</v>
@@ -4113,13 +4113,13 @@
         <v>270</v>
       </c>
       <c r="I34" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J34" s="38" t="s">
         <v>310</v>
       </c>
       <c r="K34" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L34" s="38">
         <v>2</v>
@@ -4132,7 +4132,7 @@
         <v>12</v>
       </c>
       <c r="O34" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P34" s="39">
         <v>0.1734</v>
@@ -4154,28 +4154,28 @@
         <v>14</v>
       </c>
       <c r="D35" s="62" t="s">
+        <v>415</v>
+      </c>
+      <c r="E35" s="62" t="s">
         <v>416</v>
-      </c>
-      <c r="E35" s="62" t="s">
-        <v>417</v>
       </c>
       <c r="F35" s="62">
         <v>1051330011</v>
       </c>
       <c r="G35" s="62" t="s">
+        <v>417</v>
+      </c>
+      <c r="H35" s="62" t="s">
         <v>418</v>
       </c>
-      <c r="H35" s="62" t="s">
+      <c r="I35" s="62" t="s">
+        <v>380</v>
+      </c>
+      <c r="J35" s="62" t="s">
         <v>419</v>
       </c>
-      <c r="I35" s="62" t="s">
-        <v>381</v>
-      </c>
-      <c r="J35" s="62" t="s">
-        <v>420</v>
-      </c>
       <c r="K35" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L35" s="62">
         <v>1</v>
@@ -4188,7 +4188,7 @@
         <v>6</v>
       </c>
       <c r="O35" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P35" s="63">
         <v>0.41049999999999998</v>
@@ -4213,23 +4213,23 @@
         <v>48</v>
       </c>
       <c r="E36" s="38" t="s">
+        <v>421</v>
+      </c>
+      <c r="F36" s="38" t="s">
+        <v>392</v>
+      </c>
+      <c r="G36" s="38" t="s">
         <v>422</v>
       </c>
-      <c r="F36" s="38" t="s">
-        <v>393</v>
-      </c>
-      <c r="G36" s="38" t="s">
+      <c r="H36" s="38" t="s">
         <v>423</v>
-      </c>
-      <c r="H36" s="38" t="s">
-        <v>424</v>
       </c>
       <c r="I36" s="38"/>
       <c r="J36" s="38" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="K36" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L36" s="38">
         <v>6</v>
@@ -4242,7 +4242,7 @@
         <v>32</v>
       </c>
       <c r="O36" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P36" s="39">
         <v>0.55530000000000002</v>
@@ -4252,7 +4252,7 @@
         <v>17.769600000000001</v>
       </c>
       <c r="R36" s="65" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="S36" s="38"/>
     </row>
@@ -4263,7 +4263,7 @@
         <v>28</v>
       </c>
       <c r="C37" s="59" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D37" s="62" t="s">
         <v>49</v>
@@ -4272,7 +4272,7 @@
         <v>114</v>
       </c>
       <c r="F37" s="62" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G37" s="62" t="s">
         <v>221</v>
@@ -4281,13 +4281,13 @@
         <v>271</v>
       </c>
       <c r="I37" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J37" s="62" t="s">
         <v>311</v>
       </c>
       <c r="K37" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L37" s="62">
         <v>2</v>
@@ -4300,7 +4300,7 @@
         <v>15</v>
       </c>
       <c r="O37" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P37" s="63">
         <v>8.9399999999999993E-2</v>
@@ -4328,7 +4328,7 @@
         <v>115</v>
       </c>
       <c r="F38" s="38" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G38" s="38" t="s">
         <v>174</v>
@@ -4337,13 +4337,13 @@
         <v>272</v>
       </c>
       <c r="I38" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J38" s="38" t="s">
         <v>312</v>
       </c>
       <c r="K38" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L38" s="38">
         <v>1</v>
@@ -4356,7 +4356,7 @@
         <v>6</v>
       </c>
       <c r="O38" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P38" s="39">
         <v>0.66820000000000002</v>
@@ -4384,7 +4384,7 @@
         <v>116</v>
       </c>
       <c r="F39" s="62" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G39" s="62" t="s">
         <v>175</v>
@@ -4393,13 +4393,13 @@
         <v>273</v>
       </c>
       <c r="I39" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J39" s="62" t="s">
         <v>313</v>
       </c>
       <c r="K39" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L39" s="62">
         <v>1</v>
@@ -4412,7 +4412,7 @@
         <v>10</v>
       </c>
       <c r="O39" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P39" s="63">
         <v>9.3600000000000003E-2</v>
@@ -4440,7 +4440,7 @@
         <v>117</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G40" s="38" t="s">
         <v>176</v>
@@ -4449,13 +4449,13 @@
         <v>273</v>
       </c>
       <c r="I40" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J40" s="38" t="s">
-        <v>314</v>
+        <v>380</v>
       </c>
       <c r="K40" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L40" s="38">
         <v>1</v>
@@ -4468,16 +4468,17 @@
         <v>10</v>
       </c>
       <c r="O40" s="58" t="s">
-        <v>394</v>
-      </c>
-      <c r="P40" s="39">
-        <v>7.8100000000000003E-2</v>
-      </c>
-      <c r="Q40" s="39">
-        <f t="shared" ref="Q40" si="33">P40*N40</f>
-        <v>0.78100000000000003</v>
-      </c>
-      <c r="R40" s="38"/>
+        <v>393</v>
+      </c>
+      <c r="P40" s="39" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q40" s="39" t="s">
+        <v>380</v>
+      </c>
+      <c r="R40" s="65" t="s">
+        <v>446</v>
+      </c>
       <c r="S40" s="38"/>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
@@ -4496,7 +4497,7 @@
         <v>118</v>
       </c>
       <c r="F41" s="62" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G41" s="62" t="s">
         <v>177</v>
@@ -4505,13 +4506,13 @@
         <v>271</v>
       </c>
       <c r="I41" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J41" s="62" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K41" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L41" s="62">
         <v>1</v>
@@ -4524,7 +4525,7 @@
         <v>6</v>
       </c>
       <c r="O41" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P41" s="63">
         <v>1.4222999999999999</v>
@@ -4552,7 +4553,7 @@
         <v>119</v>
       </c>
       <c r="F42" s="38" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G42" s="38" t="s">
         <v>178</v>
@@ -4561,32 +4562,32 @@
         <v>274</v>
       </c>
       <c r="I42" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J42" s="38" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K42" s="38" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L42" s="38">
         <v>1</v>
       </c>
       <c r="M42" s="38">
-        <f t="shared" ref="M42" si="34">L42*5</f>
+        <f t="shared" ref="M42" si="33">L42*5</f>
         <v>5</v>
       </c>
       <c r="N42" s="38">
         <v>10</v>
       </c>
       <c r="O42" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P42" s="39">
         <v>0.19500000000000001</v>
       </c>
       <c r="Q42" s="39">
-        <f t="shared" ref="Q42" si="35">P42*N42</f>
+        <f t="shared" ref="Q42" si="34">P42*N42</f>
         <v>1.9500000000000002</v>
       </c>
       <c r="R42" s="38"/>
@@ -4608,7 +4609,7 @@
         <v>120</v>
       </c>
       <c r="F43" s="62" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G43" s="62" t="s">
         <v>179</v>
@@ -4617,13 +4618,13 @@
         <v>275</v>
       </c>
       <c r="I43" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J43" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="K43" s="62" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L43" s="62">
         <v>1</v>
@@ -4636,7 +4637,7 @@
         <v>6</v>
       </c>
       <c r="O43" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P43" s="63">
         <v>0.35439999999999999</v>
@@ -4673,32 +4674,32 @@
         <v>259</v>
       </c>
       <c r="I44" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J44" s="38" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="K44" s="38" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="L44" s="38">
         <v>1</v>
       </c>
       <c r="M44" s="38">
-        <f t="shared" ref="M44" si="36">L44*5</f>
+        <f t="shared" ref="M44" si="35">L44*5</f>
         <v>5</v>
       </c>
       <c r="N44" s="38">
         <v>10</v>
       </c>
       <c r="O44" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P44" s="39">
         <v>6.4600000000000005E-2</v>
       </c>
       <c r="Q44" s="39">
-        <f t="shared" ref="Q44" si="37">P44*N44</f>
+        <f t="shared" ref="Q44" si="36">P44*N44</f>
         <v>0.64600000000000002</v>
       </c>
       <c r="R44" s="38"/>
@@ -4714,7 +4715,7 @@
         <v>20</v>
       </c>
       <c r="D45" s="62" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E45" s="62" t="s">
         <v>122</v>
@@ -4729,32 +4730,32 @@
         <v>276</v>
       </c>
       <c r="I45" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J45" s="62" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="K45" s="62" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L45" s="62">
         <v>3</v>
       </c>
       <c r="M45" s="62">
-        <f t="shared" ref="M45" si="38">L45*5</f>
+        <f t="shared" ref="M45" si="37">L45*5</f>
         <v>15</v>
       </c>
       <c r="N45" s="62">
         <v>20</v>
       </c>
       <c r="O45" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P45" s="63">
         <v>4.9099999999999998E-2</v>
       </c>
       <c r="Q45" s="63">
-        <f t="shared" ref="Q45" si="39">P45*N45</f>
+        <f t="shared" ref="Q45" si="38">P45*N45</f>
         <v>0.98199999999999998</v>
       </c>
       <c r="R45" s="61"/>
@@ -4770,7 +4771,7 @@
         <v>20</v>
       </c>
       <c r="D46" s="64" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E46" s="38" t="s">
         <v>124</v>
@@ -4785,13 +4786,13 @@
         <v>276</v>
       </c>
       <c r="I46" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J46" s="38" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="K46" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L46" s="38">
         <v>4</v>
@@ -4804,7 +4805,7 @@
         <v>40</v>
       </c>
       <c r="O46" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P46" s="39">
         <v>3.2099999999999997E-2</v>
@@ -4841,19 +4842,19 @@
         <v>277</v>
       </c>
       <c r="I47" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J47" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="K47" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L47" s="62">
         <v>1</v>
       </c>
       <c r="M47" s="62">
-        <f t="shared" ref="M47" si="40">L47*5</f>
+        <f t="shared" ref="M47" si="39">L47*5</f>
         <v>5</v>
       </c>
       <c r="N47" s="62">
@@ -4866,7 +4867,7 @@
         <v>16.59</v>
       </c>
       <c r="Q47" s="63">
-        <f t="shared" ref="Q47" si="41">P47*N47</f>
+        <f t="shared" ref="Q47" si="40">P47*N47</f>
         <v>99.539999999999992</v>
       </c>
       <c r="R47" s="61"/>
@@ -4888,7 +4889,7 @@
         <v>125</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G48" s="38" t="s">
         <v>183</v>
@@ -4898,16 +4899,16 @@
       </c>
       <c r="I48" s="38"/>
       <c r="J48" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="K48" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L48" s="38">
         <v>1</v>
       </c>
       <c r="M48" s="38">
-        <f t="shared" ref="M48" si="42">L48*5</f>
+        <f t="shared" ref="M48" si="41">L48*5</f>
         <v>5</v>
       </c>
       <c r="N48" s="38">
@@ -4920,7 +4921,7 @@
         <v>13.9</v>
       </c>
       <c r="Q48" s="39">
-        <f t="shared" ref="Q48" si="43">P48*N48</f>
+        <f t="shared" ref="Q48" si="42">P48*N48</f>
         <v>83.4</v>
       </c>
       <c r="R48" s="38"/>
@@ -4932,54 +4933,54 @@
         <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
-      <c r="C49" s="89" t="s">
-        <v>363</v>
-      </c>
-      <c r="D49" s="90" t="s">
+      <c r="C49" s="79" t="s">
+        <v>362</v>
+      </c>
+      <c r="D49" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="E49" s="90" t="s">
+      <c r="E49" s="80" t="s">
         <v>126</v>
       </c>
-      <c r="F49" s="90" t="s">
+      <c r="F49" s="80" t="s">
         <v>184</v>
       </c>
-      <c r="G49" s="90" t="s">
-        <v>381</v>
-      </c>
-      <c r="H49" s="90" t="s">
-        <v>381</v>
-      </c>
-      <c r="I49" s="90" t="s">
-        <v>381</v>
-      </c>
-      <c r="J49" s="90" t="s">
-        <v>381</v>
-      </c>
-      <c r="K49" s="90" t="s">
-        <v>381</v>
-      </c>
-      <c r="L49" s="90">
+      <c r="G49" s="80" t="s">
+        <v>380</v>
+      </c>
+      <c r="H49" s="80" t="s">
+        <v>380</v>
+      </c>
+      <c r="I49" s="80" t="s">
+        <v>380</v>
+      </c>
+      <c r="J49" s="80" t="s">
+        <v>380</v>
+      </c>
+      <c r="K49" s="80" t="s">
+        <v>380</v>
+      </c>
+      <c r="L49" s="80">
         <v>6</v>
       </c>
-      <c r="M49" s="90">
+      <c r="M49" s="80">
         <f>L49*5</f>
         <v>30</v>
       </c>
-      <c r="N49" s="90" t="s">
-        <v>381</v>
-      </c>
-      <c r="O49" s="91" t="s">
-        <v>381</v>
-      </c>
-      <c r="P49" s="92" t="s">
-        <v>381</v>
-      </c>
-      <c r="Q49" s="92" t="s">
-        <v>381</v>
-      </c>
-      <c r="R49" s="90"/>
-      <c r="S49" s="90"/>
+      <c r="N49" s="80" t="s">
+        <v>380</v>
+      </c>
+      <c r="O49" s="81" t="s">
+        <v>380</v>
+      </c>
+      <c r="P49" s="82" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q49" s="82" t="s">
+        <v>380</v>
+      </c>
+      <c r="R49" s="80"/>
+      <c r="S49" s="80"/>
     </row>
     <row r="50" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
@@ -5006,32 +5007,32 @@
         <v>279</v>
       </c>
       <c r="I50" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J50" s="38" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K50" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L50" s="38">
         <v>4</v>
       </c>
       <c r="M50" s="38">
-        <f t="shared" ref="M50" si="44">L50*5</f>
+        <f t="shared" ref="M50" si="43">L50*5</f>
         <v>20</v>
       </c>
       <c r="N50" s="38">
         <v>40</v>
       </c>
       <c r="O50" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P50" s="39">
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="Q50" s="39">
-        <f t="shared" ref="Q50" si="45">P50*N50</f>
+        <f t="shared" ref="Q50" si="44">P50*N50</f>
         <v>1.3159999999999998</v>
       </c>
       <c r="R50" s="38"/>
@@ -5062,13 +5063,13 @@
         <v>256</v>
       </c>
       <c r="I51" s="62" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J51" s="62" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="K51" s="62" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="L51" s="62">
         <v>1</v>
@@ -5081,7 +5082,7 @@
         <v>20</v>
       </c>
       <c r="O51" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P51" s="63">
         <v>2.7699999999999999E-2</v>
@@ -5118,32 +5119,32 @@
         <v>256</v>
       </c>
       <c r="I52" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J52" s="38" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="K52" s="38" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="L52" s="38">
         <v>1</v>
       </c>
       <c r="M52" s="38">
-        <f t="shared" ref="M52" si="46">L52*5</f>
+        <f t="shared" ref="M52" si="45">L52*5</f>
         <v>5</v>
       </c>
       <c r="N52" s="38">
         <v>20</v>
       </c>
       <c r="O52" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P52" s="39">
         <v>2.18E-2</v>
       </c>
       <c r="Q52" s="39">
-        <f t="shared" ref="Q52" si="47">P52*N52</f>
+        <f t="shared" ref="Q52" si="46">P52*N52</f>
         <v>0.436</v>
       </c>
       <c r="R52" s="38"/>
@@ -5174,13 +5175,13 @@
         <v>256</v>
       </c>
       <c r="I53" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J53" s="62" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="K53" s="62" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="L53" s="62">
         <v>13</v>
@@ -5193,7 +5194,7 @@
         <v>100</v>
       </c>
       <c r="O53" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P53" s="63">
         <v>1E-3</v>
@@ -5230,32 +5231,32 @@
         <v>256</v>
       </c>
       <c r="I54" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J54" s="38" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K54" s="38" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="L54" s="38">
         <v>1</v>
       </c>
       <c r="M54" s="38">
-        <f t="shared" ref="M54" si="48">L54*5</f>
+        <f t="shared" ref="M54" si="47">L54*5</f>
         <v>5</v>
       </c>
       <c r="N54" s="38">
         <v>20</v>
       </c>
       <c r="O54" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P54" s="39">
         <v>2.81E-2</v>
       </c>
       <c r="Q54" s="39">
-        <f t="shared" ref="Q54" si="49">P54*N54</f>
+        <f t="shared" ref="Q54" si="48">P54*N54</f>
         <v>0.56200000000000006</v>
       </c>
       <c r="R54" s="38"/>
@@ -5286,13 +5287,13 @@
         <v>256</v>
       </c>
       <c r="I55" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J55" s="62" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K55" s="62" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="L55" s="62">
         <v>1</v>
@@ -5305,7 +5306,7 @@
         <v>20</v>
       </c>
       <c r="O55" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P55" s="63">
         <v>3.2300000000000002E-2</v>
@@ -5342,32 +5343,32 @@
         <v>256</v>
       </c>
       <c r="I56" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J56" s="38" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="K56" s="38" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L56" s="38">
         <v>2</v>
       </c>
       <c r="M56" s="38">
-        <f t="shared" ref="M56" si="50">L56*5</f>
+        <f t="shared" ref="M56" si="49">L56*5</f>
         <v>10</v>
       </c>
       <c r="N56" s="38">
         <v>100</v>
       </c>
       <c r="O56" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P56" s="39">
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q56" s="39">
-        <f t="shared" ref="Q56" si="51">P56*N56</f>
+        <f t="shared" ref="Q56" si="50">P56*N56</f>
         <v>0.12</v>
       </c>
       <c r="R56" s="38"/>
@@ -5398,13 +5399,13 @@
         <v>256</v>
       </c>
       <c r="I57" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J57" s="62" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K57" s="62" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="L57" s="62">
         <v>3</v>
@@ -5417,7 +5418,7 @@
         <v>100</v>
       </c>
       <c r="O57" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P57" s="63">
         <v>1.2999999999999999E-3</v>
@@ -5454,32 +5455,32 @@
         <v>256</v>
       </c>
       <c r="I58" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J58" s="38" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="K58" s="38" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="L58" s="38">
         <v>4</v>
       </c>
       <c r="M58" s="38">
-        <f t="shared" ref="M58" si="52">L58*5</f>
+        <f t="shared" ref="M58" si="51">L58*5</f>
         <v>20</v>
       </c>
       <c r="N58" s="38">
         <v>50</v>
       </c>
       <c r="O58" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P58" s="39">
         <v>9.2999999999999992E-3</v>
       </c>
       <c r="Q58" s="39">
-        <f t="shared" ref="Q58" si="53">P58*N58</f>
+        <f t="shared" ref="Q58" si="52">P58*N58</f>
         <v>0.46499999999999997</v>
       </c>
       <c r="R58" s="38"/>
@@ -5510,13 +5511,13 @@
         <v>256</v>
       </c>
       <c r="I59" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J59" s="62" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="K59" s="62" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="L59" s="62">
         <v>1</v>
@@ -5529,7 +5530,7 @@
         <v>100</v>
       </c>
       <c r="O59" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P59" s="63">
         <v>3.0000000000000001E-3</v>
@@ -5566,32 +5567,32 @@
         <v>256</v>
       </c>
       <c r="I60" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J60" s="38" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K60" s="38" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L60" s="38">
         <v>3</v>
       </c>
       <c r="M60" s="38">
-        <f t="shared" ref="M60" si="54">L60*5</f>
+        <f t="shared" ref="M60" si="53">L60*5</f>
         <v>15</v>
       </c>
       <c r="N60" s="38">
         <v>100</v>
       </c>
       <c r="O60" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P60" s="39">
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q60" s="39">
-        <f t="shared" ref="Q60" si="55">P60*N60</f>
+        <f t="shared" ref="Q60" si="54">P60*N60</f>
         <v>0.12</v>
       </c>
       <c r="R60" s="38"/>
@@ -5622,13 +5623,13 @@
         <v>256</v>
       </c>
       <c r="I61" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J61" s="62" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="K61" s="62" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L61" s="62">
         <v>6</v>
@@ -5641,7 +5642,7 @@
         <v>100</v>
       </c>
       <c r="O61" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P61" s="63">
         <v>1.1000000000000001E-3</v>
@@ -5678,32 +5679,32 @@
         <v>256</v>
       </c>
       <c r="I62" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J62" s="38" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K62" s="38" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L62" s="38">
         <v>4</v>
       </c>
       <c r="M62" s="38">
-        <f t="shared" ref="M62" si="56">L62*5</f>
+        <f t="shared" ref="M62" si="55">L62*5</f>
         <v>20</v>
       </c>
       <c r="N62" s="38">
         <v>100</v>
       </c>
       <c r="O62" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P62" s="39">
         <v>1E-3</v>
       </c>
       <c r="Q62" s="39">
-        <f t="shared" ref="Q62" si="57">P62*N62</f>
+        <f t="shared" ref="Q62" si="56">P62*N62</f>
         <v>0.1</v>
       </c>
       <c r="R62" s="38"/>
@@ -5734,13 +5735,13 @@
         <v>256</v>
       </c>
       <c r="I63" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J63" s="62" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K63" s="62" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L63" s="62">
         <v>1</v>
@@ -5753,7 +5754,7 @@
         <v>100</v>
       </c>
       <c r="O63" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P63" s="63">
         <v>1.2999999999999999E-3</v>
@@ -5790,32 +5791,32 @@
         <v>256</v>
       </c>
       <c r="I64" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J64" s="38" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K64" s="38" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L64" s="38">
         <v>3</v>
       </c>
       <c r="M64" s="38">
-        <f t="shared" ref="M64" si="58">L64*5</f>
+        <f t="shared" ref="M64" si="57">L64*5</f>
         <v>15</v>
       </c>
       <c r="N64" s="38">
         <v>100</v>
       </c>
       <c r="O64" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P64" s="39">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q64" s="39">
-        <f t="shared" ref="Q64" si="59">P64*N64</f>
+        <f t="shared" ref="Q64" si="58">P64*N64</f>
         <v>0.13</v>
       </c>
       <c r="R64" s="38"/>
@@ -5846,13 +5847,13 @@
         <v>256</v>
       </c>
       <c r="I65" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J65" s="62" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="K65" s="62" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L65" s="62">
         <v>1</v>
@@ -5865,7 +5866,7 @@
         <v>100</v>
       </c>
       <c r="O65" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P65" s="63">
         <v>1.8E-3</v>
@@ -5902,32 +5903,32 @@
         <v>256</v>
       </c>
       <c r="I66" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J66" s="38" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="K66" s="38" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="L66" s="38">
         <v>1</v>
       </c>
       <c r="M66" s="38">
-        <f t="shared" ref="M66" si="60">L66*5</f>
+        <f t="shared" ref="M66" si="59">L66*5</f>
         <v>5</v>
       </c>
       <c r="N66" s="38">
         <v>100</v>
       </c>
       <c r="O66" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P66" s="39">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q66" s="39">
-        <f t="shared" ref="Q66" si="61">P66*N66</f>
+        <f t="shared" ref="Q66" si="60">P66*N66</f>
         <v>0.13</v>
       </c>
       <c r="R66" s="38"/>
@@ -5958,13 +5959,13 @@
         <v>256</v>
       </c>
       <c r="I67" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J67" s="62" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="K67" s="62" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L67" s="62">
         <v>1</v>
@@ -5977,7 +5978,7 @@
         <v>100</v>
       </c>
       <c r="O67" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P67" s="63">
         <v>6.9999999999999999E-4</v>
@@ -6014,32 +6015,32 @@
         <v>256</v>
       </c>
       <c r="I68" s="38" t="s">
+        <v>380</v>
+      </c>
+      <c r="J68" s="38" t="s">
         <v>381</v>
       </c>
-      <c r="J68" s="38" t="s">
-        <v>382</v>
-      </c>
       <c r="K68" s="38" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L68" s="38">
         <v>1</v>
       </c>
       <c r="M68" s="38">
-        <f t="shared" ref="M68" si="62">L68*5</f>
+        <f t="shared" ref="M68" si="61">L68*5</f>
         <v>5</v>
       </c>
       <c r="N68" s="38">
         <v>100</v>
       </c>
       <c r="O68" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P68" s="39">
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q68" s="39">
-        <f t="shared" ref="Q68" si="63">P68*N68</f>
+        <f t="shared" ref="Q68" si="62">P68*N68</f>
         <v>0.05</v>
       </c>
       <c r="R68" s="38"/>
@@ -6051,54 +6052,54 @@
         <f>ROW(B69) - ROW($B$9)</f>
         <v>60</v>
       </c>
-      <c r="C69" s="89" t="s">
-        <v>397</v>
-      </c>
-      <c r="D69" s="90" t="s">
+      <c r="C69" s="79" t="s">
+        <v>396</v>
+      </c>
+      <c r="D69" s="80" t="s">
         <v>79</v>
       </c>
-      <c r="E69" s="90" t="s">
+      <c r="E69" s="80" t="s">
         <v>146</v>
       </c>
-      <c r="F69" s="90" t="s">
-        <v>381</v>
-      </c>
-      <c r="G69" s="90" t="s">
+      <c r="F69" s="80" t="s">
+        <v>380</v>
+      </c>
+      <c r="G69" s="80" t="s">
         <v>188</v>
       </c>
-      <c r="H69" s="90" t="s">
-        <v>381</v>
-      </c>
-      <c r="I69" s="90" t="s">
-        <v>381</v>
-      </c>
-      <c r="J69" s="90" t="s">
-        <v>381</v>
-      </c>
-      <c r="K69" s="90" t="s">
-        <v>381</v>
-      </c>
-      <c r="L69" s="90">
+      <c r="H69" s="80" t="s">
+        <v>380</v>
+      </c>
+      <c r="I69" s="80" t="s">
+        <v>380</v>
+      </c>
+      <c r="J69" s="80" t="s">
+        <v>380</v>
+      </c>
+      <c r="K69" s="80" t="s">
+        <v>380</v>
+      </c>
+      <c r="L69" s="80">
         <v>2</v>
       </c>
-      <c r="M69" s="90">
+      <c r="M69" s="80">
         <f>L69*5</f>
         <v>10</v>
       </c>
-      <c r="N69" s="90" t="s">
-        <v>381</v>
-      </c>
-      <c r="O69" s="91" t="s">
-        <v>381</v>
-      </c>
-      <c r="P69" s="92" t="s">
-        <v>381</v>
-      </c>
-      <c r="Q69" s="92" t="s">
-        <v>381</v>
-      </c>
-      <c r="R69" s="90"/>
-      <c r="S69" s="90"/>
+      <c r="N69" s="80" t="s">
+        <v>380</v>
+      </c>
+      <c r="O69" s="81" t="s">
+        <v>380</v>
+      </c>
+      <c r="P69" s="82" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q69" s="82" t="s">
+        <v>380</v>
+      </c>
+      <c r="R69" s="80"/>
+      <c r="S69" s="80"/>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
@@ -6107,7 +6108,7 @@
         <v>61</v>
       </c>
       <c r="C70" s="60" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D70" s="64" t="s">
         <v>80</v>
@@ -6116,7 +6117,7 @@
         <v>147</v>
       </c>
       <c r="F70" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G70" s="38" t="s">
         <v>245</v>
@@ -6125,32 +6126,32 @@
         <v>280</v>
       </c>
       <c r="I70" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J70" s="38" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K70" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L70" s="38">
         <v>1</v>
       </c>
       <c r="M70" s="38">
-        <f t="shared" ref="M70" si="64">L70*5</f>
+        <f t="shared" ref="M70" si="63">L70*5</f>
         <v>5</v>
       </c>
       <c r="N70" s="38">
         <v>6</v>
       </c>
       <c r="O70" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P70" s="39">
         <v>0.54410000000000003</v>
       </c>
       <c r="Q70" s="39">
-        <f t="shared" ref="Q70" si="65">P70*N70</f>
+        <f t="shared" ref="Q70" si="64">P70*N70</f>
         <v>3.2646000000000002</v>
       </c>
       <c r="R70" s="38"/>
@@ -6181,13 +6182,13 @@
         <v>281</v>
       </c>
       <c r="I71" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J71" s="62" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="K71" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L71" s="62">
         <v>1</v>
@@ -6200,7 +6201,7 @@
         <v>10</v>
       </c>
       <c r="O71" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P71" s="63">
         <v>7.6300000000000007E-2</v>
@@ -6237,32 +6238,32 @@
         <v>282</v>
       </c>
       <c r="I72" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J72" s="38" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K72" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L72" s="38">
         <v>1</v>
       </c>
       <c r="M72" s="38">
-        <f t="shared" ref="M72" si="66">L72*5</f>
+        <f t="shared" ref="M72" si="65">L72*5</f>
         <v>5</v>
       </c>
       <c r="N72" s="38">
         <v>6</v>
       </c>
       <c r="O72" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P72" s="39">
         <v>3.1484999999999999</v>
       </c>
       <c r="Q72" s="39">
-        <f t="shared" ref="Q72" si="67">P72*N72</f>
+        <f t="shared" ref="Q72" si="66">P72*N72</f>
         <v>18.890999999999998</v>
       </c>
       <c r="R72" s="38"/>
@@ -6293,13 +6294,13 @@
         <v>283</v>
       </c>
       <c r="I73" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J73" s="62" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="K73" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L73" s="62">
         <v>1</v>
@@ -6312,7 +6313,7 @@
         <v>10</v>
       </c>
       <c r="O73" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P73" s="63">
         <v>0.10920000000000001</v>
@@ -6349,32 +6350,32 @@
         <v>284</v>
       </c>
       <c r="I74" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J74" s="38" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K74" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L74" s="38">
         <v>4</v>
       </c>
       <c r="M74" s="38">
-        <f t="shared" ref="M74" si="68">L74*5</f>
+        <f t="shared" ref="M74" si="67">L74*5</f>
         <v>20</v>
       </c>
       <c r="N74" s="38">
         <v>21</v>
       </c>
       <c r="O74" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P74" s="39">
         <v>7.5918999999999999</v>
       </c>
       <c r="Q74" s="39">
-        <f t="shared" ref="Q74" si="69">P74*N74</f>
+        <f t="shared" ref="Q74" si="68">P74*N74</f>
         <v>159.4299</v>
       </c>
       <c r="R74" s="38"/>
@@ -6405,13 +6406,13 @@
         <v>285</v>
       </c>
       <c r="I75" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J75" s="62" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="K75" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L75" s="62">
         <v>2</v>
@@ -6424,7 +6425,7 @@
         <v>11</v>
       </c>
       <c r="O75" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P75" s="63">
         <v>0.73819999999999997</v>
@@ -6461,32 +6462,32 @@
         <v>285</v>
       </c>
       <c r="I76" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J76" s="38" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="K76" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L76" s="38">
         <v>1</v>
       </c>
       <c r="M76" s="38">
-        <f t="shared" ref="M76" si="70">L76*5</f>
+        <f t="shared" ref="M76" si="69">L76*5</f>
         <v>5</v>
       </c>
       <c r="N76" s="38">
         <v>6</v>
       </c>
       <c r="O76" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P76" s="39">
         <v>0.6905</v>
       </c>
       <c r="Q76" s="39">
-        <f t="shared" ref="Q76" si="71">P76*N76</f>
+        <f t="shared" ref="Q76" si="70">P76*N76</f>
         <v>4.1429999999999998</v>
       </c>
       <c r="R76" s="38"/>
@@ -6508,7 +6509,7 @@
         <v>154</v>
       </c>
       <c r="F77" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G77" s="62" t="s">
         <v>194</v>
@@ -6517,13 +6518,13 @@
         <v>286</v>
       </c>
       <c r="I77" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J77" s="62" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K77" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L77" s="62">
         <v>1</v>
@@ -6536,7 +6537,7 @@
         <v>6</v>
       </c>
       <c r="O77" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P77" s="63">
         <v>20.79</v>
@@ -6573,32 +6574,32 @@
         <v>287</v>
       </c>
       <c r="I78" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J78" s="38" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K78" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L78" s="38">
         <v>1</v>
       </c>
       <c r="M78" s="38">
-        <f t="shared" ref="M78" si="72">L78*5</f>
+        <f t="shared" ref="M78" si="71">L78*5</f>
         <v>5</v>
       </c>
       <c r="N78" s="38">
         <v>6</v>
       </c>
       <c r="O78" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P78" s="39">
         <v>11.400499999999999</v>
       </c>
       <c r="Q78" s="39">
-        <f t="shared" ref="Q78" si="73">P78*N78</f>
+        <f t="shared" ref="Q78" si="72">P78*N78</f>
         <v>68.402999999999992</v>
       </c>
       <c r="R78" s="38"/>
@@ -6629,13 +6630,13 @@
         <v>288</v>
       </c>
       <c r="I79" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J79" s="62" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="K79" s="62" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L79" s="62">
         <v>1</v>
@@ -6648,7 +6649,7 @@
         <v>6</v>
       </c>
       <c r="O79" s="57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P79" s="63">
         <v>2.8128000000000002</v>
@@ -6685,32 +6686,32 @@
         <v>289</v>
       </c>
       <c r="I80" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J80" s="38" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K80" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L80" s="38">
         <v>1</v>
       </c>
       <c r="M80" s="38">
-        <f t="shared" ref="M80:M83" si="74">L80*5</f>
+        <f t="shared" ref="M80:M83" si="73">L80*5</f>
         <v>5</v>
       </c>
       <c r="N80" s="38">
         <v>10</v>
       </c>
       <c r="O80" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P80" s="39">
         <v>8.3400000000000002E-2</v>
       </c>
       <c r="Q80" s="39">
-        <f t="shared" ref="Q80" si="75">P80*N80</f>
+        <f t="shared" ref="Q80" si="74">P80*N80</f>
         <v>0.83400000000000007</v>
       </c>
       <c r="R80" s="38"/>
@@ -6722,101 +6723,101 @@
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="C81" s="82" t="s">
+      <c r="C81" s="72" t="s">
+        <v>434</v>
+      </c>
+      <c r="D81" s="83" t="s">
+        <v>439</v>
+      </c>
+      <c r="E81" s="74" t="s">
+        <v>438</v>
+      </c>
+      <c r="F81" s="74" t="s">
+        <v>392</v>
+      </c>
+      <c r="G81" s="74" t="s">
         <v>435</v>
       </c>
-      <c r="D81" s="93" t="s">
-        <v>440</v>
-      </c>
-      <c r="E81" s="84" t="s">
-        <v>439</v>
-      </c>
-      <c r="F81" s="84" t="s">
+      <c r="H81" s="74" t="s">
+        <v>437</v>
+      </c>
+      <c r="I81" s="74" t="s">
+        <v>380</v>
+      </c>
+      <c r="J81" s="74" t="s">
+        <v>436</v>
+      </c>
+      <c r="K81" s="74" t="s">
+        <v>380</v>
+      </c>
+      <c r="L81" s="74">
+        <v>1</v>
+      </c>
+      <c r="M81" s="74">
+        <f t="shared" si="73"/>
+        <v>5</v>
+      </c>
+      <c r="N81" s="74">
+        <v>6</v>
+      </c>
+      <c r="O81" s="76" t="s">
         <v>393</v>
       </c>
-      <c r="G81" s="84" t="s">
-        <v>436</v>
-      </c>
-      <c r="H81" s="84" t="s">
-        <v>438</v>
-      </c>
-      <c r="I81" s="84" t="s">
-        <v>381</v>
-      </c>
-      <c r="J81" s="84" t="s">
-        <v>437</v>
-      </c>
-      <c r="K81" s="84" t="s">
-        <v>381</v>
-      </c>
-      <c r="L81" s="84">
-        <v>1</v>
-      </c>
-      <c r="M81" s="84">
-        <f t="shared" si="74"/>
-        <v>5</v>
-      </c>
-      <c r="N81" s="84">
-        <v>6</v>
-      </c>
-      <c r="O81" s="86" t="s">
-        <v>394</v>
-      </c>
-      <c r="P81" s="87">
+      <c r="P81" s="77">
         <v>1.5643</v>
       </c>
-      <c r="Q81" s="87">
+      <c r="Q81" s="77">
         <f>P81*N81</f>
         <v>9.3857999999999997</v>
       </c>
-      <c r="R81" s="84"/>
-      <c r="S81" s="84"/>
+      <c r="R81" s="74"/>
+      <c r="S81" s="74"/>
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="47">
-        <f t="shared" ref="B82:B83" si="76">ROW(B82) - ROW($B$9)</f>
+        <f t="shared" ref="B82:B83" si="75">ROW(B82) - ROW($B$9)</f>
         <v>73</v>
       </c>
       <c r="C82" s="60" t="s">
-        <v>435</v>
-      </c>
-      <c r="D82" s="94" t="s">
+        <v>434</v>
+      </c>
+      <c r="D82" s="84" t="s">
+        <v>439</v>
+      </c>
+      <c r="E82" s="38" t="s">
+        <v>442</v>
+      </c>
+      <c r="F82" s="38" t="s">
+        <v>392</v>
+      </c>
+      <c r="G82" s="38" t="s">
         <v>440</v>
       </c>
-      <c r="E82" s="38" t="s">
-        <v>443</v>
-      </c>
-      <c r="F82" s="38" t="s">
-        <v>393</v>
-      </c>
-      <c r="G82" s="38" t="s">
+      <c r="H82" s="38" t="s">
+        <v>437</v>
+      </c>
+      <c r="I82" s="38" t="s">
+        <v>380</v>
+      </c>
+      <c r="J82" s="38" t="s">
         <v>441</v>
       </c>
-      <c r="H82" s="38" t="s">
-        <v>438</v>
-      </c>
-      <c r="I82" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="J82" s="38" t="s">
-        <v>442</v>
-      </c>
       <c r="K82" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L82" s="38">
         <v>1</v>
       </c>
       <c r="M82" s="38">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>5</v>
       </c>
       <c r="N82" s="38">
         <v>6</v>
       </c>
       <c r="O82" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P82" s="39">
         <v>2.0146999999999999</v>
@@ -6831,58 +6832,58 @@
     <row r="83" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="47">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>74</v>
       </c>
-      <c r="C83" s="82" t="s">
-        <v>435</v>
-      </c>
-      <c r="D83" s="93" t="s">
-        <v>440</v>
-      </c>
-      <c r="E83" s="84" t="s">
+      <c r="C83" s="72" t="s">
+        <v>434</v>
+      </c>
+      <c r="D83" s="83" t="s">
+        <v>439</v>
+      </c>
+      <c r="E83" s="74" t="s">
+        <v>444</v>
+      </c>
+      <c r="F83" s="74" t="s">
+        <v>392</v>
+      </c>
+      <c r="G83" s="74" t="s">
+        <v>443</v>
+      </c>
+      <c r="H83" s="74" t="s">
+        <v>437</v>
+      </c>
+      <c r="I83" s="74" t="s">
+        <v>380</v>
+      </c>
+      <c r="J83" s="74" t="s">
         <v>445</v>
       </c>
-      <c r="F83" s="84" t="s">
+      <c r="K83" s="74" t="s">
+        <v>380</v>
+      </c>
+      <c r="L83" s="74">
+        <v>1</v>
+      </c>
+      <c r="M83" s="74">
+        <f t="shared" si="73"/>
+        <v>5</v>
+      </c>
+      <c r="N83" s="74">
+        <v>6</v>
+      </c>
+      <c r="O83" s="76" t="s">
         <v>393</v>
       </c>
-      <c r="G83" s="84" t="s">
-        <v>444</v>
-      </c>
-      <c r="H83" s="84" t="s">
-        <v>438</v>
-      </c>
-      <c r="I83" s="84" t="s">
-        <v>381</v>
-      </c>
-      <c r="J83" s="84" t="s">
-        <v>446</v>
-      </c>
-      <c r="K83" s="84" t="s">
-        <v>381</v>
-      </c>
-      <c r="L83" s="84">
-        <v>1</v>
-      </c>
-      <c r="M83" s="84">
-        <f t="shared" si="74"/>
-        <v>5</v>
-      </c>
-      <c r="N83" s="84">
-        <v>6</v>
-      </c>
-      <c r="O83" s="86" t="s">
-        <v>394</v>
-      </c>
-      <c r="P83" s="87">
+      <c r="P83" s="77">
         <v>0.80110000000000003</v>
       </c>
-      <c r="Q83" s="87">
+      <c r="Q83" s="77">
         <f>P83*N83</f>
         <v>4.8066000000000004</v>
       </c>
-      <c r="R83" s="84"/>
-      <c r="S83" s="84"/>
+      <c r="R83" s="74"/>
+      <c r="S83" s="74"/>
     </row>
     <row r="84" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
@@ -6898,17 +6899,17 @@
       <c r="K84" s="45"/>
       <c r="L84" s="45"/>
       <c r="M84" s="45"/>
-      <c r="N84" s="74" t="s">
+      <c r="N84" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="O84" s="75"/>
-      <c r="P84" s="75"/>
+      <c r="O84" s="97"/>
+      <c r="P84" s="97"/>
       <c r="Q84" s="48">
-        <f>SUM(Q10:Q81)</f>
-        <v>687.65389999999991</v>
-      </c>
-      <c r="R84" s="70"/>
-      <c r="S84" s="71"/>
+        <f>SUM(Q10:Q83)</f>
+        <v>703.76769999999999</v>
+      </c>
+      <c r="R84" s="92"/>
+      <c r="S84" s="93"/>
     </row>
     <row r="85" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
@@ -6924,17 +6925,17 @@
       <c r="K85" s="10"/>
       <c r="L85" s="10"/>
       <c r="M85" s="10"/>
-      <c r="N85" s="74" t="s">
+      <c r="N85" s="96" t="s">
         <v>6</v>
       </c>
-      <c r="O85" s="75"/>
-      <c r="P85" s="75"/>
+      <c r="O85" s="97"/>
+      <c r="P85" s="97"/>
       <c r="Q85" s="49">
         <f>Q84/5</f>
-        <v>137.53077999999999</v>
-      </c>
-      <c r="R85" s="72"/>
-      <c r="S85" s="73"/>
+        <v>140.75353999999999</v>
+      </c>
+      <c r="R85" s="94"/>
+      <c r="S85" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6970,54 +6971,54 @@
     <hyperlink ref="O37" r:id="rId22" xr:uid="{7898B0DE-B99C-422B-93A1-C64000A2710F}"/>
     <hyperlink ref="O38" r:id="rId23" xr:uid="{60F5EA99-FC5D-42DA-83AB-2503145247E5}"/>
     <hyperlink ref="O39" r:id="rId24" xr:uid="{6EA8AF8A-1CB3-451C-A1FF-53A54C702D59}"/>
-    <hyperlink ref="O40" r:id="rId25" xr:uid="{B317581D-06A6-4EB4-891A-C0C139D8E474}"/>
-    <hyperlink ref="O41" r:id="rId26" xr:uid="{FDCBF760-4B93-4276-A3BA-7715546260C9}"/>
-    <hyperlink ref="O42" r:id="rId27" xr:uid="{8E648B41-42DE-4F16-91A7-315D4267BDAC}"/>
-    <hyperlink ref="O43" r:id="rId28" xr:uid="{90524ED7-C00A-44AB-8E3C-CF9BE029B7F7}"/>
-    <hyperlink ref="O44" r:id="rId29" xr:uid="{1F66A3F1-2879-418E-A260-EBF5779ADB9A}"/>
-    <hyperlink ref="O45" r:id="rId30" xr:uid="{D6253230-F78F-4F57-841E-6E32DA3F6F6B}"/>
-    <hyperlink ref="O47" r:id="rId31" xr:uid="{F92A08BD-DC56-49CB-BB49-C672D65AF7B6}"/>
-    <hyperlink ref="O46" r:id="rId32" xr:uid="{C983EB1D-0C91-45E9-BE66-3F32EFEBF11E}"/>
-    <hyperlink ref="O50" r:id="rId33" xr:uid="{D166F96C-85E9-4ECC-95F1-3B236295E9EA}"/>
-    <hyperlink ref="O51" r:id="rId34" xr:uid="{74E89379-FE6D-4A6D-9086-2E5F06F276D3}"/>
-    <hyperlink ref="O52" r:id="rId35" xr:uid="{9500BE23-7086-4D84-96D7-5D20AD5CA396}"/>
-    <hyperlink ref="O53" r:id="rId36" xr:uid="{7959F19A-CC8B-4CCD-9543-CFA937F95FE0}"/>
-    <hyperlink ref="O54" r:id="rId37" xr:uid="{C1A12F9C-529D-4C71-B8D0-1E662F17A4CF}"/>
-    <hyperlink ref="O55" r:id="rId38" xr:uid="{9FB226EB-05D0-4756-90EC-AB74DF432825}"/>
-    <hyperlink ref="O56" r:id="rId39" xr:uid="{2A083DAE-370B-4D83-8484-60F664F4D0FB}"/>
-    <hyperlink ref="O57" r:id="rId40" xr:uid="{2C97F014-F5E8-4B24-963D-FE80A7631953}"/>
-    <hyperlink ref="O58" r:id="rId41" xr:uid="{6F3D2A4A-F4D5-4F39-AA76-C26734A9F58D}"/>
-    <hyperlink ref="O59" r:id="rId42" xr:uid="{071B56B4-D644-4DBA-9C24-EAA419F04152}"/>
-    <hyperlink ref="O60" r:id="rId43" xr:uid="{FCEB1084-02FC-4396-A776-E5A840FCDC5C}"/>
-    <hyperlink ref="O61" r:id="rId44" xr:uid="{E366D270-8EAC-4607-849D-1D7110BF13C6}"/>
-    <hyperlink ref="O62" r:id="rId45" xr:uid="{21BB671E-15DA-47B2-9961-72F25541C5E2}"/>
-    <hyperlink ref="O63" r:id="rId46" xr:uid="{4F5D2B75-A643-4920-899E-536F91142938}"/>
-    <hyperlink ref="O64" r:id="rId47" xr:uid="{D6C832CC-6FCE-4894-B42E-1075C3474637}"/>
-    <hyperlink ref="O65" r:id="rId48" xr:uid="{46C226E9-81B8-4812-9A33-DA13B84C252D}"/>
-    <hyperlink ref="O66" r:id="rId49" xr:uid="{08B69DB7-9AAD-4B1C-BFEB-486DA2F5A169}"/>
-    <hyperlink ref="O67" r:id="rId50" xr:uid="{C942BC27-6E68-427F-9EC4-5A6A9F3691F9}"/>
-    <hyperlink ref="O68" r:id="rId51" xr:uid="{D6B78B63-B011-4041-9416-EA6C7F8D8AE7}"/>
-    <hyperlink ref="O70" r:id="rId52" xr:uid="{8429BF53-DDFF-45A2-9753-DFDC3A7EC73E}"/>
-    <hyperlink ref="O71" r:id="rId53" xr:uid="{69BB30E6-FCE6-4DD2-9033-50DBAEAFB28E}"/>
-    <hyperlink ref="O72" r:id="rId54" xr:uid="{9DBB4DF3-112E-4A0A-A8C2-64BB1FCB650F}"/>
-    <hyperlink ref="O73" r:id="rId55" xr:uid="{749C77DE-6558-4DB6-8849-7A73C148D4CE}"/>
-    <hyperlink ref="O74" r:id="rId56" xr:uid="{5FBFDDE4-D8E1-4DDC-8314-D97DA5D132A5}"/>
-    <hyperlink ref="O75" r:id="rId57" xr:uid="{FD33955C-3AAA-49E7-ADBD-08C8E8316B63}"/>
-    <hyperlink ref="O76" r:id="rId58" xr:uid="{10F92991-AF57-4F4E-ACEC-133226566204}"/>
-    <hyperlink ref="O77" r:id="rId59" xr:uid="{6027C0A4-5D1E-4433-85BF-CD2F57D6DA89}"/>
-    <hyperlink ref="O78" r:id="rId60" xr:uid="{29DDBCD9-DE51-47A5-B3C6-827913DA2387}"/>
-    <hyperlink ref="O79" r:id="rId61" xr:uid="{FC388204-E09E-47D1-A054-C8455D575E2E}"/>
-    <hyperlink ref="O80" r:id="rId62" xr:uid="{C573F08C-CF21-426E-B62B-392C975BBEB8}"/>
-    <hyperlink ref="O24" r:id="rId63" xr:uid="{A2463247-A92E-46A4-B1F2-C7859F430396}"/>
-    <hyperlink ref="O12" r:id="rId64" xr:uid="{8C42F702-13DB-4B89-BA91-C5903624B455}"/>
-    <hyperlink ref="O17" r:id="rId65" xr:uid="{71295E9A-7059-4DB8-9A46-8806E333672F}"/>
-    <hyperlink ref="O35" r:id="rId66" xr:uid="{31634445-58D7-420B-A9DF-F6B47E182EE9}"/>
-    <hyperlink ref="O36" r:id="rId67" xr:uid="{696C55EA-352D-4A6D-AE88-F7D6577A10B8}"/>
-    <hyperlink ref="O20" r:id="rId68" xr:uid="{F67ACF00-C62E-4EB8-A65F-317350E7C6CF}"/>
-    <hyperlink ref="O48" r:id="rId69" xr:uid="{B72543AB-3101-4A9B-892E-15300936BBF9}"/>
-    <hyperlink ref="O81" r:id="rId70" xr:uid="{387305BF-5056-46E6-9C42-81E1A79E261A}"/>
-    <hyperlink ref="O82" r:id="rId71" xr:uid="{EB956738-249B-40D1-8C80-EEE1E1ED8710}"/>
-    <hyperlink ref="O83" r:id="rId72" xr:uid="{6864A1C4-75C3-4A42-AD86-1617EF24C777}"/>
+    <hyperlink ref="O41" r:id="rId25" xr:uid="{FDCBF760-4B93-4276-A3BA-7715546260C9}"/>
+    <hyperlink ref="O42" r:id="rId26" xr:uid="{8E648B41-42DE-4F16-91A7-315D4267BDAC}"/>
+    <hyperlink ref="O43" r:id="rId27" xr:uid="{90524ED7-C00A-44AB-8E3C-CF9BE029B7F7}"/>
+    <hyperlink ref="O44" r:id="rId28" xr:uid="{1F66A3F1-2879-418E-A260-EBF5779ADB9A}"/>
+    <hyperlink ref="O45" r:id="rId29" xr:uid="{D6253230-F78F-4F57-841E-6E32DA3F6F6B}"/>
+    <hyperlink ref="O47" r:id="rId30" xr:uid="{F92A08BD-DC56-49CB-BB49-C672D65AF7B6}"/>
+    <hyperlink ref="O46" r:id="rId31" xr:uid="{C983EB1D-0C91-45E9-BE66-3F32EFEBF11E}"/>
+    <hyperlink ref="O50" r:id="rId32" xr:uid="{D166F96C-85E9-4ECC-95F1-3B236295E9EA}"/>
+    <hyperlink ref="O51" r:id="rId33" xr:uid="{74E89379-FE6D-4A6D-9086-2E5F06F276D3}"/>
+    <hyperlink ref="O52" r:id="rId34" xr:uid="{9500BE23-7086-4D84-96D7-5D20AD5CA396}"/>
+    <hyperlink ref="O53" r:id="rId35" xr:uid="{7959F19A-CC8B-4CCD-9543-CFA937F95FE0}"/>
+    <hyperlink ref="O54" r:id="rId36" xr:uid="{C1A12F9C-529D-4C71-B8D0-1E662F17A4CF}"/>
+    <hyperlink ref="O55" r:id="rId37" xr:uid="{9FB226EB-05D0-4756-90EC-AB74DF432825}"/>
+    <hyperlink ref="O56" r:id="rId38" xr:uid="{2A083DAE-370B-4D83-8484-60F664F4D0FB}"/>
+    <hyperlink ref="O57" r:id="rId39" xr:uid="{2C97F014-F5E8-4B24-963D-FE80A7631953}"/>
+    <hyperlink ref="O58" r:id="rId40" xr:uid="{6F3D2A4A-F4D5-4F39-AA76-C26734A9F58D}"/>
+    <hyperlink ref="O59" r:id="rId41" xr:uid="{071B56B4-D644-4DBA-9C24-EAA419F04152}"/>
+    <hyperlink ref="O60" r:id="rId42" xr:uid="{FCEB1084-02FC-4396-A776-E5A840FCDC5C}"/>
+    <hyperlink ref="O61" r:id="rId43" xr:uid="{E366D270-8EAC-4607-849D-1D7110BF13C6}"/>
+    <hyperlink ref="O62" r:id="rId44" xr:uid="{21BB671E-15DA-47B2-9961-72F25541C5E2}"/>
+    <hyperlink ref="O63" r:id="rId45" xr:uid="{4F5D2B75-A643-4920-899E-536F91142938}"/>
+    <hyperlink ref="O64" r:id="rId46" xr:uid="{D6C832CC-6FCE-4894-B42E-1075C3474637}"/>
+    <hyperlink ref="O65" r:id="rId47" xr:uid="{46C226E9-81B8-4812-9A33-DA13B84C252D}"/>
+    <hyperlink ref="O66" r:id="rId48" xr:uid="{08B69DB7-9AAD-4B1C-BFEB-486DA2F5A169}"/>
+    <hyperlink ref="O67" r:id="rId49" xr:uid="{C942BC27-6E68-427F-9EC4-5A6A9F3691F9}"/>
+    <hyperlink ref="O68" r:id="rId50" xr:uid="{D6B78B63-B011-4041-9416-EA6C7F8D8AE7}"/>
+    <hyperlink ref="O70" r:id="rId51" xr:uid="{8429BF53-DDFF-45A2-9753-DFDC3A7EC73E}"/>
+    <hyperlink ref="O71" r:id="rId52" xr:uid="{69BB30E6-FCE6-4DD2-9033-50DBAEAFB28E}"/>
+    <hyperlink ref="O72" r:id="rId53" xr:uid="{9DBB4DF3-112E-4A0A-A8C2-64BB1FCB650F}"/>
+    <hyperlink ref="O73" r:id="rId54" xr:uid="{749C77DE-6558-4DB6-8849-7A73C148D4CE}"/>
+    <hyperlink ref="O74" r:id="rId55" xr:uid="{5FBFDDE4-D8E1-4DDC-8314-D97DA5D132A5}"/>
+    <hyperlink ref="O75" r:id="rId56" xr:uid="{FD33955C-3AAA-49E7-ADBD-08C8E8316B63}"/>
+    <hyperlink ref="O76" r:id="rId57" xr:uid="{10F92991-AF57-4F4E-ACEC-133226566204}"/>
+    <hyperlink ref="O77" r:id="rId58" xr:uid="{6027C0A4-5D1E-4433-85BF-CD2F57D6DA89}"/>
+    <hyperlink ref="O78" r:id="rId59" xr:uid="{29DDBCD9-DE51-47A5-B3C6-827913DA2387}"/>
+    <hyperlink ref="O79" r:id="rId60" xr:uid="{FC388204-E09E-47D1-A054-C8455D575E2E}"/>
+    <hyperlink ref="O80" r:id="rId61" xr:uid="{C573F08C-CF21-426E-B62B-392C975BBEB8}"/>
+    <hyperlink ref="O24" r:id="rId62" xr:uid="{A2463247-A92E-46A4-B1F2-C7859F430396}"/>
+    <hyperlink ref="O12" r:id="rId63" xr:uid="{8C42F702-13DB-4B89-BA91-C5903624B455}"/>
+    <hyperlink ref="O17" r:id="rId64" xr:uid="{71295E9A-7059-4DB8-9A46-8806E333672F}"/>
+    <hyperlink ref="O35" r:id="rId65" xr:uid="{31634445-58D7-420B-A9DF-F6B47E182EE9}"/>
+    <hyperlink ref="O36" r:id="rId66" xr:uid="{696C55EA-352D-4A6D-AE88-F7D6577A10B8}"/>
+    <hyperlink ref="O20" r:id="rId67" xr:uid="{F67ACF00-C62E-4EB8-A65F-317350E7C6CF}"/>
+    <hyperlink ref="O48" r:id="rId68" xr:uid="{B72543AB-3101-4A9B-892E-15300936BBF9}"/>
+    <hyperlink ref="O81" r:id="rId69" xr:uid="{387305BF-5056-46E6-9C42-81E1A79E261A}"/>
+    <hyperlink ref="O82" r:id="rId70" xr:uid="{EB956738-249B-40D1-8C80-EEE1E1ED8710}"/>
+    <hyperlink ref="O83" r:id="rId71" xr:uid="{6864A1C4-75C3-4A42-AD86-1617EF24C777}"/>
+    <hyperlink ref="O40" r:id="rId72" xr:uid="{B317581D-06A6-4EB4-891A-C0C139D8E474}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId73"/>

--- a/BOM/eSpark-BOM.xlsx
+++ b/BOM/eSpark-BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\matthewgraff-arduinomegapcb\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CA6982-4EE4-4D13-B070-D6F62FFA9621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70227F28-46B6-4EF3-92D0-4A8C7DCAC3F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/BOM/eSpark-BOM.xlsx
+++ b/BOM/eSpark-BOM.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\matthewgraff-arduinomegapcb\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70227F28-46B6-4EF3-92D0-4A8C7DCAC3F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E0CDEDA-94C2-416C-A1B8-2DF503589C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="5 boards" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="452">
   <si>
     <t>Component list</t>
   </si>
@@ -277,9 +277,6 @@
     <t>U4, U5, U6, U7</t>
   </si>
   <si>
-    <t>U8, U9</t>
-  </si>
-  <si>
     <t>U10</t>
   </si>
   <si>
@@ -1361,6 +1358,24 @@
   </si>
   <si>
     <t>DNP</t>
+  </si>
+  <si>
+    <t>U8</t>
+  </si>
+  <si>
+    <t>U9</t>
+  </si>
+  <si>
+    <t>IC TRANSLTR BIDIRECTIONAL 8VSSOP</t>
+  </si>
+  <si>
+    <t>8-VSSOP</t>
+  </si>
+  <si>
+    <t>TXS0102DCUR</t>
+  </si>
+  <si>
+    <t>C53434</t>
   </si>
 </sst>
 </file>
@@ -1581,7 +1596,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1597,12 +1612,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF03A4CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1863,7 +1872,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1931,7 +1940,7 @@
     <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1956,12 +1965,6 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1982,10 +1985,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2006,25 +2009,19 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2034,30 +2031,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="19" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2096,18 +2069,6 @@
     <xf numFmtId="0" fontId="28" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2139,6 +2100,15 @@
     <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2482,13 +2452,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S85"/>
+  <dimension ref="A1:S86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
     <col min="3" max="3" width="18" style="26" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.42578125" customWidth="1"/>
-    <col min="5" max="5" width="30.85546875" customWidth="1"/>
+    <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="6" width="21.140625" customWidth="1"/>
     <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
@@ -2516,15 +2486,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="88"/>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="88"/>
-      <c r="R1" s="88"/>
-      <c r="S1" s="89"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
+      <c r="P1" s="72"/>
+      <c r="Q1" s="72"/>
+      <c r="R1" s="72"/>
+      <c r="S1" s="73"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2534,8 +2504,8 @@
         <v>0</v>
       </c>
       <c r="E2" s="11"/>
-      <c r="F2" s="50" t="s">
-        <v>406</v>
+      <c r="F2" s="48" t="s">
+        <v>405</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2559,8 +2529,8 @@
         <v>1</v>
       </c>
       <c r="E3" s="13"/>
-      <c r="F3" s="51" t="s">
-        <v>407</v>
+      <c r="F3" s="49" t="s">
+        <v>406</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2574,7 +2544,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="90"/>
+      <c r="S3" s="74"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2584,8 +2554,8 @@
         <v>2</v>
       </c>
       <c r="E4" s="13"/>
-      <c r="F4" s="52" t="s">
-        <v>407</v>
+      <c r="F4" s="50" t="s">
+        <v>406</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2599,7 +2569,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="91"/>
+      <c r="S4" s="75"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2609,7 +2579,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="13"/>
-      <c r="F5" s="53" t="s">
+      <c r="F5" s="51" t="s">
         <v>7</v>
       </c>
       <c r="G5" s="15"/>
@@ -2624,7 +2594,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="91"/>
+      <c r="S5" s="75"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2645,7 +2615,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="91"/>
+      <c r="S6" s="75"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2666,7 +2636,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="91"/>
+      <c r="S7" s="75"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2687,7 +2657,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="91"/>
+      <c r="S8" s="75"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2697,4253 +2667,4306 @@
       <c r="C9" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="54" t="s">
+      <c r="D9" s="52" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="F9" s="54" t="s">
-        <v>158</v>
+        <v>90</v>
+      </c>
+      <c r="F9" s="52" t="s">
+        <v>157</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>198</v>
-      </c>
-      <c r="H9" s="54" t="s">
-        <v>255</v>
+        <v>197</v>
+      </c>
+      <c r="H9" s="52" t="s">
+        <v>254</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>382</v>
+      </c>
+      <c r="J9" s="52" t="s">
+        <v>289</v>
+      </c>
+      <c r="K9" s="53" t="s">
         <v>383</v>
       </c>
-      <c r="J9" s="54" t="s">
-        <v>290</v>
-      </c>
-      <c r="K9" s="55" t="s">
+      <c r="L9" s="30" t="s">
+        <v>378</v>
+      </c>
+      <c r="M9" s="54" t="s">
+        <v>387</v>
+      </c>
+      <c r="N9" s="52" t="s">
+        <v>388</v>
+      </c>
+      <c r="O9" s="30" t="s">
         <v>384</v>
       </c>
-      <c r="L9" s="30" t="s">
-        <v>379</v>
-      </c>
-      <c r="M9" s="56" t="s">
-        <v>388</v>
-      </c>
-      <c r="N9" s="54" t="s">
+      <c r="P9" s="52" t="s">
         <v>389</v>
       </c>
-      <c r="O9" s="30" t="s">
+      <c r="Q9" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="R9" s="52" t="s">
         <v>385</v>
       </c>
-      <c r="P9" s="54" t="s">
-        <v>390</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>391</v>
-      </c>
-      <c r="R9" s="54" t="s">
+      <c r="S9" s="30" t="s">
         <v>386</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="46">
+      <c r="B10" s="44">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="66" t="s">
+      <c r="C10" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="67" t="s">
+      <c r="D10" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="68" t="s">
-        <v>92</v>
-      </c>
-      <c r="F10" s="68" t="s">
-        <v>159</v>
-      </c>
-      <c r="G10" s="68" t="s">
-        <v>199</v>
-      </c>
-      <c r="H10" s="68" t="s">
-        <v>256</v>
-      </c>
-      <c r="I10" s="68" t="s">
-        <v>380</v>
-      </c>
-      <c r="J10" s="68" t="s">
-        <v>291</v>
-      </c>
-      <c r="K10" s="68" t="s">
-        <v>348</v>
-      </c>
-      <c r="L10" s="68">
+      <c r="E10" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>379</v>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>290</v>
+      </c>
+      <c r="K10" s="37" t="s">
+        <v>347</v>
+      </c>
+      <c r="L10" s="37">
         <v>1</v>
       </c>
-      <c r="M10" s="68">
+      <c r="M10" s="37">
         <f>L10*5</f>
         <v>5</v>
       </c>
-      <c r="N10" s="68">
+      <c r="N10" s="37">
         <v>10</v>
       </c>
-      <c r="O10" s="69" t="s">
-        <v>393</v>
-      </c>
-      <c r="P10" s="70">
+      <c r="O10" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P10" s="82">
         <v>0.15939999999999999</v>
       </c>
-      <c r="Q10" s="70">
+      <c r="Q10" s="82">
         <f>P10*N10</f>
         <v>1.5939999999999999</v>
       </c>
-      <c r="R10" s="68"/>
-      <c r="S10" s="87"/>
+      <c r="R10" s="37"/>
+      <c r="S10" s="83"/>
     </row>
     <row r="11" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="47">
-        <f t="shared" ref="B11:B81" si="0">ROW(B11) - ROW($B$9)</f>
+      <c r="B11" s="45">
+        <f t="shared" ref="B11:B82" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="72" t="s">
+      <c r="C11" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="73" t="s">
-        <v>414</v>
-      </c>
-      <c r="E11" s="74" t="s">
-        <v>93</v>
-      </c>
-      <c r="F11" s="74" t="s">
-        <v>159</v>
-      </c>
-      <c r="G11" s="75" t="s">
-        <v>200</v>
-      </c>
-      <c r="H11" s="74" t="s">
-        <v>256</v>
-      </c>
-      <c r="I11" s="74" t="s">
-        <v>394</v>
-      </c>
-      <c r="J11" s="74" t="s">
-        <v>292</v>
-      </c>
-      <c r="K11" s="74" t="s">
-        <v>349</v>
-      </c>
-      <c r="L11" s="74">
+      <c r="D11" s="61" t="s">
+        <v>413</v>
+      </c>
+      <c r="E11" s="62" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11" s="62" t="s">
+        <v>158</v>
+      </c>
+      <c r="G11" s="63" t="s">
+        <v>199</v>
+      </c>
+      <c r="H11" s="62" t="s">
+        <v>255</v>
+      </c>
+      <c r="I11" s="62" t="s">
+        <v>393</v>
+      </c>
+      <c r="J11" s="62" t="s">
+        <v>291</v>
+      </c>
+      <c r="K11" s="62" t="s">
+        <v>348</v>
+      </c>
+      <c r="L11" s="62">
         <v>28</v>
       </c>
-      <c r="M11" s="74">
+      <c r="M11" s="62">
         <f t="shared" ref="M11" si="1">L11*5</f>
         <v>140</v>
       </c>
-      <c r="N11" s="74">
+      <c r="N11" s="62">
         <v>150</v>
       </c>
-      <c r="O11" s="76" t="s">
-        <v>393</v>
-      </c>
-      <c r="P11" s="77">
+      <c r="O11" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P11" s="65">
         <v>1.04E-2</v>
       </c>
-      <c r="Q11" s="77">
+      <c r="Q11" s="65">
         <f t="shared" ref="Q11" si="2">P11*N11</f>
         <v>1.5599999999999998</v>
       </c>
-      <c r="R11" s="74"/>
-      <c r="S11" s="74"/>
+      <c r="R11" s="62"/>
+      <c r="S11" s="62"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="46">
+      <c r="B12" s="44">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="66" t="s">
+      <c r="C12" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="67" t="s">
+      <c r="D12" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="67" t="s">
+      <c r="E12" s="58" t="s">
+        <v>407</v>
+      </c>
+      <c r="F12" s="58" t="s">
         <v>408</v>
       </c>
-      <c r="F12" s="67" t="s">
+      <c r="G12" s="58" t="s">
         <v>409</v>
       </c>
-      <c r="G12" s="67" t="s">
+      <c r="H12" s="58" t="s">
         <v>410</v>
       </c>
-      <c r="H12" s="67" t="s">
+      <c r="I12" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J12" s="58" t="s">
         <v>411</v>
       </c>
-      <c r="I12" s="67" t="s">
-        <v>380</v>
-      </c>
-      <c r="J12" s="67" t="s">
-        <v>412</v>
-      </c>
-      <c r="K12" s="67" t="s">
-        <v>350</v>
-      </c>
-      <c r="L12" s="67">
+      <c r="K12" s="58" t="s">
+        <v>349</v>
+      </c>
+      <c r="L12" s="58">
         <v>2</v>
       </c>
-      <c r="M12" s="67">
+      <c r="M12" s="58">
         <f>L12*5</f>
         <v>10</v>
       </c>
-      <c r="N12" s="67">
+      <c r="N12" s="58">
         <v>20</v>
       </c>
-      <c r="O12" s="69" t="s">
-        <v>393</v>
-      </c>
-      <c r="P12" s="85">
+      <c r="O12" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P12" s="59">
         <v>6.2E-2</v>
       </c>
-      <c r="Q12" s="85">
+      <c r="Q12" s="59">
         <f>P12*N12</f>
         <v>1.24</v>
       </c>
-      <c r="R12" s="86"/>
-      <c r="S12" s="68"/>
+      <c r="R12" s="57"/>
+      <c r="S12" s="37"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="47">
+      <c r="B13" s="45">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="72" t="s">
+      <c r="C13" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="73" t="s">
-        <v>428</v>
-      </c>
-      <c r="E13" s="74" t="s">
-        <v>94</v>
-      </c>
-      <c r="F13" s="74" t="s">
-        <v>392</v>
-      </c>
-      <c r="G13" s="74" t="s">
-        <v>160</v>
-      </c>
-      <c r="H13" s="74" t="s">
-        <v>258</v>
-      </c>
-      <c r="I13" s="74" t="s">
-        <v>380</v>
-      </c>
-      <c r="J13" s="74" t="s">
-        <v>293</v>
-      </c>
-      <c r="K13" s="74" t="s">
-        <v>351</v>
-      </c>
-      <c r="L13" s="74">
+      <c r="D13" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="E13" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="F13" s="62" t="s">
+        <v>391</v>
+      </c>
+      <c r="G13" s="62" t="s">
+        <v>159</v>
+      </c>
+      <c r="H13" s="62" t="s">
+        <v>257</v>
+      </c>
+      <c r="I13" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J13" s="62" t="s">
+        <v>292</v>
+      </c>
+      <c r="K13" s="62" t="s">
+        <v>350</v>
+      </c>
+      <c r="L13" s="62">
         <v>3</v>
       </c>
-      <c r="M13" s="74">
+      <c r="M13" s="62">
         <f t="shared" ref="M13" si="3">L13*5</f>
         <v>15</v>
       </c>
-      <c r="N13" s="74">
+      <c r="N13" s="62">
         <v>17</v>
       </c>
-      <c r="O13" s="76" t="s">
-        <v>393</v>
-      </c>
-      <c r="P13" s="77">
+      <c r="O13" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P13" s="65">
         <v>0.49540000000000001</v>
       </c>
-      <c r="Q13" s="77">
+      <c r="Q13" s="65">
         <f t="shared" ref="Q13" si="4">P13*N13</f>
         <v>8.4217999999999993</v>
       </c>
-      <c r="R13" s="78"/>
-      <c r="S13" s="74"/>
+      <c r="R13" s="66"/>
+      <c r="S13" s="62"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="47">
+      <c r="B14" s="45">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="66" t="s">
+      <c r="C14" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="67" t="s">
+      <c r="D14" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="67" t="s">
-        <v>95</v>
-      </c>
-      <c r="F14" s="67" t="s">
-        <v>161</v>
-      </c>
-      <c r="G14" s="67" t="s">
-        <v>201</v>
-      </c>
-      <c r="H14" s="67" t="s">
-        <v>258</v>
-      </c>
-      <c r="I14" s="67" t="s">
-        <v>380</v>
-      </c>
-      <c r="J14" s="67" t="s">
-        <v>294</v>
-      </c>
-      <c r="K14" s="67" t="s">
-        <v>352</v>
-      </c>
-      <c r="L14" s="67">
+      <c r="E14" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="F14" s="58" t="s">
+        <v>160</v>
+      </c>
+      <c r="G14" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="H14" s="58" t="s">
+        <v>257</v>
+      </c>
+      <c r="I14" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J14" s="58" t="s">
+        <v>293</v>
+      </c>
+      <c r="K14" s="58" t="s">
+        <v>351</v>
+      </c>
+      <c r="L14" s="58">
         <v>1</v>
       </c>
-      <c r="M14" s="67">
+      <c r="M14" s="58">
         <f t="shared" ref="M14" si="5">L14*5</f>
         <v>5</v>
       </c>
-      <c r="N14" s="67">
+      <c r="N14" s="58">
         <v>6</v>
       </c>
-      <c r="O14" s="69" t="s">
-        <v>393</v>
-      </c>
-      <c r="P14" s="85">
+      <c r="O14" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P14" s="59">
         <v>0.91320000000000001</v>
       </c>
-      <c r="Q14" s="85">
+      <c r="Q14" s="59">
         <f t="shared" ref="Q14" si="6">P14*N14</f>
         <v>5.4792000000000005</v>
       </c>
-      <c r="R14" s="86"/>
-      <c r="S14" s="68"/>
+      <c r="R14" s="57"/>
+      <c r="S14" s="37"/>
     </row>
     <row r="15" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="46">
+      <c r="B15" s="44">
         <f>ROW(B15) - ROW($B$9)</f>
         <v>6</v>
       </c>
-      <c r="C15" s="72" t="s">
+      <c r="C15" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="73" t="s">
+      <c r="D15" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="74" t="s">
-        <v>96</v>
-      </c>
-      <c r="F15" s="74" t="s">
-        <v>159</v>
-      </c>
-      <c r="G15" s="74" t="s">
-        <v>202</v>
-      </c>
-      <c r="H15" s="74" t="s">
-        <v>256</v>
-      </c>
-      <c r="I15" s="74" t="s">
-        <v>380</v>
-      </c>
-      <c r="J15" s="74" t="s">
-        <v>295</v>
-      </c>
-      <c r="K15" s="74" t="s">
-        <v>353</v>
-      </c>
-      <c r="L15" s="74">
+      <c r="E15" s="62" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" s="62" t="s">
+        <v>158</v>
+      </c>
+      <c r="G15" s="62" t="s">
+        <v>201</v>
+      </c>
+      <c r="H15" s="62" t="s">
+        <v>255</v>
+      </c>
+      <c r="I15" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J15" s="62" t="s">
+        <v>294</v>
+      </c>
+      <c r="K15" s="62" t="s">
+        <v>352</v>
+      </c>
+      <c r="L15" s="62">
         <v>12</v>
       </c>
-      <c r="M15" s="74">
+      <c r="M15" s="62">
         <f>L15*5</f>
         <v>60</v>
       </c>
-      <c r="N15" s="74">
+      <c r="N15" s="62">
         <v>100</v>
       </c>
-      <c r="O15" s="76" t="s">
-        <v>393</v>
-      </c>
-      <c r="P15" s="77">
+      <c r="O15" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P15" s="65">
         <v>2.8E-3</v>
       </c>
-      <c r="Q15" s="77">
+      <c r="Q15" s="65">
         <f>P15*N15</f>
         <v>0.27999999999999997</v>
       </c>
-      <c r="R15" s="74"/>
-      <c r="S15" s="74"/>
+      <c r="R15" s="62"/>
+      <c r="S15" s="62"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="47">
+      <c r="B16" s="45">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="66" t="s">
+      <c r="C16" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="67" t="s">
+      <c r="D16" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="E16" s="67" t="s">
-        <v>97</v>
-      </c>
-      <c r="F16" s="67" t="s">
-        <v>159</v>
-      </c>
-      <c r="G16" s="67" t="s">
-        <v>203</v>
-      </c>
-      <c r="H16" s="67" t="s">
-        <v>256</v>
-      </c>
-      <c r="I16" s="67" t="s">
-        <v>380</v>
-      </c>
-      <c r="J16" s="67" t="s">
-        <v>296</v>
-      </c>
-      <c r="K16" s="67" t="s">
-        <v>354</v>
-      </c>
-      <c r="L16" s="67">
+      <c r="E16" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" s="58" t="s">
+        <v>158</v>
+      </c>
+      <c r="G16" s="58" t="s">
+        <v>202</v>
+      </c>
+      <c r="H16" s="58" t="s">
+        <v>255</v>
+      </c>
+      <c r="I16" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J16" s="58" t="s">
+        <v>295</v>
+      </c>
+      <c r="K16" s="58" t="s">
+        <v>353</v>
+      </c>
+      <c r="L16" s="58">
         <v>1</v>
       </c>
-      <c r="M16" s="67">
+      <c r="M16" s="58">
         <f t="shared" ref="M16" si="7">L16*5</f>
         <v>5</v>
       </c>
-      <c r="N16" s="67">
+      <c r="N16" s="58">
         <v>100</v>
       </c>
-      <c r="O16" s="69" t="s">
-        <v>393</v>
-      </c>
-      <c r="P16" s="85">
+      <c r="O16" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P16" s="59">
         <v>4.8999999999999998E-3</v>
       </c>
-      <c r="Q16" s="85">
+      <c r="Q16" s="59">
         <f t="shared" ref="Q16" si="8">P16*N16</f>
         <v>0.49</v>
       </c>
-      <c r="R16" s="86"/>
-      <c r="S16" s="68"/>
+      <c r="R16" s="57"/>
+      <c r="S16" s="37"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="46">
+      <c r="B17" s="44">
         <f>ROW(B17) - ROW($B$9)</f>
         <v>8</v>
       </c>
-      <c r="C17" s="72" t="s">
+      <c r="C17" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="73" t="s">
+      <c r="D17" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="74" t="s">
-        <v>98</v>
-      </c>
-      <c r="F17" s="74" t="s">
-        <v>162</v>
-      </c>
-      <c r="G17" s="75" t="s">
-        <v>204</v>
-      </c>
-      <c r="H17" s="74" t="s">
-        <v>259</v>
-      </c>
-      <c r="I17" s="74" t="s">
-        <v>426</v>
-      </c>
-      <c r="J17" s="74" t="s">
+      <c r="E17" s="62" t="s">
+        <v>97</v>
+      </c>
+      <c r="F17" s="62" t="s">
+        <v>161</v>
+      </c>
+      <c r="G17" s="63" t="s">
+        <v>203</v>
+      </c>
+      <c r="H17" s="62" t="s">
+        <v>258</v>
+      </c>
+      <c r="I17" s="62" t="s">
         <v>425</v>
       </c>
-      <c r="K17" s="74" t="s">
-        <v>355</v>
-      </c>
-      <c r="L17" s="74">
+      <c r="J17" s="62" t="s">
+        <v>424</v>
+      </c>
+      <c r="K17" s="62" t="s">
+        <v>354</v>
+      </c>
+      <c r="L17" s="62">
         <v>1</v>
       </c>
-      <c r="M17" s="74">
+      <c r="M17" s="62">
         <f>L17*5</f>
         <v>5</v>
       </c>
-      <c r="N17" s="74">
+      <c r="N17" s="62">
         <v>100</v>
       </c>
-      <c r="O17" s="76" t="s">
-        <v>393</v>
-      </c>
-      <c r="P17" s="77">
+      <c r="O17" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P17" s="65">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q17" s="77">
+      <c r="Q17" s="65">
         <f>P17*N17</f>
         <v>0.13</v>
       </c>
-      <c r="R17" s="74"/>
-      <c r="S17" s="74"/>
+      <c r="R17" s="62"/>
+      <c r="S17" s="62"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="47">
+      <c r="B18" s="45">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="66" t="s">
+      <c r="C18" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="67" t="s">
+      <c r="D18" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="E18" s="67" t="s">
-        <v>99</v>
-      </c>
-      <c r="F18" s="67" t="s">
-        <v>159</v>
-      </c>
-      <c r="G18" s="67" t="s">
-        <v>205</v>
-      </c>
-      <c r="H18" s="67" t="s">
-        <v>256</v>
-      </c>
-      <c r="I18" s="67" t="s">
-        <v>380</v>
-      </c>
-      <c r="J18" s="67" t="s">
-        <v>297</v>
-      </c>
-      <c r="K18" s="67" t="s">
-        <v>356</v>
-      </c>
-      <c r="L18" s="67">
+      <c r="E18" s="58" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" s="58" t="s">
+        <v>158</v>
+      </c>
+      <c r="G18" s="58" t="s">
+        <v>204</v>
+      </c>
+      <c r="H18" s="58" t="s">
+        <v>255</v>
+      </c>
+      <c r="I18" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J18" s="58" t="s">
+        <v>296</v>
+      </c>
+      <c r="K18" s="58" t="s">
+        <v>355</v>
+      </c>
+      <c r="L18" s="58">
         <v>2</v>
       </c>
-      <c r="M18" s="67">
+      <c r="M18" s="58">
         <f t="shared" ref="M18" si="9">L18*5</f>
         <v>10</v>
       </c>
-      <c r="N18" s="67">
+      <c r="N18" s="58">
         <v>100</v>
       </c>
-      <c r="O18" s="69" t="s">
-        <v>393</v>
-      </c>
-      <c r="P18" s="85">
+      <c r="O18" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P18" s="59">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="Q18" s="85">
+      <c r="Q18" s="59">
         <f t="shared" ref="Q18" si="10">P18*N18</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="R18" s="86"/>
-      <c r="S18" s="68"/>
+      <c r="R18" s="57"/>
+      <c r="S18" s="37"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="46">
+      <c r="B19" s="44">
         <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="72" t="s">
+      <c r="C19" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="73" t="s">
-        <v>413</v>
-      </c>
-      <c r="E19" s="74" t="s">
-        <v>100</v>
-      </c>
-      <c r="F19" s="74" t="s">
-        <v>159</v>
-      </c>
-      <c r="G19" s="74" t="s">
-        <v>206</v>
-      </c>
-      <c r="H19" s="74" t="s">
-        <v>256</v>
-      </c>
-      <c r="I19" s="74" t="s">
-        <v>380</v>
-      </c>
-      <c r="J19" s="74" t="s">
-        <v>298</v>
-      </c>
-      <c r="K19" s="74" t="s">
-        <v>357</v>
-      </c>
-      <c r="L19" s="74">
+      <c r="D19" s="61" t="s">
+        <v>412</v>
+      </c>
+      <c r="E19" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="F19" s="62" t="s">
+        <v>158</v>
+      </c>
+      <c r="G19" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="H19" s="62" t="s">
+        <v>255</v>
+      </c>
+      <c r="I19" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J19" s="62" t="s">
+        <v>297</v>
+      </c>
+      <c r="K19" s="62" t="s">
+        <v>356</v>
+      </c>
+      <c r="L19" s="62">
         <v>2</v>
       </c>
-      <c r="M19" s="74">
+      <c r="M19" s="62">
         <f>L19*5</f>
         <v>10</v>
       </c>
-      <c r="N19" s="74">
+      <c r="N19" s="62">
         <v>20</v>
       </c>
-      <c r="O19" s="76" t="s">
-        <v>393</v>
-      </c>
-      <c r="P19" s="77">
+      <c r="O19" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P19" s="65">
         <v>2.3599999999999999E-2</v>
       </c>
-      <c r="Q19" s="77">
+      <c r="Q19" s="65">
         <f>P19*N19</f>
         <v>0.47199999999999998</v>
       </c>
-      <c r="R19" s="74"/>
-      <c r="S19" s="74"/>
+      <c r="R19" s="62"/>
+      <c r="S19" s="62"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="46">
+      <c r="B20" s="44">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
       <c r="C20" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="68" t="s">
+      <c r="D20" s="37" t="s">
+        <v>428</v>
+      </c>
+      <c r="E20" s="37" t="s">
         <v>429</v>
       </c>
-      <c r="E20" s="68" t="s">
+      <c r="F20" s="37" t="s">
+        <v>391</v>
+      </c>
+      <c r="G20" s="37" t="s">
         <v>430</v>
       </c>
-      <c r="F20" s="68" t="s">
-        <v>392</v>
-      </c>
-      <c r="G20" s="68" t="s">
+      <c r="H20" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="I20" s="37" t="s">
+        <v>379</v>
+      </c>
+      <c r="J20" s="37" t="s">
         <v>431</v>
       </c>
-      <c r="H20" s="68" t="s">
-        <v>258</v>
-      </c>
-      <c r="I20" s="68" t="s">
-        <v>380</v>
-      </c>
-      <c r="J20" s="68" t="s">
+      <c r="K20" s="37" t="s">
         <v>432</v>
       </c>
-      <c r="K20" s="68" t="s">
-        <v>433</v>
-      </c>
-      <c r="L20" s="68">
+      <c r="L20" s="37">
         <v>1</v>
       </c>
-      <c r="M20" s="68">
+      <c r="M20" s="37">
         <f>L20*5</f>
         <v>5</v>
       </c>
-      <c r="N20" s="68">
+      <c r="N20" s="37">
         <v>6</v>
       </c>
-      <c r="O20" s="69" t="s">
-        <v>393</v>
-      </c>
-      <c r="P20" s="70">
+      <c r="O20" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P20" s="82">
         <v>0.51590000000000003</v>
       </c>
-      <c r="Q20" s="70">
+      <c r="Q20" s="82">
         <f>P20*N20</f>
         <v>3.0954000000000002</v>
       </c>
-      <c r="R20" s="68"/>
-      <c r="S20" s="71"/>
+      <c r="R20" s="37"/>
+      <c r="S20" s="84"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="47">
+      <c r="B21" s="45">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="59" t="s">
+      <c r="C21" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="62" t="s">
+      <c r="D21" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="62" t="s">
-        <v>101</v>
-      </c>
-      <c r="F21" s="62" t="s">
-        <v>163</v>
-      </c>
-      <c r="G21" s="62" t="s">
-        <v>207</v>
-      </c>
-      <c r="H21" s="62" t="s">
-        <v>260</v>
-      </c>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62" t="s">
-        <v>299</v>
-      </c>
-      <c r="K21" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="L21" s="62">
+      <c r="E21" s="58" t="s">
+        <v>100</v>
+      </c>
+      <c r="F21" s="58" t="s">
+        <v>162</v>
+      </c>
+      <c r="G21" s="58" t="s">
+        <v>206</v>
+      </c>
+      <c r="H21" s="58" t="s">
+        <v>259</v>
+      </c>
+      <c r="I21" s="58"/>
+      <c r="J21" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="K21" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="L21" s="58">
         <v>7</v>
       </c>
-      <c r="M21" s="62">
+      <c r="M21" s="58">
         <f t="shared" ref="M21" si="11">L21*5</f>
         <v>35</v>
       </c>
-      <c r="N21" s="62">
+      <c r="N21" s="58">
         <v>40</v>
       </c>
-      <c r="O21" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P21" s="63">
+      <c r="O21" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P21" s="59">
         <v>6.3700000000000007E-2</v>
       </c>
-      <c r="Q21" s="63">
+      <c r="Q21" s="59">
         <f t="shared" ref="Q21" si="12">P21*N21</f>
         <v>2.548</v>
       </c>
-      <c r="R21" s="61"/>
+      <c r="R21" s="57"/>
       <c r="S21" s="37"/>
     </row>
     <row r="22" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="46">
+      <c r="B22" s="44">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
       <c r="C22" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="64" t="s">
+      <c r="D22" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="E22" s="38" t="s">
-        <v>102</v>
-      </c>
-      <c r="F22" s="38" t="s">
-        <v>164</v>
-      </c>
-      <c r="G22" s="38" t="s">
-        <v>208</v>
-      </c>
-      <c r="H22" s="38" t="s">
-        <v>261</v>
-      </c>
-      <c r="I22" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J22" s="38" t="s">
-        <v>300</v>
-      </c>
-      <c r="K22" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="L22" s="38">
+      <c r="E22" s="62" t="s">
+        <v>101</v>
+      </c>
+      <c r="F22" s="62" t="s">
+        <v>163</v>
+      </c>
+      <c r="G22" s="62" t="s">
+        <v>207</v>
+      </c>
+      <c r="H22" s="62" t="s">
+        <v>260</v>
+      </c>
+      <c r="I22" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J22" s="62" t="s">
+        <v>299</v>
+      </c>
+      <c r="K22" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="L22" s="62">
         <v>2</v>
       </c>
-      <c r="M22" s="38">
+      <c r="M22" s="62">
         <f>L22*5</f>
         <v>10</v>
       </c>
-      <c r="N22" s="38">
+      <c r="N22" s="62">
         <v>15</v>
       </c>
-      <c r="O22" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P22" s="39">
+      <c r="O22" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P22" s="65">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="Q22" s="39">
+      <c r="Q22" s="65">
         <f>P22*N22</f>
         <v>1.296</v>
       </c>
-      <c r="R22" s="38"/>
-      <c r="S22" s="38"/>
+      <c r="R22" s="62"/>
+      <c r="S22" s="62"/>
     </row>
     <row r="23" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="47">
+      <c r="B23" s="45">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="59" t="s">
+      <c r="C23" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="62" t="s">
+      <c r="D23" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="E23" s="62" t="s">
-        <v>103</v>
-      </c>
-      <c r="F23" s="62" t="s">
-        <v>165</v>
-      </c>
-      <c r="G23" s="62" t="s">
-        <v>209</v>
-      </c>
-      <c r="H23" s="62" t="s">
-        <v>262</v>
-      </c>
-      <c r="I23" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J23" s="62" t="s">
-        <v>301</v>
-      </c>
-      <c r="K23" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="L23" s="62">
+      <c r="E23" s="58" t="s">
+        <v>102</v>
+      </c>
+      <c r="F23" s="58" t="s">
+        <v>164</v>
+      </c>
+      <c r="G23" s="58" t="s">
+        <v>208</v>
+      </c>
+      <c r="H23" s="58" t="s">
+        <v>261</v>
+      </c>
+      <c r="I23" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J23" s="58" t="s">
+        <v>300</v>
+      </c>
+      <c r="K23" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="L23" s="58">
         <v>1</v>
       </c>
-      <c r="M23" s="62">
+      <c r="M23" s="58">
         <f t="shared" ref="M23" si="13">L23*5</f>
         <v>5</v>
       </c>
-      <c r="N23" s="62">
+      <c r="N23" s="58">
         <v>20</v>
       </c>
-      <c r="O23" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P23" s="63">
+      <c r="O23" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P23" s="59">
         <v>3.32E-2</v>
       </c>
-      <c r="Q23" s="63">
+      <c r="Q23" s="59">
         <f t="shared" ref="Q23" si="14">P23*N23</f>
         <v>0.66400000000000003</v>
       </c>
-      <c r="R23" s="61"/>
+      <c r="R23" s="57"/>
       <c r="S23" s="37"/>
     </row>
     <row r="24" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="46">
+      <c r="B24" s="44">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
       <c r="C24" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="64" t="s">
+      <c r="D24" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="E24" s="38" t="s">
+      <c r="E24" s="62" t="s">
+        <v>400</v>
+      </c>
+      <c r="F24" s="62" t="s">
         <v>401</v>
       </c>
-      <c r="F24" s="38" t="s">
+      <c r="G24" s="62" t="s">
+        <v>209</v>
+      </c>
+      <c r="H24" s="62" t="s">
+        <v>262</v>
+      </c>
+      <c r="I24" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J24" s="62" t="s">
         <v>402</v>
       </c>
-      <c r="G24" s="38" t="s">
-        <v>210</v>
-      </c>
-      <c r="H24" s="38" t="s">
-        <v>263</v>
-      </c>
-      <c r="I24" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J24" s="38" t="s">
-        <v>403</v>
-      </c>
-      <c r="K24" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="L24" s="38">
+      <c r="K24" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="L24" s="62">
         <v>1</v>
       </c>
-      <c r="M24" s="38">
+      <c r="M24" s="62">
         <f>L24*5</f>
         <v>5</v>
       </c>
-      <c r="N24" s="38">
+      <c r="N24" s="62">
         <v>20</v>
       </c>
-      <c r="O24" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P24" s="39">
+      <c r="O24" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P24" s="65">
         <v>3.6200000000000003E-2</v>
       </c>
-      <c r="Q24" s="39">
+      <c r="Q24" s="65">
         <f>P24*N24</f>
         <v>0.72400000000000009</v>
       </c>
-      <c r="R24" s="38"/>
-      <c r="S24" s="38"/>
+      <c r="R24" s="62"/>
+      <c r="S24" s="62"/>
     </row>
     <row r="25" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="47">
+      <c r="B25" s="45">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="59" t="s">
+      <c r="C25" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="62" t="s">
+      <c r="D25" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="62" t="s">
-        <v>104</v>
-      </c>
-      <c r="F25" s="62" t="s">
-        <v>166</v>
-      </c>
-      <c r="G25" s="62" t="s">
-        <v>211</v>
-      </c>
-      <c r="H25" s="62" t="s">
-        <v>264</v>
-      </c>
-      <c r="I25" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J25" s="62" t="s">
-        <v>302</v>
-      </c>
-      <c r="K25" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="L25" s="62">
+      <c r="E25" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" s="58" t="s">
+        <v>165</v>
+      </c>
+      <c r="G25" s="58" t="s">
+        <v>210</v>
+      </c>
+      <c r="H25" s="58" t="s">
+        <v>263</v>
+      </c>
+      <c r="I25" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J25" s="58" t="s">
+        <v>301</v>
+      </c>
+      <c r="K25" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="L25" s="58">
         <v>8</v>
       </c>
-      <c r="M25" s="62">
+      <c r="M25" s="58">
         <f t="shared" ref="M25" si="15">L25*5</f>
         <v>40</v>
       </c>
-      <c r="N25" s="62">
+      <c r="N25" s="58">
         <v>60</v>
       </c>
-      <c r="O25" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P25" s="63">
+      <c r="O25" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P25" s="59">
         <v>2.0400000000000001E-2</v>
       </c>
-      <c r="Q25" s="63">
+      <c r="Q25" s="59">
         <f t="shared" ref="Q25" si="16">P25*N25</f>
         <v>1.2240000000000002</v>
       </c>
-      <c r="R25" s="61"/>
+      <c r="R25" s="57"/>
       <c r="S25" s="37"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="46">
+      <c r="B26" s="44">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
       <c r="C26" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="64" t="s">
+      <c r="D26" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="38" t="s">
-        <v>105</v>
-      </c>
-      <c r="F26" s="38" t="s">
-        <v>167</v>
-      </c>
-      <c r="G26" s="38" t="s">
-        <v>212</v>
-      </c>
-      <c r="H26" s="38" t="s">
-        <v>265</v>
-      </c>
-      <c r="I26" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J26" s="38" t="s">
-        <v>303</v>
-      </c>
-      <c r="K26" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="L26" s="38">
+      <c r="E26" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26" s="62" t="s">
+        <v>166</v>
+      </c>
+      <c r="G26" s="62" t="s">
+        <v>211</v>
+      </c>
+      <c r="H26" s="62" t="s">
+        <v>264</v>
+      </c>
+      <c r="I26" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J26" s="62" t="s">
+        <v>302</v>
+      </c>
+      <c r="K26" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="L26" s="62">
         <v>1</v>
       </c>
-      <c r="M26" s="38">
+      <c r="M26" s="62">
         <f>L26*5</f>
         <v>5</v>
       </c>
-      <c r="N26" s="38">
+      <c r="N26" s="62">
         <v>10</v>
       </c>
-      <c r="O26" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P26" s="39">
+      <c r="O26" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P26" s="65">
         <v>0.104</v>
       </c>
-      <c r="Q26" s="39">
+      <c r="Q26" s="65">
         <f>P26*N26</f>
         <v>1.04</v>
       </c>
-      <c r="R26" s="38"/>
-      <c r="S26" s="38"/>
+      <c r="R26" s="62"/>
+      <c r="S26" s="62"/>
     </row>
     <row r="27" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="47">
+      <c r="B27" s="45">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="59" t="s">
+      <c r="C27" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="62" t="s">
+      <c r="D27" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="62" t="s">
-        <v>106</v>
-      </c>
-      <c r="F27" s="62" t="s">
-        <v>168</v>
-      </c>
-      <c r="G27" s="62" t="s">
-        <v>213</v>
-      </c>
-      <c r="H27" s="62" t="s">
-        <v>266</v>
-      </c>
-      <c r="I27" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J27" s="62" t="s">
-        <v>304</v>
-      </c>
-      <c r="K27" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="L27" s="62">
+      <c r="E27" s="58" t="s">
+        <v>105</v>
+      </c>
+      <c r="F27" s="58" t="s">
+        <v>167</v>
+      </c>
+      <c r="G27" s="58" t="s">
+        <v>212</v>
+      </c>
+      <c r="H27" s="58" t="s">
+        <v>265</v>
+      </c>
+      <c r="I27" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J27" s="58" t="s">
+        <v>303</v>
+      </c>
+      <c r="K27" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="L27" s="58">
         <v>3</v>
       </c>
-      <c r="M27" s="62">
+      <c r="M27" s="58">
         <f t="shared" ref="M27" si="17">L27*5</f>
         <v>15</v>
       </c>
-      <c r="N27" s="62">
+      <c r="N27" s="58">
         <v>20</v>
       </c>
-      <c r="O27" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P27" s="63">
+      <c r="O27" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P27" s="59">
         <v>3.1699999999999999E-2</v>
       </c>
-      <c r="Q27" s="63">
+      <c r="Q27" s="59">
         <f t="shared" ref="Q27" si="18">P27*N27</f>
         <v>0.63400000000000001</v>
       </c>
-      <c r="R27" s="61"/>
+      <c r="R27" s="57"/>
       <c r="S27" s="37"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="46">
+      <c r="B28" s="44">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
       <c r="C28" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="D28" s="64" t="s">
+      <c r="D28" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="E28" s="38" t="s">
-        <v>107</v>
-      </c>
-      <c r="F28" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="G28" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="H28" s="38" t="s">
-        <v>267</v>
-      </c>
-      <c r="I28" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J28" s="38" t="s">
-        <v>305</v>
-      </c>
-      <c r="K28" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="L28" s="38">
+      <c r="E28" s="62" t="s">
+        <v>106</v>
+      </c>
+      <c r="F28" s="62" t="s">
+        <v>168</v>
+      </c>
+      <c r="G28" s="62" t="s">
+        <v>213</v>
+      </c>
+      <c r="H28" s="62" t="s">
+        <v>266</v>
+      </c>
+      <c r="I28" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J28" s="62" t="s">
+        <v>304</v>
+      </c>
+      <c r="K28" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="L28" s="62">
         <v>1</v>
       </c>
-      <c r="M28" s="38">
+      <c r="M28" s="62">
         <f>L28*5</f>
         <v>5</v>
       </c>
-      <c r="N28" s="38">
+      <c r="N28" s="62">
         <v>10</v>
       </c>
-      <c r="O28" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P28" s="39">
+      <c r="O28" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P28" s="65">
         <v>3.5400000000000001E-2</v>
       </c>
-      <c r="Q28" s="39">
+      <c r="Q28" s="65">
         <f>P28*N28</f>
         <v>0.35399999999999998</v>
       </c>
-      <c r="R28" s="38"/>
-      <c r="S28" s="38"/>
+      <c r="R28" s="62"/>
+      <c r="S28" s="62"/>
     </row>
     <row r="29" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="47">
+      <c r="B29" s="45">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="59" t="s">
+      <c r="C29" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="62" t="s">
+      <c r="D29" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="E29" s="62" t="s">
-        <v>108</v>
-      </c>
-      <c r="F29" s="62" t="s">
-        <v>168</v>
-      </c>
-      <c r="G29" s="62" t="s">
-        <v>215</v>
-      </c>
-      <c r="H29" s="62" t="s">
-        <v>261</v>
-      </c>
-      <c r="I29" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J29" s="62" t="s">
-        <v>306</v>
-      </c>
-      <c r="K29" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="L29" s="62">
+      <c r="E29" s="58" t="s">
+        <v>107</v>
+      </c>
+      <c r="F29" s="58" t="s">
+        <v>167</v>
+      </c>
+      <c r="G29" s="58" t="s">
+        <v>214</v>
+      </c>
+      <c r="H29" s="58" t="s">
+        <v>260</v>
+      </c>
+      <c r="I29" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J29" s="58" t="s">
+        <v>305</v>
+      </c>
+      <c r="K29" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="L29" s="58">
         <v>5</v>
       </c>
-      <c r="M29" s="62">
+      <c r="M29" s="58">
         <f t="shared" ref="M29" si="19">L29*5</f>
         <v>25</v>
       </c>
-      <c r="N29" s="62">
+      <c r="N29" s="58">
         <v>50</v>
       </c>
-      <c r="O29" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P29" s="63">
+      <c r="O29" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P29" s="59">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="Q29" s="63">
+      <c r="Q29" s="59">
         <f t="shared" ref="Q29" si="20">P29*N29</f>
         <v>0.89999999999999991</v>
       </c>
-      <c r="R29" s="61"/>
+      <c r="R29" s="57"/>
       <c r="S29" s="37"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="46">
+      <c r="B30" s="44">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
       <c r="C30" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="D30" s="64" t="s">
+      <c r="D30" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="E30" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="F30" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="G30" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="H30" s="38" t="s">
-        <v>268</v>
-      </c>
-      <c r="I30" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J30" s="38" t="s">
-        <v>307</v>
-      </c>
-      <c r="K30" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="L30" s="38">
+      <c r="E30" s="62" t="s">
+        <v>108</v>
+      </c>
+      <c r="F30" s="62" t="s">
+        <v>169</v>
+      </c>
+      <c r="G30" s="62" t="s">
+        <v>215</v>
+      </c>
+      <c r="H30" s="62" t="s">
+        <v>267</v>
+      </c>
+      <c r="I30" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J30" s="62" t="s">
+        <v>306</v>
+      </c>
+      <c r="K30" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="L30" s="62">
         <v>1</v>
       </c>
-      <c r="M30" s="38">
+      <c r="M30" s="62">
         <f>L30*5</f>
         <v>5</v>
       </c>
-      <c r="N30" s="38">
+      <c r="N30" s="62">
         <v>6</v>
       </c>
-      <c r="O30" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P30" s="39">
+      <c r="O30" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P30" s="65">
         <v>0.2319</v>
       </c>
-      <c r="Q30" s="39">
+      <c r="Q30" s="65">
         <f>P30*N30</f>
         <v>1.3914</v>
       </c>
-      <c r="R30" s="38"/>
-      <c r="S30" s="38"/>
+      <c r="R30" s="62"/>
+      <c r="S30" s="62"/>
     </row>
     <row r="31" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="47">
+      <c r="B31" s="45">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="59" t="s">
+      <c r="C31" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="D31" s="62" t="s">
+      <c r="D31" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="62" t="s">
-        <v>110</v>
-      </c>
-      <c r="F31" s="62" t="s">
-        <v>171</v>
-      </c>
-      <c r="G31" s="62" t="s">
-        <v>217</v>
-      </c>
-      <c r="H31" s="62" t="s">
-        <v>269</v>
-      </c>
-      <c r="I31" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J31" s="62" t="s">
-        <v>398</v>
-      </c>
-      <c r="K31" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="L31" s="62">
+      <c r="E31" s="58" t="s">
+        <v>109</v>
+      </c>
+      <c r="F31" s="58" t="s">
+        <v>170</v>
+      </c>
+      <c r="G31" s="58" t="s">
+        <v>216</v>
+      </c>
+      <c r="H31" s="58" t="s">
+        <v>268</v>
+      </c>
+      <c r="I31" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J31" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="K31" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="L31" s="58">
         <v>2</v>
       </c>
-      <c r="M31" s="62">
+      <c r="M31" s="58">
         <f t="shared" ref="M31" si="21">L31*5</f>
         <v>10</v>
       </c>
-      <c r="N31" s="62">
+      <c r="N31" s="58">
         <v>20</v>
       </c>
-      <c r="O31" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P31" s="63">
+      <c r="O31" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P31" s="59">
         <v>4.5900000000000003E-2</v>
       </c>
-      <c r="Q31" s="63">
+      <c r="Q31" s="59">
         <f t="shared" ref="Q31" si="22">P31*N31</f>
         <v>0.91800000000000004</v>
       </c>
-      <c r="R31" s="61"/>
+      <c r="R31" s="57"/>
       <c r="S31" s="37"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="46">
+      <c r="B32" s="44">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
       <c r="C32" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="64" t="s">
+      <c r="D32" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="E32" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="F32" s="38" t="s">
-        <v>172</v>
-      </c>
-      <c r="G32" s="38" t="s">
-        <v>218</v>
-      </c>
-      <c r="H32" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="I32" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J32" s="38" t="s">
-        <v>308</v>
-      </c>
-      <c r="K32" s="38" t="s">
-        <v>358</v>
-      </c>
-      <c r="L32" s="38">
+      <c r="E32" s="62" t="s">
+        <v>110</v>
+      </c>
+      <c r="F32" s="62" t="s">
+        <v>171</v>
+      </c>
+      <c r="G32" s="62" t="s">
+        <v>217</v>
+      </c>
+      <c r="H32" s="62" t="s">
+        <v>258</v>
+      </c>
+      <c r="I32" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J32" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="K32" s="62" t="s">
+        <v>357</v>
+      </c>
+      <c r="L32" s="62">
         <v>1</v>
       </c>
-      <c r="M32" s="38">
+      <c r="M32" s="62">
         <f>L32*5</f>
         <v>5</v>
       </c>
-      <c r="N32" s="38">
+      <c r="N32" s="62">
         <v>10</v>
       </c>
-      <c r="O32" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P32" s="39">
+      <c r="O32" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P32" s="65">
         <v>0.1193</v>
       </c>
-      <c r="Q32" s="39">
+      <c r="Q32" s="65">
         <f>P32*N32</f>
         <v>1.1930000000000001</v>
       </c>
-      <c r="R32" s="38"/>
-      <c r="S32" s="38"/>
+      <c r="R32" s="62"/>
+      <c r="S32" s="62"/>
     </row>
     <row r="33" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="47">
+      <c r="B33" s="45">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="59" t="s">
+      <c r="C33" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="62" t="s">
+      <c r="D33" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="E33" s="62" t="s">
-        <v>112</v>
-      </c>
-      <c r="F33" s="62" t="s">
-        <v>173</v>
-      </c>
-      <c r="G33" s="62" t="s">
-        <v>219</v>
-      </c>
-      <c r="H33" s="62" t="s">
-        <v>257</v>
-      </c>
-      <c r="I33" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J33" s="62" t="s">
-        <v>309</v>
-      </c>
-      <c r="K33" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="L33" s="62">
+      <c r="E33" s="58" t="s">
+        <v>111</v>
+      </c>
+      <c r="F33" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="G33" s="58" t="s">
+        <v>218</v>
+      </c>
+      <c r="H33" s="58" t="s">
+        <v>256</v>
+      </c>
+      <c r="I33" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J33" s="58" t="s">
+        <v>308</v>
+      </c>
+      <c r="K33" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="L33" s="58">
         <v>8</v>
       </c>
-      <c r="M33" s="62">
+      <c r="M33" s="58">
         <f t="shared" ref="M33" si="23">L33*5</f>
         <v>40</v>
       </c>
-      <c r="N33" s="62">
+      <c r="N33" s="58">
         <v>50</v>
       </c>
-      <c r="O33" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P33" s="63">
+      <c r="O33" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P33" s="59">
         <v>4.5600000000000002E-2</v>
       </c>
-      <c r="Q33" s="63">
+      <c r="Q33" s="59">
         <f t="shared" ref="Q33" si="24">P33*N33</f>
         <v>2.2800000000000002</v>
       </c>
-      <c r="R33" s="61"/>
+      <c r="R33" s="57"/>
       <c r="S33" s="37"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="46">
+      <c r="B34" s="44">
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
       <c r="C34" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="D34" s="64" t="s">
-        <v>420</v>
-      </c>
-      <c r="E34" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="F34" s="38" t="s">
-        <v>392</v>
-      </c>
-      <c r="G34" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="H34" s="38" t="s">
-        <v>270</v>
-      </c>
-      <c r="I34" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J34" s="38" t="s">
-        <v>310</v>
-      </c>
-      <c r="K34" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="L34" s="38">
+      <c r="D34" s="61" t="s">
+        <v>419</v>
+      </c>
+      <c r="E34" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="F34" s="62" t="s">
+        <v>391</v>
+      </c>
+      <c r="G34" s="62" t="s">
+        <v>219</v>
+      </c>
+      <c r="H34" s="62" t="s">
+        <v>269</v>
+      </c>
+      <c r="I34" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J34" s="62" t="s">
+        <v>309</v>
+      </c>
+      <c r="K34" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="L34" s="62">
         <v>2</v>
       </c>
-      <c r="M34" s="38">
+      <c r="M34" s="62">
         <f>L34*5</f>
         <v>10</v>
       </c>
-      <c r="N34" s="38">
+      <c r="N34" s="62">
         <v>12</v>
       </c>
-      <c r="O34" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P34" s="39">
+      <c r="O34" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P34" s="65">
         <v>0.1734</v>
       </c>
-      <c r="Q34" s="39">
+      <c r="Q34" s="65">
         <f>P34*N34</f>
         <v>2.0808</v>
       </c>
-      <c r="R34" s="38"/>
-      <c r="S34" s="38"/>
+      <c r="R34" s="62"/>
+      <c r="S34" s="62"/>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
-      <c r="B35" s="47">
+      <c r="B35" s="45">
         <f t="shared" ref="B35" si="25">ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="59" t="s">
+      <c r="C35" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="D35" s="62" t="s">
+      <c r="D35" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="E35" s="58" t="s">
         <v>415</v>
       </c>
-      <c r="E35" s="62" t="s">
+      <c r="F35" s="58">
+        <v>1051330011</v>
+      </c>
+      <c r="G35" s="58" t="s">
         <v>416</v>
       </c>
-      <c r="F35" s="62">
-        <v>1051330011</v>
-      </c>
-      <c r="G35" s="62" t="s">
+      <c r="H35" s="58" t="s">
         <v>417</v>
       </c>
-      <c r="H35" s="62" t="s">
+      <c r="I35" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J35" s="58" t="s">
         <v>418</v>
       </c>
-      <c r="I35" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J35" s="62" t="s">
-        <v>419</v>
-      </c>
-      <c r="K35" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="L35" s="62">
+      <c r="K35" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="L35" s="58">
         <v>1</v>
       </c>
-      <c r="M35" s="62">
+      <c r="M35" s="58">
         <f t="shared" ref="M35" si="26">L35*5</f>
         <v>5</v>
       </c>
-      <c r="N35" s="62">
+      <c r="N35" s="58">
         <v>6</v>
       </c>
-      <c r="O35" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P35" s="63">
+      <c r="O35" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P35" s="59">
         <v>0.41049999999999998</v>
       </c>
-      <c r="Q35" s="63">
+      <c r="Q35" s="59">
         <f t="shared" ref="Q35" si="27">P35*N35</f>
         <v>2.4630000000000001</v>
       </c>
-      <c r="R35" s="61"/>
+      <c r="R35" s="57"/>
       <c r="S35" s="37"/>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="47">
+      <c r="B36" s="45">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C36" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="D36" s="64" t="s">
+      <c r="D36" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="E36" s="38" t="s">
+      <c r="E36" s="62" t="s">
+        <v>420</v>
+      </c>
+      <c r="F36" s="62" t="s">
+        <v>391</v>
+      </c>
+      <c r="G36" s="62" t="s">
         <v>421</v>
       </c>
-      <c r="F36" s="38" t="s">
-        <v>392</v>
-      </c>
-      <c r="G36" s="38" t="s">
+      <c r="H36" s="62" t="s">
         <v>422</v>
       </c>
-      <c r="H36" s="38" t="s">
+      <c r="I36" s="62"/>
+      <c r="J36" s="62" t="s">
         <v>423</v>
       </c>
-      <c r="I36" s="38"/>
-      <c r="J36" s="38" t="s">
-        <v>424</v>
-      </c>
-      <c r="K36" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="L36" s="38">
+      <c r="K36" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="L36" s="62">
         <v>6</v>
       </c>
-      <c r="M36" s="38">
+      <c r="M36" s="62">
         <f t="shared" ref="M36" si="28">L36*5</f>
         <v>30</v>
       </c>
-      <c r="N36" s="38">
+      <c r="N36" s="62">
         <v>32</v>
       </c>
-      <c r="O36" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P36" s="39">
+      <c r="O36" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P36" s="65">
         <v>0.55530000000000002</v>
       </c>
-      <c r="Q36" s="39">
+      <c r="Q36" s="65">
         <f t="shared" ref="Q36" si="29">P36*N36</f>
         <v>17.769600000000001</v>
       </c>
-      <c r="R36" s="65" t="s">
-        <v>427</v>
-      </c>
-      <c r="S36" s="38"/>
+      <c r="R36" s="66" t="s">
+        <v>426</v>
+      </c>
+      <c r="S36" s="62"/>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="B37" s="46">
+      <c r="B37" s="44">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="59" t="s">
-        <v>395</v>
-      </c>
-      <c r="D37" s="62" t="s">
+      <c r="C37" s="56" t="s">
+        <v>394</v>
+      </c>
+      <c r="D37" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="E37" s="62" t="s">
-        <v>114</v>
-      </c>
-      <c r="F37" s="62" t="s">
-        <v>392</v>
-      </c>
-      <c r="G37" s="62" t="s">
-        <v>221</v>
-      </c>
-      <c r="H37" s="62" t="s">
-        <v>271</v>
-      </c>
-      <c r="I37" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J37" s="62" t="s">
-        <v>311</v>
-      </c>
-      <c r="K37" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="L37" s="62">
+      <c r="E37" s="58" t="s">
+        <v>113</v>
+      </c>
+      <c r="F37" s="58" t="s">
+        <v>391</v>
+      </c>
+      <c r="G37" s="58" t="s">
+        <v>220</v>
+      </c>
+      <c r="H37" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="I37" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J37" s="58" t="s">
+        <v>310</v>
+      </c>
+      <c r="K37" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="L37" s="58">
         <v>2</v>
       </c>
-      <c r="M37" s="62">
+      <c r="M37" s="58">
         <f>L37*5</f>
         <v>10</v>
       </c>
-      <c r="N37" s="62">
+      <c r="N37" s="58">
         <v>15</v>
       </c>
-      <c r="O37" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P37" s="63">
+      <c r="O37" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P37" s="59">
         <v>8.9399999999999993E-2</v>
       </c>
-      <c r="Q37" s="63">
+      <c r="Q37" s="59">
         <f>P37*N37</f>
         <v>1.341</v>
       </c>
-      <c r="R37" s="61"/>
+      <c r="R37" s="57"/>
       <c r="S37" s="37"/>
     </row>
     <row r="38" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="47">
+      <c r="B38" s="45">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C38" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="D38" s="64" t="s">
+      <c r="D38" s="61" t="s">
         <v>50</v>
       </c>
-      <c r="E38" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="F38" s="38" t="s">
-        <v>392</v>
-      </c>
-      <c r="G38" s="38" t="s">
-        <v>174</v>
-      </c>
-      <c r="H38" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="I38" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J38" s="38" t="s">
-        <v>312</v>
-      </c>
-      <c r="K38" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="L38" s="38">
+      <c r="E38" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="F38" s="62" t="s">
+        <v>391</v>
+      </c>
+      <c r="G38" s="62" t="s">
+        <v>173</v>
+      </c>
+      <c r="H38" s="62" t="s">
+        <v>271</v>
+      </c>
+      <c r="I38" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J38" s="62" t="s">
+        <v>311</v>
+      </c>
+      <c r="K38" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="L38" s="62">
         <v>1</v>
       </c>
-      <c r="M38" s="38">
+      <c r="M38" s="62">
         <f t="shared" ref="M38" si="30">L38*5</f>
         <v>5</v>
       </c>
-      <c r="N38" s="38">
+      <c r="N38" s="62">
         <v>6</v>
       </c>
-      <c r="O38" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P38" s="39">
+      <c r="O38" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P38" s="65">
         <v>0.66820000000000002</v>
       </c>
-      <c r="Q38" s="39">
+      <c r="Q38" s="65">
         <f t="shared" ref="Q38" si="31">P38*N38</f>
         <v>4.0091999999999999</v>
       </c>
-      <c r="R38" s="38"/>
-      <c r="S38" s="38"/>
+      <c r="R38" s="62"/>
+      <c r="S38" s="62"/>
     </row>
     <row r="39" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="B39" s="46">
+      <c r="B39" s="44">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="59" t="s">
+      <c r="C39" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="D39" s="62" t="s">
+      <c r="D39" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="E39" s="62" t="s">
-        <v>116</v>
-      </c>
-      <c r="F39" s="62" t="s">
-        <v>392</v>
-      </c>
-      <c r="G39" s="62" t="s">
-        <v>175</v>
-      </c>
-      <c r="H39" s="62" t="s">
-        <v>273</v>
-      </c>
-      <c r="I39" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J39" s="62" t="s">
-        <v>313</v>
-      </c>
-      <c r="K39" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="L39" s="62">
+      <c r="E39" s="58" t="s">
+        <v>115</v>
+      </c>
+      <c r="F39" s="58" t="s">
+        <v>391</v>
+      </c>
+      <c r="G39" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="H39" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="I39" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J39" s="58" t="s">
+        <v>312</v>
+      </c>
+      <c r="K39" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="L39" s="58">
         <v>1</v>
       </c>
-      <c r="M39" s="62">
+      <c r="M39" s="58">
         <f>L39*5</f>
         <v>5</v>
       </c>
-      <c r="N39" s="62">
+      <c r="N39" s="58">
         <v>10</v>
       </c>
-      <c r="O39" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P39" s="63">
+      <c r="O39" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P39" s="59">
         <v>9.3600000000000003E-2</v>
       </c>
-      <c r="Q39" s="63">
+      <c r="Q39" s="59">
         <f>P39*N39</f>
         <v>0.93600000000000005</v>
       </c>
-      <c r="R39" s="61"/>
+      <c r="R39" s="57"/>
       <c r="S39" s="37"/>
     </row>
     <row r="40" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
-      <c r="B40" s="47">
+      <c r="B40" s="45">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="C40" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="D40" s="64" t="s">
+      <c r="D40" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="E40" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="F40" s="38" t="s">
-        <v>392</v>
-      </c>
-      <c r="G40" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="H40" s="38" t="s">
-        <v>273</v>
-      </c>
-      <c r="I40" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J40" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="K40" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="L40" s="38">
+      <c r="E40" s="62" t="s">
+        <v>116</v>
+      </c>
+      <c r="F40" s="62" t="s">
+        <v>391</v>
+      </c>
+      <c r="G40" s="62" t="s">
+        <v>175</v>
+      </c>
+      <c r="H40" s="62" t="s">
+        <v>272</v>
+      </c>
+      <c r="I40" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J40" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="K40" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="L40" s="62">
         <v>1</v>
       </c>
-      <c r="M40" s="38">
+      <c r="M40" s="62">
         <f t="shared" ref="M40" si="32">L40*5</f>
         <v>5</v>
       </c>
-      <c r="N40" s="38">
+      <c r="N40" s="62">
         <v>10</v>
       </c>
-      <c r="O40" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P40" s="39" t="s">
-        <v>380</v>
-      </c>
-      <c r="Q40" s="39" t="s">
-        <v>380</v>
-      </c>
-      <c r="R40" s="65" t="s">
-        <v>446</v>
-      </c>
-      <c r="S40" s="38"/>
+      <c r="O40" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P40" s="65" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q40" s="65" t="s">
+        <v>379</v>
+      </c>
+      <c r="R40" s="66" t="s">
+        <v>445</v>
+      </c>
+      <c r="S40" s="62"/>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
-      <c r="B41" s="46">
+      <c r="B41" s="44">
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
-      <c r="C41" s="59" t="s">
+      <c r="C41" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="D41" s="62" t="s">
+      <c r="D41" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="E41" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="F41" s="62" t="s">
-        <v>392</v>
-      </c>
-      <c r="G41" s="62" t="s">
-        <v>177</v>
-      </c>
-      <c r="H41" s="62" t="s">
-        <v>271</v>
-      </c>
-      <c r="I41" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J41" s="62" t="s">
-        <v>314</v>
-      </c>
-      <c r="K41" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="L41" s="62">
+      <c r="E41" s="58" t="s">
+        <v>117</v>
+      </c>
+      <c r="F41" s="58" t="s">
+        <v>391</v>
+      </c>
+      <c r="G41" s="58" t="s">
+        <v>176</v>
+      </c>
+      <c r="H41" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="I41" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J41" s="58" t="s">
+        <v>313</v>
+      </c>
+      <c r="K41" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="L41" s="58">
         <v>1</v>
       </c>
-      <c r="M41" s="62">
+      <c r="M41" s="58">
         <f>L41*5</f>
         <v>5</v>
       </c>
-      <c r="N41" s="62">
+      <c r="N41" s="58">
         <v>6</v>
       </c>
-      <c r="O41" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P41" s="63">
+      <c r="O41" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P41" s="59">
         <v>1.4222999999999999</v>
       </c>
-      <c r="Q41" s="63">
+      <c r="Q41" s="59">
         <f>P41*N41</f>
         <v>8.5337999999999994</v>
       </c>
-      <c r="R41" s="61"/>
+      <c r="R41" s="57"/>
       <c r="S41" s="37"/>
     </row>
     <row r="42" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
-      <c r="B42" s="47">
+      <c r="B42" s="45">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="C42" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="D42" s="64" t="s">
+      <c r="D42" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="E42" s="38" t="s">
-        <v>119</v>
-      </c>
-      <c r="F42" s="38" t="s">
-        <v>392</v>
-      </c>
-      <c r="G42" s="38" t="s">
-        <v>178</v>
-      </c>
-      <c r="H42" s="38" t="s">
-        <v>274</v>
-      </c>
-      <c r="I42" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J42" s="38" t="s">
-        <v>315</v>
-      </c>
-      <c r="K42" s="38" t="s">
-        <v>359</v>
-      </c>
-      <c r="L42" s="38">
+      <c r="E42" s="62" t="s">
+        <v>118</v>
+      </c>
+      <c r="F42" s="62" t="s">
+        <v>391</v>
+      </c>
+      <c r="G42" s="62" t="s">
+        <v>177</v>
+      </c>
+      <c r="H42" s="62" t="s">
+        <v>273</v>
+      </c>
+      <c r="I42" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J42" s="62" t="s">
+        <v>314</v>
+      </c>
+      <c r="K42" s="62" t="s">
+        <v>358</v>
+      </c>
+      <c r="L42" s="62">
         <v>1</v>
       </c>
-      <c r="M42" s="38">
+      <c r="M42" s="62">
         <f t="shared" ref="M42" si="33">L42*5</f>
         <v>5</v>
       </c>
-      <c r="N42" s="38">
+      <c r="N42" s="62">
         <v>10</v>
       </c>
-      <c r="O42" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P42" s="39">
+      <c r="O42" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P42" s="65">
         <v>0.19500000000000001</v>
       </c>
-      <c r="Q42" s="39">
+      <c r="Q42" s="65">
         <f t="shared" ref="Q42" si="34">P42*N42</f>
         <v>1.9500000000000002</v>
       </c>
-      <c r="R42" s="38"/>
-      <c r="S42" s="38"/>
+      <c r="R42" s="62"/>
+      <c r="S42" s="62"/>
     </row>
     <row r="43" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
-      <c r="B43" s="46">
+      <c r="B43" s="44">
         <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
-      <c r="C43" s="59" t="s">
+      <c r="C43" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="D43" s="62" t="s">
+      <c r="D43" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="E43" s="62" t="s">
-        <v>120</v>
-      </c>
-      <c r="F43" s="62" t="s">
-        <v>392</v>
-      </c>
-      <c r="G43" s="62" t="s">
-        <v>179</v>
-      </c>
-      <c r="H43" s="62" t="s">
-        <v>275</v>
-      </c>
-      <c r="I43" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J43" s="62" t="s">
-        <v>316</v>
-      </c>
-      <c r="K43" s="62" t="s">
-        <v>359</v>
-      </c>
-      <c r="L43" s="62">
+      <c r="E43" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="F43" s="58" t="s">
+        <v>391</v>
+      </c>
+      <c r="G43" s="58" t="s">
+        <v>178</v>
+      </c>
+      <c r="H43" s="58" t="s">
+        <v>274</v>
+      </c>
+      <c r="I43" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J43" s="58" t="s">
+        <v>315</v>
+      </c>
+      <c r="K43" s="58" t="s">
+        <v>358</v>
+      </c>
+      <c r="L43" s="58">
         <v>1</v>
       </c>
-      <c r="M43" s="62">
+      <c r="M43" s="58">
         <f>L43*5</f>
         <v>5</v>
       </c>
-      <c r="N43" s="62">
+      <c r="N43" s="58">
         <v>6</v>
       </c>
-      <c r="O43" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P43" s="63">
+      <c r="O43" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P43" s="59">
         <v>0.35439999999999999</v>
       </c>
-      <c r="Q43" s="63">
+      <c r="Q43" s="59">
         <f>P43*N43</f>
         <v>2.1263999999999998</v>
       </c>
-      <c r="R43" s="61"/>
+      <c r="R43" s="57"/>
       <c r="S43" s="37"/>
     </row>
     <row r="44" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
-      <c r="B44" s="47">
+      <c r="B44" s="45">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="C44" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="D44" s="64" t="s">
+      <c r="D44" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="E44" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="F44" s="38" t="s">
-        <v>180</v>
-      </c>
-      <c r="G44" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="H44" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="I44" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J44" s="38" t="s">
-        <v>317</v>
-      </c>
-      <c r="K44" s="38" t="s">
-        <v>360</v>
-      </c>
-      <c r="L44" s="38">
+      <c r="E44" s="62" t="s">
+        <v>120</v>
+      </c>
+      <c r="F44" s="62" t="s">
+        <v>179</v>
+      </c>
+      <c r="G44" s="62" t="s">
+        <v>221</v>
+      </c>
+      <c r="H44" s="62" t="s">
+        <v>258</v>
+      </c>
+      <c r="I44" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J44" s="62" t="s">
+        <v>316</v>
+      </c>
+      <c r="K44" s="62" t="s">
+        <v>359</v>
+      </c>
+      <c r="L44" s="62">
         <v>1</v>
       </c>
-      <c r="M44" s="38">
+      <c r="M44" s="62">
         <f t="shared" ref="M44" si="35">L44*5</f>
         <v>5</v>
       </c>
-      <c r="N44" s="38">
+      <c r="N44" s="62">
         <v>10</v>
       </c>
-      <c r="O44" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P44" s="39">
+      <c r="O44" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P44" s="65">
         <v>6.4600000000000005E-2</v>
       </c>
-      <c r="Q44" s="39">
+      <c r="Q44" s="65">
         <f t="shared" ref="Q44" si="36">P44*N44</f>
         <v>0.64600000000000002</v>
       </c>
-      <c r="R44" s="38"/>
-      <c r="S44" s="38"/>
+      <c r="R44" s="62"/>
+      <c r="S44" s="62"/>
     </row>
     <row r="45" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
-      <c r="B45" s="47">
+      <c r="B45" s="45">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="59" t="s">
+      <c r="C45" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="D45" s="62" t="s">
-        <v>404</v>
-      </c>
-      <c r="E45" s="62" t="s">
-        <v>122</v>
-      </c>
-      <c r="F45" s="62" t="s">
-        <v>181</v>
-      </c>
-      <c r="G45" s="62" t="s">
-        <v>223</v>
-      </c>
-      <c r="H45" s="62" t="s">
-        <v>276</v>
-      </c>
-      <c r="I45" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J45" s="62" t="s">
-        <v>318</v>
-      </c>
-      <c r="K45" s="62" t="s">
-        <v>361</v>
-      </c>
-      <c r="L45" s="62">
+      <c r="D45" s="58" t="s">
+        <v>403</v>
+      </c>
+      <c r="E45" s="58" t="s">
+        <v>121</v>
+      </c>
+      <c r="F45" s="58" t="s">
+        <v>180</v>
+      </c>
+      <c r="G45" s="58" t="s">
+        <v>222</v>
+      </c>
+      <c r="H45" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="I45" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J45" s="58" t="s">
+        <v>317</v>
+      </c>
+      <c r="K45" s="58" t="s">
+        <v>360</v>
+      </c>
+      <c r="L45" s="58">
         <v>3</v>
       </c>
-      <c r="M45" s="62">
+      <c r="M45" s="58">
         <f t="shared" ref="M45" si="37">L45*5</f>
         <v>15</v>
       </c>
-      <c r="N45" s="62">
+      <c r="N45" s="58">
         <v>20</v>
       </c>
-      <c r="O45" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P45" s="63">
+      <c r="O45" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P45" s="59">
         <v>4.9099999999999998E-2</v>
       </c>
-      <c r="Q45" s="63">
+      <c r="Q45" s="59">
         <f t="shared" ref="Q45" si="38">P45*N45</f>
         <v>0.98199999999999998</v>
       </c>
-      <c r="R45" s="61"/>
+      <c r="R45" s="57"/>
       <c r="S45" s="37"/>
     </row>
     <row r="46" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
-      <c r="B46" s="46">
+      <c r="B46" s="44">
         <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
       <c r="C46" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="D46" s="64" t="s">
-        <v>405</v>
-      </c>
-      <c r="E46" s="38" t="s">
-        <v>124</v>
-      </c>
-      <c r="F46" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="G46" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="H46" s="38" t="s">
-        <v>276</v>
-      </c>
-      <c r="I46" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J46" s="38" t="s">
-        <v>319</v>
-      </c>
-      <c r="K46" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="L46" s="38">
+      <c r="D46" s="61" t="s">
+        <v>404</v>
+      </c>
+      <c r="E46" s="62" t="s">
+        <v>123</v>
+      </c>
+      <c r="F46" s="62" t="s">
+        <v>180</v>
+      </c>
+      <c r="G46" s="62" t="s">
+        <v>224</v>
+      </c>
+      <c r="H46" s="62" t="s">
+        <v>275</v>
+      </c>
+      <c r="I46" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J46" s="62" t="s">
+        <v>318</v>
+      </c>
+      <c r="K46" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="L46" s="62">
         <v>4</v>
       </c>
-      <c r="M46" s="38">
+      <c r="M46" s="62">
         <f>L46*5</f>
         <v>20</v>
       </c>
-      <c r="N46" s="38">
+      <c r="N46" s="62">
         <v>40</v>
       </c>
-      <c r="O46" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P46" s="39">
+      <c r="O46" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P46" s="65">
         <v>3.2099999999999997E-2</v>
       </c>
-      <c r="Q46" s="39">
+      <c r="Q46" s="65">
         <f>P46*N46</f>
         <v>1.2839999999999998</v>
       </c>
-      <c r="R46" s="38"/>
-      <c r="S46" s="38"/>
+      <c r="R46" s="62"/>
+      <c r="S46" s="62"/>
     </row>
     <row r="47" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
-      <c r="B47" s="47">
+      <c r="B47" s="45">
         <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
-      <c r="C47" s="59" t="s">
+      <c r="C47" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="D47" s="62" t="s">
+      <c r="D47" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="E47" s="62" t="s">
-        <v>123</v>
-      </c>
-      <c r="F47" s="62" t="s">
-        <v>182</v>
-      </c>
-      <c r="G47" s="62" t="s">
-        <v>224</v>
-      </c>
-      <c r="H47" s="62" t="s">
-        <v>277</v>
-      </c>
-      <c r="I47" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J47" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="K47" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="L47" s="62">
+      <c r="E47" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="F47" s="58" t="s">
+        <v>181</v>
+      </c>
+      <c r="G47" s="58" t="s">
+        <v>223</v>
+      </c>
+      <c r="H47" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="I47" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J47" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="K47" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="L47" s="58">
         <v>1</v>
       </c>
-      <c r="M47" s="62">
+      <c r="M47" s="58">
         <f t="shared" ref="M47" si="39">L47*5</f>
         <v>5</v>
       </c>
-      <c r="N47" s="62">
+      <c r="N47" s="58">
         <v>6</v>
       </c>
-      <c r="O47" s="57" t="s">
-        <v>277</v>
-      </c>
-      <c r="P47" s="63">
+      <c r="O47" s="55" t="s">
+        <v>276</v>
+      </c>
+      <c r="P47" s="59">
         <v>16.59</v>
       </c>
-      <c r="Q47" s="63">
+      <c r="Q47" s="59">
         <f t="shared" ref="Q47" si="40">P47*N47</f>
         <v>99.539999999999992</v>
       </c>
-      <c r="R47" s="61"/>
+      <c r="R47" s="57"/>
       <c r="S47" s="37"/>
     </row>
     <row r="48" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
-      <c r="B48" s="47">
+      <c r="B48" s="45">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="C48" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="D48" s="64" t="s">
+      <c r="D48" s="61" t="s">
         <v>58</v>
       </c>
-      <c r="E48" s="38" t="s">
-        <v>125</v>
-      </c>
-      <c r="F48" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="G48" s="38" t="s">
-        <v>183</v>
-      </c>
-      <c r="H48" s="38" t="s">
-        <v>278</v>
-      </c>
-      <c r="I48" s="38"/>
-      <c r="J48" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="K48" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="L48" s="38">
+      <c r="E48" s="62" t="s">
+        <v>124</v>
+      </c>
+      <c r="F48" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="G48" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="H48" s="62" t="s">
+        <v>277</v>
+      </c>
+      <c r="I48" s="62"/>
+      <c r="J48" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="K48" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="L48" s="62">
         <v>1</v>
       </c>
-      <c r="M48" s="38">
+      <c r="M48" s="62">
         <f t="shared" ref="M48" si="41">L48*5</f>
         <v>5</v>
       </c>
-      <c r="N48" s="38">
+      <c r="N48" s="62">
         <v>6</v>
       </c>
-      <c r="O48" s="58" t="s">
-        <v>278</v>
-      </c>
-      <c r="P48" s="39">
+      <c r="O48" s="64" t="s">
+        <v>277</v>
+      </c>
+      <c r="P48" s="65">
         <v>13.9</v>
       </c>
-      <c r="Q48" s="39">
+      <c r="Q48" s="65">
         <f t="shared" ref="Q48" si="42">P48*N48</f>
         <v>83.4</v>
       </c>
-      <c r="R48" s="38"/>
-      <c r="S48" s="38"/>
+      <c r="R48" s="62"/>
+      <c r="S48" s="62"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
-      <c r="B49" s="46">
+      <c r="B49" s="44">
         <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
-      <c r="C49" s="79" t="s">
-        <v>362</v>
-      </c>
-      <c r="D49" s="80" t="s">
+      <c r="C49" s="67" t="s">
+        <v>361</v>
+      </c>
+      <c r="D49" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="E49" s="80" t="s">
-        <v>126</v>
-      </c>
-      <c r="F49" s="80" t="s">
-        <v>184</v>
-      </c>
-      <c r="G49" s="80" t="s">
-        <v>380</v>
-      </c>
-      <c r="H49" s="80" t="s">
-        <v>380</v>
-      </c>
-      <c r="I49" s="80" t="s">
-        <v>380</v>
-      </c>
-      <c r="J49" s="80" t="s">
-        <v>380</v>
-      </c>
-      <c r="K49" s="80" t="s">
-        <v>380</v>
-      </c>
-      <c r="L49" s="80">
+      <c r="E49" s="68" t="s">
+        <v>125</v>
+      </c>
+      <c r="F49" s="68" t="s">
+        <v>183</v>
+      </c>
+      <c r="G49" s="68" t="s">
+        <v>379</v>
+      </c>
+      <c r="H49" s="68" t="s">
+        <v>379</v>
+      </c>
+      <c r="I49" s="68" t="s">
+        <v>379</v>
+      </c>
+      <c r="J49" s="68" t="s">
+        <v>379</v>
+      </c>
+      <c r="K49" s="68" t="s">
+        <v>379</v>
+      </c>
+      <c r="L49" s="68">
         <v>6</v>
       </c>
-      <c r="M49" s="80">
+      <c r="M49" s="68">
         <f>L49*5</f>
         <v>30</v>
       </c>
-      <c r="N49" s="80" t="s">
-        <v>380</v>
-      </c>
-      <c r="O49" s="81" t="s">
-        <v>380</v>
-      </c>
-      <c r="P49" s="82" t="s">
-        <v>380</v>
-      </c>
-      <c r="Q49" s="82" t="s">
-        <v>380</v>
-      </c>
-      <c r="R49" s="80"/>
-      <c r="S49" s="80"/>
+      <c r="N49" s="68" t="s">
+        <v>379</v>
+      </c>
+      <c r="O49" s="69" t="s">
+        <v>379</v>
+      </c>
+      <c r="P49" s="70" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q49" s="70" t="s">
+        <v>379</v>
+      </c>
+      <c r="R49" s="68"/>
+      <c r="S49" s="68"/>
     </row>
     <row r="50" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
-      <c r="B50" s="47">
+      <c r="B50" s="45">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="C50" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="D50" s="64" t="s">
+      <c r="D50" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="E50" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="F50" s="38" t="s">
-        <v>185</v>
-      </c>
-      <c r="G50" s="38" t="s">
-        <v>226</v>
-      </c>
-      <c r="H50" s="38" t="s">
-        <v>279</v>
-      </c>
-      <c r="I50" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J50" s="38" t="s">
-        <v>320</v>
-      </c>
-      <c r="K50" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="L50" s="38">
+      <c r="E50" s="62" t="s">
+        <v>126</v>
+      </c>
+      <c r="F50" s="62" t="s">
+        <v>184</v>
+      </c>
+      <c r="G50" s="62" t="s">
+        <v>225</v>
+      </c>
+      <c r="H50" s="62" t="s">
+        <v>278</v>
+      </c>
+      <c r="I50" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J50" s="62" t="s">
+        <v>319</v>
+      </c>
+      <c r="K50" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="L50" s="62">
         <v>4</v>
       </c>
-      <c r="M50" s="38">
+      <c r="M50" s="62">
         <f t="shared" ref="M50" si="43">L50*5</f>
         <v>20</v>
       </c>
-      <c r="N50" s="38">
+      <c r="N50" s="62">
         <v>40</v>
       </c>
-      <c r="O50" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P50" s="39">
+      <c r="O50" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P50" s="65">
         <v>3.2899999999999999E-2</v>
       </c>
-      <c r="Q50" s="39">
+      <c r="Q50" s="65">
         <f t="shared" ref="Q50" si="44">P50*N50</f>
         <v>1.3159999999999998</v>
       </c>
-      <c r="R50" s="38"/>
-      <c r="S50" s="38"/>
+      <c r="R50" s="62"/>
+      <c r="S50" s="62"/>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
-      <c r="B51" s="46">
+      <c r="B51" s="44">
         <f>ROW(B51) - ROW($B$9)</f>
         <v>42</v>
       </c>
-      <c r="C51" s="59" t="s">
+      <c r="C51" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="D51" s="62" t="s">
+      <c r="D51" s="58" t="s">
         <v>61</v>
       </c>
-      <c r="E51" s="62" t="s">
-        <v>128</v>
-      </c>
-      <c r="F51" s="62" t="s">
-        <v>186</v>
-      </c>
-      <c r="G51" s="62" t="s">
-        <v>227</v>
-      </c>
-      <c r="H51" s="62" t="s">
-        <v>256</v>
-      </c>
-      <c r="I51" s="62" t="s">
-        <v>399</v>
-      </c>
-      <c r="J51" s="62" t="s">
-        <v>321</v>
-      </c>
-      <c r="K51" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="L51" s="62">
+      <c r="E51" s="58" t="s">
+        <v>127</v>
+      </c>
+      <c r="F51" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="G51" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="H51" s="58" t="s">
+        <v>255</v>
+      </c>
+      <c r="I51" s="58" t="s">
+        <v>398</v>
+      </c>
+      <c r="J51" s="58" t="s">
+        <v>320</v>
+      </c>
+      <c r="K51" s="58" t="s">
+        <v>362</v>
+      </c>
+      <c r="L51" s="58">
         <v>1</v>
       </c>
-      <c r="M51" s="62">
+      <c r="M51" s="58">
         <f>L51*5</f>
         <v>5</v>
       </c>
-      <c r="N51" s="62">
+      <c r="N51" s="58">
         <v>20</v>
       </c>
-      <c r="O51" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P51" s="63">
+      <c r="O51" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P51" s="59">
         <v>2.7699999999999999E-2</v>
       </c>
-      <c r="Q51" s="63">
+      <c r="Q51" s="59">
         <f>P51*N51</f>
         <v>0.55399999999999994</v>
       </c>
-      <c r="R51" s="61"/>
+      <c r="R51" s="57"/>
       <c r="S51" s="37"/>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
-      <c r="B52" s="47">
+      <c r="B52" s="45">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="C52" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="D52" s="64" t="s">
+      <c r="D52" s="61" t="s">
         <v>62</v>
       </c>
-      <c r="E52" s="38" t="s">
-        <v>129</v>
-      </c>
-      <c r="F52" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="G52" s="38" t="s">
-        <v>228</v>
-      </c>
-      <c r="H52" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="I52" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J52" s="38" t="s">
-        <v>322</v>
-      </c>
-      <c r="K52" s="38" t="s">
-        <v>382</v>
-      </c>
-      <c r="L52" s="38">
+      <c r="E52" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="F52" s="62" t="s">
+        <v>185</v>
+      </c>
+      <c r="G52" s="62" t="s">
+        <v>227</v>
+      </c>
+      <c r="H52" s="62" t="s">
+        <v>255</v>
+      </c>
+      <c r="I52" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J52" s="62" t="s">
+        <v>321</v>
+      </c>
+      <c r="K52" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="L52" s="62">
         <v>1</v>
       </c>
-      <c r="M52" s="38">
+      <c r="M52" s="62">
         <f t="shared" ref="M52" si="45">L52*5</f>
         <v>5</v>
       </c>
-      <c r="N52" s="38">
+      <c r="N52" s="62">
         <v>20</v>
       </c>
-      <c r="O52" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P52" s="39">
+      <c r="O52" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P52" s="65">
         <v>2.18E-2</v>
       </c>
-      <c r="Q52" s="39">
+      <c r="Q52" s="65">
         <f t="shared" ref="Q52" si="46">P52*N52</f>
         <v>0.436</v>
       </c>
-      <c r="R52" s="38"/>
-      <c r="S52" s="38"/>
+      <c r="R52" s="62"/>
+      <c r="S52" s="62"/>
     </row>
     <row r="53" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
-      <c r="B53" s="46">
+      <c r="B53" s="44">
         <f>ROW(B53) - ROW($B$9)</f>
         <v>44</v>
       </c>
-      <c r="C53" s="59" t="s">
+      <c r="C53" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="D53" s="62" t="s">
+      <c r="D53" s="58" t="s">
         <v>63</v>
       </c>
-      <c r="E53" s="62" t="s">
-        <v>130</v>
-      </c>
-      <c r="F53" s="62" t="s">
-        <v>186</v>
-      </c>
-      <c r="G53" s="62" t="s">
-        <v>229</v>
-      </c>
-      <c r="H53" s="62" t="s">
-        <v>256</v>
-      </c>
-      <c r="I53" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J53" s="62" t="s">
-        <v>323</v>
-      </c>
-      <c r="K53" s="62" t="s">
-        <v>364</v>
-      </c>
-      <c r="L53" s="62">
+      <c r="E53" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="F53" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="G53" s="58" t="s">
+        <v>228</v>
+      </c>
+      <c r="H53" s="58" t="s">
+        <v>255</v>
+      </c>
+      <c r="I53" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J53" s="58" t="s">
+        <v>322</v>
+      </c>
+      <c r="K53" s="58" t="s">
+        <v>363</v>
+      </c>
+      <c r="L53" s="58">
         <v>13</v>
       </c>
-      <c r="M53" s="62">
+      <c r="M53" s="58">
         <f>L53*5</f>
         <v>65</v>
       </c>
-      <c r="N53" s="62">
+      <c r="N53" s="58">
         <v>100</v>
       </c>
-      <c r="O53" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P53" s="63">
+      <c r="O53" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P53" s="59">
         <v>1E-3</v>
       </c>
-      <c r="Q53" s="63">
+      <c r="Q53" s="59">
         <f>P53*N53</f>
         <v>0.1</v>
       </c>
-      <c r="R53" s="61"/>
+      <c r="R53" s="57"/>
       <c r="S53" s="37"/>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
-      <c r="B54" s="47">
+      <c r="B54" s="45">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="C54" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="D54" s="64" t="s">
+      <c r="D54" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="E54" s="38" t="s">
-        <v>131</v>
-      </c>
-      <c r="F54" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="G54" s="38" t="s">
-        <v>230</v>
-      </c>
-      <c r="H54" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="I54" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J54" s="38" t="s">
-        <v>324</v>
-      </c>
-      <c r="K54" s="38" t="s">
-        <v>365</v>
-      </c>
-      <c r="L54" s="38">
+      <c r="E54" s="62" t="s">
+        <v>130</v>
+      </c>
+      <c r="F54" s="62" t="s">
+        <v>185</v>
+      </c>
+      <c r="G54" s="62" t="s">
+        <v>229</v>
+      </c>
+      <c r="H54" s="62" t="s">
+        <v>255</v>
+      </c>
+      <c r="I54" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J54" s="62" t="s">
+        <v>323</v>
+      </c>
+      <c r="K54" s="62" t="s">
+        <v>364</v>
+      </c>
+      <c r="L54" s="62">
         <v>1</v>
       </c>
-      <c r="M54" s="38">
+      <c r="M54" s="62">
         <f t="shared" ref="M54" si="47">L54*5</f>
         <v>5</v>
       </c>
-      <c r="N54" s="38">
+      <c r="N54" s="62">
         <v>20</v>
       </c>
-      <c r="O54" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P54" s="39">
+      <c r="O54" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P54" s="65">
         <v>2.81E-2</v>
       </c>
-      <c r="Q54" s="39">
+      <c r="Q54" s="65">
         <f t="shared" ref="Q54" si="48">P54*N54</f>
         <v>0.56200000000000006</v>
       </c>
-      <c r="R54" s="38"/>
-      <c r="S54" s="38"/>
+      <c r="R54" s="62"/>
+      <c r="S54" s="62"/>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
-      <c r="B55" s="46">
+      <c r="B55" s="44">
         <f>ROW(B55) - ROW($B$9)</f>
         <v>46</v>
       </c>
-      <c r="C55" s="59" t="s">
+      <c r="C55" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="D55" s="62" t="s">
+      <c r="D55" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="E55" s="62" t="s">
-        <v>132</v>
-      </c>
-      <c r="F55" s="62" t="s">
-        <v>186</v>
-      </c>
-      <c r="G55" s="62" t="s">
-        <v>231</v>
-      </c>
-      <c r="H55" s="62" t="s">
-        <v>256</v>
-      </c>
-      <c r="I55" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J55" s="62" t="s">
-        <v>325</v>
-      </c>
-      <c r="K55" s="62" t="s">
-        <v>366</v>
-      </c>
-      <c r="L55" s="62">
+      <c r="E55" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="F55" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="G55" s="58" t="s">
+        <v>230</v>
+      </c>
+      <c r="H55" s="58" t="s">
+        <v>255</v>
+      </c>
+      <c r="I55" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J55" s="58" t="s">
+        <v>324</v>
+      </c>
+      <c r="K55" s="58" t="s">
+        <v>365</v>
+      </c>
+      <c r="L55" s="58">
         <v>1</v>
       </c>
-      <c r="M55" s="62">
+      <c r="M55" s="58">
         <f>L55*5</f>
         <v>5</v>
       </c>
-      <c r="N55" s="62">
+      <c r="N55" s="58">
         <v>20</v>
       </c>
-      <c r="O55" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P55" s="63">
+      <c r="O55" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P55" s="59">
         <v>3.2300000000000002E-2</v>
       </c>
-      <c r="Q55" s="63">
+      <c r="Q55" s="59">
         <f>P55*N55</f>
         <v>0.64600000000000002</v>
       </c>
-      <c r="R55" s="61"/>
+      <c r="R55" s="57"/>
       <c r="S55" s="37"/>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
-      <c r="B56" s="47">
+      <c r="B56" s="45">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="C56" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="D56" s="64" t="s">
+      <c r="D56" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="E56" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="F56" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="G56" s="38" t="s">
-        <v>232</v>
-      </c>
-      <c r="H56" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="I56" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J56" s="38" t="s">
-        <v>326</v>
-      </c>
-      <c r="K56" s="38" t="s">
-        <v>367</v>
-      </c>
-      <c r="L56" s="38">
+      <c r="E56" s="62" t="s">
+        <v>132</v>
+      </c>
+      <c r="F56" s="62" t="s">
+        <v>185</v>
+      </c>
+      <c r="G56" s="62" t="s">
+        <v>231</v>
+      </c>
+      <c r="H56" s="62" t="s">
+        <v>255</v>
+      </c>
+      <c r="I56" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J56" s="62" t="s">
+        <v>325</v>
+      </c>
+      <c r="K56" s="62" t="s">
+        <v>366</v>
+      </c>
+      <c r="L56" s="62">
         <v>2</v>
       </c>
-      <c r="M56" s="38">
+      <c r="M56" s="62">
         <f t="shared" ref="M56" si="49">L56*5</f>
         <v>10</v>
       </c>
-      <c r="N56" s="38">
+      <c r="N56" s="62">
         <v>100</v>
       </c>
-      <c r="O56" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P56" s="39">
+      <c r="O56" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P56" s="65">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q56" s="39">
+      <c r="Q56" s="65">
         <f t="shared" ref="Q56" si="50">P56*N56</f>
         <v>0.12</v>
       </c>
-      <c r="R56" s="38"/>
-      <c r="S56" s="38"/>
+      <c r="R56" s="62"/>
+      <c r="S56" s="62"/>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
-      <c r="B57" s="46">
+      <c r="B57" s="44">
         <f>ROW(B57) - ROW($B$9)</f>
         <v>48</v>
       </c>
-      <c r="C57" s="59" t="s">
+      <c r="C57" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="D57" s="62" t="s">
+      <c r="D57" s="58" t="s">
         <v>67</v>
       </c>
-      <c r="E57" s="62" t="s">
-        <v>134</v>
-      </c>
-      <c r="F57" s="62" t="s">
-        <v>186</v>
-      </c>
-      <c r="G57" s="62" t="s">
-        <v>233</v>
-      </c>
-      <c r="H57" s="62" t="s">
-        <v>256</v>
-      </c>
-      <c r="I57" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J57" s="62" t="s">
-        <v>327</v>
-      </c>
-      <c r="K57" s="62" t="s">
-        <v>368</v>
-      </c>
-      <c r="L57" s="62">
+      <c r="E57" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="F57" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="G57" s="58" t="s">
+        <v>232</v>
+      </c>
+      <c r="H57" s="58" t="s">
+        <v>255</v>
+      </c>
+      <c r="I57" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J57" s="58" t="s">
+        <v>326</v>
+      </c>
+      <c r="K57" s="58" t="s">
+        <v>367</v>
+      </c>
+      <c r="L57" s="58">
         <v>3</v>
       </c>
-      <c r="M57" s="62">
+      <c r="M57" s="58">
         <f>L57*5</f>
         <v>15</v>
       </c>
-      <c r="N57" s="62">
+      <c r="N57" s="58">
         <v>100</v>
       </c>
-      <c r="O57" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P57" s="63">
+      <c r="O57" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P57" s="59">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q57" s="63">
+      <c r="Q57" s="59">
         <f>P57*N57</f>
         <v>0.13</v>
       </c>
-      <c r="R57" s="61"/>
+      <c r="R57" s="57"/>
       <c r="S57" s="37"/>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
-      <c r="B58" s="47">
+      <c r="B58" s="45">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="C58" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="D58" s="64" t="s">
+      <c r="D58" s="61" t="s">
         <v>68</v>
       </c>
-      <c r="E58" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="F58" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="G58" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="H58" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="I58" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J58" s="38" t="s">
-        <v>328</v>
-      </c>
-      <c r="K58" s="38" t="s">
-        <v>369</v>
-      </c>
-      <c r="L58" s="38">
+      <c r="E58" s="62" t="s">
+        <v>134</v>
+      </c>
+      <c r="F58" s="62" t="s">
+        <v>185</v>
+      </c>
+      <c r="G58" s="62" t="s">
+        <v>233</v>
+      </c>
+      <c r="H58" s="62" t="s">
+        <v>255</v>
+      </c>
+      <c r="I58" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J58" s="62" t="s">
+        <v>327</v>
+      </c>
+      <c r="K58" s="62" t="s">
+        <v>368</v>
+      </c>
+      <c r="L58" s="62">
         <v>4</v>
       </c>
-      <c r="M58" s="38">
+      <c r="M58" s="62">
         <f t="shared" ref="M58" si="51">L58*5</f>
         <v>20</v>
       </c>
-      <c r="N58" s="38">
+      <c r="N58" s="62">
         <v>50</v>
       </c>
-      <c r="O58" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P58" s="39">
+      <c r="O58" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P58" s="65">
         <v>9.2999999999999992E-3</v>
       </c>
-      <c r="Q58" s="39">
+      <c r="Q58" s="65">
         <f t="shared" ref="Q58" si="52">P58*N58</f>
         <v>0.46499999999999997</v>
       </c>
-      <c r="R58" s="38"/>
-      <c r="S58" s="38"/>
+      <c r="R58" s="62"/>
+      <c r="S58" s="62"/>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
-      <c r="B59" s="46">
+      <c r="B59" s="44">
         <f>ROW(B59) - ROW($B$9)</f>
         <v>50</v>
       </c>
-      <c r="C59" s="59" t="s">
+      <c r="C59" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="D59" s="62" t="s">
+      <c r="D59" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="E59" s="62" t="s">
-        <v>136</v>
-      </c>
-      <c r="F59" s="62" t="s">
-        <v>186</v>
-      </c>
-      <c r="G59" s="62" t="s">
-        <v>235</v>
-      </c>
-      <c r="H59" s="62" t="s">
-        <v>256</v>
-      </c>
-      <c r="I59" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J59" s="62" t="s">
-        <v>329</v>
-      </c>
-      <c r="K59" s="62" t="s">
-        <v>370</v>
-      </c>
-      <c r="L59" s="62">
+      <c r="E59" s="58" t="s">
+        <v>135</v>
+      </c>
+      <c r="F59" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="G59" s="58" t="s">
+        <v>234</v>
+      </c>
+      <c r="H59" s="58" t="s">
+        <v>255</v>
+      </c>
+      <c r="I59" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J59" s="58" t="s">
+        <v>328</v>
+      </c>
+      <c r="K59" s="58" t="s">
+        <v>369</v>
+      </c>
+      <c r="L59" s="58">
         <v>1</v>
       </c>
-      <c r="M59" s="62">
+      <c r="M59" s="58">
         <f>L59*5</f>
         <v>5</v>
       </c>
-      <c r="N59" s="62">
+      <c r="N59" s="58">
         <v>100</v>
       </c>
-      <c r="O59" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P59" s="63">
+      <c r="O59" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P59" s="59">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="Q59" s="63">
+      <c r="Q59" s="59">
         <f>P59*N59</f>
         <v>0.3</v>
       </c>
-      <c r="R59" s="61"/>
+      <c r="R59" s="57"/>
       <c r="S59" s="37"/>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
-      <c r="B60" s="47">
+      <c r="B60" s="45">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="C60" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="D60" s="64" t="s">
+      <c r="D60" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="E60" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="F60" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="G60" s="38" t="s">
-        <v>236</v>
-      </c>
-      <c r="H60" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="I60" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J60" s="38" t="s">
-        <v>330</v>
-      </c>
-      <c r="K60" s="38" t="s">
-        <v>371</v>
-      </c>
-      <c r="L60" s="38">
+      <c r="E60" s="62" t="s">
+        <v>136</v>
+      </c>
+      <c r="F60" s="62" t="s">
+        <v>185</v>
+      </c>
+      <c r="G60" s="62" t="s">
+        <v>235</v>
+      </c>
+      <c r="H60" s="62" t="s">
+        <v>255</v>
+      </c>
+      <c r="I60" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J60" s="62" t="s">
+        <v>329</v>
+      </c>
+      <c r="K60" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="L60" s="62">
         <v>3</v>
       </c>
-      <c r="M60" s="38">
+      <c r="M60" s="62">
         <f t="shared" ref="M60" si="53">L60*5</f>
         <v>15</v>
       </c>
-      <c r="N60" s="38">
+      <c r="N60" s="62">
         <v>100</v>
       </c>
-      <c r="O60" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P60" s="39">
+      <c r="O60" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P60" s="65">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q60" s="39">
+      <c r="Q60" s="65">
         <f t="shared" ref="Q60" si="54">P60*N60</f>
         <v>0.12</v>
       </c>
-      <c r="R60" s="38"/>
-      <c r="S60" s="38"/>
+      <c r="R60" s="62"/>
+      <c r="S60" s="62"/>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
-      <c r="B61" s="46">
+      <c r="B61" s="44">
         <f>ROW(B61) - ROW($B$9)</f>
         <v>52</v>
       </c>
-      <c r="C61" s="59" t="s">
+      <c r="C61" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="D61" s="62" t="s">
+      <c r="D61" s="58" t="s">
         <v>71</v>
       </c>
-      <c r="E61" s="62" t="s">
-        <v>138</v>
-      </c>
-      <c r="F61" s="62" t="s">
-        <v>186</v>
-      </c>
-      <c r="G61" s="62" t="s">
-        <v>237</v>
-      </c>
-      <c r="H61" s="62" t="s">
-        <v>256</v>
-      </c>
-      <c r="I61" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J61" s="62" t="s">
-        <v>331</v>
-      </c>
-      <c r="K61" s="62" t="s">
-        <v>372</v>
-      </c>
-      <c r="L61" s="62">
+      <c r="E61" s="58" t="s">
+        <v>137</v>
+      </c>
+      <c r="F61" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="G61" s="58" t="s">
+        <v>236</v>
+      </c>
+      <c r="H61" s="58" t="s">
+        <v>255</v>
+      </c>
+      <c r="I61" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J61" s="58" t="s">
+        <v>330</v>
+      </c>
+      <c r="K61" s="58" t="s">
+        <v>371</v>
+      </c>
+      <c r="L61" s="58">
         <v>6</v>
       </c>
-      <c r="M61" s="62">
+      <c r="M61" s="58">
         <f>L61*5</f>
         <v>30</v>
       </c>
-      <c r="N61" s="62">
+      <c r="N61" s="58">
         <v>100</v>
       </c>
-      <c r="O61" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P61" s="63">
+      <c r="O61" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P61" s="59">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="Q61" s="63">
+      <c r="Q61" s="59">
         <f>P61*N61</f>
         <v>0.11</v>
       </c>
-      <c r="R61" s="61"/>
+      <c r="R61" s="57"/>
       <c r="S61" s="37"/>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
-      <c r="B62" s="47">
+      <c r="B62" s="45">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
       <c r="C62" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="D62" s="64" t="s">
+      <c r="D62" s="61" t="s">
         <v>72</v>
       </c>
-      <c r="E62" s="38" t="s">
-        <v>139</v>
-      </c>
-      <c r="F62" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="G62" s="38" t="s">
-        <v>238</v>
-      </c>
-      <c r="H62" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="I62" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J62" s="38" t="s">
-        <v>332</v>
-      </c>
-      <c r="K62" s="38" t="s">
-        <v>373</v>
-      </c>
-      <c r="L62" s="38">
+      <c r="E62" s="62" t="s">
+        <v>138</v>
+      </c>
+      <c r="F62" s="62" t="s">
+        <v>185</v>
+      </c>
+      <c r="G62" s="62" t="s">
+        <v>237</v>
+      </c>
+      <c r="H62" s="62" t="s">
+        <v>255</v>
+      </c>
+      <c r="I62" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J62" s="62" t="s">
+        <v>331</v>
+      </c>
+      <c r="K62" s="62" t="s">
+        <v>372</v>
+      </c>
+      <c r="L62" s="62">
         <v>4</v>
       </c>
-      <c r="M62" s="38">
+      <c r="M62" s="62">
         <f t="shared" ref="M62" si="55">L62*5</f>
         <v>20</v>
       </c>
-      <c r="N62" s="38">
+      <c r="N62" s="62">
         <v>100</v>
       </c>
-      <c r="O62" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P62" s="39">
+      <c r="O62" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P62" s="65">
         <v>1E-3</v>
       </c>
-      <c r="Q62" s="39">
+      <c r="Q62" s="65">
         <f t="shared" ref="Q62" si="56">P62*N62</f>
         <v>0.1</v>
       </c>
-      <c r="R62" s="38"/>
-      <c r="S62" s="38"/>
+      <c r="R62" s="62"/>
+      <c r="S62" s="62"/>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
-      <c r="B63" s="46">
+      <c r="B63" s="44">
         <f>ROW(B63) - ROW($B$9)</f>
         <v>54</v>
       </c>
-      <c r="C63" s="59" t="s">
+      <c r="C63" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="D63" s="62" t="s">
+      <c r="D63" s="58" t="s">
         <v>73</v>
       </c>
-      <c r="E63" s="62" t="s">
-        <v>140</v>
-      </c>
-      <c r="F63" s="62" t="s">
-        <v>186</v>
-      </c>
-      <c r="G63" s="62" t="s">
-        <v>239</v>
-      </c>
-      <c r="H63" s="62" t="s">
-        <v>256</v>
-      </c>
-      <c r="I63" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J63" s="62" t="s">
-        <v>333</v>
-      </c>
-      <c r="K63" s="62" t="s">
-        <v>374</v>
-      </c>
-      <c r="L63" s="62">
+      <c r="E63" s="58" t="s">
+        <v>139</v>
+      </c>
+      <c r="F63" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="G63" s="58" t="s">
+        <v>238</v>
+      </c>
+      <c r="H63" s="58" t="s">
+        <v>255</v>
+      </c>
+      <c r="I63" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J63" s="58" t="s">
+        <v>332</v>
+      </c>
+      <c r="K63" s="58" t="s">
+        <v>373</v>
+      </c>
+      <c r="L63" s="58">
         <v>1</v>
       </c>
-      <c r="M63" s="62">
+      <c r="M63" s="58">
         <f>L63*5</f>
         <v>5</v>
       </c>
-      <c r="N63" s="62">
+      <c r="N63" s="58">
         <v>100</v>
       </c>
-      <c r="O63" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P63" s="63">
+      <c r="O63" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P63" s="59">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q63" s="63">
+      <c r="Q63" s="59">
         <f>P63*N63</f>
         <v>0.13</v>
       </c>
-      <c r="R63" s="61"/>
+      <c r="R63" s="57"/>
       <c r="S63" s="37"/>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
-      <c r="B64" s="47">
+      <c r="B64" s="45">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="C64" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="D64" s="64" t="s">
+      <c r="D64" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="E64" s="38" t="s">
-        <v>141</v>
-      </c>
-      <c r="F64" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="G64" s="38" t="s">
-        <v>240</v>
-      </c>
-      <c r="H64" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="I64" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J64" s="38" t="s">
-        <v>334</v>
-      </c>
-      <c r="K64" s="38" t="s">
-        <v>375</v>
-      </c>
-      <c r="L64" s="38">
+      <c r="E64" s="62" t="s">
+        <v>140</v>
+      </c>
+      <c r="F64" s="62" t="s">
+        <v>185</v>
+      </c>
+      <c r="G64" s="62" t="s">
+        <v>239</v>
+      </c>
+      <c r="H64" s="62" t="s">
+        <v>255</v>
+      </c>
+      <c r="I64" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J64" s="62" t="s">
+        <v>333</v>
+      </c>
+      <c r="K64" s="62" t="s">
+        <v>374</v>
+      </c>
+      <c r="L64" s="62">
         <v>3</v>
       </c>
-      <c r="M64" s="38">
+      <c r="M64" s="62">
         <f t="shared" ref="M64" si="57">L64*5</f>
         <v>15</v>
       </c>
-      <c r="N64" s="38">
+      <c r="N64" s="62">
         <v>100</v>
       </c>
-      <c r="O64" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P64" s="39">
+      <c r="O64" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P64" s="65">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q64" s="39">
+      <c r="Q64" s="65">
         <f t="shared" ref="Q64" si="58">P64*N64</f>
         <v>0.13</v>
       </c>
-      <c r="R64" s="38"/>
-      <c r="S64" s="38"/>
+      <c r="R64" s="62"/>
+      <c r="S64" s="62"/>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
-      <c r="B65" s="46">
+      <c r="B65" s="44">
         <f>ROW(B65) - ROW($B$9)</f>
         <v>56</v>
       </c>
-      <c r="C65" s="59" t="s">
+      <c r="C65" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="D65" s="62" t="s">
+      <c r="D65" s="58" t="s">
         <v>75</v>
       </c>
-      <c r="E65" s="62" t="s">
-        <v>142</v>
-      </c>
-      <c r="F65" s="62" t="s">
-        <v>186</v>
-      </c>
-      <c r="G65" s="62" t="s">
-        <v>241</v>
-      </c>
-      <c r="H65" s="62" t="s">
-        <v>256</v>
-      </c>
-      <c r="I65" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J65" s="62" t="s">
-        <v>335</v>
-      </c>
-      <c r="K65" s="62" t="s">
-        <v>376</v>
-      </c>
-      <c r="L65" s="62">
+      <c r="E65" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="F65" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="G65" s="58" t="s">
+        <v>240</v>
+      </c>
+      <c r="H65" s="58" t="s">
+        <v>255</v>
+      </c>
+      <c r="I65" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J65" s="58" t="s">
+        <v>334</v>
+      </c>
+      <c r="K65" s="58" t="s">
+        <v>375</v>
+      </c>
+      <c r="L65" s="58">
         <v>1</v>
       </c>
-      <c r="M65" s="62">
+      <c r="M65" s="58">
         <f>L65*5</f>
         <v>5</v>
       </c>
-      <c r="N65" s="62">
+      <c r="N65" s="58">
         <v>100</v>
       </c>
-      <c r="O65" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P65" s="63">
+      <c r="O65" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P65" s="59">
         <v>1.8E-3</v>
       </c>
-      <c r="Q65" s="63">
+      <c r="Q65" s="59">
         <f>P65*N65</f>
         <v>0.18</v>
       </c>
-      <c r="R65" s="61"/>
+      <c r="R65" s="57"/>
       <c r="S65" s="37"/>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
-      <c r="B66" s="47">
+      <c r="B66" s="45">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
       <c r="C66" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="D66" s="64" t="s">
+      <c r="D66" s="61" t="s">
         <v>76</v>
       </c>
-      <c r="E66" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="F66" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="G66" s="38" t="s">
-        <v>242</v>
-      </c>
-      <c r="H66" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="I66" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J66" s="38" t="s">
-        <v>336</v>
-      </c>
-      <c r="K66" s="38" t="s">
-        <v>377</v>
-      </c>
-      <c r="L66" s="38">
+      <c r="E66" s="62" t="s">
+        <v>142</v>
+      </c>
+      <c r="F66" s="62" t="s">
+        <v>185</v>
+      </c>
+      <c r="G66" s="62" t="s">
+        <v>241</v>
+      </c>
+      <c r="H66" s="62" t="s">
+        <v>255</v>
+      </c>
+      <c r="I66" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J66" s="62" t="s">
+        <v>335</v>
+      </c>
+      <c r="K66" s="62" t="s">
+        <v>376</v>
+      </c>
+      <c r="L66" s="62">
         <v>1</v>
       </c>
-      <c r="M66" s="38">
+      <c r="M66" s="62">
         <f t="shared" ref="M66" si="59">L66*5</f>
         <v>5</v>
       </c>
-      <c r="N66" s="38">
+      <c r="N66" s="62">
         <v>100</v>
       </c>
-      <c r="O66" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P66" s="39">
+      <c r="O66" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P66" s="65">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q66" s="39">
+      <c r="Q66" s="65">
         <f t="shared" ref="Q66" si="60">P66*N66</f>
         <v>0.13</v>
       </c>
-      <c r="R66" s="38"/>
-      <c r="S66" s="38"/>
+      <c r="R66" s="62"/>
+      <c r="S66" s="62"/>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
-      <c r="B67" s="46">
+      <c r="B67" s="44">
         <f>ROW(B67) - ROW($B$9)</f>
         <v>58</v>
       </c>
-      <c r="C67" s="59" t="s">
+      <c r="C67" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="D67" s="62" t="s">
+      <c r="D67" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="E67" s="62" t="s">
-        <v>144</v>
-      </c>
-      <c r="F67" s="62" t="s">
-        <v>187</v>
-      </c>
-      <c r="G67" s="62" t="s">
-        <v>243</v>
-      </c>
-      <c r="H67" s="62" t="s">
-        <v>256</v>
-      </c>
-      <c r="I67" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J67" s="62" t="s">
-        <v>400</v>
-      </c>
-      <c r="K67" s="62" t="s">
-        <v>371</v>
-      </c>
-      <c r="L67" s="62">
+      <c r="E67" s="58" t="s">
+        <v>143</v>
+      </c>
+      <c r="F67" s="58" t="s">
+        <v>186</v>
+      </c>
+      <c r="G67" s="58" t="s">
+        <v>242</v>
+      </c>
+      <c r="H67" s="58" t="s">
+        <v>255</v>
+      </c>
+      <c r="I67" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J67" s="58" t="s">
+        <v>399</v>
+      </c>
+      <c r="K67" s="58" t="s">
+        <v>370</v>
+      </c>
+      <c r="L67" s="58">
         <v>1</v>
       </c>
-      <c r="M67" s="62">
+      <c r="M67" s="58">
         <f>L67*5</f>
         <v>5</v>
       </c>
-      <c r="N67" s="62">
+      <c r="N67" s="58">
         <v>100</v>
       </c>
-      <c r="O67" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P67" s="63">
+      <c r="O67" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P67" s="59">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="Q67" s="63">
+      <c r="Q67" s="59">
         <f>P67*N67</f>
         <v>6.9999999999999993E-2</v>
       </c>
-      <c r="R67" s="61"/>
+      <c r="R67" s="57"/>
       <c r="S67" s="37"/>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
-      <c r="B68" s="47">
+      <c r="B68" s="45">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="C68" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="D68" s="64" t="s">
+      <c r="D68" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="E68" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="F68" s="38" t="s">
-        <v>187</v>
-      </c>
-      <c r="G68" s="38" t="s">
-        <v>244</v>
-      </c>
-      <c r="H68" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="I68" s="38" t="s">
+      <c r="E68" s="62" t="s">
+        <v>144</v>
+      </c>
+      <c r="F68" s="62" t="s">
+        <v>186</v>
+      </c>
+      <c r="G68" s="62" t="s">
+        <v>243</v>
+      </c>
+      <c r="H68" s="62" t="s">
+        <v>255</v>
+      </c>
+      <c r="I68" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J68" s="62" t="s">
         <v>380</v>
       </c>
-      <c r="J68" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="K68" s="38" t="s">
-        <v>378</v>
-      </c>
-      <c r="L68" s="38">
+      <c r="K68" s="62" t="s">
+        <v>377</v>
+      </c>
+      <c r="L68" s="62">
         <v>1</v>
       </c>
-      <c r="M68" s="38">
+      <c r="M68" s="62">
         <f t="shared" ref="M68" si="61">L68*5</f>
         <v>5</v>
       </c>
-      <c r="N68" s="38">
+      <c r="N68" s="62">
         <v>100</v>
       </c>
-      <c r="O68" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P68" s="39">
+      <c r="O68" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P68" s="65">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="Q68" s="39">
+      <c r="Q68" s="65">
         <f t="shared" ref="Q68" si="62">P68*N68</f>
         <v>0.05</v>
       </c>
-      <c r="R68" s="38"/>
-      <c r="S68" s="38"/>
+      <c r="R68" s="62"/>
+      <c r="S68" s="62"/>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
-      <c r="B69" s="46">
+      <c r="B69" s="44">
         <f>ROW(B69) - ROW($B$9)</f>
         <v>60</v>
       </c>
-      <c r="C69" s="79" t="s">
-        <v>396</v>
-      </c>
-      <c r="D69" s="80" t="s">
+      <c r="C69" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="D69" s="68" t="s">
         <v>79</v>
       </c>
-      <c r="E69" s="80" t="s">
-        <v>146</v>
-      </c>
-      <c r="F69" s="80" t="s">
-        <v>380</v>
-      </c>
-      <c r="G69" s="80" t="s">
-        <v>188</v>
-      </c>
-      <c r="H69" s="80" t="s">
-        <v>380</v>
-      </c>
-      <c r="I69" s="80" t="s">
-        <v>380</v>
-      </c>
-      <c r="J69" s="80" t="s">
-        <v>380</v>
-      </c>
-      <c r="K69" s="80" t="s">
-        <v>380</v>
-      </c>
-      <c r="L69" s="80">
+      <c r="E69" s="68" t="s">
+        <v>145</v>
+      </c>
+      <c r="F69" s="68" t="s">
+        <v>379</v>
+      </c>
+      <c r="G69" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="H69" s="68" t="s">
+        <v>379</v>
+      </c>
+      <c r="I69" s="68" t="s">
+        <v>379</v>
+      </c>
+      <c r="J69" s="68" t="s">
+        <v>379</v>
+      </c>
+      <c r="K69" s="68" t="s">
+        <v>379</v>
+      </c>
+      <c r="L69" s="68">
         <v>2</v>
       </c>
-      <c r="M69" s="80">
+      <c r="M69" s="68">
         <f>L69*5</f>
         <v>10</v>
       </c>
-      <c r="N69" s="80" t="s">
-        <v>380</v>
-      </c>
-      <c r="O69" s="81" t="s">
-        <v>380</v>
-      </c>
-      <c r="P69" s="82" t="s">
-        <v>380</v>
-      </c>
-      <c r="Q69" s="82" t="s">
-        <v>380</v>
-      </c>
-      <c r="R69" s="80"/>
-      <c r="S69" s="80"/>
+      <c r="N69" s="68" t="s">
+        <v>379</v>
+      </c>
+      <c r="O69" s="69" t="s">
+        <v>379</v>
+      </c>
+      <c r="P69" s="70" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q69" s="70" t="s">
+        <v>379</v>
+      </c>
+      <c r="R69" s="68"/>
+      <c r="S69" s="68"/>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
-      <c r="B70" s="47">
+      <c r="B70" s="45">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
       <c r="C70" s="60" t="s">
-        <v>397</v>
-      </c>
-      <c r="D70" s="64" t="s">
+        <v>396</v>
+      </c>
+      <c r="D70" s="61" t="s">
         <v>80</v>
       </c>
-      <c r="E70" s="38" t="s">
-        <v>147</v>
-      </c>
-      <c r="F70" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="G70" s="38" t="s">
-        <v>245</v>
-      </c>
-      <c r="H70" s="38" t="s">
-        <v>280</v>
-      </c>
-      <c r="I70" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J70" s="38" t="s">
-        <v>337</v>
-      </c>
-      <c r="K70" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="L70" s="38">
+      <c r="E70" s="62" t="s">
+        <v>146</v>
+      </c>
+      <c r="F70" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="G70" s="62" t="s">
+        <v>244</v>
+      </c>
+      <c r="H70" s="62" t="s">
+        <v>279</v>
+      </c>
+      <c r="I70" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J70" s="62" t="s">
+        <v>336</v>
+      </c>
+      <c r="K70" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="L70" s="62">
         <v>1</v>
       </c>
-      <c r="M70" s="38">
+      <c r="M70" s="62">
         <f t="shared" ref="M70" si="63">L70*5</f>
         <v>5</v>
       </c>
-      <c r="N70" s="38">
+      <c r="N70" s="62">
         <v>6</v>
       </c>
-      <c r="O70" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P70" s="39">
+      <c r="O70" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P70" s="65">
         <v>0.54410000000000003</v>
       </c>
-      <c r="Q70" s="39">
+      <c r="Q70" s="65">
         <f t="shared" ref="Q70" si="64">P70*N70</f>
         <v>3.2646000000000002</v>
       </c>
-      <c r="R70" s="38"/>
-      <c r="S70" s="38"/>
+      <c r="R70" s="62"/>
+      <c r="S70" s="62"/>
     </row>
     <row r="71" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
-      <c r="B71" s="46">
+      <c r="B71" s="44">
         <f>ROW(B71) - ROW($B$9)</f>
         <v>62</v>
       </c>
-      <c r="C71" s="59" t="s">
+      <c r="C71" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="D71" s="62" t="s">
+      <c r="D71" s="58" t="s">
         <v>81</v>
       </c>
-      <c r="E71" s="62" t="s">
-        <v>148</v>
-      </c>
-      <c r="F71" s="62" t="s">
-        <v>189</v>
-      </c>
-      <c r="G71" s="62" t="s">
-        <v>246</v>
-      </c>
-      <c r="H71" s="62" t="s">
-        <v>281</v>
-      </c>
-      <c r="I71" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J71" s="62" t="s">
-        <v>338</v>
-      </c>
-      <c r="K71" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="L71" s="62">
+      <c r="E71" s="58" t="s">
+        <v>147</v>
+      </c>
+      <c r="F71" s="58" t="s">
+        <v>188</v>
+      </c>
+      <c r="G71" s="58" t="s">
+        <v>245</v>
+      </c>
+      <c r="H71" s="58" t="s">
+        <v>280</v>
+      </c>
+      <c r="I71" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J71" s="58" t="s">
+        <v>337</v>
+      </c>
+      <c r="K71" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="L71" s="58">
         <v>1</v>
       </c>
-      <c r="M71" s="62">
+      <c r="M71" s="58">
         <f>L71*5</f>
         <v>5</v>
       </c>
-      <c r="N71" s="62">
+      <c r="N71" s="58">
         <v>10</v>
       </c>
-      <c r="O71" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P71" s="63">
+      <c r="O71" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P71" s="59">
         <v>7.6300000000000007E-2</v>
       </c>
-      <c r="Q71" s="63">
+      <c r="Q71" s="59">
         <f>P71*N71</f>
         <v>0.76300000000000012</v>
       </c>
-      <c r="R71" s="61"/>
+      <c r="R71" s="57"/>
       <c r="S71" s="37"/>
     </row>
     <row r="72" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
-      <c r="B72" s="47">
+      <c r="B72" s="45">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="C72" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="D72" s="64" t="s">
+      <c r="D72" s="61" t="s">
         <v>82</v>
       </c>
-      <c r="E72" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="F72" s="38" t="s">
-        <v>190</v>
-      </c>
-      <c r="G72" s="38" t="s">
-        <v>247</v>
-      </c>
-      <c r="H72" s="38" t="s">
-        <v>282</v>
-      </c>
-      <c r="I72" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J72" s="38" t="s">
-        <v>339</v>
-      </c>
-      <c r="K72" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="L72" s="38">
+      <c r="E72" s="62" t="s">
+        <v>148</v>
+      </c>
+      <c r="F72" s="62" t="s">
+        <v>189</v>
+      </c>
+      <c r="G72" s="62" t="s">
+        <v>246</v>
+      </c>
+      <c r="H72" s="62" t="s">
+        <v>281</v>
+      </c>
+      <c r="I72" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J72" s="62" t="s">
+        <v>338</v>
+      </c>
+      <c r="K72" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="L72" s="62">
         <v>1</v>
       </c>
-      <c r="M72" s="38">
+      <c r="M72" s="62">
         <f t="shared" ref="M72" si="65">L72*5</f>
         <v>5</v>
       </c>
-      <c r="N72" s="38">
+      <c r="N72" s="62">
         <v>6</v>
       </c>
-      <c r="O72" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P72" s="39">
+      <c r="O72" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P72" s="65">
         <v>3.1484999999999999</v>
       </c>
-      <c r="Q72" s="39">
+      <c r="Q72" s="65">
         <f t="shared" ref="Q72" si="66">P72*N72</f>
         <v>18.890999999999998</v>
       </c>
-      <c r="R72" s="38"/>
-      <c r="S72" s="38"/>
+      <c r="R72" s="62"/>
+      <c r="S72" s="62"/>
     </row>
     <row r="73" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
-      <c r="B73" s="46">
+      <c r="B73" s="44">
         <f>ROW(B73) - ROW($B$9)</f>
         <v>64</v>
       </c>
-      <c r="C73" s="59" t="s">
+      <c r="C73" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="D73" s="62" t="s">
+      <c r="D73" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="E73" s="62" t="s">
-        <v>150</v>
-      </c>
-      <c r="F73" s="62" t="s">
-        <v>191</v>
-      </c>
-      <c r="G73" s="62" t="s">
-        <v>248</v>
-      </c>
-      <c r="H73" s="62" t="s">
-        <v>283</v>
-      </c>
-      <c r="I73" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J73" s="62" t="s">
-        <v>340</v>
-      </c>
-      <c r="K73" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="L73" s="62">
+      <c r="E73" s="58" t="s">
+        <v>149</v>
+      </c>
+      <c r="F73" s="58" t="s">
+        <v>190</v>
+      </c>
+      <c r="G73" s="58" t="s">
+        <v>247</v>
+      </c>
+      <c r="H73" s="58" t="s">
+        <v>282</v>
+      </c>
+      <c r="I73" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J73" s="58" t="s">
+        <v>339</v>
+      </c>
+      <c r="K73" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="L73" s="58">
         <v>1</v>
       </c>
-      <c r="M73" s="62">
+      <c r="M73" s="58">
         <f>L73*5</f>
         <v>5</v>
       </c>
-      <c r="N73" s="62">
+      <c r="N73" s="58">
         <v>10</v>
       </c>
-      <c r="O73" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P73" s="63">
+      <c r="O73" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P73" s="59">
         <v>0.10920000000000001</v>
       </c>
-      <c r="Q73" s="63">
+      <c r="Q73" s="59">
         <f>P73*N73</f>
         <v>1.0920000000000001</v>
       </c>
-      <c r="R73" s="61"/>
+      <c r="R73" s="57"/>
       <c r="S73" s="37"/>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
-      <c r="B74" s="47">
+      <c r="B74" s="45">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
       <c r="C74" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="D74" s="64" t="s">
+      <c r="D74" s="61" t="s">
         <v>84</v>
       </c>
-      <c r="E74" s="38" t="s">
-        <v>151</v>
-      </c>
-      <c r="F74" s="38" t="s">
-        <v>192</v>
-      </c>
-      <c r="G74" s="38" t="s">
-        <v>249</v>
-      </c>
-      <c r="H74" s="38" t="s">
-        <v>284</v>
-      </c>
-      <c r="I74" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J74" s="38" t="s">
-        <v>341</v>
-      </c>
-      <c r="K74" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="L74" s="38">
+      <c r="E74" s="62" t="s">
+        <v>150</v>
+      </c>
+      <c r="F74" s="62" t="s">
+        <v>191</v>
+      </c>
+      <c r="G74" s="62" t="s">
+        <v>248</v>
+      </c>
+      <c r="H74" s="62" t="s">
+        <v>283</v>
+      </c>
+      <c r="I74" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J74" s="62" t="s">
+        <v>340</v>
+      </c>
+      <c r="K74" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="L74" s="62">
         <v>4</v>
       </c>
-      <c r="M74" s="38">
+      <c r="M74" s="62">
         <f t="shared" ref="M74" si="67">L74*5</f>
         <v>20</v>
       </c>
-      <c r="N74" s="38">
+      <c r="N74" s="62">
         <v>21</v>
       </c>
-      <c r="O74" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P74" s="39">
+      <c r="O74" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P74" s="65">
         <v>7.5918999999999999</v>
       </c>
-      <c r="Q74" s="39">
+      <c r="Q74" s="65">
         <f t="shared" ref="Q74" si="68">P74*N74</f>
         <v>159.4299</v>
       </c>
-      <c r="R74" s="38"/>
-      <c r="S74" s="38"/>
+      <c r="R74" s="62"/>
+      <c r="S74" s="62"/>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
-      <c r="B75" s="46">
+      <c r="B75" s="44">
         <f>ROW(B75) - ROW($B$9)</f>
         <v>66</v>
       </c>
-      <c r="C75" s="59" t="s">
+      <c r="C75" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="D75" s="62" t="s">
-        <v>85</v>
-      </c>
-      <c r="E75" s="62" t="s">
-        <v>152</v>
-      </c>
-      <c r="F75" s="62" t="s">
-        <v>193</v>
-      </c>
-      <c r="G75" s="62" t="s">
-        <v>250</v>
-      </c>
-      <c r="H75" s="62" t="s">
-        <v>285</v>
-      </c>
-      <c r="I75" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="J75" s="62" t="s">
-        <v>342</v>
-      </c>
-      <c r="K75" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="L75" s="62">
-        <v>2</v>
-      </c>
-      <c r="M75" s="62">
+      <c r="D75" s="58" t="s">
+        <v>446</v>
+      </c>
+      <c r="E75" s="58" t="s">
+        <v>151</v>
+      </c>
+      <c r="F75" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="G75" s="58" t="s">
+        <v>249</v>
+      </c>
+      <c r="H75" s="58" t="s">
+        <v>284</v>
+      </c>
+      <c r="I75" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J75" s="58" t="s">
+        <v>341</v>
+      </c>
+      <c r="K75" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="L75" s="58">
+        <v>1</v>
+      </c>
+      <c r="M75" s="58">
         <f>L75*5</f>
-        <v>10</v>
-      </c>
-      <c r="N75" s="62">
-        <v>11</v>
-      </c>
-      <c r="O75" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P75" s="63">
+        <v>5</v>
+      </c>
+      <c r="N75" s="58">
+        <v>6</v>
+      </c>
+      <c r="O75" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P75" s="59">
         <v>0.73819999999999997</v>
       </c>
-      <c r="Q75" s="63">
+      <c r="Q75" s="59">
         <f>P75*N75</f>
-        <v>8.1202000000000005</v>
-      </c>
-      <c r="R75" s="61"/>
+        <v>4.4291999999999998</v>
+      </c>
+      <c r="R75" s="57"/>
       <c r="S75" s="37"/>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
-      <c r="B76" s="47">
+      <c r="B76" s="44"/>
+      <c r="C76" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="D76" s="37" t="s">
+        <v>447</v>
+      </c>
+      <c r="E76" s="37" t="s">
+        <v>448</v>
+      </c>
+      <c r="F76" s="37" t="s">
+        <v>449</v>
+      </c>
+      <c r="G76" s="37" t="s">
+        <v>450</v>
+      </c>
+      <c r="H76" s="37" t="s">
+        <v>284</v>
+      </c>
+      <c r="I76" s="37" t="s">
+        <v>379</v>
+      </c>
+      <c r="J76" s="37" t="s">
+        <v>451</v>
+      </c>
+      <c r="K76" s="37" t="s">
+        <v>379</v>
+      </c>
+      <c r="L76" s="37">
+        <v>1</v>
+      </c>
+      <c r="M76" s="58">
+        <f>L76*5</f>
+        <v>5</v>
+      </c>
+      <c r="N76" s="58">
+        <v>6</v>
+      </c>
+      <c r="O76" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P76" s="59">
+        <v>0.39460000000000001</v>
+      </c>
+      <c r="Q76" s="59">
+        <f>P76*N76</f>
+        <v>2.3675999999999999</v>
+      </c>
+      <c r="R76" s="57"/>
+      <c r="S76" s="37"/>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A77" s="1"/>
+      <c r="B77" s="45">
         <f t="shared" si="0"/>
-        <v>67</v>
-      </c>
-      <c r="C76" s="60" t="s">
+        <v>68</v>
+      </c>
+      <c r="C77" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="D76" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="E76" s="38" t="s">
-        <v>153</v>
-      </c>
-      <c r="F76" s="38" t="s">
-        <v>192</v>
-      </c>
-      <c r="G76" s="38" t="s">
-        <v>251</v>
-      </c>
-      <c r="H76" s="38" t="s">
-        <v>285</v>
-      </c>
-      <c r="I76" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J76" s="38" t="s">
-        <v>343</v>
-      </c>
-      <c r="K76" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="L76" s="38">
-        <v>1</v>
-      </c>
-      <c r="M76" s="38">
-        <f t="shared" ref="M76" si="69">L76*5</f>
-        <v>5</v>
-      </c>
-      <c r="N76" s="38">
-        <v>6</v>
-      </c>
-      <c r="O76" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P76" s="39">
-        <v>0.6905</v>
-      </c>
-      <c r="Q76" s="39">
-        <f t="shared" ref="Q76" si="70">P76*N76</f>
-        <v>4.1429999999999998</v>
-      </c>
-      <c r="R76" s="38"/>
-      <c r="S76" s="38"/>
-    </row>
-    <row r="77" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A77" s="1"/>
-      <c r="B77" s="46">
-        <f>ROW(B77) - ROW($B$9)</f>
-        <v>68</v>
-      </c>
-      <c r="C77" s="59" t="s">
-        <v>25</v>
-      </c>
-      <c r="D77" s="62" t="s">
-        <v>87</v>
+      <c r="D77" s="61" t="s">
+        <v>85</v>
       </c>
       <c r="E77" s="62" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F77" s="62" t="s">
-        <v>380</v>
+        <v>191</v>
       </c>
       <c r="G77" s="62" t="s">
-        <v>194</v>
+        <v>250</v>
       </c>
       <c r="H77" s="62" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I77" s="62" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J77" s="62" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="K77" s="62" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="L77" s="62">
         <v>1</v>
       </c>
       <c r="M77" s="62">
-        <f>L77*5</f>
+        <f t="shared" ref="M77" si="69">L77*5</f>
         <v>5</v>
       </c>
       <c r="N77" s="62">
         <v>6</v>
       </c>
-      <c r="O77" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P77" s="63">
+      <c r="O77" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P77" s="65">
+        <v>0.6905</v>
+      </c>
+      <c r="Q77" s="65">
+        <f t="shared" ref="Q77" si="70">P77*N77</f>
+        <v>4.1429999999999998</v>
+      </c>
+      <c r="R77" s="62"/>
+      <c r="S77" s="62"/>
+    </row>
+    <row r="78" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A78" s="1"/>
+      <c r="B78" s="44">
+        <f>ROW(B78) - ROW($B$9)</f>
+        <v>69</v>
+      </c>
+      <c r="C78" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="D78" s="58" t="s">
+        <v>86</v>
+      </c>
+      <c r="E78" s="58" t="s">
+        <v>153</v>
+      </c>
+      <c r="F78" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="G78" s="58" t="s">
+        <v>193</v>
+      </c>
+      <c r="H78" s="58" t="s">
+        <v>285</v>
+      </c>
+      <c r="I78" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J78" s="58" t="s">
+        <v>343</v>
+      </c>
+      <c r="K78" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="L78" s="58">
+        <v>1</v>
+      </c>
+      <c r="M78" s="58">
+        <f>L78*5</f>
+        <v>5</v>
+      </c>
+      <c r="N78" s="58">
+        <v>6</v>
+      </c>
+      <c r="O78" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P78" s="59">
         <v>20.79</v>
       </c>
-      <c r="Q77" s="63">
-        <f>P77*N77</f>
+      <c r="Q78" s="59">
+        <f>P78*N78</f>
         <v>124.74</v>
       </c>
-      <c r="R77" s="61"/>
-      <c r="S77" s="37"/>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A78" s="1"/>
-      <c r="B78" s="47">
-        <f t="shared" si="0"/>
-        <v>69</v>
-      </c>
-      <c r="C78" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="D78" s="64" t="s">
-        <v>88</v>
-      </c>
-      <c r="E78" s="38" t="s">
-        <v>155</v>
-      </c>
-      <c r="F78" s="38" t="s">
-        <v>195</v>
-      </c>
-      <c r="G78" s="38" t="s">
-        <v>252</v>
-      </c>
-      <c r="H78" s="38" t="s">
-        <v>287</v>
-      </c>
-      <c r="I78" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J78" s="38" t="s">
-        <v>345</v>
-      </c>
-      <c r="K78" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="L78" s="38">
-        <v>1</v>
-      </c>
-      <c r="M78" s="38">
-        <f t="shared" ref="M78" si="71">L78*5</f>
-        <v>5</v>
-      </c>
-      <c r="N78" s="38">
-        <v>6</v>
-      </c>
-      <c r="O78" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P78" s="39">
-        <v>11.400499999999999</v>
-      </c>
-      <c r="Q78" s="39">
-        <f t="shared" ref="Q78" si="72">P78*N78</f>
-        <v>68.402999999999992</v>
-      </c>
-      <c r="R78" s="38"/>
-      <c r="S78" s="38"/>
+      <c r="R78" s="57"/>
+      <c r="S78" s="37"/>
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
-      <c r="B79" s="46">
-        <f>ROW(B79) - ROW($B$9)</f>
+      <c r="B79" s="45">
+        <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="C79" s="59" t="s">
+      <c r="C79" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="D79" s="62" t="s">
-        <v>89</v>
+      <c r="D79" s="61" t="s">
+        <v>87</v>
       </c>
       <c r="E79" s="62" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F79" s="62" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G79" s="62" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H79" s="62" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="I79" s="62" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J79" s="62" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K79" s="62" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="L79" s="62">
         <v>1</v>
       </c>
       <c r="M79" s="62">
-        <f>L79*5</f>
+        <f t="shared" ref="M79" si="71">L79*5</f>
         <v>5</v>
       </c>
       <c r="N79" s="62">
         <v>6</v>
       </c>
-      <c r="O79" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="P79" s="63">
+      <c r="O79" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P79" s="65">
+        <v>11.400499999999999</v>
+      </c>
+      <c r="Q79" s="65">
+        <f t="shared" ref="Q79" si="72">P79*N79</f>
+        <v>68.402999999999992</v>
+      </c>
+      <c r="R79" s="62"/>
+      <c r="S79" s="62"/>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A80" s="1"/>
+      <c r="B80" s="44">
+        <f>ROW(B80) - ROW($B$9)</f>
+        <v>71</v>
+      </c>
+      <c r="C80" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="D80" s="58" t="s">
+        <v>88</v>
+      </c>
+      <c r="E80" s="58" t="s">
+        <v>155</v>
+      </c>
+      <c r="F80" s="58" t="s">
+        <v>195</v>
+      </c>
+      <c r="G80" s="58" t="s">
+        <v>252</v>
+      </c>
+      <c r="H80" s="58" t="s">
+        <v>287</v>
+      </c>
+      <c r="I80" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="J80" s="58" t="s">
+        <v>345</v>
+      </c>
+      <c r="K80" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="L80" s="58">
+        <v>1</v>
+      </c>
+      <c r="M80" s="58">
+        <f>L80*5</f>
+        <v>5</v>
+      </c>
+      <c r="N80" s="58">
+        <v>6</v>
+      </c>
+      <c r="O80" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="P80" s="59">
         <v>2.8128000000000002</v>
       </c>
-      <c r="Q79" s="63">
-        <f>P79*N79</f>
+      <c r="Q80" s="59">
+        <f>P80*N80</f>
         <v>16.876800000000003</v>
       </c>
-      <c r="R79" s="61"/>
-      <c r="S79" s="37"/>
-    </row>
-    <row r="80" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A80" s="1"/>
-      <c r="B80" s="47">
-        <f t="shared" si="0"/>
-        <v>71</v>
-      </c>
-      <c r="C80" s="60" t="s">
-        <v>26</v>
-      </c>
-      <c r="D80" s="64" t="s">
-        <v>90</v>
-      </c>
-      <c r="E80" s="38" t="s">
-        <v>157</v>
-      </c>
-      <c r="F80" s="38" t="s">
-        <v>197</v>
-      </c>
-      <c r="G80" s="38" t="s">
-        <v>254</v>
-      </c>
-      <c r="H80" s="38" t="s">
-        <v>289</v>
-      </c>
-      <c r="I80" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J80" s="38" t="s">
-        <v>347</v>
-      </c>
-      <c r="K80" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="L80" s="38">
-        <v>1</v>
-      </c>
-      <c r="M80" s="38">
-        <f t="shared" ref="M80:M83" si="73">L80*5</f>
-        <v>5</v>
-      </c>
-      <c r="N80" s="38">
-        <v>10</v>
-      </c>
-      <c r="O80" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P80" s="39">
-        <v>8.3400000000000002E-2</v>
-      </c>
-      <c r="Q80" s="39">
-        <f t="shared" ref="Q80" si="74">P80*N80</f>
-        <v>0.83400000000000007</v>
-      </c>
-      <c r="R80" s="38"/>
-      <c r="S80" s="38"/>
-    </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R80" s="57"/>
+      <c r="S80" s="37"/>
+    </row>
+    <row r="81" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
-      <c r="B81" s="47">
+      <c r="B81" s="45">
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="C81" s="72" t="s">
+      <c r="C81" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="D81" s="61" t="s">
+        <v>89</v>
+      </c>
+      <c r="E81" s="62" t="s">
+        <v>156</v>
+      </c>
+      <c r="F81" s="62" t="s">
+        <v>196</v>
+      </c>
+      <c r="G81" s="62" t="s">
+        <v>253</v>
+      </c>
+      <c r="H81" s="62" t="s">
+        <v>288</v>
+      </c>
+      <c r="I81" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J81" s="62" t="s">
+        <v>346</v>
+      </c>
+      <c r="K81" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="L81" s="62">
+        <v>1</v>
+      </c>
+      <c r="M81" s="62">
+        <f t="shared" ref="M81:M84" si="73">L81*5</f>
+        <v>5</v>
+      </c>
+      <c r="N81" s="62">
+        <v>10</v>
+      </c>
+      <c r="O81" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P81" s="65">
+        <v>8.3400000000000002E-2</v>
+      </c>
+      <c r="Q81" s="65">
+        <f t="shared" ref="Q81" si="74">P81*N81</f>
+        <v>0.83400000000000007</v>
+      </c>
+      <c r="R81" s="62"/>
+      <c r="S81" s="62"/>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A82" s="1"/>
+      <c r="B82" s="45">
+        <f t="shared" si="0"/>
+        <v>73</v>
+      </c>
+      <c r="C82" s="60" t="s">
+        <v>433</v>
+      </c>
+      <c r="D82" s="71" t="s">
+        <v>438</v>
+      </c>
+      <c r="E82" s="62" t="s">
+        <v>437</v>
+      </c>
+      <c r="F82" s="62" t="s">
+        <v>391</v>
+      </c>
+      <c r="G82" s="62" t="s">
         <v>434</v>
       </c>
-      <c r="D81" s="83" t="s">
-        <v>439</v>
-      </c>
-      <c r="E81" s="74" t="s">
-        <v>438</v>
-      </c>
-      <c r="F81" s="74" t="s">
-        <v>392</v>
-      </c>
-      <c r="G81" s="74" t="s">
+      <c r="H82" s="62" t="s">
+        <v>436</v>
+      </c>
+      <c r="I82" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J82" s="62" t="s">
         <v>435</v>
       </c>
-      <c r="H81" s="74" t="s">
-        <v>437</v>
-      </c>
-      <c r="I81" s="74" t="s">
-        <v>380</v>
-      </c>
-      <c r="J81" s="74" t="s">
-        <v>436</v>
-      </c>
-      <c r="K81" s="74" t="s">
-        <v>380</v>
-      </c>
-      <c r="L81" s="74">
+      <c r="K82" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="L82" s="62">
         <v>1</v>
       </c>
-      <c r="M81" s="74">
+      <c r="M82" s="62">
         <f t="shared" si="73"/>
         <v>5</v>
       </c>
-      <c r="N81" s="74">
+      <c r="N82" s="62">
         <v>6</v>
       </c>
-      <c r="O81" s="76" t="s">
-        <v>393</v>
-      </c>
-      <c r="P81" s="77">
+      <c r="O82" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P82" s="65">
         <v>1.5643</v>
       </c>
-      <c r="Q81" s="77">
-        <f>P81*N81</f>
+      <c r="Q82" s="65">
+        <f>P82*N82</f>
         <v>9.3857999999999997</v>
       </c>
-      <c r="R81" s="74"/>
-      <c r="S81" s="74"/>
-    </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A82" s="1"/>
-      <c r="B82" s="47">
-        <f t="shared" ref="B82:B83" si="75">ROW(B82) - ROW($B$9)</f>
-        <v>73</v>
-      </c>
-      <c r="C82" s="60" t="s">
-        <v>434</v>
-      </c>
-      <c r="D82" s="84" t="s">
+      <c r="R82" s="62"/>
+      <c r="S82" s="62"/>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A83" s="1"/>
+      <c r="B83" s="45">
+        <f t="shared" ref="B83:B84" si="75">ROW(B83) - ROW($B$9)</f>
+        <v>74</v>
+      </c>
+      <c r="C83" s="60" t="s">
+        <v>433</v>
+      </c>
+      <c r="D83" s="71" t="s">
+        <v>438</v>
+      </c>
+      <c r="E83" s="62" t="s">
+        <v>441</v>
+      </c>
+      <c r="F83" s="62" t="s">
+        <v>391</v>
+      </c>
+      <c r="G83" s="62" t="s">
         <v>439</v>
       </c>
-      <c r="E82" s="38" t="s">
-        <v>442</v>
-      </c>
-      <c r="F82" s="38" t="s">
-        <v>392</v>
-      </c>
-      <c r="G82" s="38" t="s">
+      <c r="H83" s="62" t="s">
+        <v>436</v>
+      </c>
+      <c r="I83" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J83" s="62" t="s">
         <v>440</v>
       </c>
-      <c r="H82" s="38" t="s">
-        <v>437</v>
-      </c>
-      <c r="I82" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="J82" s="38" t="s">
-        <v>441</v>
-      </c>
-      <c r="K82" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="L82" s="38">
+      <c r="K83" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="L83" s="62">
         <v>1</v>
       </c>
-      <c r="M82" s="38">
+      <c r="M83" s="62">
         <f t="shared" si="73"/>
         <v>5</v>
       </c>
-      <c r="N82" s="38">
+      <c r="N83" s="62">
         <v>6</v>
       </c>
-      <c r="O82" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="P82" s="39">
+      <c r="O83" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P83" s="65">
         <v>2.0146999999999999</v>
       </c>
-      <c r="Q82" s="39">
-        <f>P82*N82</f>
+      <c r="Q83" s="65">
+        <f>P83*N83</f>
         <v>12.088200000000001</v>
       </c>
-      <c r="R82" s="38"/>
-      <c r="S82" s="38"/>
-    </row>
-    <row r="83" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="1"/>
-      <c r="B83" s="47">
+      <c r="R83" s="62"/>
+      <c r="S83" s="62"/>
+    </row>
+    <row r="84" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="1"/>
+      <c r="B84" s="45">
         <f t="shared" si="75"/>
-        <v>74</v>
-      </c>
-      <c r="C83" s="72" t="s">
-        <v>434</v>
-      </c>
-      <c r="D83" s="83" t="s">
-        <v>439</v>
-      </c>
-      <c r="E83" s="74" t="s">
+        <v>75</v>
+      </c>
+      <c r="C84" s="60" t="s">
+        <v>433</v>
+      </c>
+      <c r="D84" s="71" t="s">
+        <v>438</v>
+      </c>
+      <c r="E84" s="62" t="s">
+        <v>443</v>
+      </c>
+      <c r="F84" s="62" t="s">
+        <v>391</v>
+      </c>
+      <c r="G84" s="62" t="s">
+        <v>442</v>
+      </c>
+      <c r="H84" s="62" t="s">
+        <v>436</v>
+      </c>
+      <c r="I84" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="J84" s="62" t="s">
         <v>444</v>
       </c>
-      <c r="F83" s="74" t="s">
-        <v>392</v>
-      </c>
-      <c r="G83" s="74" t="s">
-        <v>443</v>
-      </c>
-      <c r="H83" s="74" t="s">
-        <v>437</v>
-      </c>
-      <c r="I83" s="74" t="s">
-        <v>380</v>
-      </c>
-      <c r="J83" s="74" t="s">
-        <v>445</v>
-      </c>
-      <c r="K83" s="74" t="s">
-        <v>380</v>
-      </c>
-      <c r="L83" s="74">
+      <c r="K84" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="L84" s="62">
         <v>1</v>
       </c>
-      <c r="M83" s="74">
+      <c r="M84" s="62">
         <f t="shared" si="73"/>
         <v>5</v>
       </c>
-      <c r="N83" s="74">
+      <c r="N84" s="62">
         <v>6</v>
       </c>
-      <c r="O83" s="76" t="s">
-        <v>393</v>
-      </c>
-      <c r="P83" s="77">
+      <c r="O84" s="64" t="s">
+        <v>392</v>
+      </c>
+      <c r="P84" s="65">
         <v>0.80110000000000003</v>
       </c>
-      <c r="Q83" s="77">
-        <f>P83*N83</f>
+      <c r="Q84" s="65">
+        <f>P84*N84</f>
         <v>4.8066000000000004</v>
       </c>
-      <c r="R83" s="74"/>
-      <c r="S83" s="74"/>
-    </row>
-    <row r="84" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="1"/>
-      <c r="B84" s="40"/>
-      <c r="C84" s="41"/>
-      <c r="D84" s="42"/>
-      <c r="E84" s="43"/>
-      <c r="F84" s="44"/>
-      <c r="G84" s="45"/>
-      <c r="H84" s="44"/>
-      <c r="I84" s="45"/>
-      <c r="J84" s="44"/>
-      <c r="K84" s="45"/>
-      <c r="L84" s="45"/>
-      <c r="M84" s="45"/>
-      <c r="N84" s="96" t="s">
-        <v>5</v>
-      </c>
-      <c r="O84" s="97"/>
-      <c r="P84" s="97"/>
-      <c r="Q84" s="48">
-        <f>SUM(Q10:Q83)</f>
-        <v>703.76769999999999</v>
-      </c>
-      <c r="R84" s="92"/>
-      <c r="S84" s="93"/>
+      <c r="R84" s="62"/>
+      <c r="S84" s="62"/>
     </row>
     <row r="85" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
-      <c r="B85" s="25"/>
-      <c r="C85" s="36"/>
-      <c r="D85" s="9"/>
-      <c r="E85" s="10"/>
-      <c r="F85" s="10"/>
-      <c r="G85" s="10"/>
-      <c r="H85" s="10"/>
-      <c r="I85" s="10"/>
-      <c r="J85" s="10"/>
-      <c r="K85" s="10"/>
-      <c r="L85" s="10"/>
-      <c r="M85" s="10"/>
-      <c r="N85" s="96" t="s">
+      <c r="B85" s="38"/>
+      <c r="C85" s="39"/>
+      <c r="D85" s="40"/>
+      <c r="E85" s="41"/>
+      <c r="F85" s="42"/>
+      <c r="G85" s="43"/>
+      <c r="H85" s="42"/>
+      <c r="I85" s="43"/>
+      <c r="J85" s="42"/>
+      <c r="K85" s="43"/>
+      <c r="L85" s="43"/>
+      <c r="M85" s="43"/>
+      <c r="N85" s="80" t="s">
+        <v>5</v>
+      </c>
+      <c r="O85" s="81"/>
+      <c r="P85" s="81"/>
+      <c r="Q85" s="46">
+        <f>SUM(Q10:Q84)</f>
+        <v>702.44429999999988</v>
+      </c>
+      <c r="R85" s="76"/>
+      <c r="S85" s="77"/>
+    </row>
+    <row r="86" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="1"/>
+      <c r="B86" s="25"/>
+      <c r="C86" s="36"/>
+      <c r="D86" s="9"/>
+      <c r="E86" s="10"/>
+      <c r="F86" s="10"/>
+      <c r="G86" s="10"/>
+      <c r="H86" s="10"/>
+      <c r="I86" s="10"/>
+      <c r="J86" s="10"/>
+      <c r="K86" s="10"/>
+      <c r="L86" s="10"/>
+      <c r="M86" s="10"/>
+      <c r="N86" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="O85" s="97"/>
-      <c r="P85" s="97"/>
-      <c r="Q85" s="49">
-        <f>Q84/5</f>
-        <v>140.75353999999999</v>
-      </c>
-      <c r="R85" s="94"/>
-      <c r="S85" s="95"/>
+      <c r="O86" s="81"/>
+      <c r="P86" s="81"/>
+      <c r="Q86" s="47">
+        <f>Q85/5</f>
+        <v>140.48885999999999</v>
+      </c>
+      <c r="R86" s="78"/>
+      <c r="S86" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R84:S85"/>
-    <mergeCell ref="N84:P84"/>
+    <mergeCell ref="R85:S86"/>
     <mergeCell ref="N85:P85"/>
+    <mergeCell ref="N86:P86"/>
   </mergeCells>
   <phoneticPr fontId="27" type="noConversion"/>
   <hyperlinks>
@@ -7003,11 +7026,11 @@
     <hyperlink ref="O73" r:id="rId54" xr:uid="{749C77DE-6558-4DB6-8849-7A73C148D4CE}"/>
     <hyperlink ref="O74" r:id="rId55" xr:uid="{5FBFDDE4-D8E1-4DDC-8314-D97DA5D132A5}"/>
     <hyperlink ref="O75" r:id="rId56" xr:uid="{FD33955C-3AAA-49E7-ADBD-08C8E8316B63}"/>
-    <hyperlink ref="O76" r:id="rId57" xr:uid="{10F92991-AF57-4F4E-ACEC-133226566204}"/>
-    <hyperlink ref="O77" r:id="rId58" xr:uid="{6027C0A4-5D1E-4433-85BF-CD2F57D6DA89}"/>
-    <hyperlink ref="O78" r:id="rId59" xr:uid="{29DDBCD9-DE51-47A5-B3C6-827913DA2387}"/>
-    <hyperlink ref="O79" r:id="rId60" xr:uid="{FC388204-E09E-47D1-A054-C8455D575E2E}"/>
-    <hyperlink ref="O80" r:id="rId61" xr:uid="{C573F08C-CF21-426E-B62B-392C975BBEB8}"/>
+    <hyperlink ref="O77" r:id="rId57" xr:uid="{10F92991-AF57-4F4E-ACEC-133226566204}"/>
+    <hyperlink ref="O78" r:id="rId58" xr:uid="{6027C0A4-5D1E-4433-85BF-CD2F57D6DA89}"/>
+    <hyperlink ref="O79" r:id="rId59" xr:uid="{29DDBCD9-DE51-47A5-B3C6-827913DA2387}"/>
+    <hyperlink ref="O80" r:id="rId60" xr:uid="{FC388204-E09E-47D1-A054-C8455D575E2E}"/>
+    <hyperlink ref="O81" r:id="rId61" xr:uid="{C573F08C-CF21-426E-B62B-392C975BBEB8}"/>
     <hyperlink ref="O24" r:id="rId62" xr:uid="{A2463247-A92E-46A4-B1F2-C7859F430396}"/>
     <hyperlink ref="O12" r:id="rId63" xr:uid="{8C42F702-13DB-4B89-BA91-C5903624B455}"/>
     <hyperlink ref="O17" r:id="rId64" xr:uid="{71295E9A-7059-4DB8-9A46-8806E333672F}"/>
@@ -7015,13 +7038,14 @@
     <hyperlink ref="O36" r:id="rId66" xr:uid="{696C55EA-352D-4A6D-AE88-F7D6577A10B8}"/>
     <hyperlink ref="O20" r:id="rId67" xr:uid="{F67ACF00-C62E-4EB8-A65F-317350E7C6CF}"/>
     <hyperlink ref="O48" r:id="rId68" xr:uid="{B72543AB-3101-4A9B-892E-15300936BBF9}"/>
-    <hyperlink ref="O81" r:id="rId69" xr:uid="{387305BF-5056-46E6-9C42-81E1A79E261A}"/>
-    <hyperlink ref="O82" r:id="rId70" xr:uid="{EB956738-249B-40D1-8C80-EEE1E1ED8710}"/>
-    <hyperlink ref="O83" r:id="rId71" xr:uid="{6864A1C4-75C3-4A42-AD86-1617EF24C777}"/>
+    <hyperlink ref="O82" r:id="rId69" xr:uid="{387305BF-5056-46E6-9C42-81E1A79E261A}"/>
+    <hyperlink ref="O83" r:id="rId70" xr:uid="{EB956738-249B-40D1-8C80-EEE1E1ED8710}"/>
+    <hyperlink ref="O84" r:id="rId71" xr:uid="{6864A1C4-75C3-4A42-AD86-1617EF24C777}"/>
     <hyperlink ref="O40" r:id="rId72" xr:uid="{B317581D-06A6-4EB4-891A-C0C139D8E474}"/>
+    <hyperlink ref="O76" r:id="rId73" xr:uid="{15F91159-E821-434C-89D0-043DAE667696}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId73"/>
-  <drawing r:id="rId74"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId74"/>
+  <drawing r:id="rId75"/>
 </worksheet>
 </file>
--- a/BOM/eSpark-BOM.xlsx
+++ b/BOM/eSpark-BOM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="484">
   <si>
     <t>Component list</t>
   </si>
@@ -1469,6 +1469,9 @@
   </si>
   <si>
     <t>C492441</t>
+  </si>
+  <si>
+    <t>Cx3, Cx4</t>
   </si>
 </sst>
 </file>
@@ -8393,7 +8396,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="62" t="s">
-        <v>445</v>
+        <v>483</v>
       </c>
       <c r="E21" s="62" t="s">
         <v>446</v>
@@ -9445,7 +9448,7 @@
       <c r="R39" s="57"/>
       <c r="S39" s="37"/>
     </row>
-    <row r="40" spans="1:19" s="77" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" s="77" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A40" s="75"/>
       <c r="B40" s="45">
         <f t="shared" si="0"/>
@@ -10117,7 +10120,7 @@
       </c>
       <c r="S51" s="68"/>
     </row>
-    <row r="52" spans="1:19" s="77" customFormat="1" ht="72" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" s="77" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A52" s="75"/>
       <c r="B52" s="45">
         <f t="shared" si="0"/>
@@ -11181,7 +11184,7 @@
       <c r="R70" s="62"/>
       <c r="S70" s="62"/>
     </row>
-    <row r="71" spans="1:19" s="77" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A71" s="75"/>
       <c r="B71" s="44">
         <f>ROW(B71) - ROW($B$9)</f>
@@ -12021,7 +12024,7 @@
       <c r="R85" s="62"/>
       <c r="S85" s="74"/>
     </row>
-    <row r="86" spans="1:19" s="77" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19" s="77" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A86" s="75"/>
       <c r="B86" s="45">
         <f t="shared" si="0"/>

--- a/BOM/eSpark-BOM.xlsx
+++ b/BOM/eSpark-BOM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1674" uniqueCount="483">
   <si>
     <t>Component list</t>
   </si>
@@ -187,9 +187,6 @@
     <t>L3</t>
   </si>
   <si>
-    <t>LED7</t>
-  </si>
-  <si>
     <t>P1, P2, P3, P4, P5, P6</t>
   </si>
   <si>
@@ -247,9 +244,6 @@
     <t>R48</t>
   </si>
   <si>
-    <t>SB1, SB2</t>
-  </si>
-  <si>
     <t>SW1</t>
   </si>
   <si>
@@ -379,9 +373,6 @@
     <t>Yellow-Green 572nm LED Indication - Discrete 2.05V 0603 (1608 Metric)</t>
   </si>
   <si>
-    <t>ZIO QWIIC 1.5INCH OLED DISPLAY</t>
-  </si>
-  <si>
     <t>Test Point ON</t>
   </si>
   <si>
@@ -550,9 +541,6 @@
     <t>LED-0603</t>
   </si>
   <si>
-    <t>ZIO-101954</t>
-  </si>
-  <si>
     <t>Test-point</t>
   </si>
   <si>
@@ -829,9 +817,6 @@
     <t>Everlight Elec</t>
   </si>
   <si>
-    <t>Smart Prototyping</t>
-  </si>
-  <si>
     <t>TECH PUBLIC</t>
   </si>
   <si>
@@ -1348,9 +1333,6 @@
     <t>C53434</t>
   </si>
   <si>
-    <t>C2, C7, C9, C10, C12, C13, C19, C20, C21, C22, C29, C30, C31, C32, C33, C34, C35, C37, C40, C41, C44, C45, C46, C47, C48, C49, C51, C54, C56, C57</t>
-  </si>
-  <si>
     <t>C4, C6, C36</t>
   </si>
   <si>
@@ -1372,9 +1354,6 @@
     <t>2.2uF</t>
   </si>
   <si>
-    <t>LED10</t>
-  </si>
-  <si>
     <t>R3, R8, R9, R12, R13, R14, R15, R18, R19, R24, R38, R39, R40, R49</t>
   </si>
   <si>
@@ -1472,6 +1451,25 @@
   </si>
   <si>
     <t>Cx3, Cx4</t>
+  </si>
+  <si>
+    <t>OLED7</t>
+  </si>
+  <si>
+    <t>OLED10</t>
+  </si>
+  <si>
+    <t>C2, C7, C9, C10, C12, C13, C19, C20, C21, C22, C29, C30, C31, C32, C33, C34, C35, C37, C40, C41, C44, C45, C46, C47, C48, C49, C51, C54, Cx1, Cx2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54mm Plugin 3A bronze -40℃~+105℃ Straight 1x4P Top 4 Square Holes Plugin,P=2.54mm Female Headers ROHS
+</t>
+  </si>
+  <si>
+    <t>C2718488</t>
+  </si>
+  <si>
+    <t>BOOMELE</t>
   </si>
 </sst>
 </file>
@@ -2676,7 +2674,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="48" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2701,7 +2699,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="49" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2726,7 +2724,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="50" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2842,49 +2840,49 @@
         <v>27</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F9" s="52" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="H9" s="52" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>369</v>
+      </c>
+      <c r="J9" s="52" t="s">
+        <v>276</v>
+      </c>
+      <c r="K9" s="53" t="s">
+        <v>370</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>365</v>
+      </c>
+      <c r="M9" s="54" t="s">
         <v>374</v>
       </c>
-      <c r="J9" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="K9" s="53" t="s">
+      <c r="N9" s="52" t="s">
         <v>375</v>
       </c>
-      <c r="L9" s="30" t="s">
-        <v>370</v>
-      </c>
-      <c r="M9" s="54" t="s">
-        <v>379</v>
-      </c>
-      <c r="N9" s="52" t="s">
-        <v>380</v>
-      </c>
       <c r="O9" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="P9" s="52" t="s">
         <v>376</v>
       </c>
-      <c r="P9" s="52" t="s">
-        <v>381</v>
-      </c>
       <c r="Q9" s="30" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="R9" s="52" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="S9" s="30" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -2897,28 +2895,28 @@
         <v>9</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="L10" s="37">
         <v>3</v>
@@ -2931,7 +2929,7 @@
         <v>20</v>
       </c>
       <c r="O10" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P10" s="72">
         <v>0.15939999999999999</v>
@@ -2952,29 +2950,29 @@
       <c r="C11" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="62" t="s">
-        <v>442</v>
+      <c r="D11" s="61" t="s">
+        <v>479</v>
       </c>
       <c r="E11" s="62" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F11" s="62" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G11" s="63" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="H11" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I11" s="62" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="J11" s="62" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="K11" s="62" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="L11" s="62">
         <v>30</v>
@@ -2987,7 +2985,7 @@
         <v>200</v>
       </c>
       <c r="O11" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P11" s="65">
         <v>1.04E-2</v>
@@ -3012,25 +3010,25 @@
         <v>28</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="H12" s="58" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="I12" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J12" s="58" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="K12" s="58" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="L12" s="58">
         <v>2</v>
@@ -3043,7 +3041,7 @@
         <v>20</v>
       </c>
       <c r="O12" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P12" s="59">
         <v>6.2E-2</v>
@@ -3065,28 +3063,28 @@
         <v>9</v>
       </c>
       <c r="D13" s="62" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="E13" s="62" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F13" s="62" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G13" s="62" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H13" s="62" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="I13" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J13" s="62" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="K13" s="62" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="L13" s="62">
         <v>3</v>
@@ -3099,7 +3097,7 @@
         <v>17</v>
       </c>
       <c r="O13" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P13" s="65">
         <v>0.49540000000000001</v>
@@ -3124,25 +3122,25 @@
         <v>29</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F14" s="58" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G14" s="58" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="H14" s="58" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="I14" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J14" s="58" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="K14" s="58" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="L14" s="58">
         <v>1</v>
@@ -3155,7 +3153,7 @@
         <v>6</v>
       </c>
       <c r="O14" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P14" s="59">
         <v>0.91320000000000001</v>
@@ -3180,25 +3178,25 @@
         <v>30</v>
       </c>
       <c r="E15" s="62" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F15" s="62" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G15" s="62" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H15" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I15" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J15" s="62" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="K15" s="62" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="L15" s="62">
         <v>12</v>
@@ -3211,7 +3209,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P15" s="65">
         <v>2.8E-3</v>
@@ -3233,28 +3231,28 @@
         <v>9</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="E16" s="58" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F16" s="58" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G16" s="58" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H16" s="58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I16" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J16" s="58" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="K16" s="58" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="L16" s="58">
         <v>2</v>
@@ -3267,7 +3265,7 @@
         <v>100</v>
       </c>
       <c r="O16" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P16" s="59">
         <v>4.8999999999999998E-3</v>
@@ -3292,25 +3290,25 @@
         <v>31</v>
       </c>
       <c r="E17" s="62" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F17" s="62" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G17" s="63" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="H17" s="62" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="I17" s="62" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="J17" s="62" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="K17" s="62" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="L17" s="62">
         <v>1</v>
@@ -3323,7 +3321,7 @@
         <v>100</v>
       </c>
       <c r="O17" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P17" s="65">
         <v>1.2999999999999999E-3</v>
@@ -3348,25 +3346,25 @@
         <v>32</v>
       </c>
       <c r="E18" s="58" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F18" s="58" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G18" s="58" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="H18" s="58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I18" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J18" s="58" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="K18" s="58" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="L18" s="58">
         <v>2</v>
@@ -3379,7 +3377,7 @@
         <v>100</v>
       </c>
       <c r="O18" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P18" s="59">
         <v>2.8999999999999998E-3</v>
@@ -3401,28 +3399,28 @@
         <v>9</v>
       </c>
       <c r="D19" s="61" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E19" s="62" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F19" s="62" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G19" s="62" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="H19" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I19" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J19" s="62" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="K19" s="62" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="L19" s="62">
         <v>2</v>
@@ -3435,7 +3433,7 @@
         <v>20</v>
       </c>
       <c r="O19" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P19" s="65">
         <v>2.3599999999999999E-2</v>
@@ -3457,28 +3455,28 @@
         <v>9</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J20" s="37" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="K20" s="37" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="L20" s="37">
         <v>1</v>
@@ -3491,7 +3489,7 @@
         <v>6</v>
       </c>
       <c r="O20" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P20" s="72">
         <v>0.51590000000000003</v>
@@ -3512,28 +3510,28 @@
         <v>9</v>
       </c>
       <c r="D21" s="62" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="E21" s="62" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="F21" s="62" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G21" s="62" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="H21" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I21" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J21" s="62" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="K21" s="62" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="L21" s="62">
         <v>2</v>
@@ -3546,7 +3544,7 @@
         <v>100</v>
       </c>
       <c r="O21" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P21" s="72">
         <v>3.2399999999999998E-2</v>
@@ -3571,23 +3569,23 @@
         <v>33</v>
       </c>
       <c r="E22" s="58" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F22" s="58" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G22" s="58" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="H22" s="58" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I22" s="58"/>
       <c r="J22" s="58" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="K22" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L22" s="58">
         <v>7</v>
@@ -3600,7 +3598,7 @@
         <v>40</v>
       </c>
       <c r="O22" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P22" s="59">
         <v>6.3700000000000007E-2</v>
@@ -3625,25 +3623,25 @@
         <v>34</v>
       </c>
       <c r="E23" s="62" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F23" s="62" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G23" s="62" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H23" s="62" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="I23" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J23" s="62" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="K23" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L23" s="62">
         <v>2</v>
@@ -3656,7 +3654,7 @@
         <v>15</v>
       </c>
       <c r="O23" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P23" s="65">
         <v>8.6400000000000005E-2</v>
@@ -3681,25 +3679,25 @@
         <v>35</v>
       </c>
       <c r="E24" s="58" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F24" s="58" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G24" s="58" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="H24" s="58" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="I24" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J24" s="58" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="K24" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L24" s="58">
         <v>1</v>
@@ -3712,7 +3710,7 @@
         <v>20</v>
       </c>
       <c r="O24" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P24" s="59">
         <v>3.32E-2</v>
@@ -3737,25 +3735,25 @@
         <v>36</v>
       </c>
       <c r="E25" s="62" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F25" s="62" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="G25" s="62" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="H25" s="62" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="I25" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J25" s="62" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="K25" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L25" s="62">
         <v>1</v>
@@ -3768,7 +3766,7 @@
         <v>20</v>
       </c>
       <c r="O25" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P25" s="65">
         <v>3.6200000000000003E-2</v>
@@ -3793,25 +3791,25 @@
         <v>37</v>
       </c>
       <c r="E26" s="58" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F26" s="58" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G26" s="58" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="H26" s="58" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I26" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J26" s="58" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="K26" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L26" s="58">
         <v>8</v>
@@ -3824,7 +3822,7 @@
         <v>60</v>
       </c>
       <c r="O26" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P26" s="59">
         <v>2.0400000000000001E-2</v>
@@ -3849,25 +3847,25 @@
         <v>38</v>
       </c>
       <c r="E27" s="62" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F27" s="62" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G27" s="62" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H27" s="62" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="I27" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J27" s="62" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="K27" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L27" s="62">
         <v>1</v>
@@ -3880,7 +3878,7 @@
         <v>10</v>
       </c>
       <c r="O27" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P27" s="65">
         <v>0.104</v>
@@ -3905,25 +3903,25 @@
         <v>39</v>
       </c>
       <c r="E28" s="58" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F28" s="58" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G28" s="58" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="H28" s="58" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I28" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J28" s="58" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="K28" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L28" s="58">
         <v>3</v>
@@ -3936,7 +3934,7 @@
         <v>20</v>
       </c>
       <c r="O28" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P28" s="59">
         <v>3.1699999999999999E-2</v>
@@ -3961,25 +3959,25 @@
         <v>40</v>
       </c>
       <c r="E29" s="62" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F29" s="62" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G29" s="62" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="H29" s="62" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="I29" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J29" s="62" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="K29" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L29" s="62">
         <v>1</v>
@@ -3992,7 +3990,7 @@
         <v>10</v>
       </c>
       <c r="O29" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P29" s="65">
         <v>3.5400000000000001E-2</v>
@@ -4017,25 +4015,25 @@
         <v>41</v>
       </c>
       <c r="E30" s="58" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F30" s="58" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G30" s="58" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="H30" s="58" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="I30" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J30" s="58" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="K30" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L30" s="58">
         <v>5</v>
@@ -4048,7 +4046,7 @@
         <v>50</v>
       </c>
       <c r="O30" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P30" s="59">
         <v>1.7999999999999999E-2</v>
@@ -4073,25 +4071,25 @@
         <v>42</v>
       </c>
       <c r="E31" s="62" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F31" s="62" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G31" s="62" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H31" s="62" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I31" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J31" s="62" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="K31" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L31" s="62">
         <v>1</v>
@@ -4104,7 +4102,7 @@
         <v>6</v>
       </c>
       <c r="O31" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P31" s="65">
         <v>0.2319</v>
@@ -4129,25 +4127,25 @@
         <v>43</v>
       </c>
       <c r="E32" s="58" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F32" s="58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G32" s="58" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="H32" s="58" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I32" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J32" s="58" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="K32" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L32" s="58">
         <v>2</v>
@@ -4160,7 +4158,7 @@
         <v>20</v>
       </c>
       <c r="O32" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P32" s="59">
         <v>4.5900000000000003E-2</v>
@@ -4185,25 +4183,25 @@
         <v>44</v>
       </c>
       <c r="E33" s="62" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F33" s="62" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G33" s="62" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H33" s="62" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="I33" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J33" s="62" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="K33" s="62" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="L33" s="62">
         <v>1</v>
@@ -4216,7 +4214,7 @@
         <v>10</v>
       </c>
       <c r="O33" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P33" s="65">
         <v>0.1193</v>
@@ -4241,25 +4239,25 @@
         <v>45</v>
       </c>
       <c r="E34" s="58" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F34" s="58" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G34" s="58" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="H34" s="58" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="I34" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J34" s="58" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="K34" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L34" s="58">
         <v>8</v>
@@ -4272,7 +4270,7 @@
         <v>50</v>
       </c>
       <c r="O34" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P34" s="59">
         <v>4.5600000000000002E-2</v>
@@ -4294,28 +4292,28 @@
         <v>13</v>
       </c>
       <c r="D35" s="62" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="E35" s="62" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="F35" s="62" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="G35" s="62" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="H35" s="62" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="I35" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J35" s="62" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="K35" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L35" s="62">
         <v>1</v>
@@ -4328,7 +4326,7 @@
         <v>100</v>
       </c>
       <c r="O35" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P35" s="65">
         <v>5.5999999999999999E-3</v>
@@ -4350,28 +4348,28 @@
         <v>14</v>
       </c>
       <c r="D36" s="61" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="E36" s="62" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F36" s="62" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G36" s="62" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="H36" s="62" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I36" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J36" s="62" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="K36" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L36" s="62">
         <v>2</v>
@@ -4384,7 +4382,7 @@
         <v>12</v>
       </c>
       <c r="O36" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P36" s="65">
         <v>0.1734</v>
@@ -4406,28 +4404,28 @@
         <v>14</v>
       </c>
       <c r="D37" s="58" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="E37" s="58" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="F37" s="58">
         <v>1051330011</v>
       </c>
       <c r="G37" s="58" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H37" s="58" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="I37" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J37" s="58" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="K37" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L37" s="58">
         <v>1</v>
@@ -4440,7 +4438,7 @@
         <v>6</v>
       </c>
       <c r="O37" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P37" s="59">
         <v>0.41049999999999998</v>
@@ -4465,23 +4463,23 @@
         <v>46</v>
       </c>
       <c r="E38" s="62" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="F38" s="62" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G38" s="62" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="H38" s="62" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="I38" s="62"/>
       <c r="J38" s="62" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="K38" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L38" s="62">
         <v>6</v>
@@ -4494,7 +4492,7 @@
         <v>32</v>
       </c>
       <c r="O38" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P38" s="65">
         <v>0.55530000000000002</v>
@@ -4504,7 +4502,7 @@
         <v>17.769600000000001</v>
       </c>
       <c r="R38" s="66" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="S38" s="62"/>
     </row>
@@ -4515,31 +4513,31 @@
         <v>30</v>
       </c>
       <c r="C39" s="56" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="D39" s="58" t="s">
         <v>47</v>
       </c>
       <c r="E39" s="58" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F39" s="58" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G39" s="58" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="H39" s="58" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="I39" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J39" s="58" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="K39" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L39" s="58">
         <v>2</v>
@@ -4552,7 +4550,7 @@
         <v>15</v>
       </c>
       <c r="O39" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P39" s="59">
         <v>8.9399999999999993E-2</v>
@@ -4577,25 +4575,25 @@
         <v>48</v>
       </c>
       <c r="E40" s="62" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F40" s="62" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G40" s="62" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H40" s="62" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="I40" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J40" s="62" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="K40" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L40" s="62">
         <v>1</v>
@@ -4608,7 +4606,7 @@
         <v>6</v>
       </c>
       <c r="O40" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P40" s="65">
         <v>0.66820000000000002</v>
@@ -4633,25 +4631,25 @@
         <v>49</v>
       </c>
       <c r="E41" s="58" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F41" s="58" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G41" s="58" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H41" s="58" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="I41" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J41" s="58" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="K41" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L41" s="58">
         <v>1</v>
@@ -4664,7 +4662,7 @@
         <v>10</v>
       </c>
       <c r="O41" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P41" s="59">
         <v>9.3600000000000003E-2</v>
@@ -4689,25 +4687,25 @@
         <v>50</v>
       </c>
       <c r="E42" s="62" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F42" s="62" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G42" s="62" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H42" s="62" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="I42" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J42" s="62" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="K42" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L42" s="62">
         <v>1</v>
@@ -4720,7 +4718,7 @@
         <v>10</v>
       </c>
       <c r="O42" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P42" s="65">
         <v>7.6899999999999996E-2</v>
@@ -4745,25 +4743,25 @@
         <v>51</v>
       </c>
       <c r="E43" s="58" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F43" s="58" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G43" s="58" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H43" s="58" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="I43" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J43" s="58" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="K43" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L43" s="58">
         <v>1</v>
@@ -4776,7 +4774,7 @@
         <v>6</v>
       </c>
       <c r="O43" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P43" s="59">
         <v>1.4222999999999999</v>
@@ -4801,25 +4799,25 @@
         <v>52</v>
       </c>
       <c r="E44" s="62" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F44" s="62" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G44" s="62" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H44" s="62" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="I44" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J44" s="62" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K44" s="62" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="L44" s="62">
         <v>1</v>
@@ -4832,7 +4830,7 @@
         <v>10</v>
       </c>
       <c r="O44" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P44" s="65">
         <v>0.19500000000000001</v>
@@ -4857,25 +4855,25 @@
         <v>53</v>
       </c>
       <c r="E45" s="58" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F45" s="58" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G45" s="58" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H45" s="58" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="I45" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J45" s="58" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="K45" s="58" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="L45" s="58">
         <v>1</v>
@@ -4888,7 +4886,7 @@
         <v>6</v>
       </c>
       <c r="O45" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P45" s="59">
         <v>0.35439999999999999</v>
@@ -4913,25 +4911,25 @@
         <v>54</v>
       </c>
       <c r="E46" s="62" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F46" s="62" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G46" s="62" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="H46" s="62" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="I46" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J46" s="62" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="K46" s="62" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="L46" s="62">
         <v>1</v>
@@ -4944,7 +4942,7 @@
         <v>10</v>
       </c>
       <c r="O46" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P46" s="65">
         <v>6.4600000000000005E-2</v>
@@ -4966,28 +4964,28 @@
         <v>20</v>
       </c>
       <c r="D47" s="58" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="E47" s="58" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F47" s="58" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G47" s="58" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="H47" s="58" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="I47" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J47" s="58" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="K47" s="58" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="L47" s="58">
         <v>3</v>
@@ -5000,7 +4998,7 @@
         <v>20</v>
       </c>
       <c r="O47" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P47" s="59">
         <v>4.9099999999999998E-2</v>
@@ -5022,28 +5020,28 @@
         <v>20</v>
       </c>
       <c r="D48" s="61" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="E48" s="62" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F48" s="62" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G48" s="62" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H48" s="62" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="I48" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J48" s="62" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="K48" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L48" s="62">
         <v>4</v>
@@ -5056,7 +5054,7 @@
         <v>40</v>
       </c>
       <c r="O48" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P48" s="65">
         <v>3.2099999999999997E-2</v>
@@ -5068,7 +5066,7 @@
       <c r="R48" s="62"/>
       <c r="S48" s="62"/>
     </row>
-    <row r="49" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="45">
         <f>ROW(B49) - ROW($B$9)</f>
@@ -5077,29 +5075,29 @@
       <c r="C49" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="D49" s="37" t="s">
-        <v>55</v>
+      <c r="D49" s="62" t="s">
+        <v>477</v>
       </c>
       <c r="E49" s="37" t="s">
-        <v>119</v>
+        <v>480</v>
       </c>
       <c r="F49" s="37" t="s">
-        <v>176</v>
+        <v>378</v>
       </c>
       <c r="G49" s="37" t="s">
-        <v>176</v>
+        <v>481</v>
       </c>
       <c r="H49" s="37" t="s">
-        <v>269</v>
+        <v>482</v>
       </c>
       <c r="I49" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J49" s="58" t="s">
-        <v>371</v>
+        <v>481</v>
       </c>
       <c r="K49" s="58" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="L49" s="58">
         <v>1</v>
@@ -5109,21 +5107,23 @@
         <v>5</v>
       </c>
       <c r="N49" s="58">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O49" s="64" t="s">
-        <v>269</v>
-      </c>
-      <c r="P49" s="59"/>
+        <v>379</v>
+      </c>
+      <c r="P49" s="59" t="s">
+        <v>366</v>
+      </c>
       <c r="Q49" s="59" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="R49" s="57" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="S49" s="37"/>
     </row>
-    <row r="50" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="45">
         <f t="shared" si="0"/>
@@ -5132,27 +5132,29 @@
       <c r="C50" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="D50" s="62" t="s">
-        <v>450</v>
+      <c r="D50" s="37" t="s">
+        <v>478</v>
       </c>
       <c r="E50" s="62" t="s">
-        <v>119</v>
+        <v>480</v>
       </c>
       <c r="F50" s="62" t="s">
-        <v>176</v>
+        <v>378</v>
       </c>
       <c r="G50" s="62" t="s">
-        <v>176</v>
+        <v>481</v>
       </c>
       <c r="H50" s="62" t="s">
-        <v>269</v>
-      </c>
-      <c r="I50" s="62"/>
+        <v>482</v>
+      </c>
+      <c r="I50" s="62" t="s">
+        <v>366</v>
+      </c>
       <c r="J50" s="62" t="s">
-        <v>371</v>
+        <v>481</v>
       </c>
       <c r="K50" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L50" s="62">
         <v>1</v>
@@ -5162,17 +5164,17 @@
         <v>5</v>
       </c>
       <c r="N50" s="62">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O50" s="64" t="s">
-        <v>269</v>
+        <v>379</v>
       </c>
       <c r="P50" s="65">
-        <v>13.9</v>
+        <v>4.2200000000000001E-2</v>
       </c>
       <c r="Q50" s="65">
         <f t="shared" ref="Q50" si="41">P50*N50</f>
-        <v>83.4</v>
+        <v>0.42200000000000004</v>
       </c>
       <c r="R50" s="62"/>
       <c r="S50" s="62"/>
@@ -5184,31 +5186,31 @@
         <v>42</v>
       </c>
       <c r="C51" s="67" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D51" s="68" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E51" s="68" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F51" s="68" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="G51" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H51" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="I51" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J51" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="K51" s="68" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="L51" s="68">
         <v>6</v>
@@ -5218,19 +5220,19 @@
         <v>30</v>
       </c>
       <c r="N51" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="O51" s="69" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="P51" s="70" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="Q51" s="70" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="R51" s="78" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="S51" s="68"/>
     </row>
@@ -5244,28 +5246,28 @@
         <v>22</v>
       </c>
       <c r="D52" s="61" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E52" s="62" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F52" s="62" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="G52" s="62" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="H52" s="62" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="I52" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J52" s="62" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="K52" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L52" s="62">
         <v>4</v>
@@ -5278,7 +5280,7 @@
         <v>40</v>
       </c>
       <c r="O52" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P52" s="65">
         <v>3.2899999999999999E-2</v>
@@ -5300,28 +5302,28 @@
         <v>23</v>
       </c>
       <c r="D53" s="58" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E53" s="58" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F53" s="58" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G53" s="58" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="H53" s="58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I53" s="58" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="J53" s="58" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="K53" s="58" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L53" s="58">
         <v>1</v>
@@ -5334,7 +5336,7 @@
         <v>20</v>
       </c>
       <c r="O53" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P53" s="59">
         <v>2.7699999999999999E-2</v>
@@ -5356,28 +5358,28 @@
         <v>23</v>
       </c>
       <c r="D54" s="61" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E54" s="62" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F54" s="62" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G54" s="62" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="H54" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I54" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J54" s="62" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="K54" s="62" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="L54" s="62">
         <v>1</v>
@@ -5390,7 +5392,7 @@
         <v>20</v>
       </c>
       <c r="O54" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P54" s="65">
         <v>2.18E-2</v>
@@ -5412,28 +5414,28 @@
         <v>23</v>
       </c>
       <c r="D55" s="58" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="E55" s="58" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F55" s="58" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G55" s="58" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="H55" s="58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I55" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J55" s="58" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="K55" s="58" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="L55" s="58">
         <v>14</v>
@@ -5446,7 +5448,7 @@
         <v>100</v>
       </c>
       <c r="O55" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P55" s="59">
         <v>1E-3</v>
@@ -5468,28 +5470,28 @@
         <v>23</v>
       </c>
       <c r="D56" s="61" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E56" s="62" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F56" s="62" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G56" s="62" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="H56" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I56" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J56" s="62" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="K56" s="62" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="L56" s="62">
         <v>1</v>
@@ -5502,7 +5504,7 @@
         <v>20</v>
       </c>
       <c r="O56" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P56" s="65">
         <v>2.81E-2</v>
@@ -5524,28 +5526,28 @@
         <v>23</v>
       </c>
       <c r="D57" s="58" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E57" s="58" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F57" s="58" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G57" s="58" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="H57" s="58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I57" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J57" s="58" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="K57" s="58" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="L57" s="58">
         <v>1</v>
@@ -5558,7 +5560,7 @@
         <v>20</v>
       </c>
       <c r="O57" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P57" s="59">
         <v>3.2300000000000002E-2</v>
@@ -5580,28 +5582,28 @@
         <v>23</v>
       </c>
       <c r="D58" s="61" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E58" s="62" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F58" s="62" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G58" s="62" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="H58" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I58" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J58" s="62" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="K58" s="62" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="L58" s="62">
         <v>2</v>
@@ -5614,7 +5616,7 @@
         <v>100</v>
       </c>
       <c r="O58" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P58" s="65">
         <v>1.1999999999999999E-3</v>
@@ -5636,28 +5638,28 @@
         <v>23</v>
       </c>
       <c r="D59" s="58" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E59" s="58" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F59" s="58" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G59" s="58" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="H59" s="58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I59" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J59" s="58" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K59" s="58" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="L59" s="58">
         <v>3</v>
@@ -5670,7 +5672,7 @@
         <v>100</v>
       </c>
       <c r="O59" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P59" s="59">
         <v>1.2999999999999999E-3</v>
@@ -5692,28 +5694,28 @@
         <v>23</v>
       </c>
       <c r="D60" s="61" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E60" s="62" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F60" s="62" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G60" s="62" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H60" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I60" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J60" s="62" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="K60" s="62" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="L60" s="62">
         <v>4</v>
@@ -5726,7 +5728,7 @@
         <v>50</v>
       </c>
       <c r="O60" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P60" s="65">
         <v>9.2999999999999992E-3</v>
@@ -5748,28 +5750,28 @@
         <v>23</v>
       </c>
       <c r="D61" s="58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E61" s="58" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F61" s="58" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G61" s="58" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="H61" s="58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I61" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J61" s="58" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="K61" s="58" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="L61" s="58">
         <v>1</v>
@@ -5782,7 +5784,7 @@
         <v>100</v>
       </c>
       <c r="O61" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P61" s="59">
         <v>3.0000000000000001E-3</v>
@@ -5804,28 +5806,28 @@
         <v>23</v>
       </c>
       <c r="D62" s="61" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E62" s="62" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F62" s="62" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G62" s="62" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H62" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I62" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J62" s="62" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="K62" s="62" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="L62" s="62">
         <v>3</v>
@@ -5838,7 +5840,7 @@
         <v>100</v>
       </c>
       <c r="O62" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P62" s="65">
         <v>1.1999999999999999E-3</v>
@@ -5860,28 +5862,28 @@
         <v>23</v>
       </c>
       <c r="D63" s="58" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E63" s="58" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F63" s="58" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G63" s="58" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="H63" s="58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I63" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J63" s="58" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="K63" s="58" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="L63" s="58">
         <v>6</v>
@@ -5894,7 +5896,7 @@
         <v>100</v>
       </c>
       <c r="O63" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P63" s="59">
         <v>1.1000000000000001E-3</v>
@@ -5916,28 +5918,28 @@
         <v>23</v>
       </c>
       <c r="D64" s="61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E64" s="62" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F64" s="62" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G64" s="62" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="H64" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I64" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J64" s="62" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="K64" s="62" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="L64" s="62">
         <v>4</v>
@@ -5950,7 +5952,7 @@
         <v>100</v>
       </c>
       <c r="O64" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P64" s="65">
         <v>1E-3</v>
@@ -5972,28 +5974,28 @@
         <v>23</v>
       </c>
       <c r="D65" s="58" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E65" s="58" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F65" s="58" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G65" s="58" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="H65" s="58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I65" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J65" s="58" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="K65" s="58" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="L65" s="58">
         <v>1</v>
@@ -6006,7 +6008,7 @@
         <v>100</v>
       </c>
       <c r="O65" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P65" s="59">
         <v>1.2999999999999999E-3</v>
@@ -6028,28 +6030,28 @@
         <v>23</v>
       </c>
       <c r="D66" s="61" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E66" s="62" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F66" s="62" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G66" s="62" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H66" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I66" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J66" s="62" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="K66" s="62" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="L66" s="62">
         <v>3</v>
@@ -6062,7 +6064,7 @@
         <v>100</v>
       </c>
       <c r="O66" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P66" s="65">
         <v>1.2999999999999999E-3</v>
@@ -6084,28 +6086,28 @@
         <v>23</v>
       </c>
       <c r="D67" s="58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E67" s="58" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F67" s="58" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G67" s="58" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H67" s="58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I67" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J67" s="58" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="K67" s="58" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="L67" s="58">
         <v>1</v>
@@ -6118,7 +6120,7 @@
         <v>100</v>
       </c>
       <c r="O67" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P67" s="59">
         <v>1.8E-3</v>
@@ -6140,28 +6142,28 @@
         <v>23</v>
       </c>
       <c r="D68" s="61" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E68" s="62" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F68" s="62" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G68" s="62" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H68" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I68" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J68" s="62" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="K68" s="62" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="L68" s="62">
         <v>1</v>
@@ -6174,7 +6176,7 @@
         <v>100</v>
       </c>
       <c r="O68" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P68" s="65">
         <v>1.2999999999999999E-3</v>
@@ -6196,28 +6198,28 @@
         <v>23</v>
       </c>
       <c r="D69" s="58" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E69" s="58" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F69" s="58" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G69" s="58" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H69" s="58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I69" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J69" s="58" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="K69" s="58" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="L69" s="58">
         <v>1</v>
@@ -6230,7 +6232,7 @@
         <v>100</v>
       </c>
       <c r="O69" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P69" s="59">
         <v>6.9999999999999999E-4</v>
@@ -6252,28 +6254,28 @@
         <v>23</v>
       </c>
       <c r="D70" s="61" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E70" s="62" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F70" s="62" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G70" s="62" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="H70" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I70" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J70" s="62" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="K70" s="62" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="L70" s="62">
         <v>1</v>
@@ -6286,7 +6288,7 @@
         <v>100</v>
       </c>
       <c r="O70" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P70" s="65">
         <v>5.0000000000000001E-4</v>
@@ -6308,28 +6310,28 @@
         <v>23</v>
       </c>
       <c r="D71" s="37" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="E71" s="37" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="F71" s="37" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="G71" s="37" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="H71" s="37" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="I71" s="37" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J71" s="37" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="K71" s="37" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="L71" s="37">
         <v>1</v>
@@ -6342,7 +6344,7 @@
         <v>10</v>
       </c>
       <c r="O71" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P71" s="72">
         <v>5.8099999999999999E-2</v>
@@ -6364,28 +6366,28 @@
         <v>23</v>
       </c>
       <c r="D72" s="62" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="E72" s="62" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="F72" s="62" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G72" s="62" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="H72" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I72" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J72" s="62" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="K72" s="62" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="L72" s="62">
         <v>2</v>
@@ -6398,7 +6400,7 @@
         <v>100</v>
       </c>
       <c r="O72" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P72" s="65">
         <v>1.1999999999999999E-3</v>
@@ -6417,50 +6419,50 @@
         <v>64</v>
       </c>
       <c r="C73" s="67" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="D73" s="68" t="s">
-        <v>75</v>
+        <v>463</v>
       </c>
       <c r="E73" s="68" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F73" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="G73" s="68" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="H73" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="I73" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J73" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="K73" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L73" s="68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M73" s="68">
         <f>L73*5</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N73" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="O73" s="69" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="P73" s="70" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="Q73" s="70" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="R73" s="68"/>
       <c r="S73" s="68"/>
@@ -6472,31 +6474,31 @@
         <v>65</v>
       </c>
       <c r="C74" s="60" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D74" s="61" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E74" s="62" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F74" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="G74" s="62" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="H74" s="62" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="I74" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J74" s="62" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="K74" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L74" s="62">
         <v>1</v>
@@ -6509,7 +6511,7 @@
         <v>6</v>
       </c>
       <c r="O74" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P74" s="65">
         <v>0.54410000000000003</v>
@@ -6531,28 +6533,28 @@
         <v>24</v>
       </c>
       <c r="D75" s="58" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E75" s="58" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F75" s="58" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G75" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="H75" s="58" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="I75" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J75" s="58" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="K75" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L75" s="58">
         <v>1</v>
@@ -6565,7 +6567,7 @@
         <v>10</v>
       </c>
       <c r="O75" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P75" s="59">
         <v>7.6300000000000007E-2</v>
@@ -6587,28 +6589,28 @@
         <v>24</v>
       </c>
       <c r="D76" s="61" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E76" s="62" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F76" s="62" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="G76" s="62" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H76" s="62" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I76" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J76" s="62" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="K76" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L76" s="62">
         <v>1</v>
@@ -6621,7 +6623,7 @@
         <v>6</v>
       </c>
       <c r="O76" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P76" s="65">
         <v>3.1484999999999999</v>
@@ -6643,28 +6645,28 @@
         <v>24</v>
       </c>
       <c r="D77" s="58" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E77" s="58" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F77" s="58" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G77" s="58" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="H77" s="58" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="I77" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J77" s="58" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="K77" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L77" s="58">
         <v>1</v>
@@ -6677,7 +6679,7 @@
         <v>10</v>
       </c>
       <c r="O77" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P77" s="59">
         <v>0.10920000000000001</v>
@@ -6699,28 +6701,28 @@
         <v>24</v>
       </c>
       <c r="D78" s="61" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E78" s="62" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F78" s="62" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G78" s="62" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H78" s="62" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="I78" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J78" s="62" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="K78" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L78" s="62">
         <v>4</v>
@@ -6733,7 +6735,7 @@
         <v>21</v>
       </c>
       <c r="O78" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P78" s="65">
         <v>7.5918999999999999</v>
@@ -6755,28 +6757,28 @@
         <v>24</v>
       </c>
       <c r="D79" s="58" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="E79" s="58" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F79" s="58" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G79" s="58" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="H79" s="58" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="I79" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J79" s="58" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="K79" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L79" s="58">
         <v>1</v>
@@ -6789,7 +6791,7 @@
         <v>6</v>
       </c>
       <c r="O79" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P79" s="59">
         <v>0.73819999999999997</v>
@@ -6808,28 +6810,28 @@
         <v>24</v>
       </c>
       <c r="D80" s="37" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="E80" s="37" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="F80" s="37" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="G80" s="37" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="H80" s="37" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="I80" s="37" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J80" s="37" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="K80" s="37" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L80" s="37">
         <v>1</v>
@@ -6842,7 +6844,7 @@
         <v>6</v>
       </c>
       <c r="O80" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P80" s="59">
         <v>0.39460000000000001</v>
@@ -6864,28 +6866,28 @@
         <v>24</v>
       </c>
       <c r="D81" s="61" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E81" s="62" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F81" s="62" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G81" s="62" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H81" s="62" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="I81" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J81" s="62" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="K81" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L81" s="62">
         <v>1</v>
@@ -6898,7 +6900,7 @@
         <v>6</v>
       </c>
       <c r="O81" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P81" s="65">
         <v>0.6905</v>
@@ -6920,28 +6922,28 @@
         <v>25</v>
       </c>
       <c r="D82" s="58" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E82" s="58" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F82" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="G82" s="58" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="H82" s="58" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="I82" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J82" s="58" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K82" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L82" s="58">
         <v>1</v>
@@ -6954,7 +6956,7 @@
         <v>6</v>
       </c>
       <c r="O82" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P82" s="59">
         <v>20.79</v>
@@ -6976,28 +6978,28 @@
         <v>24</v>
       </c>
       <c r="D83" s="61" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E83" s="62" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F83" s="62" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G83" s="62" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H83" s="62" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="I83" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J83" s="62" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="K83" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L83" s="62">
         <v>1</v>
@@ -7010,7 +7012,7 @@
         <v>6</v>
       </c>
       <c r="O83" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P83" s="65">
         <v>11.400499999999999</v>
@@ -7032,28 +7034,28 @@
         <v>24</v>
       </c>
       <c r="D84" s="58" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E84" s="58" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F84" s="58" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G84" s="58" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H84" s="58" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="I84" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J84" s="58" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="K84" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L84" s="58">
         <v>1</v>
@@ -7066,7 +7068,7 @@
         <v>6</v>
       </c>
       <c r="O84" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P84" s="59">
         <v>2.8128000000000002</v>
@@ -7088,28 +7090,28 @@
         <v>24</v>
       </c>
       <c r="D85" s="62" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="E85" s="37" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="F85" s="37" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="G85" s="37" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="H85" s="37" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="I85" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J85" s="37" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="K85" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L85" s="62">
         <v>2</v>
@@ -7122,7 +7124,7 @@
         <v>11</v>
       </c>
       <c r="O85" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P85" s="65">
         <v>0.3755</v>
@@ -7144,28 +7146,28 @@
         <v>26</v>
       </c>
       <c r="D86" s="61" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E86" s="62" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F86" s="62" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G86" s="62" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="H86" s="62" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="I86" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J86" s="62" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="K86" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L86" s="62">
         <v>1</v>
@@ -7178,7 +7180,7 @@
         <v>10</v>
       </c>
       <c r="O86" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P86" s="65">
         <v>8.3400000000000002E-2</v>
@@ -7197,31 +7199,31 @@
         <v>78</v>
       </c>
       <c r="C87" s="60" t="s">
+        <v>418</v>
+      </c>
+      <c r="D87" s="71" t="s">
         <v>423</v>
       </c>
-      <c r="D87" s="71" t="s">
-        <v>428</v>
-      </c>
       <c r="E87" s="62" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="F87" s="62" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G87" s="62" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="H87" s="62" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="I87" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J87" s="62" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="K87" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L87" s="62">
         <v>1</v>
@@ -7234,7 +7236,7 @@
         <v>6</v>
       </c>
       <c r="O87" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P87" s="65">
         <v>1.5643</v>
@@ -7253,31 +7255,31 @@
         <v>79</v>
       </c>
       <c r="C88" s="60" t="s">
+        <v>418</v>
+      </c>
+      <c r="D88" s="71" t="s">
         <v>423</v>
       </c>
-      <c r="D88" s="71" t="s">
-        <v>428</v>
-      </c>
       <c r="E88" s="62" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="F88" s="62" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G88" s="62" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="H88" s="62" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="I88" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J88" s="62" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="K88" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L88" s="62">
         <v>1</v>
@@ -7290,7 +7292,7 @@
         <v>6</v>
       </c>
       <c r="O88" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P88" s="65">
         <v>2.0146999999999999</v>
@@ -7309,31 +7311,31 @@
         <v>80</v>
       </c>
       <c r="C89" s="60" t="s">
+        <v>418</v>
+      </c>
+      <c r="D89" s="71" t="s">
         <v>423</v>
       </c>
-      <c r="D89" s="71" t="s">
+      <c r="E89" s="62" t="s">
         <v>428</v>
       </c>
-      <c r="E89" s="62" t="s">
-        <v>433</v>
-      </c>
       <c r="F89" s="62" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G89" s="62" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="H89" s="62" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="I89" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J89" s="62" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="K89" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L89" s="62">
         <v>1</v>
@@ -7346,7 +7348,7 @@
         <v>6</v>
       </c>
       <c r="O89" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P89" s="65">
         <v>0.80110000000000003</v>
@@ -7379,7 +7381,7 @@
       <c r="P90" s="88"/>
       <c r="Q90" s="46">
         <f>SUM(Q10:Q89)</f>
-        <v>614.41879999999992</v>
+        <v>531.44079999999997</v>
       </c>
       <c r="R90" s="83"/>
       <c r="S90" s="84"/>
@@ -7405,7 +7407,7 @@
       <c r="P91" s="88"/>
       <c r="Q91" s="47">
         <f>Q90/5</f>
-        <v>122.88375999999998</v>
+        <v>106.28815999999999</v>
       </c>
       <c r="R91" s="85"/>
       <c r="S91" s="86"/>
@@ -7486,18 +7488,18 @@
     <hyperlink ref="O37" r:id="rId64"/>
     <hyperlink ref="O38" r:id="rId65"/>
     <hyperlink ref="O20" r:id="rId66"/>
-    <hyperlink ref="O50" r:id="rId67"/>
-    <hyperlink ref="O87" r:id="rId68"/>
-    <hyperlink ref="O88" r:id="rId69"/>
-    <hyperlink ref="O89" r:id="rId70"/>
-    <hyperlink ref="O42" r:id="rId71"/>
-    <hyperlink ref="O80" r:id="rId72"/>
-    <hyperlink ref="O49" r:id="rId73"/>
-    <hyperlink ref="O71" r:id="rId74"/>
-    <hyperlink ref="O72" r:id="rId75"/>
-    <hyperlink ref="O21" r:id="rId76"/>
-    <hyperlink ref="O35" r:id="rId77"/>
-    <hyperlink ref="O85" r:id="rId78"/>
+    <hyperlink ref="O87" r:id="rId67"/>
+    <hyperlink ref="O88" r:id="rId68"/>
+    <hyperlink ref="O89" r:id="rId69"/>
+    <hyperlink ref="O42" r:id="rId70"/>
+    <hyperlink ref="O80" r:id="rId71"/>
+    <hyperlink ref="O71" r:id="rId72"/>
+    <hyperlink ref="O72" r:id="rId73"/>
+    <hyperlink ref="O21" r:id="rId74"/>
+    <hyperlink ref="O35" r:id="rId75"/>
+    <hyperlink ref="O85" r:id="rId76"/>
+    <hyperlink ref="O49" r:id="rId77"/>
+    <hyperlink ref="O50" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId79"/>
@@ -7560,7 +7562,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="48" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -7585,7 +7587,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="49" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -7610,7 +7612,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="50" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -7726,49 +7728,49 @@
         <v>27</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F9" s="52" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="H9" s="52" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="J9" s="52" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="K9" s="53" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="L9" s="30" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="M9" s="54" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="N9" s="52" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="O9" s="30" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="P9" s="52" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="R9" s="52" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="S9" s="30" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
@@ -7781,28 +7783,28 @@
         <v>9</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="L10" s="37">
         <v>3</v>
@@ -7815,7 +7817,7 @@
         <v>125</v>
       </c>
       <c r="O10" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P10" s="72">
         <v>0.1217</v>
@@ -7836,29 +7838,29 @@
       <c r="C11" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="62" t="s">
-        <v>442</v>
+      <c r="D11" s="61" t="s">
+        <v>479</v>
       </c>
       <c r="E11" s="62" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F11" s="62" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G11" s="63" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="H11" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I11" s="62" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="J11" s="62" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="K11" s="62" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="L11" s="62">
         <v>30</v>
@@ -7871,7 +7873,7 @@
         <v>1250</v>
       </c>
       <c r="O11" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P11" s="65">
         <v>1.04E-2</v>
@@ -7896,25 +7898,25 @@
         <v>28</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="H12" s="58" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="I12" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J12" s="58" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="K12" s="58" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="L12" s="58">
         <v>2</v>
@@ -7927,7 +7929,7 @@
         <v>90</v>
       </c>
       <c r="O12" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P12" s="59">
         <v>5.5899999999999998E-2</v>
@@ -7949,28 +7951,28 @@
         <v>9</v>
       </c>
       <c r="D13" s="62" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="E13" s="62" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F13" s="62" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G13" s="62" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H13" s="62" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="I13" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J13" s="62" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="K13" s="62" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="L13" s="62">
         <v>3</v>
@@ -7983,7 +7985,7 @@
         <v>122</v>
       </c>
       <c r="O13" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P13" s="65">
         <v>0.37869999999999998</v>
@@ -8008,25 +8010,25 @@
         <v>29</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F14" s="58" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G14" s="58" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="H14" s="58" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="I14" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J14" s="58" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="K14" s="58" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="L14" s="58">
         <v>1</v>
@@ -8039,7 +8041,7 @@
         <v>42</v>
       </c>
       <c r="O14" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P14" s="59">
         <v>0.70009999999999994</v>
@@ -8064,25 +8066,25 @@
         <v>30</v>
       </c>
       <c r="E15" s="62" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F15" s="62" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G15" s="62" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H15" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I15" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J15" s="62" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="K15" s="62" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="L15" s="62">
         <v>12</v>
@@ -8095,7 +8097,7 @@
         <v>500</v>
       </c>
       <c r="O15" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P15" s="65">
         <v>2.8E-3</v>
@@ -8117,28 +8119,28 @@
         <v>9</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="E16" s="58" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F16" s="58" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G16" s="58" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H16" s="58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I16" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J16" s="58" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="K16" s="58" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="L16" s="58">
         <v>3</v>
@@ -8151,7 +8153,7 @@
         <v>200</v>
       </c>
       <c r="O16" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P16" s="59">
         <v>4.8999999999999998E-3</v>
@@ -8176,25 +8178,25 @@
         <v>31</v>
       </c>
       <c r="E17" s="62" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F17" s="62" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G17" s="63" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="H17" s="62" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="I17" s="62" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="J17" s="62" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="K17" s="62" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="L17" s="62">
         <v>1</v>
@@ -8207,7 +8209,7 @@
         <v>100</v>
       </c>
       <c r="O17" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P17" s="65">
         <v>1.2999999999999999E-3</v>
@@ -8232,25 +8234,25 @@
         <v>32</v>
       </c>
       <c r="E18" s="58" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F18" s="58" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G18" s="58" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="H18" s="58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I18" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J18" s="58" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="K18" s="58" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="L18" s="58">
         <v>2</v>
@@ -8263,7 +8265,7 @@
         <v>100</v>
       </c>
       <c r="O18" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P18" s="59">
         <v>2.8999999999999998E-3</v>
@@ -8285,28 +8287,28 @@
         <v>9</v>
       </c>
       <c r="D19" s="61" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E19" s="62" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F19" s="62" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G19" s="62" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="H19" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I19" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J19" s="62" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="K19" s="62" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="L19" s="62">
         <v>2</v>
@@ -8319,7 +8321,7 @@
         <v>100</v>
       </c>
       <c r="O19" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P19" s="65">
         <v>2.3599999999999999E-2</v>
@@ -8341,28 +8343,28 @@
         <v>9</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J20" s="37" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="K20" s="37" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="L20" s="37">
         <v>1</v>
@@ -8375,7 +8377,7 @@
         <v>42</v>
       </c>
       <c r="O20" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P20" s="72">
         <v>0.35399999999999998</v>
@@ -8396,28 +8398,28 @@
         <v>9</v>
       </c>
       <c r="D21" s="62" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="E21" s="62" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="F21" s="62" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G21" s="62" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="H21" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I21" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J21" s="62" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="K21" s="62" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="L21" s="62">
         <v>2</v>
@@ -8430,7 +8432,7 @@
         <v>100</v>
       </c>
       <c r="O21" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P21" s="72">
         <v>3.2399999999999998E-2</v>
@@ -8455,25 +8457,25 @@
         <v>33</v>
       </c>
       <c r="E22" s="58" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F22" s="58" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G22" s="58" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="H22" s="58" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I22" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J22" s="58" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="K22" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L22" s="58">
         <v>7</v>
@@ -8486,7 +8488,7 @@
         <v>290</v>
       </c>
       <c r="O22" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P22" s="59">
         <v>5.0200000000000002E-2</v>
@@ -8511,25 +8513,25 @@
         <v>34</v>
       </c>
       <c r="E23" s="62" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F23" s="62" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G23" s="62" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H23" s="62" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="I23" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J23" s="62" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="K23" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L23" s="62">
         <v>2</v>
@@ -8542,7 +8544,7 @@
         <v>85</v>
       </c>
       <c r="O23" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P23" s="65">
         <v>7.0999999999999994E-2</v>
@@ -8567,25 +8569,25 @@
         <v>35</v>
       </c>
       <c r="E24" s="58" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F24" s="58" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G24" s="58" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="H24" s="58" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="I24" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J24" s="58" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="K24" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L24" s="58">
         <v>1</v>
@@ -8598,7 +8600,7 @@
         <v>60</v>
       </c>
       <c r="O24" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P24" s="59">
         <v>2.8199999999999999E-2</v>
@@ -8623,25 +8625,25 @@
         <v>36</v>
       </c>
       <c r="E25" s="62" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F25" s="62" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="G25" s="62" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="H25" s="62" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="I25" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J25" s="62" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="K25" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L25" s="62">
         <v>1</v>
@@ -8654,7 +8656,7 @@
         <v>60</v>
       </c>
       <c r="O25" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P25" s="65">
         <v>3.1600000000000003E-2</v>
@@ -8679,25 +8681,25 @@
         <v>37</v>
       </c>
       <c r="E26" s="58" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F26" s="58" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G26" s="58" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="H26" s="58" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I26" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J26" s="58" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="K26" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L26" s="58">
         <v>8</v>
@@ -8710,7 +8712,7 @@
         <v>340</v>
       </c>
       <c r="O26" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P26" s="59">
         <v>1.11E-2</v>
@@ -8735,25 +8737,25 @@
         <v>38</v>
       </c>
       <c r="E27" s="62" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F27" s="62" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G27" s="62" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H27" s="62" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="I27" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J27" s="62" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="K27" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L27" s="62">
         <v>1</v>
@@ -8766,7 +8768,7 @@
         <v>45</v>
       </c>
       <c r="O27" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P27" s="65">
         <v>9.35E-2</v>
@@ -8791,25 +8793,25 @@
         <v>39</v>
       </c>
       <c r="E28" s="58" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F28" s="58" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G28" s="58" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="H28" s="58" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I28" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J28" s="58" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="K28" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L28" s="58">
         <v>3</v>
@@ -8822,7 +8824,7 @@
         <v>140</v>
       </c>
       <c r="O28" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P28" s="59">
         <v>3.1699999999999999E-2</v>
@@ -8847,25 +8849,25 @@
         <v>40</v>
       </c>
       <c r="E29" s="62" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F29" s="62" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G29" s="62" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="H29" s="62" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="I29" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J29" s="62" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="K29" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L29" s="62">
         <v>1</v>
@@ -8878,7 +8880,7 @@
         <v>50</v>
       </c>
       <c r="O29" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P29" s="65">
         <v>3.5400000000000001E-2</v>
@@ -8903,25 +8905,25 @@
         <v>41</v>
       </c>
       <c r="E30" s="58" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F30" s="58" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G30" s="58" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="H30" s="58" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="I30" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J30" s="58" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="K30" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L30" s="58">
         <v>5</v>
@@ -8934,7 +8936,7 @@
         <v>250</v>
       </c>
       <c r="O30" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P30" s="59">
         <v>1.7999999999999999E-2</v>
@@ -8959,25 +8961,25 @@
         <v>42</v>
       </c>
       <c r="E31" s="62" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F31" s="62" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G31" s="62" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H31" s="62" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I31" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J31" s="62" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="K31" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L31" s="62">
         <v>1</v>
@@ -8990,7 +8992,7 @@
         <v>45</v>
       </c>
       <c r="O31" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P31" s="65">
         <v>0.22259999999999999</v>
@@ -9015,25 +9017,25 @@
         <v>43</v>
       </c>
       <c r="E32" s="58" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F32" s="58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G32" s="58" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="H32" s="58" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I32" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J32" s="58" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="K32" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L32" s="58">
         <v>2</v>
@@ -9046,7 +9048,7 @@
         <v>90</v>
       </c>
       <c r="O32" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P32" s="59">
         <v>4.7399999999999998E-2</v>
@@ -9058,7 +9060,7 @@
       <c r="R32" s="57"/>
       <c r="S32" s="37"/>
     </row>
-    <row r="33" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="75"/>
       <c r="B33" s="44">
         <f>ROW(B33) - ROW($B$9)</f>
@@ -9071,25 +9073,25 @@
         <v>44</v>
       </c>
       <c r="E33" s="62" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F33" s="62" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G33" s="62" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H33" s="62" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="I33" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J33" s="62" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="K33" s="62" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="L33" s="62">
         <v>1</v>
@@ -9102,7 +9104,7 @@
         <v>45</v>
       </c>
       <c r="O33" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P33" s="65">
         <v>9.4100000000000003E-2</v>
@@ -9114,7 +9116,7 @@
       <c r="R33" s="62"/>
       <c r="S33" s="62"/>
     </row>
-    <row r="34" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="75"/>
       <c r="B34" s="45">
         <f t="shared" si="0"/>
@@ -9127,25 +9129,25 @@
         <v>45</v>
       </c>
       <c r="E34" s="58" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F34" s="58" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G34" s="58" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="H34" s="58" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="I34" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J34" s="58" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="K34" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L34" s="58">
         <v>8</v>
@@ -9158,7 +9160,7 @@
         <v>330</v>
       </c>
       <c r="O34" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P34" s="59">
         <v>3.32E-2</v>
@@ -9180,26 +9182,26 @@
         <v>13</v>
       </c>
       <c r="D35" s="62" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="E35" s="62" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="F35" s="62" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="G35" s="62" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="H35" s="62" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="I35" s="62"/>
       <c r="J35" s="62" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="K35" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L35" s="62">
         <v>1</v>
@@ -9212,7 +9214,7 @@
         <v>100</v>
       </c>
       <c r="O35" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P35" s="65">
         <v>5.5999999999999999E-3</v>
@@ -9234,28 +9236,28 @@
         <v>14</v>
       </c>
       <c r="D36" s="61" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="E36" s="62" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F36" s="62" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G36" s="62" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="H36" s="62" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I36" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J36" s="62" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="K36" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L36" s="62">
         <v>2</v>
@@ -9268,7 +9270,7 @@
         <v>82</v>
       </c>
       <c r="O36" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P36" s="65">
         <v>0.1532</v>
@@ -9280,7 +9282,7 @@
       <c r="R36" s="62"/>
       <c r="S36" s="62"/>
     </row>
-    <row r="37" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="75"/>
       <c r="B37" s="45">
         <f t="shared" ref="B37" si="13">ROW(B37) - ROW($B$9)</f>
@@ -9290,28 +9292,28 @@
         <v>14</v>
       </c>
       <c r="D37" s="58" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="E37" s="58" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="F37" s="58">
         <v>1051330011</v>
       </c>
       <c r="G37" s="58" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H37" s="58" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="I37" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J37" s="58" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="K37" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L37" s="58">
         <v>1</v>
@@ -9324,7 +9326,7 @@
         <v>42</v>
       </c>
       <c r="O37" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P37" s="59">
         <v>0.28639999999999999</v>
@@ -9349,23 +9351,23 @@
         <v>46</v>
       </c>
       <c r="E38" s="62" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="F38" s="62" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G38" s="62" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="H38" s="62" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="I38" s="62"/>
       <c r="J38" s="62" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="K38" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L38" s="62">
         <v>6</v>
@@ -9378,7 +9380,7 @@
         <v>242</v>
       </c>
       <c r="O38" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P38" s="65">
         <v>0.49320000000000003</v>
@@ -9388,42 +9390,42 @@
         <v>119.35440000000001</v>
       </c>
       <c r="R38" s="66" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="S38" s="62"/>
     </row>
-    <row r="39" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="75"/>
       <c r="B39" s="44">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
       <c r="C39" s="56" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="D39" s="58" t="s">
         <v>47</v>
       </c>
       <c r="E39" s="58" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F39" s="58" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G39" s="58" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="H39" s="58" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="I39" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J39" s="58" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="K39" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L39" s="58">
         <v>2</v>
@@ -9436,7 +9438,7 @@
         <v>85</v>
       </c>
       <c r="O39" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P39" s="59">
         <v>6.4799999999999996E-2</v>
@@ -9461,25 +9463,25 @@
         <v>48</v>
       </c>
       <c r="E40" s="62" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F40" s="62" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G40" s="62" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H40" s="62" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="I40" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J40" s="62" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="K40" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L40" s="62">
         <v>1</v>
@@ -9492,7 +9494,7 @@
         <v>42</v>
       </c>
       <c r="O40" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P40" s="65">
         <v>0.49480000000000002</v>
@@ -9517,25 +9519,25 @@
         <v>49</v>
       </c>
       <c r="E41" s="58" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F41" s="58" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G41" s="58" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H41" s="58" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="I41" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J41" s="58" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="K41" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L41" s="58">
         <v>1</v>
@@ -9548,7 +9550,7 @@
         <v>45</v>
       </c>
       <c r="O41" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P41" s="59">
         <v>9.3600000000000003E-2</v>
@@ -9573,25 +9575,25 @@
         <v>50</v>
       </c>
       <c r="E42" s="62" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F42" s="62" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G42" s="62" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H42" s="62" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="I42" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J42" s="62" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="K42" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L42" s="62">
         <v>1</v>
@@ -9604,7 +9606,7 @@
         <v>45</v>
       </c>
       <c r="O42" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P42" s="65">
         <v>7.6899999999999996E-2</v>
@@ -9629,25 +9631,25 @@
         <v>51</v>
       </c>
       <c r="E43" s="58" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F43" s="58" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G43" s="58" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H43" s="58" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="I43" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J43" s="58" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="K43" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L43" s="58">
         <v>1</v>
@@ -9660,7 +9662,7 @@
         <v>42</v>
       </c>
       <c r="O43" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P43" s="59">
         <v>1.1438999999999999</v>
@@ -9685,25 +9687,25 @@
         <v>52</v>
       </c>
       <c r="E44" s="62" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F44" s="62" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G44" s="62" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H44" s="62" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="I44" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J44" s="62" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K44" s="62" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="L44" s="62">
         <v>1</v>
@@ -9716,7 +9718,7 @@
         <v>45</v>
       </c>
       <c r="O44" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P44" s="65">
         <v>0.19500000000000001</v>
@@ -9741,25 +9743,25 @@
         <v>53</v>
       </c>
       <c r="E45" s="58" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F45" s="58" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G45" s="58" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H45" s="58" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="I45" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J45" s="58" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="K45" s="58" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="L45" s="58">
         <v>1</v>
@@ -9772,7 +9774,7 @@
         <v>42</v>
       </c>
       <c r="O45" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P45" s="59">
         <v>0.20810000000000001</v>
@@ -9797,25 +9799,25 @@
         <v>54</v>
       </c>
       <c r="E46" s="62" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F46" s="62" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G46" s="62" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="H46" s="62" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="I46" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J46" s="62" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="K46" s="62" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="L46" s="62">
         <v>1</v>
@@ -9828,7 +9830,7 @@
         <v>50</v>
       </c>
       <c r="O46" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P46" s="65">
         <v>6.4600000000000005E-2</v>
@@ -9840,7 +9842,7 @@
       <c r="R46" s="62"/>
       <c r="S46" s="62"/>
     </row>
-    <row r="47" spans="1:19" s="77" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A47" s="75"/>
       <c r="B47" s="45">
         <f t="shared" si="0"/>
@@ -9850,28 +9852,28 @@
         <v>20</v>
       </c>
       <c r="D47" s="58" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="E47" s="58" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F47" s="58" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G47" s="58" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="H47" s="58" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="I47" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J47" s="58" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="K47" s="58" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="L47" s="58">
         <v>3</v>
@@ -9884,7 +9886,7 @@
         <v>130</v>
       </c>
       <c r="O47" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P47" s="59">
         <v>4.2599999999999999E-2</v>
@@ -9906,28 +9908,28 @@
         <v>20</v>
       </c>
       <c r="D48" s="61" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="E48" s="62" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F48" s="62" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G48" s="62" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H48" s="62" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="I48" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J48" s="62" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="K48" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L48" s="62">
         <v>4</v>
@@ -9940,7 +9942,7 @@
         <v>180</v>
       </c>
       <c r="O48" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P48" s="65">
         <v>4.0099999999999997E-2</v>
@@ -9952,7 +9954,7 @@
       <c r="R48" s="62"/>
       <c r="S48" s="62"/>
     </row>
-    <row r="49" spans="1:19" s="77" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" s="77" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A49" s="75"/>
       <c r="B49" s="45">
         <f>ROW(B49) - ROW($B$9)</f>
@@ -9961,29 +9963,29 @@
       <c r="C49" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="D49" s="37" t="s">
-        <v>55</v>
+      <c r="D49" s="62" t="s">
+        <v>477</v>
       </c>
       <c r="E49" s="37" t="s">
-        <v>119</v>
+        <v>480</v>
       </c>
       <c r="F49" s="37" t="s">
-        <v>176</v>
+        <v>378</v>
       </c>
       <c r="G49" s="37" t="s">
-        <v>176</v>
+        <v>481</v>
       </c>
       <c r="H49" s="37" t="s">
-        <v>269</v>
+        <v>482</v>
       </c>
       <c r="I49" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J49" s="58" t="s">
-        <v>371</v>
+        <v>481</v>
       </c>
       <c r="K49" s="58" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="L49" s="58">
         <v>1</v>
@@ -9993,23 +9995,23 @@
         <v>40</v>
       </c>
       <c r="N49" s="58">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O49" s="64" t="s">
-        <v>269</v>
+        <v>379</v>
       </c>
       <c r="P49" s="59" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="Q49" s="59" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="R49" s="57" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="S49" s="37"/>
     </row>
-    <row r="50" spans="1:19" s="77" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" s="77" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="75"/>
       <c r="B50" s="45">
         <f t="shared" si="0"/>
@@ -10018,27 +10020,29 @@
       <c r="C50" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="D50" s="62" t="s">
-        <v>450</v>
+      <c r="D50" s="37" t="s">
+        <v>478</v>
       </c>
       <c r="E50" s="62" t="s">
-        <v>119</v>
+        <v>480</v>
       </c>
       <c r="F50" s="62" t="s">
-        <v>176</v>
+        <v>378</v>
       </c>
       <c r="G50" s="62" t="s">
-        <v>176</v>
+        <v>481</v>
       </c>
       <c r="H50" s="62" t="s">
-        <v>269</v>
-      </c>
-      <c r="I50" s="62"/>
+        <v>482</v>
+      </c>
+      <c r="I50" s="62" t="s">
+        <v>366</v>
+      </c>
       <c r="J50" s="62" t="s">
-        <v>371</v>
+        <v>481</v>
       </c>
       <c r="K50" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L50" s="62">
         <v>1</v>
@@ -10048,17 +10052,17 @@
         <v>40</v>
       </c>
       <c r="N50" s="62">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O50" s="64" t="s">
-        <v>269</v>
+        <v>379</v>
       </c>
       <c r="P50" s="65">
-        <v>13.9</v>
+        <v>4.2200000000000001E-2</v>
       </c>
       <c r="Q50" s="65">
         <f t="shared" ref="Q50" si="18">P50*N50</f>
-        <v>556</v>
+        <v>2.11</v>
       </c>
       <c r="R50" s="62"/>
       <c r="S50" s="62"/>
@@ -10070,31 +10074,31 @@
         <v>42</v>
       </c>
       <c r="C51" s="67" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D51" s="68" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E51" s="68" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F51" s="68" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="G51" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H51" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="I51" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J51" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="K51" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L51" s="68">
         <v>6</v>
@@ -10104,19 +10108,19 @@
         <v>240</v>
       </c>
       <c r="N51" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="O51" s="69" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="P51" s="70" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="Q51" s="70" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="R51" s="68" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="S51" s="68"/>
     </row>
@@ -10130,28 +10134,28 @@
         <v>22</v>
       </c>
       <c r="D52" s="61" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E52" s="62" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F52" s="62" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="G52" s="62" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="H52" s="62" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="I52" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J52" s="62" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="K52" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L52" s="62">
         <v>4</v>
@@ -10164,7 +10168,7 @@
         <v>180</v>
       </c>
       <c r="O52" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P52" s="65">
         <v>3.3500000000000002E-2</v>
@@ -10186,28 +10190,28 @@
         <v>23</v>
       </c>
       <c r="D53" s="58" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E53" s="58" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F53" s="58" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G53" s="58" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="H53" s="58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I53" s="58" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="J53" s="58" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="K53" s="58" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L53" s="58">
         <v>1</v>
@@ -10220,7 +10224,7 @@
         <v>60</v>
       </c>
       <c r="O53" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P53" s="59">
         <v>2.93E-2</v>
@@ -10242,28 +10246,28 @@
         <v>23</v>
       </c>
       <c r="D54" s="61" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E54" s="62" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F54" s="62" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G54" s="62" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="H54" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I54" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J54" s="62" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="K54" s="62" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="L54" s="62">
         <v>1</v>
@@ -10276,7 +10280,7 @@
         <v>60</v>
       </c>
       <c r="O54" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P54" s="65">
         <v>2.1600000000000001E-2</v>
@@ -10298,28 +10302,28 @@
         <v>23</v>
       </c>
       <c r="D55" s="58" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="E55" s="58" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F55" s="58" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G55" s="58" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="H55" s="58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I55" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J55" s="58" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="K55" s="58" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="L55" s="58">
         <v>14</v>
@@ -10332,7 +10336,7 @@
         <v>600</v>
       </c>
       <c r="O55" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P55" s="59">
         <v>1E-3</v>
@@ -10354,28 +10358,28 @@
         <v>23</v>
       </c>
       <c r="D56" s="61" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E56" s="62" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F56" s="62" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G56" s="62" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="H56" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I56" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J56" s="62" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="K56" s="62" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="L56" s="62">
         <v>1</v>
@@ -10388,7 +10392,7 @@
         <v>60</v>
       </c>
       <c r="O56" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P56" s="65">
         <v>2.81E-2</v>
@@ -10410,28 +10414,28 @@
         <v>23</v>
       </c>
       <c r="D57" s="58" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E57" s="58" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F57" s="58" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G57" s="58" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="H57" s="58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I57" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J57" s="58" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="K57" s="58" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="L57" s="58">
         <v>1</v>
@@ -10444,7 +10448,7 @@
         <v>60</v>
       </c>
       <c r="O57" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P57" s="59">
         <v>2.9600000000000001E-2</v>
@@ -10466,28 +10470,28 @@
         <v>23</v>
       </c>
       <c r="D58" s="61" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E58" s="62" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F58" s="62" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G58" s="62" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="H58" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I58" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J58" s="62" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="K58" s="62" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="L58" s="62">
         <v>2</v>
@@ -10500,7 +10504,7 @@
         <v>100</v>
       </c>
       <c r="O58" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P58" s="65">
         <v>1.1999999999999999E-3</v>
@@ -10522,28 +10526,28 @@
         <v>23</v>
       </c>
       <c r="D59" s="58" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E59" s="58" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F59" s="58" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G59" s="58" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="H59" s="58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I59" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J59" s="58" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K59" s="58" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="L59" s="58">
         <v>3</v>
@@ -10556,7 +10560,7 @@
         <v>200</v>
       </c>
       <c r="O59" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P59" s="59">
         <v>1.2999999999999999E-3</v>
@@ -10568,7 +10572,7 @@
       <c r="R59" s="57"/>
       <c r="S59" s="37"/>
     </row>
-    <row r="60" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="75"/>
       <c r="B60" s="45">
         <f t="shared" si="0"/>
@@ -10578,28 +10582,28 @@
         <v>23</v>
       </c>
       <c r="D60" s="61" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E60" s="62" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F60" s="62" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G60" s="62" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H60" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I60" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J60" s="62" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="K60" s="62" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="L60" s="62">
         <v>4</v>
@@ -10612,7 +10616,7 @@
         <v>200</v>
       </c>
       <c r="O60" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P60" s="65">
         <v>9.2999999999999992E-3</v>
@@ -10624,7 +10628,7 @@
       <c r="R60" s="62"/>
       <c r="S60" s="62"/>
     </row>
-    <row r="61" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="75"/>
       <c r="B61" s="44">
         <f>ROW(B61) - ROW($B$9)</f>
@@ -10634,28 +10638,28 @@
         <v>23</v>
       </c>
       <c r="D61" s="58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E61" s="58" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F61" s="58" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G61" s="58" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="H61" s="58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I61" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J61" s="58" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="K61" s="58" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="L61" s="58">
         <v>1</v>
@@ -10668,7 +10672,7 @@
         <v>100</v>
       </c>
       <c r="O61" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P61" s="59">
         <v>3.0000000000000001E-3</v>
@@ -10690,28 +10694,28 @@
         <v>23</v>
       </c>
       <c r="D62" s="61" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E62" s="62" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F62" s="62" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G62" s="62" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H62" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I62" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J62" s="62" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="K62" s="62" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="L62" s="62">
         <v>3</v>
@@ -10724,7 +10728,7 @@
         <v>200</v>
       </c>
       <c r="O62" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P62" s="65">
         <v>1.1999999999999999E-3</v>
@@ -10746,28 +10750,28 @@
         <v>23</v>
       </c>
       <c r="D63" s="58" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E63" s="58" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F63" s="58" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G63" s="58" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="H63" s="58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I63" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J63" s="58" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="K63" s="58" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="L63" s="58">
         <v>6</v>
@@ -10780,7 +10784,7 @@
         <v>300</v>
       </c>
       <c r="O63" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P63" s="59">
         <v>1.1000000000000001E-3</v>
@@ -10802,28 +10806,28 @@
         <v>23</v>
       </c>
       <c r="D64" s="61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E64" s="62" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F64" s="62" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G64" s="62" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="H64" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I64" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J64" s="62" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="K64" s="62" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="L64" s="62">
         <v>4</v>
@@ -10836,7 +10840,7 @@
         <v>200</v>
       </c>
       <c r="O64" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P64" s="65">
         <v>1E-3</v>
@@ -10848,7 +10852,7 @@
       <c r="R64" s="62"/>
       <c r="S64" s="62"/>
     </row>
-    <row r="65" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="75"/>
       <c r="B65" s="44">
         <f>ROW(B65) - ROW($B$9)</f>
@@ -10858,28 +10862,28 @@
         <v>23</v>
       </c>
       <c r="D65" s="58" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E65" s="58" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F65" s="58" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G65" s="58" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="H65" s="58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I65" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J65" s="58" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="K65" s="58" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="L65" s="58">
         <v>1</v>
@@ -10892,7 +10896,7 @@
         <v>100</v>
       </c>
       <c r="O65" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P65" s="59">
         <v>1.2999999999999999E-3</v>
@@ -10914,28 +10918,28 @@
         <v>23</v>
       </c>
       <c r="D66" s="61" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E66" s="62" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F66" s="62" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G66" s="62" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H66" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I66" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J66" s="62" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="K66" s="62" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="L66" s="62">
         <v>3</v>
@@ -10948,7 +10952,7 @@
         <v>200</v>
       </c>
       <c r="O66" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P66" s="65">
         <v>1.2999999999999999E-3</v>
@@ -10960,7 +10964,7 @@
       <c r="R66" s="62"/>
       <c r="S66" s="62"/>
     </row>
-    <row r="67" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="75"/>
       <c r="B67" s="44">
         <f>ROW(B67) - ROW($B$9)</f>
@@ -10970,28 +10974,28 @@
         <v>23</v>
       </c>
       <c r="D67" s="58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E67" s="58" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F67" s="58" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G67" s="58" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H67" s="58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I67" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J67" s="58" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="K67" s="58" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="L67" s="58">
         <v>1</v>
@@ -11004,7 +11008,7 @@
         <v>100</v>
       </c>
       <c r="O67" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P67" s="59">
         <v>1.8E-3</v>
@@ -11016,7 +11020,7 @@
       <c r="R67" s="57"/>
       <c r="S67" s="37"/>
     </row>
-    <row r="68" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="75"/>
       <c r="B68" s="45">
         <f t="shared" si="0"/>
@@ -11026,28 +11030,28 @@
         <v>23</v>
       </c>
       <c r="D68" s="61" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E68" s="62" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F68" s="62" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G68" s="62" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H68" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I68" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J68" s="62" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="K68" s="62" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="L68" s="62">
         <v>1</v>
@@ -11060,7 +11064,7 @@
         <v>100</v>
       </c>
       <c r="O68" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P68" s="65">
         <v>1.2999999999999999E-3</v>
@@ -11082,28 +11086,28 @@
         <v>23</v>
       </c>
       <c r="D69" s="58" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E69" s="58" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F69" s="58" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G69" s="58" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H69" s="58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I69" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J69" s="58" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="K69" s="58" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="L69" s="58">
         <v>1</v>
@@ -11116,7 +11120,7 @@
         <v>100</v>
       </c>
       <c r="O69" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P69" s="59">
         <v>6.9999999999999999E-4</v>
@@ -11138,28 +11142,28 @@
         <v>23</v>
       </c>
       <c r="D70" s="61" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E70" s="62" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F70" s="62" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G70" s="62" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="H70" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I70" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J70" s="62" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="K70" s="62" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="L70" s="62">
         <v>1</v>
@@ -11172,7 +11176,7 @@
         <v>100</v>
       </c>
       <c r="O70" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P70" s="65">
         <v>5.0000000000000001E-4</v>
@@ -11194,28 +11198,28 @@
         <v>23</v>
       </c>
       <c r="D71" s="37" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="E71" s="37" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="F71" s="37" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="G71" s="37" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="H71" s="37" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="I71" s="37" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J71" s="37" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="K71" s="37" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="L71" s="37">
         <v>1</v>
@@ -11228,7 +11232,7 @@
         <v>50</v>
       </c>
       <c r="O71" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P71" s="72">
         <v>5.8099999999999999E-2</v>
@@ -11240,7 +11244,7 @@
       <c r="R71" s="37"/>
       <c r="S71" s="74"/>
     </row>
-    <row r="72" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="75"/>
       <c r="B72" s="45">
         <f t="shared" ref="B72" si="29">ROW(B72) - ROW($B$9)</f>
@@ -11250,28 +11254,28 @@
         <v>23</v>
       </c>
       <c r="D72" s="62" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="E72" s="62" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="F72" s="62" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G72" s="62" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="H72" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I72" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J72" s="62" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="K72" s="62" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="L72" s="62">
         <v>2</v>
@@ -11284,7 +11288,7 @@
         <v>100</v>
       </c>
       <c r="O72" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P72" s="65">
         <v>1.1999999999999999E-3</v>
@@ -11303,31 +11307,31 @@
         <v>64</v>
       </c>
       <c r="C73" s="67" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="D73" s="68" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="E73" s="68" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F73" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="G73" s="68" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="H73" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="I73" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J73" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="K73" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L73" s="68">
         <v>2</v>
@@ -11337,19 +11341,19 @@
         <v>80</v>
       </c>
       <c r="N73" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="O73" s="69" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="P73" s="70" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="Q73" s="70" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="R73" s="68" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="S73" s="68"/>
     </row>
@@ -11360,31 +11364,31 @@
         <v>65</v>
       </c>
       <c r="C74" s="60" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D74" s="61" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E74" s="62" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F74" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="G74" s="62" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="H74" s="62" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="I74" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J74" s="62" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="K74" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L74" s="62">
         <v>1</v>
@@ -11397,7 +11401,7 @@
         <v>42</v>
       </c>
       <c r="O74" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P74" s="65">
         <v>0.3241</v>
@@ -11419,28 +11423,28 @@
         <v>24</v>
       </c>
       <c r="D75" s="58" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E75" s="58" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F75" s="58" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G75" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="H75" s="58" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="I75" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J75" s="58" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="K75" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L75" s="58">
         <v>1</v>
@@ -11453,7 +11457,7 @@
         <v>50</v>
       </c>
       <c r="O75" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P75" s="59">
         <v>5.9900000000000002E-2</v>
@@ -11475,28 +11479,28 @@
         <v>24</v>
       </c>
       <c r="D76" s="61" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E76" s="62" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F76" s="62" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="G76" s="62" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H76" s="62" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I76" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J76" s="62" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="K76" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L76" s="62">
         <v>1</v>
@@ -11509,7 +11513,7 @@
         <v>41</v>
       </c>
       <c r="O76" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P76" s="65">
         <v>2.2145999999999999</v>
@@ -11531,28 +11535,28 @@
         <v>24</v>
       </c>
       <c r="D77" s="58" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E77" s="58" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F77" s="58" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G77" s="58" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="H77" s="58" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="I77" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J77" s="58" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="K77" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L77" s="58">
         <v>1</v>
@@ -11565,7 +11569,7 @@
         <v>45</v>
       </c>
       <c r="O77" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P77" s="59">
         <v>8.5000000000000006E-2</v>
@@ -11577,7 +11581,7 @@
       <c r="R77" s="57"/>
       <c r="S77" s="37"/>
     </row>
-    <row r="78" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="75"/>
       <c r="B78" s="45">
         <f t="shared" si="0"/>
@@ -11587,28 +11591,28 @@
         <v>24</v>
       </c>
       <c r="D78" s="61" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E78" s="62" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F78" s="62" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G78" s="62" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H78" s="62" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="I78" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J78" s="62" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="K78" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L78" s="62">
         <v>4</v>
@@ -11621,7 +11625,7 @@
         <v>161</v>
       </c>
       <c r="O78" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P78" s="65">
         <v>5.1132</v>
@@ -11643,28 +11647,28 @@
         <v>24</v>
       </c>
       <c r="D79" s="58" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="E79" s="58" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F79" s="58" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G79" s="58" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="H79" s="58" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="I79" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J79" s="58" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="K79" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L79" s="58">
         <v>1</v>
@@ -11677,7 +11681,7 @@
         <v>41</v>
       </c>
       <c r="O79" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P79" s="59">
         <v>0.3866</v>
@@ -11696,28 +11700,28 @@
         <v>24</v>
       </c>
       <c r="D80" s="37" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="E80" s="37" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="F80" s="37" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="G80" s="37" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="H80" s="37" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="I80" s="37" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J80" s="37" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="K80" s="37" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L80" s="37">
         <v>1</v>
@@ -11730,7 +11734,7 @@
         <v>41</v>
       </c>
       <c r="O80" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P80" s="59">
         <v>0.2848</v>
@@ -11752,28 +11756,28 @@
         <v>24</v>
       </c>
       <c r="D81" s="61" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E81" s="62" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F81" s="62" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G81" s="62" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H81" s="62" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="I81" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J81" s="62" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="K81" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L81" s="62">
         <v>1</v>
@@ -11786,7 +11790,7 @@
         <v>41</v>
       </c>
       <c r="O81" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P81" s="65">
         <v>0.58230000000000004</v>
@@ -11808,28 +11812,28 @@
         <v>25</v>
       </c>
       <c r="D82" s="58" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E82" s="58" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F82" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="G82" s="58" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="H82" s="58" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="I82" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J82" s="58" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K82" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L82" s="58">
         <v>1</v>
@@ -11842,7 +11846,7 @@
         <v>41</v>
       </c>
       <c r="O82" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P82" s="59">
         <v>19.132300000000001</v>
@@ -11852,7 +11856,7 @@
         <v>784.42430000000002</v>
       </c>
       <c r="R82" s="57" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="S82" s="37"/>
     </row>
@@ -11866,28 +11870,28 @@
         <v>24</v>
       </c>
       <c r="D83" s="61" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E83" s="62" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F83" s="62" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G83" s="62" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H83" s="62" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="I83" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J83" s="62" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="K83" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L83" s="62">
         <v>1</v>
@@ -11900,7 +11904,7 @@
         <v>41</v>
       </c>
       <c r="O83" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P83" s="65">
         <v>11.7394</v>
@@ -11912,7 +11916,7 @@
       <c r="R83" s="62"/>
       <c r="S83" s="62"/>
     </row>
-    <row r="84" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="75"/>
       <c r="B84" s="44">
         <f>ROW(B84) - ROW($B$9)</f>
@@ -11922,28 +11926,28 @@
         <v>24</v>
       </c>
       <c r="D84" s="58" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E84" s="58" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F84" s="58" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G84" s="58" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H84" s="58" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="I84" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J84" s="58" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="K84" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L84" s="58">
         <v>1</v>
@@ -11956,7 +11960,7 @@
         <v>41</v>
       </c>
       <c r="O84" s="55" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P84" s="59">
         <v>1.9091</v>
@@ -11978,28 +11982,28 @@
         <v>24</v>
       </c>
       <c r="D85" s="62" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="E85" s="37" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="F85" s="37" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="G85" s="37" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="H85" s="37" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="I85" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J85" s="37" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="K85" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L85" s="62">
         <v>2</v>
@@ -12012,7 +12016,7 @@
         <v>82</v>
       </c>
       <c r="O85" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P85" s="65">
         <v>0.32779999999999998</v>
@@ -12034,28 +12038,28 @@
         <v>26</v>
       </c>
       <c r="D86" s="61" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E86" s="62" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F86" s="62" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G86" s="62" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="H86" s="62" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="I86" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J86" s="62" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="K86" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L86" s="62">
         <v>1</v>
@@ -12068,7 +12072,7 @@
         <v>45</v>
       </c>
       <c r="O86" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P86" s="65">
         <v>7.5999999999999998E-2</v>
@@ -12087,31 +12091,31 @@
         <v>78</v>
       </c>
       <c r="C87" s="60" t="s">
+        <v>418</v>
+      </c>
+      <c r="D87" s="71" t="s">
         <v>423</v>
       </c>
-      <c r="D87" s="71" t="s">
-        <v>428</v>
-      </c>
       <c r="E87" s="62" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="F87" s="62" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G87" s="62" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="H87" s="62" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="I87" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J87" s="62" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="K87" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L87" s="62">
         <v>1</v>
@@ -12124,7 +12128,7 @@
         <v>41</v>
       </c>
       <c r="O87" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P87" s="65">
         <v>0.99439999999999995</v>
@@ -12143,31 +12147,31 @@
         <v>79</v>
       </c>
       <c r="C88" s="60" t="s">
+        <v>418</v>
+      </c>
+      <c r="D88" s="71" t="s">
         <v>423</v>
       </c>
-      <c r="D88" s="71" t="s">
-        <v>428</v>
-      </c>
       <c r="E88" s="62" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="F88" s="62" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G88" s="62" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="H88" s="62" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="I88" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J88" s="62" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="K88" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L88" s="62">
         <v>1</v>
@@ -12180,7 +12184,7 @@
         <v>41</v>
       </c>
       <c r="O88" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P88" s="65">
         <v>1.2823</v>
@@ -12199,31 +12203,31 @@
         <v>80</v>
       </c>
       <c r="C89" s="60" t="s">
+        <v>418</v>
+      </c>
+      <c r="D89" s="71" t="s">
         <v>423</v>
       </c>
-      <c r="D89" s="71" t="s">
+      <c r="E89" s="62" t="s">
         <v>428</v>
       </c>
-      <c r="E89" s="62" t="s">
-        <v>433</v>
-      </c>
       <c r="F89" s="62" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G89" s="62" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="H89" s="62" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="I89" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J89" s="62" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="K89" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L89" s="62">
         <v>1</v>
@@ -12236,7 +12240,7 @@
         <v>41</v>
       </c>
       <c r="O89" s="64" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P89" s="65">
         <v>0.54269999999999996</v>
@@ -12269,7 +12273,7 @@
       <c r="P90" s="88"/>
       <c r="Q90" s="46">
         <f>SUM(Q10:Q89)</f>
-        <v>3516.5403000000001</v>
+        <v>2962.6503000000002</v>
       </c>
       <c r="R90" s="83"/>
       <c r="S90" s="84"/>
@@ -12295,7 +12299,7 @@
       <c r="P91" s="88"/>
       <c r="Q91" s="47">
         <f>Q90/40</f>
-        <v>87.913507500000009</v>
+        <v>74.066257500000006</v>
       </c>
       <c r="R91" s="85"/>
       <c r="S91" s="86"/>
@@ -12375,18 +12379,18 @@
     <hyperlink ref="O37" r:id="rId64"/>
     <hyperlink ref="O38" r:id="rId65"/>
     <hyperlink ref="O20" r:id="rId66"/>
-    <hyperlink ref="O50" r:id="rId67"/>
-    <hyperlink ref="O87" r:id="rId68"/>
-    <hyperlink ref="O88" r:id="rId69"/>
-    <hyperlink ref="O89" r:id="rId70"/>
-    <hyperlink ref="O42" r:id="rId71"/>
-    <hyperlink ref="O80" r:id="rId72"/>
-    <hyperlink ref="O49" r:id="rId73"/>
-    <hyperlink ref="O71" r:id="rId74"/>
-    <hyperlink ref="O72" r:id="rId75"/>
-    <hyperlink ref="O21" r:id="rId76"/>
-    <hyperlink ref="O85" r:id="rId77"/>
-    <hyperlink ref="O35" r:id="rId78"/>
+    <hyperlink ref="O87" r:id="rId67"/>
+    <hyperlink ref="O88" r:id="rId68"/>
+    <hyperlink ref="O89" r:id="rId69"/>
+    <hyperlink ref="O42" r:id="rId70"/>
+    <hyperlink ref="O80" r:id="rId71"/>
+    <hyperlink ref="O71" r:id="rId72"/>
+    <hyperlink ref="O72" r:id="rId73"/>
+    <hyperlink ref="O21" r:id="rId74"/>
+    <hyperlink ref="O85" r:id="rId75"/>
+    <hyperlink ref="O35" r:id="rId76"/>
+    <hyperlink ref="O49" r:id="rId77"/>
+    <hyperlink ref="O50" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId79"/>
